--- a/hall/resources/sample/BuildingFunction.xlsx
+++ b/hall/resources/sample/BuildingFunction.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="BuildingFunction" sheetId="2" r:id="rId1"/>
@@ -131,7 +131,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="55">
   <si>
     <t>id</t>
   </si>
@@ -467,12 +467,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -3095,12 +3095,8 @@
       <c r="G38" s="1">
         <v>0</v>
       </c>
-      <c r="J38" s="1">
-        <v>4</v>
-      </c>
-      <c r="K38" t="s">
-        <v>35</v>
-      </c>
+      <c r="J38" s="1"/>
+      <c r="K38"/>
       <c r="L38" s="5">
         <f t="shared" ref="L38:L47" si="14">A39</f>
         <v>10401</v>
@@ -3142,12 +3138,8 @@
       <c r="I39" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="J39" s="1">
-        <v>4</v>
-      </c>
-      <c r="K39" t="s">
-        <v>38</v>
-      </c>
+      <c r="J39" s="1"/>
+      <c r="K39"/>
       <c r="L39" s="5">
         <f t="shared" si="14"/>
         <v>10402</v>
@@ -3187,12 +3179,8 @@
       <c r="I40" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="J40" s="1">
-        <v>4</v>
-      </c>
-      <c r="K40" t="s">
-        <v>38</v>
-      </c>
+      <c r="J40" s="1"/>
+      <c r="K40"/>
       <c r="L40" s="5">
         <f t="shared" si="14"/>
         <v>10403</v>
@@ -3232,12 +3220,8 @@
       <c r="I41" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="J41" s="1">
-        <v>4</v>
-      </c>
-      <c r="K41" t="s">
-        <v>38</v>
-      </c>
+      <c r="J41" s="1"/>
+      <c r="K41"/>
       <c r="L41" s="5">
         <f t="shared" si="14"/>
         <v>10404</v>
@@ -3277,12 +3261,8 @@
       <c r="I42" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="J42" s="1">
-        <v>4</v>
-      </c>
-      <c r="K42" t="s">
-        <v>38</v>
-      </c>
+      <c r="J42" s="1"/>
+      <c r="K42"/>
       <c r="L42" s="5">
         <f t="shared" si="14"/>
         <v>10405</v>
@@ -3322,12 +3302,8 @@
       <c r="I43" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="J43" s="1">
-        <v>4</v>
-      </c>
-      <c r="K43" t="s">
-        <v>38</v>
-      </c>
+      <c r="J43" s="1"/>
+      <c r="K43"/>
       <c r="L43" s="5">
         <f t="shared" si="14"/>
         <v>10406</v>
@@ -3367,12 +3343,8 @@
       <c r="I44" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="J44" s="1">
-        <v>4</v>
-      </c>
-      <c r="K44" t="s">
-        <v>38</v>
-      </c>
+      <c r="J44" s="1"/>
+      <c r="K44"/>
       <c r="L44" s="5">
         <f t="shared" si="14"/>
         <v>10407</v>
@@ -3412,12 +3384,8 @@
       <c r="I45" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="J45" s="1">
-        <v>4</v>
-      </c>
-      <c r="K45" t="s">
-        <v>38</v>
-      </c>
+      <c r="J45" s="1"/>
+      <c r="K45"/>
       <c r="L45" s="5">
         <f t="shared" si="14"/>
         <v>10408</v>
@@ -3457,12 +3425,8 @@
       <c r="I46" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="J46" s="1">
-        <v>4</v>
-      </c>
-      <c r="K46" t="s">
-        <v>38</v>
-      </c>
+      <c r="J46" s="1"/>
+      <c r="K46"/>
       <c r="L46" s="5">
         <f t="shared" si="14"/>
         <v>10409</v>
@@ -3502,12 +3466,8 @@
       <c r="I47" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="J47" s="1">
-        <v>4</v>
-      </c>
-      <c r="K47" t="s">
-        <v>38</v>
-      </c>
+      <c r="J47" s="1"/>
+      <c r="K47"/>
       <c r="L47" s="5">
         <f t="shared" si="14"/>
         <v>10410</v>
@@ -3544,9 +3504,7 @@
       <c r="G48" s="1">
         <v>10</v>
       </c>
-      <c r="J48" s="1">
-        <v>4</v>
-      </c>
+      <c r="J48" s="1"/>
       <c r="K48"/>
       <c r="P48" s="2">
         <f t="shared" si="15"/>

--- a/hall/resources/sample/BuildingFunction.xlsx
+++ b/hall/resources/sample/BuildingFunction.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="BuildingFunction" sheetId="2" r:id="rId1"/>
@@ -131,7 +131,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="102">
   <si>
     <t>id</t>
   </si>
@@ -238,13 +238,16 @@
     <t>slot机台</t>
   </si>
   <si>
+    <t>1023001_1</t>
+  </si>
+  <si>
     <t>1_1</t>
   </si>
   <si>
     <t>1_1990000_100</t>
   </si>
   <si>
-    <t>1020001_1;1020002_1;1020003_1</t>
+    <t>1023001_5</t>
   </si>
   <si>
     <t>1_10</t>
@@ -253,46 +256,184 @@
     <t>1_1990000_110</t>
   </si>
   <si>
+    <t>1023001_10</t>
+  </si>
+  <si>
     <t>1_1990000_120</t>
   </si>
   <si>
+    <t>1023001_20</t>
+  </si>
+  <si>
     <t>1_1990000_130</t>
   </si>
   <si>
+    <t>1023001_50</t>
+  </si>
+  <si>
     <t>1_1990000_140</t>
   </si>
   <si>
+    <t>1023001_100;1980000_1</t>
+  </si>
+  <si>
     <t>1_1990000_150</t>
   </si>
   <si>
+    <t>1023001_200;1980000_10</t>
+  </si>
+  <si>
     <t>1_1990000_160</t>
   </si>
   <si>
+    <t>1023001_500;1980000_20</t>
+  </si>
+  <si>
     <t>1_1990000_170</t>
   </si>
   <si>
+    <t>1023001_1000;1980000_50</t>
+  </si>
+  <si>
     <t>1_1990000_180</t>
   </si>
   <si>
+    <t>1023001_2000;1980000_100</t>
+  </si>
+  <si>
     <t>1_1990000_190</t>
   </si>
   <si>
     <t>扑克牌桌</t>
   </si>
   <si>
+    <t>1023101_1</t>
+  </si>
+  <si>
+    <t>1023101_5</t>
+  </si>
+  <si>
+    <t>1023101_10</t>
+  </si>
+  <si>
+    <t>1023101_20</t>
+  </si>
+  <si>
+    <t>1023101_50</t>
+  </si>
+  <si>
+    <t>1023101_100;1980000_1</t>
+  </si>
+  <si>
+    <t>1023101_200;1980000_10</t>
+  </si>
+  <si>
+    <t>1023101_500;1980000_20</t>
+  </si>
+  <si>
+    <t>1023101_1000;1980000_50</t>
+  </si>
+  <si>
+    <t>1023101_2000;1980000_100</t>
+  </si>
+  <si>
     <t>幸运转盘</t>
   </si>
   <si>
     <t>吧台区</t>
   </si>
   <si>
-    <t>1020004_1;1020005_1;1020006_1</t>
+    <t>1023401_1</t>
+  </si>
+  <si>
+    <t>1023401_10</t>
+  </si>
+  <si>
+    <t>1023401_20</t>
+  </si>
+  <si>
+    <t>1023401_50</t>
+  </si>
+  <si>
+    <t>1023401_100;1980000_1</t>
+  </si>
+  <si>
+    <t>1023401_200;1980000_10</t>
+  </si>
+  <si>
+    <t>1023401_500;1980000_20</t>
+  </si>
+  <si>
+    <t>1023401_1000;1980000_50</t>
+  </si>
+  <si>
+    <t>1023401_2000;1980000_100</t>
   </si>
   <si>
     <t>休息区</t>
   </si>
   <si>
+    <t>1023301_1</t>
+  </si>
+  <si>
+    <t>1023301_5</t>
+  </si>
+  <si>
+    <t>1023301_10</t>
+  </si>
+  <si>
+    <t>1023301_20</t>
+  </si>
+  <si>
+    <t>1023301_50</t>
+  </si>
+  <si>
+    <t>1023301_100;1980000_1</t>
+  </si>
+  <si>
+    <t>1023301_200;1980000_10</t>
+  </si>
+  <si>
+    <t>1023301_500;1980000_20</t>
+  </si>
+  <si>
+    <t>1023301_1000;1980000_50</t>
+  </si>
+  <si>
+    <t>1023301_2000;1980000_100</t>
+  </si>
+  <si>
     <t>提款机</t>
+  </si>
+  <si>
+    <t>1023201_1</t>
+  </si>
+  <si>
+    <t>1023201_5</t>
+  </si>
+  <si>
+    <t>1023201_10</t>
+  </si>
+  <si>
+    <t>1023201_20</t>
+  </si>
+  <si>
+    <t>1023201_50</t>
+  </si>
+  <si>
+    <t>1023201_100;1980000_1</t>
+  </si>
+  <si>
+    <t>1023201_200;1980000_10</t>
+  </si>
+  <si>
+    <t>1023201_500;1980000_20</t>
+  </si>
+  <si>
+    <t>1023201_1000;1980000_50</t>
+  </si>
+  <si>
+    <t>1023201_2000;1980000_100</t>
   </si>
   <si>
     <t>停机坪</t>
@@ -1466,8 +1607,7 @@
         <v>1</v>
       </c>
       <c r="E5" s="2">
-        <f t="shared" ref="E5:E10" si="1">300000+A5</f>
-        <v>310100</v>
+        <v>47027</v>
       </c>
       <c r="F5" s="2">
         <v>0</v>
@@ -1476,11 +1616,14 @@
         <v>0</v>
       </c>
       <c r="H5" s="2"/>
+      <c r="I5" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="J5" s="1">
         <v>4</v>
       </c>
       <c r="K5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L5" s="5">
         <f>A6</f>
@@ -1511,8 +1654,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="2">
-        <f t="shared" si="1"/>
-        <v>310101</v>
+        <v>47027</v>
       </c>
       <c r="F6" s="2">
         <v>0</v>
@@ -1521,19 +1663,19 @@
         <v>1</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J6" s="1">
         <v>4</v>
       </c>
       <c r="K6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L6" s="5">
-        <f t="shared" ref="L6:L14" si="2">A7</f>
+        <f t="shared" ref="L6:L14" si="1">A7</f>
         <v>10102</v>
       </c>
       <c r="M6" s="1">
@@ -1543,7 +1685,7 @@
         <v>1000</v>
       </c>
       <c r="P6" s="2">
-        <f t="shared" ref="P6:P15" si="3">400000+A6</f>
+        <f t="shared" ref="P6:P15" si="2">400000+A6</f>
         <v>410101</v>
       </c>
     </row>
@@ -1562,29 +1704,28 @@
         <v>1</v>
       </c>
       <c r="E7" s="2">
+        <v>47027</v>
+      </c>
+      <c r="F7" s="2">
+        <v>0</v>
+      </c>
+      <c r="G7" s="1">
+        <v>2</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="J7" s="1">
+        <v>4</v>
+      </c>
+      <c r="K7" t="s">
+        <v>39</v>
+      </c>
+      <c r="L7" s="5">
         <f t="shared" si="1"/>
-        <v>310102</v>
-      </c>
-      <c r="F7" s="2">
-        <v>0</v>
-      </c>
-      <c r="G7" s="1">
-        <v>2</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="J7" s="1">
-        <v>4</v>
-      </c>
-      <c r="K7" t="s">
-        <v>38</v>
-      </c>
-      <c r="L7" s="5">
-        <f t="shared" si="2"/>
         <v>10103</v>
       </c>
       <c r="M7" s="1">
@@ -1594,7 +1735,7 @@
         <v>1500</v>
       </c>
       <c r="P7" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>410102</v>
       </c>
     </row>
@@ -1613,8 +1754,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="2">
-        <f t="shared" si="1"/>
-        <v>310103</v>
+        <v>47027</v>
       </c>
       <c r="F8" s="2">
         <v>0</v>
@@ -1623,19 +1763,19 @@
         <v>3</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="J8" s="1">
         <v>4</v>
       </c>
       <c r="K8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L8" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>10104</v>
       </c>
       <c r="M8" s="1">
@@ -1645,7 +1785,7 @@
         <v>2000</v>
       </c>
       <c r="P8" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>410103</v>
       </c>
     </row>
@@ -1664,29 +1804,28 @@
         <v>1</v>
       </c>
       <c r="E9" s="2">
+        <v>47027</v>
+      </c>
+      <c r="F9" s="2">
+        <v>0</v>
+      </c>
+      <c r="G9" s="1">
+        <v>4</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J9" s="1">
+        <v>4</v>
+      </c>
+      <c r="K9" t="s">
+        <v>39</v>
+      </c>
+      <c r="L9" s="5">
         <f t="shared" si="1"/>
-        <v>310104</v>
-      </c>
-      <c r="F9" s="2">
-        <v>0</v>
-      </c>
-      <c r="G9" s="1">
-        <v>4</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="J9" s="1">
-        <v>4</v>
-      </c>
-      <c r="K9" t="s">
-        <v>38</v>
-      </c>
-      <c r="L9" s="5">
-        <f t="shared" si="2"/>
         <v>10105</v>
       </c>
       <c r="M9" s="1">
@@ -1696,7 +1835,7 @@
         <v>3500</v>
       </c>
       <c r="P9" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>410104</v>
       </c>
     </row>
@@ -1715,8 +1854,7 @@
         <v>1</v>
       </c>
       <c r="E10" s="2">
-        <f t="shared" si="1"/>
-        <v>310105</v>
+        <v>47027</v>
       </c>
       <c r="F10" s="2">
         <v>0</v>
@@ -1725,19 +1863,19 @@
         <v>5</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="J10" s="1">
         <v>4</v>
       </c>
       <c r="K10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L10" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>10106</v>
       </c>
       <c r="M10" s="1">
@@ -1747,13 +1885,13 @@
         <v>4000</v>
       </c>
       <c r="P10" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>410105</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:16">
       <c r="A11" s="1">
-        <f t="shared" ref="A11:A21" si="4">10000+G11+B11*100</f>
+        <f t="shared" ref="A11:A21" si="3">10000+G11+B11*100</f>
         <v>10106</v>
       </c>
       <c r="B11" s="1">
@@ -1766,8 +1904,7 @@
         <v>1</v>
       </c>
       <c r="E11" s="2">
-        <f t="shared" ref="E11:E21" si="5">300000+A11</f>
-        <v>310106</v>
+        <v>47027</v>
       </c>
       <c r="F11" s="2">
         <v>0</v>
@@ -1776,19 +1913,19 @@
         <v>6</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="J11" s="1">
         <v>4</v>
       </c>
       <c r="K11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L11" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>10107</v>
       </c>
       <c r="M11" s="1">
@@ -1798,13 +1935,13 @@
         <v>4500</v>
       </c>
       <c r="P11" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>410106</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="1:16">
       <c r="A12" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>10107</v>
       </c>
       <c r="B12" s="1">
@@ -1817,8 +1954,7 @@
         <v>1</v>
       </c>
       <c r="E12" s="2">
-        <f t="shared" si="5"/>
-        <v>310107</v>
+        <v>47027</v>
       </c>
       <c r="F12" s="2">
         <v>0</v>
@@ -1827,19 +1963,19 @@
         <v>7</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="J12" s="1">
         <v>4</v>
       </c>
       <c r="K12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L12" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>10108</v>
       </c>
       <c r="M12" s="1">
@@ -1849,13 +1985,13 @@
         <v>5000</v>
       </c>
       <c r="P12" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>410107</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="1:16">
       <c r="A13" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>10108</v>
       </c>
       <c r="B13" s="1">
@@ -1868,8 +2004,7 @@
         <v>1</v>
       </c>
       <c r="E13" s="2">
-        <f t="shared" si="5"/>
-        <v>310108</v>
+        <v>47027</v>
       </c>
       <c r="F13" s="2">
         <v>0</v>
@@ -1878,19 +2013,19 @@
         <v>8</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="J13" s="1">
         <v>4</v>
       </c>
       <c r="K13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L13" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>10109</v>
       </c>
       <c r="M13" s="1">
@@ -1900,13 +2035,13 @@
         <v>5500</v>
       </c>
       <c r="P13" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>410108</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:16">
       <c r="A14" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>10109</v>
       </c>
       <c r="B14" s="1">
@@ -1919,8 +2054,7 @@
         <v>1</v>
       </c>
       <c r="E14" s="2">
-        <f t="shared" si="5"/>
-        <v>310109</v>
+        <v>47027</v>
       </c>
       <c r="F14" s="2">
         <v>0</v>
@@ -1929,19 +2063,19 @@
         <v>9</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="J14" s="1">
         <v>4</v>
       </c>
       <c r="K14" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L14" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>10110</v>
       </c>
       <c r="M14" s="1">
@@ -1951,13 +2085,13 @@
         <v>6000</v>
       </c>
       <c r="P14" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>410109</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:16">
       <c r="A15" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>10110</v>
       </c>
       <c r="B15" s="1">
@@ -1970,8 +2104,7 @@
         <v>1</v>
       </c>
       <c r="E15" s="2">
-        <f t="shared" si="5"/>
-        <v>310110</v>
+        <v>47027</v>
       </c>
       <c r="F15" s="2">
         <v>0</v>
@@ -1980,34 +2113,33 @@
         <v>10</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="J15" s="1">
         <v>4</v>
       </c>
       <c r="K15"/>
       <c r="P15" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>410110</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="1:16">
       <c r="A16" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>10200</v>
       </c>
       <c r="B16" s="1">
         <v>2</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="D16" s="1">
         <v>2</v>
       </c>
       <c r="E16" s="2">
-        <f t="shared" si="5"/>
-        <v>310200</v>
+        <v>47028</v>
       </c>
       <c r="F16" s="2">
         <v>1</v>
@@ -2016,14 +2148,17 @@
         <v>0</v>
       </c>
       <c r="H16" s="2"/>
+      <c r="I16" s="3" t="s">
+        <v>58</v>
+      </c>
       <c r="J16" s="1">
         <v>4</v>
       </c>
       <c r="K16" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L16" s="5">
-        <f t="shared" ref="L16:L25" si="6">A17</f>
+        <f t="shared" ref="L16:L25" si="4">A17</f>
         <v>10201</v>
       </c>
       <c r="M16" s="1">
@@ -2038,42 +2173,41 @@
     </row>
     <row r="17" customHeight="1" spans="1:16">
       <c r="A17" s="1">
+        <f t="shared" si="3"/>
+        <v>10201</v>
+      </c>
+      <c r="B17" s="1">
+        <v>2</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D17" s="1">
+        <v>2</v>
+      </c>
+      <c r="E17" s="2">
+        <v>47028</v>
+      </c>
+      <c r="F17" s="2">
+        <v>1</v>
+      </c>
+      <c r="G17" s="1">
+        <v>1</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="J17" s="1">
+        <v>4</v>
+      </c>
+      <c r="K17" t="s">
+        <v>39</v>
+      </c>
+      <c r="L17" s="5">
         <f t="shared" si="4"/>
-        <v>10201</v>
-      </c>
-      <c r="B17" s="1">
-        <v>2</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D17" s="1">
-        <v>2</v>
-      </c>
-      <c r="E17" s="2">
-        <f t="shared" si="5"/>
-        <v>310201</v>
-      </c>
-      <c r="F17" s="2">
-        <v>1</v>
-      </c>
-      <c r="G17" s="1">
-        <v>1</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="J17" s="1">
-        <v>4</v>
-      </c>
-      <c r="K17" t="s">
-        <v>38</v>
-      </c>
-      <c r="L17" s="5">
-        <f t="shared" si="6"/>
         <v>10202</v>
       </c>
       <c r="M17" s="1">
@@ -2083,48 +2217,47 @@
         <v>1000</v>
       </c>
       <c r="P17" s="2">
-        <f t="shared" ref="P17:P26" si="7">400000+A17</f>
+        <f t="shared" ref="P17:P26" si="5">400000+A17</f>
         <v>410201</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="1:16">
       <c r="A18" s="1">
+        <f t="shared" si="3"/>
+        <v>10202</v>
+      </c>
+      <c r="B18" s="1">
+        <v>2</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D18" s="1">
+        <v>2</v>
+      </c>
+      <c r="E18" s="2">
+        <v>47028</v>
+      </c>
+      <c r="F18" s="2">
+        <v>1</v>
+      </c>
+      <c r="G18" s="1">
+        <v>2</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="J18" s="1">
+        <v>4</v>
+      </c>
+      <c r="K18" t="s">
+        <v>39</v>
+      </c>
+      <c r="L18" s="5">
         <f t="shared" si="4"/>
-        <v>10202</v>
-      </c>
-      <c r="B18" s="1">
-        <v>2</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D18" s="1">
-        <v>2</v>
-      </c>
-      <c r="E18" s="2">
-        <f t="shared" si="5"/>
-        <v>310202</v>
-      </c>
-      <c r="F18" s="2">
-        <v>1</v>
-      </c>
-      <c r="G18" s="1">
-        <v>2</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="J18" s="1">
-        <v>4</v>
-      </c>
-      <c r="K18" t="s">
-        <v>38</v>
-      </c>
-      <c r="L18" s="5">
-        <f t="shared" si="6"/>
         <v>10203</v>
       </c>
       <c r="M18" s="1">
@@ -2134,27 +2267,26 @@
         <v>1500</v>
       </c>
       <c r="P18" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>410202</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="1:16">
       <c r="A19" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>10203</v>
       </c>
       <c r="B19" s="1">
         <v>2</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="D19" s="1">
         <v>2</v>
       </c>
       <c r="E19" s="2">
-        <f t="shared" si="5"/>
-        <v>310203</v>
+        <v>47028</v>
       </c>
       <c r="F19" s="2">
         <v>1</v>
@@ -2163,19 +2295,19 @@
         <v>3</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="J19" s="1">
         <v>4</v>
       </c>
       <c r="K19" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L19" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>10204</v>
       </c>
       <c r="M19" s="1">
@@ -2185,48 +2317,47 @@
         <v>2000</v>
       </c>
       <c r="P19" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>410203</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="1:16">
       <c r="A20" s="1">
+        <f t="shared" si="3"/>
+        <v>10204</v>
+      </c>
+      <c r="B20" s="1">
+        <v>2</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D20" s="1">
+        <v>2</v>
+      </c>
+      <c r="E20" s="2">
+        <v>47028</v>
+      </c>
+      <c r="F20" s="2">
+        <v>1</v>
+      </c>
+      <c r="G20" s="1">
+        <v>4</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="J20" s="1">
+        <v>4</v>
+      </c>
+      <c r="K20" t="s">
+        <v>39</v>
+      </c>
+      <c r="L20" s="5">
         <f t="shared" si="4"/>
-        <v>10204</v>
-      </c>
-      <c r="B20" s="1">
-        <v>2</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D20" s="1">
-        <v>2</v>
-      </c>
-      <c r="E20" s="2">
-        <f t="shared" si="5"/>
-        <v>310204</v>
-      </c>
-      <c r="F20" s="2">
-        <v>1</v>
-      </c>
-      <c r="G20" s="1">
-        <v>4</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="J20" s="1">
-        <v>4</v>
-      </c>
-      <c r="K20" t="s">
-        <v>38</v>
-      </c>
-      <c r="L20" s="5">
-        <f t="shared" si="6"/>
         <v>10205</v>
       </c>
       <c r="M20" s="1">
@@ -2236,27 +2367,26 @@
         <v>3500</v>
       </c>
       <c r="P20" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>410204</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="1:16">
       <c r="A21" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>10205</v>
       </c>
       <c r="B21" s="1">
         <v>2</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="D21" s="1">
         <v>2</v>
       </c>
       <c r="E21" s="2">
-        <f t="shared" si="5"/>
-        <v>310205</v>
+        <v>47028</v>
       </c>
       <c r="F21" s="2">
         <v>1</v>
@@ -2265,19 +2395,19 @@
         <v>5</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="J21" s="1">
         <v>4</v>
       </c>
       <c r="K21" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L21" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>10206</v>
       </c>
       <c r="M21" s="1">
@@ -2287,27 +2417,26 @@
         <v>4000</v>
       </c>
       <c r="P21" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>410205</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="1:16">
       <c r="A22" s="1">
-        <f t="shared" ref="A22:A27" si="8">10000+G22+B22*100</f>
+        <f t="shared" ref="A22:A27" si="6">10000+G22+B22*100</f>
         <v>10206</v>
       </c>
       <c r="B22" s="1">
         <v>2</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="D22" s="1">
         <v>2</v>
       </c>
       <c r="E22" s="2">
-        <f t="shared" ref="E22:E27" si="9">300000+A22</f>
-        <v>310206</v>
+        <v>47028</v>
       </c>
       <c r="F22" s="2">
         <v>1</v>
@@ -2316,49 +2445,48 @@
         <v>6</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>37</v>
+        <v>64</v>
       </c>
       <c r="J22" s="1">
         <v>4</v>
       </c>
       <c r="K22" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L22" s="5">
+        <f t="shared" si="4"/>
+        <v>10207</v>
+      </c>
+      <c r="M22" s="1">
+        <v>1800</v>
+      </c>
+      <c r="N22" s="1">
+        <v>4500</v>
+      </c>
+      <c r="P22" s="2">
+        <f t="shared" si="5"/>
+        <v>410206</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="1:16">
+      <c r="A23" s="1">
         <f t="shared" si="6"/>
         <v>10207</v>
       </c>
-      <c r="M22" s="1">
-        <v>1800</v>
-      </c>
-      <c r="N22" s="1">
-        <v>4500</v>
-      </c>
-      <c r="P22" s="2">
-        <f t="shared" si="7"/>
-        <v>410206</v>
-      </c>
-    </row>
-    <row r="23" customHeight="1" spans="1:16">
-      <c r="A23" s="1">
-        <f t="shared" si="8"/>
-        <v>10207</v>
-      </c>
       <c r="B23" s="1">
         <v>2</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="D23" s="1">
         <v>2</v>
       </c>
       <c r="E23" s="2">
-        <f t="shared" si="9"/>
-        <v>310207</v>
+        <v>47028</v>
       </c>
       <c r="F23" s="2">
         <v>1</v>
@@ -2367,49 +2495,48 @@
         <v>7</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>37</v>
+        <v>65</v>
       </c>
       <c r="J23" s="1">
         <v>4</v>
       </c>
       <c r="K23" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L23" s="5">
+        <f t="shared" si="4"/>
+        <v>10208</v>
+      </c>
+      <c r="M23" s="1">
+        <v>2100</v>
+      </c>
+      <c r="N23" s="1">
+        <v>5000</v>
+      </c>
+      <c r="P23" s="2">
+        <f t="shared" si="5"/>
+        <v>410207</v>
+      </c>
+    </row>
+    <row r="24" customHeight="1" spans="1:16">
+      <c r="A24" s="1">
         <f t="shared" si="6"/>
         <v>10208</v>
       </c>
-      <c r="M23" s="1">
-        <v>2100</v>
-      </c>
-      <c r="N23" s="1">
-        <v>5000</v>
-      </c>
-      <c r="P23" s="2">
-        <f t="shared" si="7"/>
-        <v>410207</v>
-      </c>
-    </row>
-    <row r="24" customHeight="1" spans="1:16">
-      <c r="A24" s="1">
-        <f t="shared" si="8"/>
-        <v>10208</v>
-      </c>
       <c r="B24" s="1">
         <v>2</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="D24" s="1">
         <v>2</v>
       </c>
       <c r="E24" s="2">
-        <f t="shared" si="9"/>
-        <v>310208</v>
+        <v>47028</v>
       </c>
       <c r="F24" s="2">
         <v>1</v>
@@ -2418,49 +2545,48 @@
         <v>8</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="J24" s="1">
         <v>4</v>
       </c>
       <c r="K24" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L24" s="5">
+        <f t="shared" si="4"/>
+        <v>10209</v>
+      </c>
+      <c r="M24" s="1">
+        <v>2400</v>
+      </c>
+      <c r="N24" s="1">
+        <v>5500</v>
+      </c>
+      <c r="P24" s="2">
+        <f t="shared" si="5"/>
+        <v>410208</v>
+      </c>
+    </row>
+    <row r="25" customHeight="1" spans="1:16">
+      <c r="A25" s="1">
         <f t="shared" si="6"/>
         <v>10209</v>
       </c>
-      <c r="M24" s="1">
-        <v>2400</v>
-      </c>
-      <c r="N24" s="1">
-        <v>5500</v>
-      </c>
-      <c r="P24" s="2">
-        <f t="shared" si="7"/>
-        <v>410208</v>
-      </c>
-    </row>
-    <row r="25" customHeight="1" spans="1:16">
-      <c r="A25" s="1">
-        <f t="shared" si="8"/>
-        <v>10209</v>
-      </c>
       <c r="B25" s="1">
         <v>2</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="D25" s="1">
         <v>2</v>
       </c>
       <c r="E25" s="2">
-        <f t="shared" si="9"/>
-        <v>310209</v>
+        <v>47028</v>
       </c>
       <c r="F25" s="2">
         <v>1</v>
@@ -2469,49 +2595,48 @@
         <v>9</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>37</v>
+        <v>67</v>
       </c>
       <c r="J25" s="1">
         <v>4</v>
       </c>
       <c r="K25" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L25" s="5">
+        <f t="shared" si="4"/>
+        <v>10210</v>
+      </c>
+      <c r="M25" s="1">
+        <v>2700</v>
+      </c>
+      <c r="N25" s="1">
+        <v>6000</v>
+      </c>
+      <c r="P25" s="2">
+        <f t="shared" si="5"/>
+        <v>410209</v>
+      </c>
+    </row>
+    <row r="26" customHeight="1" spans="1:16">
+      <c r="A26" s="1">
         <f t="shared" si="6"/>
         <v>10210</v>
       </c>
-      <c r="M25" s="1">
-        <v>2700</v>
-      </c>
-      <c r="N25" s="1">
-        <v>6000</v>
-      </c>
-      <c r="P25" s="2">
-        <f t="shared" si="7"/>
-        <v>410209</v>
-      </c>
-    </row>
-    <row r="26" customHeight="1" spans="1:16">
-      <c r="A26" s="1">
-        <f t="shared" si="8"/>
-        <v>10210</v>
-      </c>
       <c r="B26" s="1">
         <v>2</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="D26" s="1">
         <v>2</v>
       </c>
       <c r="E26" s="2">
-        <f t="shared" si="9"/>
-        <v>310210</v>
+        <v>47028</v>
       </c>
       <c r="F26" s="2">
         <v>1</v>
@@ -2520,34 +2645,33 @@
         <v>10</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="J26" s="1">
         <v>4</v>
       </c>
       <c r="K26"/>
       <c r="P26" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>410210</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="1:16">
       <c r="A27" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>10300</v>
       </c>
       <c r="B27" s="1">
         <v>3</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="D27" s="1">
         <v>4</v>
       </c>
       <c r="E27" s="2">
-        <f t="shared" si="9"/>
-        <v>310300</v>
+        <v>47029</v>
       </c>
       <c r="F27" s="2">
         <v>1</v>
@@ -2556,14 +2680,17 @@
         <v>0</v>
       </c>
       <c r="H27" s="2"/>
+      <c r="I27" s="3" t="s">
+        <v>58</v>
+      </c>
       <c r="J27" s="1">
         <v>4</v>
       </c>
       <c r="K27" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L27" s="5">
-        <f t="shared" ref="L27:L36" si="10">A28</f>
+        <f t="shared" ref="L27:L36" si="7">A28</f>
         <v>10301</v>
       </c>
       <c r="M27" s="1">
@@ -2578,21 +2705,20 @@
     </row>
     <row r="28" customHeight="1" spans="1:16">
       <c r="A28" s="1">
-        <f t="shared" ref="A28:A43" si="11">10000+G28+B28*100</f>
+        <f t="shared" ref="A28:A43" si="8">10000+G28+B28*100</f>
         <v>10301</v>
       </c>
       <c r="B28" s="1">
         <v>3</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="D28" s="1">
         <v>4</v>
       </c>
       <c r="E28" s="2">
-        <f t="shared" ref="E28:E47" si="12">300000+A28</f>
-        <v>310301</v>
+        <v>47029</v>
       </c>
       <c r="F28" s="2">
         <v>1</v>
@@ -2601,19 +2727,19 @@
         <v>1</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="J28" s="1">
         <v>4</v>
       </c>
       <c r="K28" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L28" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>10302</v>
       </c>
       <c r="M28" s="1">
@@ -2623,27 +2749,26 @@
         <v>1000</v>
       </c>
       <c r="P28" s="2">
-        <f t="shared" ref="P28:P47" si="13">400000+A28</f>
+        <f t="shared" ref="P28:P47" si="9">400000+A28</f>
         <v>410301</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="1:16">
       <c r="A29" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>10302</v>
       </c>
       <c r="B29" s="1">
         <v>3</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="D29" s="1">
         <v>4</v>
       </c>
       <c r="E29" s="2">
-        <f t="shared" si="12"/>
-        <v>310302</v>
+        <v>47029</v>
       </c>
       <c r="F29" s="2">
         <v>1</v>
@@ -2652,19 +2777,19 @@
         <v>2</v>
       </c>
       <c r="H29" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="J29" s="1">
+        <v>4</v>
+      </c>
+      <c r="K29" t="s">
         <v>39</v>
       </c>
-      <c r="I29" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="J29" s="1">
-        <v>4</v>
-      </c>
-      <c r="K29" t="s">
-        <v>38</v>
-      </c>
       <c r="L29" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>10303</v>
       </c>
       <c r="M29" s="1">
@@ -2674,27 +2799,26 @@
         <v>1500</v>
       </c>
       <c r="P29" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v>410302</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="1:16">
       <c r="A30" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>10303</v>
       </c>
       <c r="B30" s="1">
         <v>3</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="D30" s="1">
         <v>4</v>
       </c>
       <c r="E30" s="2">
-        <f t="shared" si="12"/>
-        <v>310303</v>
+        <v>47029</v>
       </c>
       <c r="F30" s="2">
         <v>1</v>
@@ -2703,19 +2827,19 @@
         <v>3</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="J30" s="1">
         <v>4</v>
       </c>
       <c r="K30" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L30" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>10304</v>
       </c>
       <c r="M30" s="1">
@@ -2725,27 +2849,26 @@
         <v>2000</v>
       </c>
       <c r="P30" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v>410303</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="1:16">
       <c r="A31" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>10304</v>
       </c>
       <c r="B31" s="1">
         <v>3</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="D31" s="1">
         <v>4</v>
       </c>
       <c r="E31" s="2">
-        <f t="shared" si="12"/>
-        <v>310304</v>
+        <v>47029</v>
       </c>
       <c r="F31" s="2">
         <v>1</v>
@@ -2754,19 +2877,19 @@
         <v>4</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="J31" s="1">
         <v>4</v>
       </c>
       <c r="K31" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L31" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>10305</v>
       </c>
       <c r="M31" s="1">
@@ -2776,27 +2899,26 @@
         <v>3500</v>
       </c>
       <c r="P31" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v>410304</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="1:16">
       <c r="A32" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>10305</v>
       </c>
       <c r="B32" s="1">
         <v>3</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="D32" s="1">
         <v>4</v>
       </c>
       <c r="E32" s="2">
-        <f t="shared" si="12"/>
-        <v>310305</v>
+        <v>47029</v>
       </c>
       <c r="F32" s="2">
         <v>1</v>
@@ -2805,19 +2927,19 @@
         <v>5</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="J32" s="1">
         <v>4</v>
       </c>
       <c r="K32" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L32" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>10306</v>
       </c>
       <c r="M32" s="1">
@@ -2827,27 +2949,26 @@
         <v>4000</v>
       </c>
       <c r="P32" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v>410305</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="1:16">
       <c r="A33" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>10306</v>
       </c>
       <c r="B33" s="1">
         <v>3</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="D33" s="1">
         <v>4</v>
       </c>
       <c r="E33" s="2">
-        <f t="shared" si="12"/>
-        <v>310306</v>
+        <v>47029</v>
       </c>
       <c r="F33" s="2">
         <v>1</v>
@@ -2856,19 +2977,19 @@
         <v>6</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>37</v>
+        <v>64</v>
       </c>
       <c r="J33" s="1">
         <v>4</v>
       </c>
       <c r="K33" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L33" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>10307</v>
       </c>
       <c r="M33" s="1">
@@ -2878,27 +2999,26 @@
         <v>4500</v>
       </c>
       <c r="P33" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v>410306</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="1:16">
       <c r="A34" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>10307</v>
       </c>
       <c r="B34" s="1">
         <v>3</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="D34" s="1">
         <v>4</v>
       </c>
       <c r="E34" s="2">
-        <f t="shared" si="12"/>
-        <v>310307</v>
+        <v>47029</v>
       </c>
       <c r="F34" s="2">
         <v>1</v>
@@ -2907,19 +3027,19 @@
         <v>7</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>37</v>
+        <v>65</v>
       </c>
       <c r="J34" s="1">
         <v>4</v>
       </c>
       <c r="K34" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L34" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>10308</v>
       </c>
       <c r="M34" s="1">
@@ -2929,27 +3049,26 @@
         <v>5000</v>
       </c>
       <c r="P34" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v>410307</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="1:16">
       <c r="A35" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>10308</v>
       </c>
       <c r="B35" s="1">
         <v>3</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="D35" s="1">
         <v>4</v>
       </c>
       <c r="E35" s="2">
-        <f t="shared" si="12"/>
-        <v>310308</v>
+        <v>47029</v>
       </c>
       <c r="F35" s="2">
         <v>1</v>
@@ -2958,19 +3077,19 @@
         <v>8</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="J35" s="1">
         <v>4</v>
       </c>
       <c r="K35" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L35" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>10309</v>
       </c>
       <c r="M35" s="1">
@@ -2980,27 +3099,26 @@
         <v>5500</v>
       </c>
       <c r="P35" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v>410308</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="1:16">
       <c r="A36" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>10309</v>
       </c>
       <c r="B36" s="1">
         <v>3</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="D36" s="1">
         <v>4</v>
       </c>
       <c r="E36" s="2">
-        <f t="shared" si="12"/>
-        <v>310309</v>
+        <v>47029</v>
       </c>
       <c r="F36" s="2">
         <v>1</v>
@@ -3009,19 +3127,19 @@
         <v>9</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>37</v>
+        <v>67</v>
       </c>
       <c r="J36" s="1">
         <v>4</v>
       </c>
       <c r="K36" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L36" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>10310</v>
       </c>
       <c r="M36" s="1">
@@ -3031,27 +3149,26 @@
         <v>6000</v>
       </c>
       <c r="P36" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v>410309</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="1:16">
       <c r="A37" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>10310</v>
       </c>
       <c r="B37" s="1">
         <v>3</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="D37" s="1">
         <v>4</v>
       </c>
       <c r="E37" s="2">
-        <f t="shared" si="12"/>
-        <v>310310</v>
+        <v>47029</v>
       </c>
       <c r="F37" s="2">
         <v>1</v>
@@ -3060,45 +3177,47 @@
         <v>10</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="J37" s="1">
         <v>4</v>
       </c>
       <c r="K37"/>
       <c r="P37" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v>410310</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="1:16">
       <c r="A38" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>10400</v>
       </c>
       <c r="B38" s="1">
         <v>4</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="D38" s="1">
         <v>2</v>
       </c>
       <c r="E38" s="2">
-        <f t="shared" si="12"/>
-        <v>310400</v>
+        <v>47043</v>
       </c>
       <c r="F38" s="2">
         <v>0</v>
       </c>
       <c r="G38" s="1">
         <v>0</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>70</v>
       </c>
       <c r="J38" s="1"/>
       <c r="K38"/>
       <c r="L38" s="5">
-        <f t="shared" ref="L38:L47" si="14">A39</f>
+        <f t="shared" ref="L38:L47" si="10">A39</f>
         <v>10401</v>
       </c>
       <c r="M38" s="1">
@@ -3113,21 +3232,20 @@
     </row>
     <row r="39" customHeight="1" spans="1:16">
       <c r="A39" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>10401</v>
       </c>
       <c r="B39" s="1">
         <v>4</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="D39" s="1">
         <v>2</v>
       </c>
       <c r="E39" s="2">
-        <f t="shared" si="12"/>
-        <v>310401</v>
+        <v>47043</v>
       </c>
       <c r="F39" s="2">
         <v>0</v>
@@ -3136,39 +3254,38 @@
         <v>1</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="J39" s="1"/>
       <c r="K39"/>
       <c r="L39" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v>10402</v>
       </c>
       <c r="M39" s="1">
         <v>300</v>
       </c>
       <c r="P39" s="2">
-        <f t="shared" ref="P39:P48" si="15">400000+A39</f>
+        <f t="shared" ref="P39:P48" si="11">400000+A39</f>
         <v>410401</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="1:16">
       <c r="A40" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>10402</v>
       </c>
       <c r="B40" s="1">
         <v>4</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="D40" s="1">
         <v>2</v>
       </c>
       <c r="E40" s="2">
-        <f t="shared" si="12"/>
-        <v>310402</v>
+        <v>47043</v>
       </c>
       <c r="F40" s="2">
         <v>0</v>
@@ -3177,39 +3294,38 @@
         <v>2</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="J40" s="1"/>
       <c r="K40"/>
       <c r="L40" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v>10403</v>
       </c>
       <c r="M40" s="1">
         <v>600</v>
       </c>
       <c r="P40" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>410402</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="1:16">
       <c r="A41" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>10403</v>
       </c>
       <c r="B41" s="1">
         <v>4</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="D41" s="1">
         <v>2</v>
       </c>
       <c r="E41" s="2">
-        <f t="shared" si="12"/>
-        <v>310403</v>
+        <v>47043</v>
       </c>
       <c r="F41" s="2">
         <v>0</v>
@@ -3218,39 +3334,38 @@
         <v>3</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="J41" s="1"/>
       <c r="K41"/>
       <c r="L41" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v>10404</v>
       </c>
       <c r="M41" s="1">
         <v>900</v>
       </c>
       <c r="P41" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>410403</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="1:16">
       <c r="A42" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>10404</v>
       </c>
       <c r="B42" s="1">
         <v>4</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="D42" s="1">
         <v>2</v>
       </c>
       <c r="E42" s="2">
-        <f t="shared" si="12"/>
-        <v>310404</v>
+        <v>47043</v>
       </c>
       <c r="F42" s="2">
         <v>0</v>
@@ -3259,39 +3374,38 @@
         <v>4</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="J42" s="1"/>
       <c r="K42"/>
       <c r="L42" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v>10405</v>
       </c>
       <c r="M42" s="1">
         <v>1200</v>
       </c>
       <c r="P42" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>410404</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="1:16">
       <c r="A43" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>10405</v>
       </c>
       <c r="B43" s="1">
         <v>4</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="D43" s="1">
         <v>2</v>
       </c>
       <c r="E43" s="2">
-        <f t="shared" si="12"/>
-        <v>310405</v>
+        <v>47043</v>
       </c>
       <c r="F43" s="2">
         <v>0</v>
@@ -3300,39 +3414,38 @@
         <v>5</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="J43" s="1"/>
       <c r="K43"/>
       <c r="L43" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v>10406</v>
       </c>
       <c r="M43" s="1">
         <v>1500</v>
       </c>
       <c r="P43" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>410405</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="1:16">
       <c r="A44" s="1">
-        <f t="shared" ref="A44:A54" si="16">10000+G44+B44*100</f>
+        <f t="shared" ref="A44:A54" si="12">10000+G44+B44*100</f>
         <v>10406</v>
       </c>
       <c r="B44" s="1">
         <v>4</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="D44" s="1">
         <v>2</v>
       </c>
       <c r="E44" s="2">
-        <f t="shared" ref="E44:E54" si="17">300000+A44</f>
-        <v>310406</v>
+        <v>47043</v>
       </c>
       <c r="F44" s="2">
         <v>0</v>
@@ -3341,39 +3454,38 @@
         <v>6</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="J44" s="1"/>
       <c r="K44"/>
       <c r="L44" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v>10407</v>
       </c>
       <c r="M44" s="1">
         <v>1800</v>
       </c>
       <c r="P44" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>410406</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="1:16">
       <c r="A45" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="12"/>
         <v>10407</v>
       </c>
       <c r="B45" s="1">
         <v>4</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="D45" s="1">
         <v>2</v>
       </c>
       <c r="E45" s="2">
-        <f t="shared" si="17"/>
-        <v>310407</v>
+        <v>47043</v>
       </c>
       <c r="F45" s="2">
         <v>0</v>
@@ -3382,39 +3494,38 @@
         <v>7</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="J45" s="1"/>
       <c r="K45"/>
       <c r="L45" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v>10408</v>
       </c>
       <c r="M45" s="1">
         <v>2100</v>
       </c>
       <c r="P45" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>410407</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="1:16">
       <c r="A46" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="12"/>
         <v>10408</v>
       </c>
       <c r="B46" s="1">
         <v>4</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="D46" s="1">
         <v>2</v>
       </c>
       <c r="E46" s="2">
-        <f t="shared" si="17"/>
-        <v>310408</v>
+        <v>47043</v>
       </c>
       <c r="F46" s="2">
         <v>0</v>
@@ -3423,39 +3534,38 @@
         <v>8</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="J46" s="1"/>
       <c r="K46"/>
       <c r="L46" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v>10409</v>
       </c>
       <c r="M46" s="1">
         <v>2400</v>
       </c>
       <c r="P46" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>410408</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="1:16">
       <c r="A47" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="12"/>
         <v>10409</v>
       </c>
       <c r="B47" s="1">
         <v>4</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="D47" s="1">
         <v>2</v>
       </c>
       <c r="E47" s="2">
-        <f t="shared" si="17"/>
-        <v>310409</v>
+        <v>47043</v>
       </c>
       <c r="F47" s="2">
         <v>0</v>
@@ -3464,39 +3574,38 @@
         <v>9</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>51</v>
+        <v>78</v>
       </c>
       <c r="J47" s="1"/>
       <c r="K47"/>
       <c r="L47" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v>10410</v>
       </c>
       <c r="M47" s="1">
         <v>2700</v>
       </c>
       <c r="P47" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>410409</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="1:16">
       <c r="A48" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="12"/>
         <v>10410</v>
       </c>
       <c r="B48" s="1">
         <v>4</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="D48" s="1">
         <v>2</v>
       </c>
       <c r="E48" s="2">
-        <f t="shared" si="17"/>
-        <v>310410</v>
+        <v>47043</v>
       </c>
       <c r="F48" s="2">
         <v>0</v>
@@ -3507,27 +3616,26 @@
       <c r="J48" s="1"/>
       <c r="K48"/>
       <c r="P48" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>410410</v>
       </c>
     </row>
     <row r="49" customHeight="1" spans="1:16">
       <c r="A49" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="12"/>
         <v>10500</v>
       </c>
       <c r="B49" s="1">
         <v>5</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="D49" s="1">
         <v>2</v>
       </c>
       <c r="E49" s="2">
-        <f t="shared" si="17"/>
-        <v>310500</v>
+        <v>47044</v>
       </c>
       <c r="F49" s="2">
         <v>0</v>
@@ -3535,14 +3643,17 @@
       <c r="G49" s="1">
         <v>0</v>
       </c>
+      <c r="I49" s="3" t="s">
+        <v>80</v>
+      </c>
       <c r="J49" s="1">
         <v>4</v>
       </c>
       <c r="K49" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L49" s="5">
-        <f t="shared" ref="L49:L58" si="18">A50</f>
+        <f t="shared" ref="L49:L58" si="13">A50</f>
         <v>10501</v>
       </c>
       <c r="M49" s="1">
@@ -3557,21 +3668,20 @@
     </row>
     <row r="50" customHeight="1" spans="1:16">
       <c r="A50" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="12"/>
         <v>10501</v>
       </c>
       <c r="B50" s="1">
         <v>5</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="D50" s="1">
         <v>2</v>
       </c>
       <c r="E50" s="2">
-        <f t="shared" si="17"/>
-        <v>310501</v>
+        <v>47044</v>
       </c>
       <c r="F50" s="2">
         <v>0</v>
@@ -3580,16 +3690,16 @@
         <v>1</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>51</v>
+        <v>81</v>
       </c>
       <c r="J50" s="1">
         <v>4</v>
       </c>
       <c r="K50" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L50" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="13"/>
         <v>10502</v>
       </c>
       <c r="M50" s="1">
@@ -3599,27 +3709,26 @@
         <v>22001</v>
       </c>
       <c r="P50" s="2">
-        <f t="shared" ref="P50:P59" si="19">400000+A50</f>
+        <f t="shared" ref="P50:P59" si="14">400000+A50</f>
         <v>410501</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="1:16">
       <c r="A51" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="12"/>
         <v>10502</v>
       </c>
       <c r="B51" s="1">
         <v>5</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="D51" s="1">
         <v>2</v>
       </c>
       <c r="E51" s="2">
-        <f t="shared" si="17"/>
-        <v>310502</v>
+        <v>47044</v>
       </c>
       <c r="F51" s="2">
         <v>0</v>
@@ -3628,16 +3737,16 @@
         <v>2</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>51</v>
+        <v>82</v>
       </c>
       <c r="J51" s="1">
         <v>4</v>
       </c>
       <c r="K51" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L51" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="13"/>
         <v>10503</v>
       </c>
       <c r="M51" s="1">
@@ -3647,27 +3756,26 @@
         <v>22002</v>
       </c>
       <c r="P51" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="14"/>
         <v>410502</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="1:16">
       <c r="A52" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="12"/>
         <v>10503</v>
       </c>
       <c r="B52" s="1">
         <v>5</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="D52" s="1">
         <v>2</v>
       </c>
       <c r="E52" s="2">
-        <f t="shared" si="17"/>
-        <v>310503</v>
+        <v>47044</v>
       </c>
       <c r="F52" s="2">
         <v>0</v>
@@ -3676,16 +3784,16 @@
         <v>3</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>51</v>
+        <v>83</v>
       </c>
       <c r="J52" s="1">
         <v>4</v>
       </c>
       <c r="K52" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L52" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="13"/>
         <v>10504</v>
       </c>
       <c r="M52" s="1">
@@ -3695,27 +3803,26 @@
         <v>22003</v>
       </c>
       <c r="P52" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="14"/>
         <v>410503</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="1:16">
       <c r="A53" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="12"/>
         <v>10504</v>
       </c>
       <c r="B53" s="1">
         <v>5</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="D53" s="1">
         <v>2</v>
       </c>
       <c r="E53" s="2">
-        <f t="shared" si="17"/>
-        <v>310504</v>
+        <v>47044</v>
       </c>
       <c r="F53" s="2">
         <v>0</v>
@@ -3724,16 +3831,16 @@
         <v>4</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>51</v>
+        <v>84</v>
       </c>
       <c r="J53" s="1">
         <v>4</v>
       </c>
       <c r="K53" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L53" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="13"/>
         <v>10505</v>
       </c>
       <c r="M53" s="1">
@@ -3743,27 +3850,26 @@
         <v>22004</v>
       </c>
       <c r="P53" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="14"/>
         <v>410504</v>
       </c>
     </row>
     <row r="54" customHeight="1" spans="1:16">
       <c r="A54" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="12"/>
         <v>10505</v>
       </c>
       <c r="B54" s="1">
         <v>5</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="D54" s="1">
         <v>2</v>
       </c>
       <c r="E54" s="2">
-        <f t="shared" si="17"/>
-        <v>310505</v>
+        <v>47044</v>
       </c>
       <c r="F54" s="2">
         <v>0</v>
@@ -3772,16 +3878,16 @@
         <v>5</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="J54" s="1">
         <v>4</v>
       </c>
       <c r="K54" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L54" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="13"/>
         <v>10506</v>
       </c>
       <c r="M54" s="1">
@@ -3791,27 +3897,26 @@
         <v>22005</v>
       </c>
       <c r="P54" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="14"/>
         <v>410505</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="1:16">
       <c r="A55" s="1">
-        <f t="shared" ref="A55:A60" si="20">10000+G55+B55*100</f>
+        <f t="shared" ref="A55:A60" si="15">10000+G55+B55*100</f>
         <v>10506</v>
       </c>
       <c r="B55" s="1">
         <v>5</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="D55" s="1">
         <v>2</v>
       </c>
       <c r="E55" s="2">
-        <f t="shared" ref="E55:E60" si="21">300000+A55</f>
-        <v>310506</v>
+        <v>47044</v>
       </c>
       <c r="F55" s="2">
         <v>0</v>
@@ -3820,16 +3925,16 @@
         <v>6</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>51</v>
+        <v>86</v>
       </c>
       <c r="J55" s="1">
         <v>4</v>
       </c>
       <c r="K55" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L55" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="13"/>
         <v>10507</v>
       </c>
       <c r="M55" s="1">
@@ -3839,27 +3944,26 @@
         <v>22006</v>
       </c>
       <c r="P55" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="14"/>
         <v>410506</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="1:16">
       <c r="A56" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="15"/>
         <v>10507</v>
       </c>
       <c r="B56" s="1">
         <v>5</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="D56" s="1">
         <v>2</v>
       </c>
       <c r="E56" s="2">
-        <f t="shared" si="21"/>
-        <v>310507</v>
+        <v>47044</v>
       </c>
       <c r="F56" s="2">
         <v>0</v>
@@ -3868,16 +3972,16 @@
         <v>7</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>51</v>
+        <v>87</v>
       </c>
       <c r="J56" s="1">
         <v>4</v>
       </c>
       <c r="K56" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L56" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="13"/>
         <v>10508</v>
       </c>
       <c r="M56" s="1">
@@ -3887,27 +3991,26 @@
         <v>22007</v>
       </c>
       <c r="P56" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="14"/>
         <v>410507</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="1:16">
       <c r="A57" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="15"/>
         <v>10508</v>
       </c>
       <c r="B57" s="1">
         <v>5</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="D57" s="1">
         <v>2</v>
       </c>
       <c r="E57" s="2">
-        <f t="shared" si="21"/>
-        <v>310508</v>
+        <v>47044</v>
       </c>
       <c r="F57" s="2">
         <v>0</v>
@@ -3916,16 +4019,16 @@
         <v>8</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>51</v>
+        <v>88</v>
       </c>
       <c r="J57" s="1">
         <v>4</v>
       </c>
       <c r="K57" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L57" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="13"/>
         <v>10509</v>
       </c>
       <c r="M57" s="1">
@@ -3935,27 +4038,26 @@
         <v>22008</v>
       </c>
       <c r="P57" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="14"/>
         <v>410508</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="1:16">
       <c r="A58" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="15"/>
         <v>10509</v>
       </c>
       <c r="B58" s="1">
         <v>5</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="D58" s="1">
         <v>2</v>
       </c>
       <c r="E58" s="2">
-        <f t="shared" si="21"/>
-        <v>310509</v>
+        <v>47044</v>
       </c>
       <c r="F58" s="2">
         <v>0</v>
@@ -3964,16 +4066,16 @@
         <v>9</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="J58" s="1">
         <v>4</v>
       </c>
       <c r="K58" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L58" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="13"/>
         <v>10510</v>
       </c>
       <c r="M58" s="1">
@@ -3983,27 +4085,26 @@
         <v>22009</v>
       </c>
       <c r="P58" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="14"/>
         <v>410509</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="1:16">
       <c r="A59" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="15"/>
         <v>10510</v>
       </c>
       <c r="B59" s="1">
         <v>5</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="D59" s="1">
         <v>2</v>
       </c>
       <c r="E59" s="2">
-        <f t="shared" si="21"/>
-        <v>310510</v>
+        <v>47044</v>
       </c>
       <c r="F59" s="2">
         <v>0</v>
@@ -4019,27 +4120,26 @@
         <v>22010</v>
       </c>
       <c r="P59" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="14"/>
         <v>410510</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="1:16">
       <c r="A60" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="15"/>
         <v>10600</v>
       </c>
       <c r="B60" s="1">
         <v>6</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>53</v>
+        <v>90</v>
       </c>
       <c r="D60" s="1">
         <v>4</v>
       </c>
       <c r="E60" s="2">
-        <f t="shared" si="21"/>
-        <v>310600</v>
+        <v>47045</v>
       </c>
       <c r="F60" s="2">
         <v>0</v>
@@ -4047,14 +4147,17 @@
       <c r="G60" s="1">
         <v>0</v>
       </c>
+      <c r="I60" s="3" t="s">
+        <v>91</v>
+      </c>
       <c r="J60" s="1">
         <v>4</v>
       </c>
       <c r="K60" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L60" s="5">
-        <f t="shared" ref="L60:L69" si="22">A61</f>
+        <f t="shared" ref="L60:L69" si="16">A61</f>
         <v>10601</v>
       </c>
       <c r="M60" s="1">
@@ -4069,21 +4172,20 @@
     </row>
     <row r="61" customHeight="1" spans="1:16">
       <c r="A61" s="1">
-        <f t="shared" ref="A61:A72" si="23">10000+G61+B61*100</f>
+        <f t="shared" ref="A61:A72" si="17">10000+G61+B61*100</f>
         <v>10601</v>
       </c>
       <c r="B61" s="1">
         <v>6</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>53</v>
+        <v>90</v>
       </c>
       <c r="D61" s="1">
         <v>4</v>
       </c>
       <c r="E61" s="2">
-        <f t="shared" ref="E61:E72" si="24">300000+A61</f>
-        <v>310601</v>
+        <v>47045</v>
       </c>
       <c r="F61" s="2">
         <v>0</v>
@@ -4092,16 +4194,16 @@
         <v>1</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>51</v>
+        <v>92</v>
       </c>
       <c r="J61" s="1">
         <v>4</v>
       </c>
       <c r="K61" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L61" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="16"/>
         <v>10602</v>
       </c>
       <c r="M61" s="1">
@@ -4111,27 +4213,26 @@
         <v>11001</v>
       </c>
       <c r="P61" s="2">
-        <f t="shared" ref="P61:P71" si="25">400000+A61</f>
+        <f t="shared" ref="P61:P71" si="18">400000+A61</f>
         <v>410601</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="1:16">
       <c r="A62" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="17"/>
         <v>10602</v>
       </c>
       <c r="B62" s="1">
         <v>6</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>53</v>
+        <v>90</v>
       </c>
       <c r="D62" s="1">
         <v>4</v>
       </c>
       <c r="E62" s="2">
-        <f t="shared" si="24"/>
-        <v>310602</v>
+        <v>47045</v>
       </c>
       <c r="F62" s="2">
         <v>0</v>
@@ -4140,16 +4241,16 @@
         <v>2</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>51</v>
+        <v>93</v>
       </c>
       <c r="J62" s="1">
         <v>4</v>
       </c>
       <c r="K62" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L62" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="16"/>
         <v>10603</v>
       </c>
       <c r="M62" s="1">
@@ -4159,27 +4260,26 @@
         <v>11002</v>
       </c>
       <c r="P62" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="18"/>
         <v>410602</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="1:16">
       <c r="A63" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="17"/>
         <v>10603</v>
       </c>
       <c r="B63" s="1">
         <v>6</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>53</v>
+        <v>90</v>
       </c>
       <c r="D63" s="1">
         <v>4</v>
       </c>
       <c r="E63" s="2">
-        <f t="shared" si="24"/>
-        <v>310603</v>
+        <v>47045</v>
       </c>
       <c r="F63" s="2">
         <v>0</v>
@@ -4188,16 +4288,16 @@
         <v>3</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>51</v>
+        <v>94</v>
       </c>
       <c r="J63" s="1">
         <v>4</v>
       </c>
       <c r="K63" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L63" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="16"/>
         <v>10604</v>
       </c>
       <c r="M63" s="1">
@@ -4207,27 +4307,26 @@
         <v>11003</v>
       </c>
       <c r="P63" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="18"/>
         <v>410603</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="1:16">
       <c r="A64" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="17"/>
         <v>10604</v>
       </c>
       <c r="B64" s="1">
         <v>6</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>53</v>
+        <v>90</v>
       </c>
       <c r="D64" s="1">
         <v>4</v>
       </c>
       <c r="E64" s="2">
-        <f t="shared" si="24"/>
-        <v>310604</v>
+        <v>47045</v>
       </c>
       <c r="F64" s="2">
         <v>0</v>
@@ -4236,16 +4335,16 @@
         <v>4</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>51</v>
+        <v>95</v>
       </c>
       <c r="J64" s="1">
         <v>4</v>
       </c>
       <c r="K64" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L64" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="16"/>
         <v>10605</v>
       </c>
       <c r="M64" s="1">
@@ -4255,27 +4354,26 @@
         <v>11004</v>
       </c>
       <c r="P64" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="18"/>
         <v>410604</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="1:16">
       <c r="A65" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="17"/>
         <v>10605</v>
       </c>
       <c r="B65" s="1">
         <v>6</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>53</v>
+        <v>90</v>
       </c>
       <c r="D65" s="1">
         <v>4</v>
       </c>
       <c r="E65" s="2">
-        <f t="shared" si="24"/>
-        <v>310605</v>
+        <v>47045</v>
       </c>
       <c r="F65" s="2">
         <v>0</v>
@@ -4284,16 +4382,16 @@
         <v>5</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>51</v>
+        <v>96</v>
       </c>
       <c r="J65" s="1">
         <v>4</v>
       </c>
       <c r="K65" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L65" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="16"/>
         <v>10606</v>
       </c>
       <c r="M65" s="1">
@@ -4303,27 +4401,26 @@
         <v>11005</v>
       </c>
       <c r="P65" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="18"/>
         <v>410605</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="1:16">
       <c r="A66" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="17"/>
         <v>10606</v>
       </c>
       <c r="B66" s="1">
         <v>6</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>53</v>
+        <v>90</v>
       </c>
       <c r="D66" s="1">
         <v>4</v>
       </c>
       <c r="E66" s="2">
-        <f t="shared" si="24"/>
-        <v>310606</v>
+        <v>47045</v>
       </c>
       <c r="F66" s="2">
         <v>0</v>
@@ -4332,16 +4429,16 @@
         <v>6</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>51</v>
+        <v>97</v>
       </c>
       <c r="J66" s="1">
         <v>4</v>
       </c>
       <c r="K66" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L66" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="16"/>
         <v>10607</v>
       </c>
       <c r="M66" s="1">
@@ -4351,27 +4448,26 @@
         <v>11006</v>
       </c>
       <c r="P66" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="18"/>
         <v>410606</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="1:16">
       <c r="A67" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="17"/>
         <v>10607</v>
       </c>
       <c r="B67" s="1">
         <v>6</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>53</v>
+        <v>90</v>
       </c>
       <c r="D67" s="1">
         <v>4</v>
       </c>
       <c r="E67" s="2">
-        <f t="shared" si="24"/>
-        <v>310607</v>
+        <v>47045</v>
       </c>
       <c r="F67" s="2">
         <v>0</v>
@@ -4380,16 +4476,16 @@
         <v>7</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>51</v>
+        <v>98</v>
       </c>
       <c r="J67" s="1">
         <v>4</v>
       </c>
       <c r="K67" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L67" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="16"/>
         <v>10608</v>
       </c>
       <c r="M67" s="1">
@@ -4399,27 +4495,26 @@
         <v>11007</v>
       </c>
       <c r="P67" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="18"/>
         <v>410607</v>
       </c>
     </row>
     <row r="68" customHeight="1" spans="1:16">
       <c r="A68" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="17"/>
         <v>10608</v>
       </c>
       <c r="B68" s="1">
         <v>6</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>53</v>
+        <v>90</v>
       </c>
       <c r="D68" s="1">
         <v>4</v>
       </c>
       <c r="E68" s="2">
-        <f t="shared" si="24"/>
-        <v>310608</v>
+        <v>47045</v>
       </c>
       <c r="F68" s="2">
         <v>0</v>
@@ -4428,16 +4523,16 @@
         <v>8</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>51</v>
+        <v>99</v>
       </c>
       <c r="J68" s="1">
         <v>4</v>
       </c>
       <c r="K68" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L68" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="16"/>
         <v>10609</v>
       </c>
       <c r="M68" s="1">
@@ -4447,27 +4542,26 @@
         <v>11008</v>
       </c>
       <c r="P68" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="18"/>
         <v>410608</v>
       </c>
     </row>
     <row r="69" customHeight="1" spans="1:16">
       <c r="A69" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="17"/>
         <v>10609</v>
       </c>
       <c r="B69" s="1">
         <v>6</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>53</v>
+        <v>90</v>
       </c>
       <c r="D69" s="1">
         <v>4</v>
       </c>
       <c r="E69" s="2">
-        <f t="shared" si="24"/>
-        <v>310609</v>
+        <v>47045</v>
       </c>
       <c r="F69" s="2">
         <v>0</v>
@@ -4476,16 +4570,16 @@
         <v>9</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>51</v>
+        <v>100</v>
       </c>
       <c r="J69" s="1">
         <v>4</v>
       </c>
       <c r="K69" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L69" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="16"/>
         <v>10610</v>
       </c>
       <c r="M69" s="1">
@@ -4495,27 +4589,26 @@
         <v>11009</v>
       </c>
       <c r="P69" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="18"/>
         <v>410609</v>
       </c>
     </row>
     <row r="70" customHeight="1" spans="1:16">
       <c r="A70" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="17"/>
         <v>10610</v>
       </c>
       <c r="B70" s="1">
         <v>6</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>53</v>
+        <v>90</v>
       </c>
       <c r="D70" s="1">
         <v>4</v>
       </c>
       <c r="E70" s="2">
-        <f t="shared" si="24"/>
-        <v>310610</v>
+        <v>47045</v>
       </c>
       <c r="F70" s="2">
         <v>0</v>
@@ -4531,26 +4624,26 @@
         <v>11010</v>
       </c>
       <c r="P70" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="18"/>
         <v>410610</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="1:16">
       <c r="A71" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="17"/>
         <v>10700</v>
       </c>
       <c r="B71" s="1">
         <v>7</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>54</v>
+        <v>101</v>
       </c>
       <c r="D71" s="1">
         <v>4</v>
       </c>
       <c r="E71" s="2">
-        <f t="shared" si="24"/>
+        <f>300000+A71</f>
         <v>310700</v>
       </c>
       <c r="F71" s="2">
@@ -4578,20 +4671,20 @@
     </row>
     <row r="72" customHeight="1" spans="1:16">
       <c r="A72" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="17"/>
         <v>10701</v>
       </c>
       <c r="B72" s="1">
         <v>7</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>54</v>
+        <v>101</v>
       </c>
       <c r="D72" s="1">
         <v>4</v>
       </c>
       <c r="E72" s="2">
-        <f t="shared" si="24"/>
+        <f>300000+A72</f>
         <v>310701</v>
       </c>
       <c r="F72" s="2">

--- a/hall/resources/sample/BuildingFunction.xlsx
+++ b/hall/resources/sample/BuildingFunction.xlsx
@@ -608,12 +608,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2119,6 +2119,9 @@
         <v>4</v>
       </c>
       <c r="K15"/>
+      <c r="N15" s="1">
+        <v>6500</v>
+      </c>
       <c r="P15" s="2">
         <f t="shared" si="2"/>
         <v>410110</v>
@@ -2651,6 +2654,9 @@
         <v>4</v>
       </c>
       <c r="K26"/>
+      <c r="N26" s="1">
+        <v>6500</v>
+      </c>
       <c r="P26" s="2">
         <f t="shared" si="5"/>
         <v>410210</v>
@@ -3183,6 +3189,9 @@
         <v>4</v>
       </c>
       <c r="K37"/>
+      <c r="N37" s="1">
+        <v>6500</v>
+      </c>
       <c r="P37" s="2">
         <f t="shared" si="9"/>
         <v>410310</v>

--- a/hall/resources/sample/BuildingFunction.xlsx
+++ b/hall/resources/sample/BuildingFunction.xlsx
@@ -131,7 +131,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="208">
   <si>
     <t>id</t>
   </si>
@@ -238,106 +238,331 @@
     <t>slot机台</t>
   </si>
   <si>
-    <t>1023001_1</t>
+    <t>1023001_2</t>
   </si>
   <si>
     <t>1_1</t>
   </si>
   <si>
-    <t>1_1990000_100</t>
-  </si>
-  <si>
-    <t>1023001_5</t>
+    <t>5_1990000_20</t>
+  </si>
+  <si>
+    <t>1023001_4</t>
   </si>
   <si>
     <t>1_10</t>
   </si>
   <si>
-    <t>1_1990000_110</t>
-  </si>
-  <si>
-    <t>1023001_10</t>
-  </si>
-  <si>
-    <t>1_1990000_120</t>
-  </si>
-  <si>
-    <t>1023001_20</t>
-  </si>
-  <si>
-    <t>1_1990000_130</t>
-  </si>
-  <si>
-    <t>1023001_50</t>
-  </si>
-  <si>
-    <t>1_1990000_140</t>
-  </si>
-  <si>
-    <t>1023001_100;1980000_1</t>
-  </si>
-  <si>
-    <t>1_1990000_150</t>
-  </si>
-  <si>
-    <t>1023001_200;1980000_10</t>
-  </si>
-  <si>
-    <t>1_1990000_160</t>
-  </si>
-  <si>
-    <t>1023001_500;1980000_20</t>
-  </si>
-  <si>
-    <t>1_1990000_170</t>
-  </si>
-  <si>
-    <t>1023001_1000;1980000_50</t>
-  </si>
-  <si>
-    <t>1_1990000_180</t>
-  </si>
-  <si>
-    <t>1023001_2000;1980000_100</t>
-  </si>
-  <si>
-    <t>1_1990000_190</t>
+    <t>5_1990000_30</t>
+  </si>
+  <si>
+    <t>1023001_8</t>
+  </si>
+  <si>
+    <t>5_1990000_40</t>
+  </si>
+  <si>
+    <t>1023001_12</t>
+  </si>
+  <si>
+    <t>5_1990000_50</t>
+  </si>
+  <si>
+    <t>1023001_16</t>
+  </si>
+  <si>
+    <t>1_20</t>
+  </si>
+  <si>
+    <t>5_1990000_60</t>
+  </si>
+  <si>
+    <t>1023001_20;1980000_10</t>
+  </si>
+  <si>
+    <t>5_1990000_70</t>
+  </si>
+  <si>
+    <t>1023002_4</t>
+  </si>
+  <si>
+    <t>1_30</t>
+  </si>
+  <si>
+    <t>5_1990000_80</t>
+  </si>
+  <si>
+    <t>1023002_8</t>
+  </si>
+  <si>
+    <t>5_1990000_90</t>
+  </si>
+  <si>
+    <t>1023002_16</t>
+  </si>
+  <si>
+    <t>1_40</t>
+  </si>
+  <si>
+    <t>5_1990000_110</t>
+  </si>
+  <si>
+    <t>1023002_24;1980000_100</t>
+  </si>
+  <si>
+    <t>1_50</t>
+  </si>
+  <si>
+    <t>5_1990000_130</t>
+  </si>
+  <si>
+    <t>1023003_4</t>
+  </si>
+  <si>
+    <t>1_60</t>
+  </si>
+  <si>
+    <t>5_1990000_150</t>
+  </si>
+  <si>
+    <t>1023003_8</t>
+  </si>
+  <si>
+    <t>1_70</t>
+  </si>
+  <si>
+    <t>5_1990000_190</t>
+  </si>
+  <si>
+    <t>1023003_16</t>
+  </si>
+  <si>
+    <t>1_80</t>
+  </si>
+  <si>
+    <t>5_1990000_230</t>
+  </si>
+  <si>
+    <t>1023003_24;1980000_300</t>
+  </si>
+  <si>
+    <t>1_90</t>
+  </si>
+  <si>
+    <t>5_1990000_270</t>
+  </si>
+  <si>
+    <t>1023004_6</t>
+  </si>
+  <si>
+    <t>1_100</t>
+  </si>
+  <si>
+    <t>5_1990000_330</t>
+  </si>
+  <si>
+    <t>1023004_12</t>
+  </si>
+  <si>
+    <t>1_110</t>
+  </si>
+  <si>
+    <t>5_1990000_390</t>
+  </si>
+  <si>
+    <t>1023004_24;1980000_600</t>
+  </si>
+  <si>
+    <t>1_120</t>
+  </si>
+  <si>
+    <t>5_1990000_450</t>
+  </si>
+  <si>
+    <t>1023005_6</t>
+  </si>
+  <si>
+    <t>1_130</t>
+  </si>
+  <si>
+    <t>5_1990000_530</t>
+  </si>
+  <si>
+    <t>1023005_12</t>
+  </si>
+  <si>
+    <t>1_140</t>
+  </si>
+  <si>
+    <t>5_1990000_610</t>
+  </si>
+  <si>
+    <t>1023005_24</t>
+  </si>
+  <si>
+    <t>1_150</t>
+  </si>
+  <si>
+    <t>5_1990000_690</t>
   </si>
   <si>
     <t>扑克牌桌</t>
   </si>
   <si>
+    <t>1023101_2</t>
+  </si>
+  <si>
+    <t>1023101_4</t>
+  </si>
+  <si>
+    <t>1023101_8</t>
+  </si>
+  <si>
+    <t>1023101_12</t>
+  </si>
+  <si>
+    <t>5_1990000_100</t>
+  </si>
+  <si>
+    <t>1023101_16</t>
+  </si>
+  <si>
+    <t>5_1990000_120</t>
+  </si>
+  <si>
+    <t>1023101_20;1980000_10</t>
+  </si>
+  <si>
+    <t>5_1990000_140</t>
+  </si>
+  <si>
+    <t>5_1990000_160</t>
+  </si>
+  <si>
+    <t>5_1990000_180</t>
+  </si>
+  <si>
+    <t>5_1990000_220</t>
+  </si>
+  <si>
+    <t>1023101_24;1980000_100</t>
+  </si>
+  <si>
+    <t>5_1990000_260</t>
+  </si>
+  <si>
+    <t>5_1990000_300</t>
+  </si>
+  <si>
+    <t>5_1990000_380</t>
+  </si>
+  <si>
+    <t>5_1990000_460</t>
+  </si>
+  <si>
+    <t>1023101_24;1980000_300</t>
+  </si>
+  <si>
+    <t>5_1990000_540</t>
+  </si>
+  <si>
+    <t>1023101_6</t>
+  </si>
+  <si>
+    <t>5_1990000_660</t>
+  </si>
+  <si>
+    <t>5_1990000_780</t>
+  </si>
+  <si>
+    <t>1023101_24;1980000_600</t>
+  </si>
+  <si>
+    <t>5_1990000_900</t>
+  </si>
+  <si>
+    <t>5_1990000_1060</t>
+  </si>
+  <si>
+    <t>5_1990000_1220</t>
+  </si>
+  <si>
+    <t>1023101_24</t>
+  </si>
+  <si>
+    <t>5_1990000_1380</t>
+  </si>
+  <si>
+    <t>幸运转盘</t>
+  </si>
+  <si>
     <t>1023101_1</t>
   </si>
   <si>
-    <t>1023101_5</t>
-  </si>
-  <si>
-    <t>1023101_10</t>
-  </si>
-  <si>
-    <t>1023101_20</t>
-  </si>
-  <si>
-    <t>1023101_50</t>
-  </si>
-  <si>
-    <t>1023101_100;1980000_1</t>
-  </si>
-  <si>
-    <t>1023101_200;1980000_10</t>
-  </si>
-  <si>
-    <t>1023101_500;1980000_20</t>
-  </si>
-  <si>
-    <t>1023101_1000;1980000_50</t>
-  </si>
-  <si>
-    <t>1023101_2000;1980000_100</t>
-  </si>
-  <si>
-    <t>幸运转盘</t>
+    <t>5_1990000_200</t>
+  </si>
+  <si>
+    <t>5_1990000_240</t>
+  </si>
+  <si>
+    <t>1023101_10;1980000_10</t>
+  </si>
+  <si>
+    <t>5_1990000_280</t>
+  </si>
+  <si>
+    <t>5_1990000_320</t>
+  </si>
+  <si>
+    <t>5_1990000_360</t>
+  </si>
+  <si>
+    <t>5_1990000_440</t>
+  </si>
+  <si>
+    <t>1023101_12;1980000_100</t>
+  </si>
+  <si>
+    <t>5_1990000_520</t>
+  </si>
+  <si>
+    <t>5_1990000_600</t>
+  </si>
+  <si>
+    <t>5_1990000_760</t>
+  </si>
+  <si>
+    <t>5_1990000_920</t>
+  </si>
+  <si>
+    <t>1023101_12;1980000_300</t>
+  </si>
+  <si>
+    <t>5_1990000_1080</t>
+  </si>
+  <si>
+    <t>1023101_3</t>
+  </si>
+  <si>
+    <t>5_1990000_1320</t>
+  </si>
+  <si>
+    <t>5_1990000_1560</t>
+  </si>
+  <si>
+    <t>1023101_12;1980000_600</t>
+  </si>
+  <si>
+    <t>5_1990000_1800</t>
+  </si>
+  <si>
+    <t>5_1990000_2120</t>
+  </si>
+  <si>
+    <t>5_1990000_2440</t>
+  </si>
+  <si>
+    <t>5_1990000_2760</t>
   </si>
   <si>
     <t>吧台区</t>
@@ -346,28 +571,61 @@
     <t>1023401_1</t>
   </si>
   <si>
-    <t>1023401_10</t>
-  </si>
-  <si>
-    <t>1023401_20</t>
-  </si>
-  <si>
-    <t>1023401_50</t>
-  </si>
-  <si>
-    <t>1023401_100;1980000_1</t>
-  </si>
-  <si>
-    <t>1023401_200;1980000_10</t>
-  </si>
-  <si>
-    <t>1023401_500;1980000_20</t>
-  </si>
-  <si>
-    <t>1023401_1000;1980000_50</t>
-  </si>
-  <si>
-    <t>1023401_2000;1980000_100</t>
+    <t>1023401_2</t>
+  </si>
+  <si>
+    <t>1023401_4</t>
+  </si>
+  <si>
+    <t>1023401_6</t>
+  </si>
+  <si>
+    <t>1023401_8</t>
+  </si>
+  <si>
+    <t>1023401_10;1980000_10</t>
+  </si>
+  <si>
+    <t>1023402_2</t>
+  </si>
+  <si>
+    <t>1023402_4</t>
+  </si>
+  <si>
+    <t>1023402_8</t>
+  </si>
+  <si>
+    <t>1023402_12;1980000_100</t>
+  </si>
+  <si>
+    <t>1023403_2</t>
+  </si>
+  <si>
+    <t>1023403_4</t>
+  </si>
+  <si>
+    <t>1023403_8</t>
+  </si>
+  <si>
+    <t>1023403_12;1980000_300</t>
+  </si>
+  <si>
+    <t>1023404_3</t>
+  </si>
+  <si>
+    <t>1023404_6</t>
+  </si>
+  <si>
+    <t>1023404_12;1980000_600</t>
+  </si>
+  <si>
+    <t>1023405_3</t>
+  </si>
+  <si>
+    <t>1023405_6</t>
+  </si>
+  <si>
+    <t>1023405_12</t>
   </si>
   <si>
     <t>休息区</t>
@@ -376,31 +634,61 @@
     <t>1023301_1</t>
   </si>
   <si>
-    <t>1023301_5</t>
-  </si>
-  <si>
-    <t>1023301_10</t>
-  </si>
-  <si>
-    <t>1023301_20</t>
-  </si>
-  <si>
-    <t>1023301_50</t>
-  </si>
-  <si>
-    <t>1023301_100;1980000_1</t>
-  </si>
-  <si>
-    <t>1023301_200;1980000_10</t>
-  </si>
-  <si>
-    <t>1023301_500;1980000_20</t>
-  </si>
-  <si>
-    <t>1023301_1000;1980000_50</t>
-  </si>
-  <si>
-    <t>1023301_2000;1980000_100</t>
+    <t>1023301_2</t>
+  </si>
+  <si>
+    <t>1023301_4</t>
+  </si>
+  <si>
+    <t>1023301_6</t>
+  </si>
+  <si>
+    <t>1023301_8</t>
+  </si>
+  <si>
+    <t>1023301_10;1980000_10</t>
+  </si>
+  <si>
+    <t>1023302_2</t>
+  </si>
+  <si>
+    <t>1023302_4</t>
+  </si>
+  <si>
+    <t>1023302_8</t>
+  </si>
+  <si>
+    <t>1023302_12;1980000_100</t>
+  </si>
+  <si>
+    <t>1023303_2</t>
+  </si>
+  <si>
+    <t>1023303_4</t>
+  </si>
+  <si>
+    <t>1023303_8</t>
+  </si>
+  <si>
+    <t>1023303_12;1980000_300</t>
+  </si>
+  <si>
+    <t>1023304_3</t>
+  </si>
+  <si>
+    <t>1023304_6</t>
+  </si>
+  <si>
+    <t>1023304_12;1980000_600</t>
+  </si>
+  <si>
+    <t>1023305_3</t>
+  </si>
+  <si>
+    <t>1023305_6</t>
+  </si>
+  <si>
+    <t>1023305_12</t>
   </si>
   <si>
     <t>提款机</t>
@@ -409,31 +697,61 @@
     <t>1023201_1</t>
   </si>
   <si>
-    <t>1023201_5</t>
-  </si>
-  <si>
-    <t>1023201_10</t>
-  </si>
-  <si>
-    <t>1023201_20</t>
-  </si>
-  <si>
-    <t>1023201_50</t>
-  </si>
-  <si>
-    <t>1023201_100;1980000_1</t>
-  </si>
-  <si>
-    <t>1023201_200;1980000_10</t>
-  </si>
-  <si>
-    <t>1023201_500;1980000_20</t>
-  </si>
-  <si>
-    <t>1023201_1000;1980000_50</t>
-  </si>
-  <si>
-    <t>1023201_2000;1980000_100</t>
+    <t>1023201_2</t>
+  </si>
+  <si>
+    <t>1023201_4</t>
+  </si>
+  <si>
+    <t>1023201_6</t>
+  </si>
+  <si>
+    <t>1023201_8</t>
+  </si>
+  <si>
+    <t>1023201_10;1980000_10</t>
+  </si>
+  <si>
+    <t>1023202_2</t>
+  </si>
+  <si>
+    <t>1023202_4</t>
+  </si>
+  <si>
+    <t>1023202_8</t>
+  </si>
+  <si>
+    <t>1023202_12;1980000_100</t>
+  </si>
+  <si>
+    <t>1023203_2</t>
+  </si>
+  <si>
+    <t>1023203_4</t>
+  </si>
+  <si>
+    <t>1023203_8</t>
+  </si>
+  <si>
+    <t>1023203_12;1980000_300</t>
+  </si>
+  <si>
+    <t>1023204_3</t>
+  </si>
+  <si>
+    <t>1023204_6</t>
+  </si>
+  <si>
+    <t>1023204_12;1980000_600</t>
+  </si>
+  <si>
+    <t>1023205_3</t>
+  </si>
+  <si>
+    <t>1023205_6</t>
+  </si>
+  <si>
+    <t>1023205_12</t>
   </si>
   <si>
     <t>停机坪</t>
@@ -1427,7 +1745,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P72"/>
+  <dimension ref="A1:P132"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="19" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="9.625" style="1" customWidth="1"/>
@@ -1445,7 +1763,9 @@
     <col min="14" max="14" width="13.25" style="1" customWidth="1"/>
     <col min="15" max="15" width="9" style="1"/>
     <col min="16" max="16" width="17" style="2" customWidth="1"/>
-    <col min="17" max="16384" width="9" style="1"/>
+    <col min="17" max="17" width="9" style="1"/>
+    <col min="18" max="18" width="14.125" style="1"/>
+    <col min="19" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" customHeight="1" spans="1:16">
@@ -1682,7 +2002,7 @@
         <v>300</v>
       </c>
       <c r="N6" s="1">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="P6" s="2">
         <f t="shared" ref="P6:P15" si="2">400000+A6</f>
@@ -1732,7 +2052,7 @@
         <v>600</v>
       </c>
       <c r="N7" s="1">
-        <v>1500</v>
+        <v>360</v>
       </c>
       <c r="P7" s="2">
         <f t="shared" si="2"/>
@@ -1782,7 +2102,7 @@
         <v>900</v>
       </c>
       <c r="N8" s="1">
-        <v>2000</v>
+        <v>480</v>
       </c>
       <c r="P8" s="2">
         <f t="shared" si="2"/>
@@ -1822,7 +2142,7 @@
         <v>4</v>
       </c>
       <c r="K9" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="L9" s="5">
         <f t="shared" si="1"/>
@@ -1832,7 +2152,7 @@
         <v>1200</v>
       </c>
       <c r="N9" s="1">
-        <v>3500</v>
+        <v>600</v>
       </c>
       <c r="P9" s="2">
         <f t="shared" si="2"/>
@@ -1863,26 +2183,26 @@
         <v>5</v>
       </c>
       <c r="H10" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J10" s="1">
+        <v>4</v>
+      </c>
+      <c r="K10" t="s">
         <v>46</v>
       </c>
-      <c r="I10" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="J10" s="1">
-        <v>4</v>
-      </c>
-      <c r="K10" t="s">
-        <v>39</v>
-      </c>
       <c r="L10" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="L10:L24" si="3">A11</f>
         <v>10106</v>
       </c>
       <c r="M10" s="1">
         <v>1500</v>
       </c>
       <c r="N10" s="1">
-        <v>4000</v>
+        <v>720</v>
       </c>
       <c r="P10" s="2">
         <f t="shared" si="2"/>
@@ -1891,7 +2211,7 @@
     </row>
     <row r="11" customHeight="1" spans="1:16">
       <c r="A11" s="1">
-        <f t="shared" ref="A11:A21" si="3">10000+G11+B11*100</f>
+        <f>10000+G11+B11*100</f>
         <v>10106</v>
       </c>
       <c r="B11" s="1">
@@ -1913,26 +2233,27 @@
         <v>6</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J11" s="1">
         <v>4</v>
       </c>
       <c r="K11" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="L11" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>10107</v>
       </c>
       <c r="M11" s="1">
-        <v>1800</v>
+        <f>G11*600</f>
+        <v>3600</v>
       </c>
       <c r="N11" s="1">
-        <v>4500</v>
+        <v>1260</v>
       </c>
       <c r="P11" s="2">
         <f t="shared" si="2"/>
@@ -1941,7 +2262,7 @@
     </row>
     <row r="12" customHeight="1" spans="1:16">
       <c r="A12" s="1">
-        <f t="shared" si="3"/>
+        <f>10000+G12+B12*100</f>
         <v>10107</v>
       </c>
       <c r="B12" s="1">
@@ -1963,26 +2284,27 @@
         <v>7</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I12" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="J12" s="1">
+        <v>4</v>
+      </c>
+      <c r="K12" t="s">
         <v>51</v>
       </c>
-      <c r="J12" s="1">
-        <v>4</v>
-      </c>
-      <c r="K12" t="s">
-        <v>39</v>
-      </c>
       <c r="L12" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>10108</v>
       </c>
       <c r="M12" s="1">
-        <v>2100</v>
+        <f>G12*600</f>
+        <v>4200</v>
       </c>
       <c r="N12" s="1">
-        <v>5000</v>
+        <v>1440</v>
       </c>
       <c r="P12" s="2">
         <f t="shared" si="2"/>
@@ -1991,7 +2313,7 @@
     </row>
     <row r="13" customHeight="1" spans="1:16">
       <c r="A13" s="1">
-        <f t="shared" si="3"/>
+        <f>10000+G13+B13*100</f>
         <v>10108</v>
       </c>
       <c r="B13" s="1">
@@ -2013,26 +2335,27 @@
         <v>8</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="J13" s="1">
         <v>4</v>
       </c>
       <c r="K13" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="L13" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>10109</v>
       </c>
       <c r="M13" s="1">
-        <v>2400</v>
+        <f>G13*600</f>
+        <v>4800</v>
       </c>
       <c r="N13" s="1">
-        <v>5500</v>
+        <v>1620</v>
       </c>
       <c r="P13" s="2">
         <f t="shared" si="2"/>
@@ -2041,7 +2364,7 @@
     </row>
     <row r="14" customHeight="1" spans="1:16">
       <c r="A14" s="1">
-        <f t="shared" si="3"/>
+        <f>10000+G14+B14*100</f>
         <v>10109</v>
       </c>
       <c r="B14" s="1">
@@ -2063,26 +2386,27 @@
         <v>9</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J14" s="1">
         <v>4</v>
       </c>
       <c r="K14" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="L14" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>10110</v>
       </c>
       <c r="M14" s="1">
-        <v>2700</v>
+        <f>G14*600</f>
+        <v>5400</v>
       </c>
       <c r="N14" s="1">
-        <v>6000</v>
+        <v>1980</v>
       </c>
       <c r="P14" s="2">
         <f t="shared" si="2"/>
@@ -2091,7 +2415,7 @@
     </row>
     <row r="15" customHeight="1" spans="1:16">
       <c r="A15" s="1">
-        <f t="shared" si="3"/>
+        <f>10000+G15+B15*100</f>
         <v>10110</v>
       </c>
       <c r="B15" s="1">
@@ -2113,14 +2437,27 @@
         <v>10</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>61</v>
       </c>
       <c r="J15" s="1">
         <v>4</v>
       </c>
-      <c r="K15"/>
+      <c r="K15" t="s">
+        <v>62</v>
+      </c>
+      <c r="L15" s="5">
+        <f t="shared" si="3"/>
+        <v>10111</v>
+      </c>
+      <c r="M15" s="1">
+        <f>G15*1200</f>
+        <v>12000</v>
+      </c>
       <c r="N15" s="1">
-        <v>6500</v>
+        <v>2340</v>
       </c>
       <c r="P15" s="2">
         <f t="shared" si="2"/>
@@ -2129,511 +2466,512 @@
     </row>
     <row r="16" customHeight="1" spans="1:16">
       <c r="A16" s="1">
+        <f t="shared" ref="A16:A25" si="4">10000+G16+B16*100</f>
+        <v>10111</v>
+      </c>
+      <c r="B16" s="1">
+        <v>1</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D16" s="1">
+        <v>1</v>
+      </c>
+      <c r="E16" s="2">
+        <v>47027</v>
+      </c>
+      <c r="F16" s="2">
+        <v>0</v>
+      </c>
+      <c r="G16" s="1">
+        <v>11</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="J16" s="1">
+        <v>4</v>
+      </c>
+      <c r="K16" t="s">
+        <v>65</v>
+      </c>
+      <c r="L16" s="5">
         <f t="shared" si="3"/>
-        <v>10200</v>
-      </c>
-      <c r="B16" s="1">
-        <v>2</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D16" s="1">
-        <v>2</v>
-      </c>
-      <c r="E16" s="2">
-        <v>47028</v>
-      </c>
-      <c r="F16" s="2">
-        <v>1</v>
-      </c>
-      <c r="G16" s="1">
-        <v>0</v>
-      </c>
-      <c r="H16" s="2"/>
-      <c r="I16" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="J16" s="1">
-        <v>4</v>
-      </c>
-      <c r="K16" t="s">
-        <v>36</v>
-      </c>
-      <c r="L16" s="5">
-        <f t="shared" ref="L16:L25" si="4">A17</f>
-        <v>10201</v>
+        <v>10112</v>
       </c>
       <c r="M16" s="1">
-        <v>100</v>
+        <f>G16*1200</f>
+        <v>13200</v>
       </c>
       <c r="N16" s="1">
-        <v>0</v>
+        <v>2700</v>
       </c>
       <c r="P16" s="2">
-        <v>0</v>
+        <f t="shared" ref="P16:P25" si="5">400000+A16</f>
+        <v>410111</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="1:16">
       <c r="A17" s="1">
+        <f t="shared" si="4"/>
+        <v>10112</v>
+      </c>
+      <c r="B17" s="1">
+        <v>1</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D17" s="1">
+        <v>1</v>
+      </c>
+      <c r="E17" s="2">
+        <v>47027</v>
+      </c>
+      <c r="F17" s="2">
+        <v>0</v>
+      </c>
+      <c r="G17" s="1">
+        <v>12</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="J17" s="1">
+        <v>4</v>
+      </c>
+      <c r="K17" t="s">
+        <v>68</v>
+      </c>
+      <c r="L17" s="5">
         <f t="shared" si="3"/>
-        <v>10201</v>
-      </c>
-      <c r="B17" s="1">
-        <v>2</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D17" s="1">
-        <v>2</v>
-      </c>
-      <c r="E17" s="2">
-        <v>47028</v>
-      </c>
-      <c r="F17" s="2">
-        <v>1</v>
-      </c>
-      <c r="G17" s="1">
-        <v>1</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="J17" s="1">
-        <v>4</v>
-      </c>
-      <c r="K17" t="s">
-        <v>39</v>
-      </c>
-      <c r="L17" s="5">
-        <f t="shared" si="4"/>
-        <v>10202</v>
+        <v>10113</v>
       </c>
       <c r="M17" s="1">
-        <v>300</v>
+        <f>G17*1200</f>
+        <v>14400</v>
       </c>
       <c r="N17" s="1">
-        <v>1000</v>
+        <v>4560</v>
       </c>
       <c r="P17" s="2">
-        <f t="shared" ref="P17:P26" si="5">400000+A17</f>
-        <v>410201</v>
+        <f t="shared" si="5"/>
+        <v>410112</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="1:16">
       <c r="A18" s="1">
+        <f t="shared" si="4"/>
+        <v>10113</v>
+      </c>
+      <c r="B18" s="1">
+        <v>1</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D18" s="1">
+        <v>1</v>
+      </c>
+      <c r="E18" s="2">
+        <v>47027</v>
+      </c>
+      <c r="F18" s="2">
+        <v>0</v>
+      </c>
+      <c r="G18" s="1">
+        <v>13</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="J18" s="1">
+        <v>4</v>
+      </c>
+      <c r="K18" t="s">
+        <v>71</v>
+      </c>
+      <c r="L18" s="5">
         <f t="shared" si="3"/>
-        <v>10202</v>
-      </c>
-      <c r="B18" s="1">
-        <v>2</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D18" s="1">
-        <v>2</v>
-      </c>
-      <c r="E18" s="2">
-        <v>47028</v>
-      </c>
-      <c r="F18" s="2">
-        <v>1</v>
-      </c>
-      <c r="G18" s="1">
-        <v>2</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="J18" s="1">
-        <v>4</v>
-      </c>
-      <c r="K18" t="s">
-        <v>39</v>
-      </c>
-      <c r="L18" s="5">
-        <f t="shared" si="4"/>
-        <v>10203</v>
+        <v>10114</v>
       </c>
       <c r="M18" s="1">
-        <v>600</v>
+        <f>G18*1200</f>
+        <v>15600</v>
       </c>
       <c r="N18" s="1">
-        <v>1500</v>
+        <v>5520</v>
       </c>
       <c r="P18" s="2">
         <f t="shared" si="5"/>
-        <v>410202</v>
+        <v>410113</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="1:16">
       <c r="A19" s="1">
+        <f t="shared" si="4"/>
+        <v>10114</v>
+      </c>
+      <c r="B19" s="1">
+        <v>1</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D19" s="1">
+        <v>1</v>
+      </c>
+      <c r="E19" s="2">
+        <v>47027</v>
+      </c>
+      <c r="F19" s="2">
+        <v>0</v>
+      </c>
+      <c r="G19" s="1">
+        <v>14</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="J19" s="1">
+        <v>4</v>
+      </c>
+      <c r="K19" t="s">
+        <v>74</v>
+      </c>
+      <c r="L19" s="5">
         <f t="shared" si="3"/>
-        <v>10203</v>
-      </c>
-      <c r="B19" s="1">
-        <v>2</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D19" s="1">
-        <v>2</v>
-      </c>
-      <c r="E19" s="2">
-        <v>47028</v>
-      </c>
-      <c r="F19" s="2">
-        <v>1</v>
-      </c>
-      <c r="G19" s="1">
-        <v>3</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="J19" s="1">
-        <v>4</v>
-      </c>
-      <c r="K19" t="s">
-        <v>39</v>
-      </c>
-      <c r="L19" s="5">
-        <f t="shared" si="4"/>
-        <v>10204</v>
+        <v>10115</v>
       </c>
       <c r="M19" s="1">
-        <v>900</v>
+        <f>G19*2400</f>
+        <v>33600</v>
       </c>
       <c r="N19" s="1">
-        <v>2000</v>
+        <v>6480</v>
       </c>
       <c r="P19" s="2">
         <f t="shared" si="5"/>
-        <v>410203</v>
+        <v>410114</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="1:16">
       <c r="A20" s="1">
+        <f t="shared" si="4"/>
+        <v>10115</v>
+      </c>
+      <c r="B20" s="1">
+        <v>1</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D20" s="1">
+        <v>1</v>
+      </c>
+      <c r="E20" s="2">
+        <v>47027</v>
+      </c>
+      <c r="F20" s="2">
+        <v>0</v>
+      </c>
+      <c r="G20" s="1">
+        <v>15</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="J20" s="1">
+        <v>4</v>
+      </c>
+      <c r="K20" t="s">
+        <v>77</v>
+      </c>
+      <c r="L20" s="5">
         <f t="shared" si="3"/>
-        <v>10204</v>
-      </c>
-      <c r="B20" s="1">
-        <v>2</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D20" s="1">
-        <v>2</v>
-      </c>
-      <c r="E20" s="2">
-        <v>47028</v>
-      </c>
-      <c r="F20" s="2">
-        <v>1</v>
-      </c>
-      <c r="G20" s="1">
-        <v>4</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="J20" s="1">
-        <v>4</v>
-      </c>
-      <c r="K20" t="s">
-        <v>39</v>
-      </c>
-      <c r="L20" s="5">
-        <f t="shared" si="4"/>
-        <v>10205</v>
+        <v>10116</v>
       </c>
       <c r="M20" s="1">
-        <v>1200</v>
+        <f>G20*2400</f>
+        <v>36000</v>
       </c>
       <c r="N20" s="1">
-        <v>3500</v>
+        <v>9900</v>
       </c>
       <c r="P20" s="2">
         <f t="shared" si="5"/>
-        <v>410204</v>
+        <v>410115</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="1:16">
       <c r="A21" s="1">
+        <f t="shared" si="4"/>
+        <v>10116</v>
+      </c>
+      <c r="B21" s="1">
+        <v>1</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D21" s="1">
+        <v>1</v>
+      </c>
+      <c r="E21" s="2">
+        <v>47027</v>
+      </c>
+      <c r="F21" s="2">
+        <v>0</v>
+      </c>
+      <c r="G21" s="1">
+        <v>16</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="J21" s="1">
+        <v>4</v>
+      </c>
+      <c r="K21" t="s">
+        <v>80</v>
+      </c>
+      <c r="L21" s="5">
         <f t="shared" si="3"/>
-        <v>10205</v>
-      </c>
-      <c r="B21" s="1">
-        <v>2</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D21" s="1">
-        <v>2</v>
-      </c>
-      <c r="E21" s="2">
-        <v>47028</v>
-      </c>
-      <c r="F21" s="2">
-        <v>1</v>
-      </c>
-      <c r="G21" s="1">
-        <v>5</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="J21" s="1">
-        <v>4</v>
-      </c>
-      <c r="K21" t="s">
-        <v>39</v>
-      </c>
-      <c r="L21" s="5">
-        <f t="shared" si="4"/>
-        <v>10206</v>
+        <v>10117</v>
       </c>
       <c r="M21" s="1">
-        <v>1500</v>
+        <f>G21*2400</f>
+        <v>38400</v>
       </c>
       <c r="N21" s="1">
-        <v>4000</v>
+        <v>11700</v>
       </c>
       <c r="P21" s="2">
         <f t="shared" si="5"/>
-        <v>410205</v>
+        <v>410116</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="1:16">
       <c r="A22" s="1">
-        <f t="shared" ref="A22:A27" si="6">10000+G22+B22*100</f>
-        <v>10206</v>
+        <f t="shared" si="4"/>
+        <v>10117</v>
       </c>
       <c r="B22" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="D22" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E22" s="2">
-        <v>47028</v>
+        <v>47027</v>
       </c>
       <c r="F22" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G22" s="1">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>48</v>
+        <v>81</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="J22" s="1">
         <v>4</v>
       </c>
       <c r="K22" t="s">
-        <v>39</v>
+        <v>83</v>
       </c>
       <c r="L22" s="5">
-        <f t="shared" si="4"/>
-        <v>10207</v>
+        <f t="shared" si="3"/>
+        <v>10118</v>
       </c>
       <c r="M22" s="1">
-        <v>1800</v>
+        <f>G22*4800</f>
+        <v>81600</v>
       </c>
       <c r="N22" s="1">
-        <v>4500</v>
+        <v>13500</v>
       </c>
       <c r="P22" s="2">
         <f t="shared" si="5"/>
-        <v>410206</v>
+        <v>410117</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="1:16">
       <c r="A23" s="1">
-        <f t="shared" si="6"/>
-        <v>10207</v>
+        <f t="shared" si="4"/>
+        <v>10118</v>
       </c>
       <c r="B23" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="D23" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E23" s="2">
-        <v>47028</v>
+        <v>47027</v>
       </c>
       <c r="F23" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23" s="1">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="J23" s="1">
         <v>4</v>
       </c>
       <c r="K23" t="s">
-        <v>39</v>
+        <v>86</v>
       </c>
       <c r="L23" s="5">
-        <f t="shared" si="4"/>
-        <v>10208</v>
+        <f t="shared" si="3"/>
+        <v>10119</v>
       </c>
       <c r="M23" s="1">
-        <v>2100</v>
+        <f>G23*4800</f>
+        <v>86400</v>
       </c>
       <c r="N23" s="1">
-        <v>5000</v>
+        <v>19080</v>
       </c>
       <c r="P23" s="2">
         <f t="shared" si="5"/>
-        <v>410207</v>
+        <v>410118</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="1:16">
       <c r="A24" s="1">
-        <f t="shared" si="6"/>
-        <v>10208</v>
+        <f t="shared" si="4"/>
+        <v>10119</v>
       </c>
       <c r="B24" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="D24" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E24" s="2">
-        <v>47028</v>
+        <v>47027</v>
       </c>
       <c r="F24" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24" s="1">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>52</v>
+        <v>87</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="J24" s="1">
         <v>4</v>
       </c>
       <c r="K24" t="s">
-        <v>39</v>
+        <v>89</v>
       </c>
       <c r="L24" s="5">
-        <f t="shared" si="4"/>
-        <v>10209</v>
+        <f t="shared" si="3"/>
+        <v>10120</v>
       </c>
       <c r="M24" s="1">
-        <v>2400</v>
+        <f>G24*4800</f>
+        <v>91200</v>
       </c>
       <c r="N24" s="1">
-        <v>5500</v>
+        <v>21960</v>
       </c>
       <c r="P24" s="2">
         <f t="shared" si="5"/>
-        <v>410208</v>
+        <v>410119</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="1:16">
       <c r="A25" s="1">
-        <f t="shared" si="6"/>
-        <v>10209</v>
+        <f t="shared" si="4"/>
+        <v>10120</v>
       </c>
       <c r="B25" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="D25" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E25" s="2">
-        <v>47028</v>
+        <v>47027</v>
       </c>
       <c r="F25" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G25" s="1">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>67</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="I25" s="3"/>
       <c r="J25" s="1">
         <v>4</v>
       </c>
-      <c r="K25" t="s">
-        <v>39</v>
-      </c>
-      <c r="L25" s="5">
-        <f t="shared" si="4"/>
-        <v>10210</v>
-      </c>
-      <c r="M25" s="1">
-        <v>2700</v>
-      </c>
+      <c r="K25"/>
       <c r="N25" s="1">
-        <v>6000</v>
+        <v>24840</v>
       </c>
       <c r="P25" s="2">
         <f t="shared" si="5"/>
-        <v>410209</v>
+        <v>410120</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="1:16">
       <c r="A26" s="1">
-        <f t="shared" si="6"/>
-        <v>10210</v>
+        <f t="shared" ref="A26:A31" si="6">10000+G26+B26*100</f>
+        <v>10200</v>
       </c>
       <c r="B26" s="1">
         <v>2</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>57</v>
+        <v>91</v>
       </c>
       <c r="D26" s="1">
         <v>2</v>
@@ -2645,98 +2983,110 @@
         <v>1</v>
       </c>
       <c r="G26" s="1">
-        <v>10</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>56</v>
+        <v>0</v>
+      </c>
+      <c r="H26" s="2"/>
+      <c r="I26" s="3" t="s">
+        <v>92</v>
       </c>
       <c r="J26" s="1">
         <v>4</v>
       </c>
-      <c r="K26"/>
+      <c r="K26" t="s">
+        <v>36</v>
+      </c>
+      <c r="L26" s="5">
+        <f t="shared" ref="L26:L45" si="7">A27</f>
+        <v>10201</v>
+      </c>
+      <c r="M26" s="1">
+        <v>100</v>
+      </c>
       <c r="N26" s="1">
-        <v>6500</v>
+        <v>0</v>
       </c>
       <c r="P26" s="2">
-        <f t="shared" si="5"/>
-        <v>410210</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="1:16">
       <c r="A27" s="1">
         <f t="shared" si="6"/>
-        <v>10300</v>
+        <v>10201</v>
       </c>
       <c r="B27" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="D27" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E27" s="2">
-        <v>47029</v>
+        <v>47028</v>
       </c>
       <c r="F27" s="2">
         <v>1</v>
       </c>
       <c r="G27" s="1">
-        <v>0</v>
-      </c>
-      <c r="H27" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>42</v>
+      </c>
       <c r="I27" s="3" t="s">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="J27" s="1">
         <v>4</v>
       </c>
       <c r="K27" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="L27" s="5">
-        <f t="shared" ref="L27:L36" si="7">A28</f>
-        <v>10301</v>
+        <f t="shared" si="7"/>
+        <v>10202</v>
       </c>
       <c r="M27" s="1">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="N27" s="1">
-        <v>0</v>
+        <v>480</v>
       </c>
       <c r="P27" s="2">
-        <v>0</v>
+        <f t="shared" ref="P27:P36" si="8">400000+A27</f>
+        <v>410201</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="1:16">
       <c r="A28" s="1">
-        <f t="shared" ref="A28:A43" si="8">10000+G28+B28*100</f>
-        <v>10301</v>
+        <f t="shared" si="6"/>
+        <v>10202</v>
       </c>
       <c r="B28" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="D28" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E28" s="2">
-        <v>47029</v>
+        <v>47028</v>
       </c>
       <c r="F28" s="2">
         <v>1</v>
       </c>
       <c r="G28" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>59</v>
+        <v>94</v>
       </c>
       <c r="J28" s="1">
         <v>4</v>
@@ -2746,47 +3096,47 @@
       </c>
       <c r="L28" s="5">
         <f t="shared" si="7"/>
-        <v>10302</v>
+        <v>10203</v>
       </c>
       <c r="M28" s="1">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="N28" s="1">
-        <v>1000</v>
+        <v>720</v>
       </c>
       <c r="P28" s="2">
-        <f t="shared" ref="P28:P47" si="9">400000+A28</f>
-        <v>410301</v>
+        <f t="shared" si="8"/>
+        <v>410202</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="1:16">
       <c r="A29" s="1">
-        <f t="shared" si="8"/>
-        <v>10302</v>
+        <f t="shared" si="6"/>
+        <v>10203</v>
       </c>
       <c r="B29" s="1">
+        <v>2</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D29" s="1">
+        <v>2</v>
+      </c>
+      <c r="E29" s="2">
+        <v>47028</v>
+      </c>
+      <c r="F29" s="2">
+        <v>1</v>
+      </c>
+      <c r="G29" s="1">
         <v>3</v>
       </c>
-      <c r="C29" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="D29" s="1">
-        <v>4</v>
-      </c>
-      <c r="E29" s="2">
-        <v>47029</v>
-      </c>
-      <c r="F29" s="2">
-        <v>1</v>
-      </c>
-      <c r="G29" s="1">
-        <v>2</v>
-      </c>
       <c r="H29" s="2" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="J29" s="1">
         <v>4</v>
@@ -2796,910 +3146,1047 @@
       </c>
       <c r="L29" s="5">
         <f t="shared" si="7"/>
-        <v>10303</v>
+        <v>10204</v>
       </c>
       <c r="M29" s="1">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="N29" s="1">
-        <v>1500</v>
+        <v>960</v>
       </c>
       <c r="P29" s="2">
-        <f t="shared" si="9"/>
-        <v>410302</v>
+        <f t="shared" si="8"/>
+        <v>410203</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="1:16">
       <c r="A30" s="1">
-        <f t="shared" si="8"/>
-        <v>10303</v>
+        <f t="shared" si="6"/>
+        <v>10204</v>
       </c>
       <c r="B30" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="D30" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E30" s="2">
-        <v>47029</v>
+        <v>47028</v>
       </c>
       <c r="F30" s="2">
         <v>1</v>
       </c>
       <c r="G30" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>42</v>
+        <v>96</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="J30" s="1">
         <v>4</v>
       </c>
       <c r="K30" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="L30" s="5">
         <f t="shared" si="7"/>
-        <v>10304</v>
+        <v>10205</v>
       </c>
       <c r="M30" s="1">
-        <v>900</v>
+        <v>1200</v>
       </c>
       <c r="N30" s="1">
-        <v>2000</v>
+        <v>1200</v>
       </c>
       <c r="P30" s="2">
-        <f t="shared" si="9"/>
-        <v>410303</v>
+        <f t="shared" si="8"/>
+        <v>410204</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="1:16">
       <c r="A31" s="1">
-        <f t="shared" si="8"/>
-        <v>10304</v>
+        <f t="shared" si="6"/>
+        <v>10205</v>
       </c>
       <c r="B31" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="D31" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E31" s="2">
-        <v>47029</v>
+        <v>47028</v>
       </c>
       <c r="F31" s="2">
         <v>1</v>
       </c>
       <c r="G31" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>44</v>
+        <v>98</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>62</v>
+        <v>99</v>
       </c>
       <c r="J31" s="1">
         <v>4</v>
       </c>
       <c r="K31" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="L31" s="5">
         <f t="shared" si="7"/>
-        <v>10305</v>
+        <v>10206</v>
       </c>
       <c r="M31" s="1">
-        <v>1200</v>
+        <v>1500</v>
       </c>
       <c r="N31" s="1">
-        <v>3500</v>
+        <v>1440</v>
       </c>
       <c r="P31" s="2">
-        <f t="shared" si="9"/>
-        <v>410304</v>
+        <f t="shared" si="8"/>
+        <v>410205</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="1:16">
       <c r="A32" s="1">
-        <f t="shared" si="8"/>
-        <v>10305</v>
+        <f>10000+G32+B32*100</f>
+        <v>10206</v>
       </c>
       <c r="B32" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="D32" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E32" s="2">
-        <v>47029</v>
+        <v>47028</v>
       </c>
       <c r="F32" s="2">
         <v>1</v>
       </c>
       <c r="G32" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>63</v>
+        <v>93</v>
       </c>
       <c r="J32" s="1">
         <v>4</v>
       </c>
       <c r="K32" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="L32" s="5">
         <f t="shared" si="7"/>
-        <v>10306</v>
+        <v>10207</v>
       </c>
       <c r="M32" s="1">
-        <v>1500</v>
+        <f t="shared" ref="M32:M35" si="9">G32*600</f>
+        <v>3600</v>
       </c>
       <c r="N32" s="1">
-        <v>4000</v>
+        <v>2520</v>
       </c>
       <c r="P32" s="2">
-        <f t="shared" si="9"/>
-        <v>410305</v>
+        <f t="shared" si="8"/>
+        <v>410206</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="1:16">
       <c r="A33" s="1">
-        <f t="shared" si="8"/>
-        <v>10306</v>
+        <f>10000+G33+B33*100</f>
+        <v>10207</v>
       </c>
       <c r="B33" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="D33" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E33" s="2">
-        <v>47029</v>
+        <v>47028</v>
       </c>
       <c r="F33" s="2">
         <v>1</v>
       </c>
       <c r="G33" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>48</v>
+        <v>101</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>64</v>
+        <v>94</v>
       </c>
       <c r="J33" s="1">
         <v>4</v>
       </c>
       <c r="K33" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="L33" s="5">
         <f t="shared" si="7"/>
-        <v>10307</v>
+        <v>10208</v>
       </c>
       <c r="M33" s="1">
-        <v>1800</v>
+        <f t="shared" si="9"/>
+        <v>4200</v>
       </c>
       <c r="N33" s="1">
-        <v>4500</v>
+        <v>2880</v>
       </c>
       <c r="P33" s="2">
-        <f t="shared" si="9"/>
-        <v>410306</v>
+        <f t="shared" si="8"/>
+        <v>410207</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="1:16">
       <c r="A34" s="1">
-        <f t="shared" si="8"/>
-        <v>10307</v>
+        <f>10000+G34+B34*100</f>
+        <v>10208</v>
       </c>
       <c r="B34" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="D34" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E34" s="2">
-        <v>47029</v>
+        <v>47028</v>
       </c>
       <c r="F34" s="2">
         <v>1</v>
       </c>
       <c r="G34" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>50</v>
+        <v>102</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>65</v>
+        <v>97</v>
       </c>
       <c r="J34" s="1">
         <v>4</v>
       </c>
       <c r="K34" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="L34" s="5">
         <f t="shared" si="7"/>
-        <v>10308</v>
+        <v>10209</v>
       </c>
       <c r="M34" s="1">
-        <v>2100</v>
+        <f t="shared" si="9"/>
+        <v>4800</v>
       </c>
       <c r="N34" s="1">
-        <v>5000</v>
+        <v>3240</v>
       </c>
       <c r="P34" s="2">
-        <f t="shared" si="9"/>
-        <v>410307</v>
+        <f t="shared" si="8"/>
+        <v>410208</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="1:16">
       <c r="A35" s="1">
-        <f t="shared" si="8"/>
-        <v>10308</v>
+        <f>10000+G35+B35*100</f>
+        <v>10209</v>
       </c>
       <c r="B35" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="D35" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E35" s="2">
-        <v>47029</v>
+        <v>47028</v>
       </c>
       <c r="F35" s="2">
         <v>1</v>
       </c>
       <c r="G35" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>52</v>
+        <v>103</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>66</v>
+        <v>104</v>
       </c>
       <c r="J35" s="1">
         <v>4</v>
       </c>
       <c r="K35" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="L35" s="5">
         <f t="shared" si="7"/>
-        <v>10309</v>
+        <v>10210</v>
       </c>
       <c r="M35" s="1">
-        <v>2400</v>
+        <f t="shared" si="9"/>
+        <v>5400</v>
       </c>
       <c r="N35" s="1">
-        <v>5500</v>
+        <v>3960</v>
       </c>
       <c r="P35" s="2">
-        <f t="shared" si="9"/>
-        <v>410308</v>
+        <f t="shared" si="8"/>
+        <v>410209</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="1:16">
       <c r="A36" s="1">
-        <f t="shared" si="8"/>
-        <v>10309</v>
+        <f>10000+G36+B36*100</f>
+        <v>10210</v>
       </c>
       <c r="B36" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="D36" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E36" s="2">
-        <v>47029</v>
+        <v>47028</v>
       </c>
       <c r="F36" s="2">
         <v>1</v>
       </c>
       <c r="G36" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>54</v>
+        <v>105</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>67</v>
+        <v>93</v>
       </c>
       <c r="J36" s="1">
         <v>4</v>
       </c>
       <c r="K36" t="s">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="L36" s="5">
         <f t="shared" si="7"/>
-        <v>10310</v>
+        <v>10211</v>
       </c>
       <c r="M36" s="1">
-        <v>2700</v>
+        <f t="shared" ref="M36:M39" si="10">G36*1200</f>
+        <v>12000</v>
       </c>
       <c r="N36" s="1">
-        <v>6000</v>
+        <v>4680</v>
       </c>
       <c r="P36" s="2">
-        <f t="shared" si="9"/>
-        <v>410309</v>
+        <f t="shared" si="8"/>
+        <v>410210</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="1:16">
       <c r="A37" s="1">
-        <f t="shared" si="8"/>
-        <v>10310</v>
+        <f t="shared" ref="A37:A46" si="11">10000+G37+B37*100</f>
+        <v>10211</v>
       </c>
       <c r="B37" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="D37" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E37" s="2">
-        <v>47029</v>
+        <v>47028</v>
       </c>
       <c r="F37" s="2">
         <v>1</v>
       </c>
       <c r="G37" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>56</v>
+        <v>106</v>
+      </c>
+      <c r="I37" s="3" t="s">
+        <v>94</v>
       </c>
       <c r="J37" s="1">
         <v>4</v>
       </c>
-      <c r="K37"/>
+      <c r="K37" t="s">
+        <v>65</v>
+      </c>
+      <c r="L37" s="5">
+        <f t="shared" si="7"/>
+        <v>10212</v>
+      </c>
+      <c r="M37" s="1">
+        <f t="shared" si="10"/>
+        <v>13200</v>
+      </c>
       <c r="N37" s="1">
-        <v>6500</v>
+        <v>5400</v>
       </c>
       <c r="P37" s="2">
-        <f t="shared" si="9"/>
-        <v>410310</v>
+        <f t="shared" ref="P37:P46" si="12">400000+A37</f>
+        <v>410211</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="1:16">
       <c r="A38" s="1">
-        <f t="shared" si="8"/>
-        <v>10400</v>
+        <f t="shared" si="11"/>
+        <v>10212</v>
       </c>
       <c r="B38" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="D38" s="1">
         <v>2</v>
       </c>
       <c r="E38" s="2">
-        <v>47043</v>
+        <v>47028</v>
       </c>
       <c r="F38" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G38" s="1">
-        <v>0</v>
+        <v>12</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>107</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="J38" s="1"/>
-      <c r="K38"/>
+        <v>97</v>
+      </c>
+      <c r="J38" s="1">
+        <v>4</v>
+      </c>
+      <c r="K38" t="s">
+        <v>68</v>
+      </c>
       <c r="L38" s="5">
-        <f t="shared" ref="L38:L47" si="10">A39</f>
-        <v>10401</v>
+        <f t="shared" si="7"/>
+        <v>10213</v>
       </c>
       <c r="M38" s="1">
-        <v>100</v>
+        <f t="shared" si="10"/>
+        <v>14400</v>
       </c>
       <c r="N38" s="1">
-        <v>0</v>
+        <v>9120</v>
       </c>
       <c r="P38" s="2">
-        <v>0</v>
+        <f t="shared" si="12"/>
+        <v>410212</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="1:16">
       <c r="A39" s="1">
-        <f t="shared" si="8"/>
-        <v>10401</v>
+        <f t="shared" si="11"/>
+        <v>10213</v>
       </c>
       <c r="B39" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="D39" s="1">
         <v>2</v>
       </c>
       <c r="E39" s="2">
-        <v>47043</v>
+        <v>47028</v>
       </c>
       <c r="F39" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G39" s="1">
-        <v>1</v>
+        <v>13</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>108</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="J39" s="1"/>
-      <c r="K39"/>
+        <v>109</v>
+      </c>
+      <c r="J39" s="1">
+        <v>4</v>
+      </c>
+      <c r="K39" t="s">
+        <v>71</v>
+      </c>
       <c r="L39" s="5">
+        <f t="shared" si="7"/>
+        <v>10214</v>
+      </c>
+      <c r="M39" s="1">
         <f t="shared" si="10"/>
-        <v>10402</v>
-      </c>
-      <c r="M39" s="1">
-        <v>300</v>
+        <v>15600</v>
+      </c>
+      <c r="N39" s="1">
+        <v>11040</v>
       </c>
       <c r="P39" s="2">
-        <f t="shared" ref="P39:P48" si="11">400000+A39</f>
-        <v>410401</v>
+        <f t="shared" si="12"/>
+        <v>410213</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="1:16">
       <c r="A40" s="1">
-        <f t="shared" si="8"/>
-        <v>10402</v>
+        <f t="shared" si="11"/>
+        <v>10214</v>
       </c>
       <c r="B40" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="D40" s="1">
         <v>2</v>
       </c>
       <c r="E40" s="2">
-        <v>47043</v>
+        <v>47028</v>
       </c>
       <c r="F40" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G40" s="1">
-        <v>2</v>
+        <v>14</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>110</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="J40" s="1"/>
-      <c r="K40"/>
+        <v>111</v>
+      </c>
+      <c r="J40" s="1">
+        <v>4</v>
+      </c>
+      <c r="K40" t="s">
+        <v>74</v>
+      </c>
       <c r="L40" s="5">
-        <f t="shared" si="10"/>
-        <v>10403</v>
+        <f t="shared" si="7"/>
+        <v>10215</v>
       </c>
       <c r="M40" s="1">
-        <v>600</v>
+        <f t="shared" ref="M40:M42" si="13">G40*2400</f>
+        <v>33600</v>
+      </c>
+      <c r="N40" s="1">
+        <v>12960</v>
       </c>
       <c r="P40" s="2">
-        <f t="shared" si="11"/>
-        <v>410402</v>
+        <f t="shared" si="12"/>
+        <v>410214</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="1:16">
       <c r="A41" s="1">
-        <f t="shared" si="8"/>
-        <v>10403</v>
+        <f t="shared" si="11"/>
+        <v>10215</v>
       </c>
       <c r="B41" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="D41" s="1">
         <v>2</v>
       </c>
       <c r="E41" s="2">
-        <v>47043</v>
+        <v>47028</v>
       </c>
       <c r="F41" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G41" s="1">
-        <v>3</v>
+        <v>15</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>112</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="J41" s="1"/>
-      <c r="K41"/>
+        <v>95</v>
+      </c>
+      <c r="J41" s="1">
+        <v>4</v>
+      </c>
+      <c r="K41" t="s">
+        <v>77</v>
+      </c>
       <c r="L41" s="5">
-        <f t="shared" si="10"/>
-        <v>10404</v>
+        <f t="shared" si="7"/>
+        <v>10216</v>
       </c>
       <c r="M41" s="1">
-        <v>900</v>
+        <f t="shared" si="13"/>
+        <v>36000</v>
+      </c>
+      <c r="N41" s="1">
+        <v>19800</v>
       </c>
       <c r="P41" s="2">
-        <f t="shared" si="11"/>
-        <v>410403</v>
+        <f t="shared" si="12"/>
+        <v>410215</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="1:16">
       <c r="A42" s="1">
-        <f t="shared" si="8"/>
-        <v>10404</v>
+        <f t="shared" si="11"/>
+        <v>10216</v>
       </c>
       <c r="B42" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="D42" s="1">
         <v>2</v>
       </c>
       <c r="E42" s="2">
-        <v>47043</v>
+        <v>47028</v>
       </c>
       <c r="F42" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G42" s="1">
-        <v>4</v>
+        <v>16</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>113</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="J42" s="1"/>
-      <c r="K42"/>
+        <v>114</v>
+      </c>
+      <c r="J42" s="1">
+        <v>4</v>
+      </c>
+      <c r="K42" t="s">
+        <v>80</v>
+      </c>
       <c r="L42" s="5">
-        <f t="shared" si="10"/>
-        <v>10405</v>
+        <f t="shared" si="7"/>
+        <v>10217</v>
       </c>
       <c r="M42" s="1">
-        <v>1200</v>
+        <f t="shared" si="13"/>
+        <v>38400</v>
+      </c>
+      <c r="N42" s="1">
+        <v>23400</v>
       </c>
       <c r="P42" s="2">
-        <f t="shared" si="11"/>
-        <v>410404</v>
+        <f t="shared" si="12"/>
+        <v>410216</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="1:16">
       <c r="A43" s="1">
-        <f t="shared" si="8"/>
-        <v>10405</v>
+        <f t="shared" si="11"/>
+        <v>10217</v>
       </c>
       <c r="B43" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="D43" s="1">
         <v>2</v>
       </c>
       <c r="E43" s="2">
-        <v>47043</v>
+        <v>47028</v>
       </c>
       <c r="F43" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G43" s="1">
-        <v>5</v>
+        <v>17</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>115</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="J43" s="1"/>
-      <c r="K43"/>
+        <v>111</v>
+      </c>
+      <c r="J43" s="1">
+        <v>4</v>
+      </c>
+      <c r="K43" t="s">
+        <v>83</v>
+      </c>
       <c r="L43" s="5">
-        <f t="shared" si="10"/>
-        <v>10406</v>
+        <f t="shared" si="7"/>
+        <v>10218</v>
       </c>
       <c r="M43" s="1">
-        <v>1500</v>
+        <f t="shared" ref="M43:M45" si="14">G43*4800</f>
+        <v>81600</v>
+      </c>
+      <c r="N43" s="1">
+        <v>27000</v>
       </c>
       <c r="P43" s="2">
-        <f t="shared" si="11"/>
-        <v>410405</v>
+        <f t="shared" si="12"/>
+        <v>410217</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="1:16">
       <c r="A44" s="1">
-        <f t="shared" ref="A44:A54" si="12">10000+G44+B44*100</f>
-        <v>10406</v>
+        <f t="shared" si="11"/>
+        <v>10218</v>
       </c>
       <c r="B44" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="D44" s="1">
         <v>2</v>
       </c>
       <c r="E44" s="2">
-        <v>47043</v>
+        <v>47028</v>
       </c>
       <c r="F44" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G44" s="1">
-        <v>6</v>
+        <v>18</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>116</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="J44" s="1"/>
-      <c r="K44"/>
+        <v>95</v>
+      </c>
+      <c r="J44" s="1">
+        <v>4</v>
+      </c>
+      <c r="K44" t="s">
+        <v>86</v>
+      </c>
       <c r="L44" s="5">
-        <f t="shared" si="10"/>
-        <v>10407</v>
+        <f t="shared" si="7"/>
+        <v>10219</v>
       </c>
       <c r="M44" s="1">
-        <v>1800</v>
+        <f t="shared" si="14"/>
+        <v>86400</v>
+      </c>
+      <c r="N44" s="1">
+        <v>38160</v>
       </c>
       <c r="P44" s="2">
-        <f t="shared" si="11"/>
-        <v>410406</v>
+        <f t="shared" si="12"/>
+        <v>410218</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="1:16">
       <c r="A45" s="1">
+        <f t="shared" si="11"/>
+        <v>10219</v>
+      </c>
+      <c r="B45" s="1">
+        <v>2</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D45" s="1">
+        <v>2</v>
+      </c>
+      <c r="E45" s="2">
+        <v>47028</v>
+      </c>
+      <c r="F45" s="2">
+        <v>1</v>
+      </c>
+      <c r="G45" s="1">
+        <v>19</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="J45" s="1">
+        <v>4</v>
+      </c>
+      <c r="K45" t="s">
+        <v>89</v>
+      </c>
+      <c r="L45" s="5">
+        <f t="shared" si="7"/>
+        <v>10220</v>
+      </c>
+      <c r="M45" s="1">
+        <f t="shared" si="14"/>
+        <v>91200</v>
+      </c>
+      <c r="N45" s="1">
+        <v>43920</v>
+      </c>
+      <c r="P45" s="2">
         <f t="shared" si="12"/>
-        <v>10407</v>
-      </c>
-      <c r="B45" s="1">
-        <v>4</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="D45" s="1">
-        <v>2</v>
-      </c>
-      <c r="E45" s="2">
-        <v>47043</v>
-      </c>
-      <c r="F45" s="2">
-        <v>0</v>
-      </c>
-      <c r="G45" s="1">
-        <v>7</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="J45" s="1"/>
-      <c r="K45"/>
-      <c r="L45" s="5">
-        <f t="shared" si="10"/>
-        <v>10408</v>
-      </c>
-      <c r="M45" s="1">
-        <v>2100</v>
-      </c>
-      <c r="P45" s="2">
-        <f t="shared" si="11"/>
-        <v>410407</v>
+        <v>410219</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="1:16">
       <c r="A46" s="1">
+        <f t="shared" si="11"/>
+        <v>10220</v>
+      </c>
+      <c r="B46" s="1">
+        <v>2</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D46" s="1">
+        <v>2</v>
+      </c>
+      <c r="E46" s="2">
+        <v>47028</v>
+      </c>
+      <c r="F46" s="2">
+        <v>1</v>
+      </c>
+      <c r="G46" s="1">
+        <v>20</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="I46" s="3"/>
+      <c r="J46" s="1">
+        <v>4</v>
+      </c>
+      <c r="K46"/>
+      <c r="N46" s="1">
+        <v>49680</v>
+      </c>
+      <c r="P46" s="2">
         <f t="shared" si="12"/>
-        <v>10408</v>
-      </c>
-      <c r="B46" s="1">
-        <v>4</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="D46" s="1">
-        <v>2</v>
-      </c>
-      <c r="E46" s="2">
-        <v>47043</v>
-      </c>
-      <c r="F46" s="2">
-        <v>0</v>
-      </c>
-      <c r="G46" s="1">
-        <v>8</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="J46" s="1"/>
-      <c r="K46"/>
-      <c r="L46" s="5">
-        <f t="shared" si="10"/>
-        <v>10409</v>
-      </c>
-      <c r="M46" s="1">
-        <v>2400</v>
-      </c>
-      <c r="P46" s="2">
-        <f t="shared" si="11"/>
-        <v>410408</v>
+        <v>410220</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="1:16">
       <c r="A47" s="1">
-        <f t="shared" si="12"/>
-        <v>10409</v>
+        <f>10000+G47+B47*100</f>
+        <v>10300</v>
       </c>
       <c r="B47" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>69</v>
+        <v>120</v>
       </c>
       <c r="D47" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E47" s="2">
-        <v>47043</v>
+        <v>47029</v>
       </c>
       <c r="F47" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G47" s="1">
-        <v>9</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H47" s="2"/>
       <c r="I47" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="J47" s="1"/>
-      <c r="K47"/>
+        <v>121</v>
+      </c>
+      <c r="J47" s="1">
+        <v>4</v>
+      </c>
+      <c r="K47" t="s">
+        <v>36</v>
+      </c>
       <c r="L47" s="5">
-        <f t="shared" si="10"/>
-        <v>10410</v>
+        <f t="shared" ref="L47:L66" si="15">A48</f>
+        <v>10301</v>
       </c>
       <c r="M47" s="1">
-        <v>2700</v>
+        <v>100</v>
+      </c>
+      <c r="N47" s="1">
+        <v>0</v>
       </c>
       <c r="P47" s="2">
-        <f t="shared" si="11"/>
-        <v>410409</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="1:16">
       <c r="A48" s="1">
-        <f t="shared" si="12"/>
-        <v>10410</v>
+        <f t="shared" ref="A48:A63" si="16">10000+G48+B48*100</f>
+        <v>10301</v>
       </c>
       <c r="B48" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>69</v>
+        <v>120</v>
       </c>
       <c r="D48" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E48" s="2">
-        <v>47043</v>
+        <v>47029</v>
       </c>
       <c r="F48" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G48" s="1">
-        <v>10</v>
-      </c>
-      <c r="J48" s="1"/>
-      <c r="K48"/>
+        <v>1</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="J48" s="1">
+        <v>4</v>
+      </c>
+      <c r="K48" t="s">
+        <v>39</v>
+      </c>
+      <c r="L48" s="5">
+        <f t="shared" si="15"/>
+        <v>10302</v>
+      </c>
+      <c r="M48" s="1">
+        <v>300</v>
+      </c>
+      <c r="N48" s="1">
+        <v>960</v>
+      </c>
       <c r="P48" s="2">
-        <f t="shared" si="11"/>
-        <v>410410</v>
+        <f t="shared" ref="P48:P67" si="17">400000+A48</f>
+        <v>410301</v>
       </c>
     </row>
     <row r="49" customHeight="1" spans="1:16">
       <c r="A49" s="1">
-        <f t="shared" si="12"/>
-        <v>10500</v>
+        <f t="shared" si="16"/>
+        <v>10302</v>
       </c>
       <c r="B49" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>79</v>
+        <v>120</v>
       </c>
       <c r="D49" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E49" s="2">
-        <v>47044</v>
+        <v>47029</v>
       </c>
       <c r="F49" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G49" s="1">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>98</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="J49" s="1">
         <v>4</v>
       </c>
       <c r="K49" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="L49" s="5">
-        <f t="shared" ref="L49:L58" si="13">A50</f>
-        <v>10501</v>
+        <f t="shared" si="15"/>
+        <v>10303</v>
       </c>
       <c r="M49" s="1">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="N49" s="1">
-        <v>0</v>
+        <v>1440</v>
       </c>
       <c r="P49" s="2">
-        <v>0</v>
+        <f t="shared" si="17"/>
+        <v>410302</v>
       </c>
     </row>
     <row r="50" customHeight="1" spans="1:16">
       <c r="A50" s="1">
-        <f t="shared" si="12"/>
-        <v>10501</v>
+        <f t="shared" si="16"/>
+        <v>10303</v>
       </c>
       <c r="B50" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>79</v>
+        <v>120</v>
       </c>
       <c r="D50" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E50" s="2">
-        <v>47044</v>
+        <v>47029</v>
       </c>
       <c r="F50" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G50" s="1">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>101</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="J50" s="1">
         <v>4</v>
@@ -3708,1008 +4195,3808 @@
         <v>39</v>
       </c>
       <c r="L50" s="5">
-        <f t="shared" si="13"/>
-        <v>10502</v>
+        <f t="shared" si="15"/>
+        <v>10304</v>
       </c>
       <c r="M50" s="1">
-        <v>300</v>
-      </c>
-      <c r="O50" s="1">
-        <v>22001</v>
+        <v>900</v>
+      </c>
+      <c r="N50" s="1">
+        <v>1920</v>
       </c>
       <c r="P50" s="2">
-        <f t="shared" ref="P50:P59" si="14">400000+A50</f>
-        <v>410501</v>
+        <f t="shared" si="17"/>
+        <v>410303</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="1:16">
       <c r="A51" s="1">
-        <f t="shared" si="12"/>
-        <v>10502</v>
+        <f t="shared" si="16"/>
+        <v>10304</v>
       </c>
       <c r="B51" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>79</v>
+        <v>120</v>
       </c>
       <c r="D51" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E51" s="2">
-        <v>47044</v>
+        <v>47029</v>
       </c>
       <c r="F51" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G51" s="1">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>122</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J51" s="1">
         <v>4</v>
       </c>
       <c r="K51" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="L51" s="5">
-        <f t="shared" si="13"/>
-        <v>10503</v>
+        <f t="shared" si="15"/>
+        <v>10305</v>
       </c>
       <c r="M51" s="1">
-        <v>600</v>
-      </c>
-      <c r="O51" s="1">
-        <v>22002</v>
+        <v>1200</v>
+      </c>
+      <c r="N51" s="1">
+        <v>2400</v>
       </c>
       <c r="P51" s="2">
-        <f t="shared" si="14"/>
-        <v>410502</v>
+        <f t="shared" si="17"/>
+        <v>410304</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="1:16">
       <c r="A52" s="1">
-        <f t="shared" si="12"/>
-        <v>10503</v>
+        <f t="shared" si="16"/>
+        <v>10305</v>
       </c>
       <c r="B52" s="1">
+        <v>3</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D52" s="1">
+        <v>4</v>
+      </c>
+      <c r="E52" s="2">
+        <v>47029</v>
+      </c>
+      <c r="F52" s="2">
+        <v>1</v>
+      </c>
+      <c r="G52" s="1">
         <v>5</v>
       </c>
-      <c r="C52" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="D52" s="1">
-        <v>2</v>
-      </c>
-      <c r="E52" s="2">
-        <v>47044</v>
-      </c>
-      <c r="F52" s="2">
-        <v>0</v>
-      </c>
-      <c r="G52" s="1">
-        <v>3</v>
+      <c r="H52" s="2" t="s">
+        <v>123</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>83</v>
+        <v>124</v>
       </c>
       <c r="J52" s="1">
         <v>4</v>
       </c>
       <c r="K52" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="L52" s="5">
-        <f t="shared" si="13"/>
-        <v>10504</v>
+        <f t="shared" si="15"/>
+        <v>10306</v>
       </c>
       <c r="M52" s="1">
-        <v>900</v>
-      </c>
-      <c r="O52" s="1">
-        <v>22003</v>
+        <v>1500</v>
+      </c>
+      <c r="N52" s="1">
+        <v>2880</v>
       </c>
       <c r="P52" s="2">
-        <f t="shared" si="14"/>
-        <v>410503</v>
+        <f t="shared" si="17"/>
+        <v>410305</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="1:16">
       <c r="A53" s="1">
-        <f t="shared" si="12"/>
-        <v>10504</v>
+        <f t="shared" si="16"/>
+        <v>10306</v>
       </c>
       <c r="B53" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>79</v>
+        <v>120</v>
       </c>
       <c r="D53" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E53" s="2">
-        <v>47044</v>
+        <v>47029</v>
       </c>
       <c r="F53" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G53" s="1">
-        <v>4</v>
+        <v>6</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>125</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="J53" s="1">
         <v>4</v>
       </c>
       <c r="K53" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="L53" s="5">
-        <f t="shared" si="13"/>
-        <v>10505</v>
+        <f t="shared" si="15"/>
+        <v>10307</v>
       </c>
       <c r="M53" s="1">
-        <v>1200</v>
-      </c>
-      <c r="O53" s="1">
-        <v>22004</v>
+        <f t="shared" ref="M53:M56" si="18">G53*600</f>
+        <v>3600</v>
+      </c>
+      <c r="N53" s="1">
+        <v>5040</v>
       </c>
       <c r="P53" s="2">
-        <f t="shared" si="14"/>
-        <v>410504</v>
+        <f t="shared" si="17"/>
+        <v>410306</v>
       </c>
     </row>
     <row r="54" customHeight="1" spans="1:16">
       <c r="A54" s="1">
-        <f t="shared" si="12"/>
-        <v>10505</v>
+        <f t="shared" si="16"/>
+        <v>10307</v>
       </c>
       <c r="B54" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>79</v>
+        <v>120</v>
       </c>
       <c r="D54" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E54" s="2">
-        <v>47044</v>
+        <v>47029</v>
       </c>
       <c r="F54" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G54" s="1">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>126</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="J54" s="1">
         <v>4</v>
       </c>
       <c r="K54" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="L54" s="5">
-        <f t="shared" si="13"/>
-        <v>10506</v>
+        <f t="shared" si="15"/>
+        <v>10308</v>
       </c>
       <c r="M54" s="1">
-        <v>1500</v>
-      </c>
-      <c r="O54" s="1">
-        <v>22005</v>
+        <f t="shared" si="18"/>
+        <v>4200</v>
+      </c>
+      <c r="N54" s="1">
+        <v>5760</v>
       </c>
       <c r="P54" s="2">
-        <f t="shared" si="14"/>
-        <v>410505</v>
+        <f t="shared" si="17"/>
+        <v>410307</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="1:16">
       <c r="A55" s="1">
-        <f t="shared" ref="A55:A60" si="15">10000+G55+B55*100</f>
-        <v>10506</v>
+        <f t="shared" si="16"/>
+        <v>10308</v>
       </c>
       <c r="B55" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>79</v>
+        <v>120</v>
       </c>
       <c r="D55" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E55" s="2">
-        <v>47044</v>
+        <v>47029</v>
       </c>
       <c r="F55" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G55" s="1">
-        <v>6</v>
+        <v>8</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>127</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="J55" s="1">
         <v>4</v>
       </c>
       <c r="K55" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="L55" s="5">
-        <f t="shared" si="13"/>
-        <v>10507</v>
+        <f t="shared" si="15"/>
+        <v>10309</v>
       </c>
       <c r="M55" s="1">
-        <v>1800</v>
-      </c>
-      <c r="O55" s="1">
-        <v>22006</v>
+        <f t="shared" si="18"/>
+        <v>4800</v>
+      </c>
+      <c r="N55" s="1">
+        <v>6480</v>
       </c>
       <c r="P55" s="2">
-        <f t="shared" si="14"/>
-        <v>410506</v>
+        <f t="shared" si="17"/>
+        <v>410308</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="1:16">
       <c r="A56" s="1">
+        <f t="shared" si="16"/>
+        <v>10309</v>
+      </c>
+      <c r="B56" s="1">
+        <v>3</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D56" s="1">
+        <v>4</v>
+      </c>
+      <c r="E56" s="2">
+        <v>47029</v>
+      </c>
+      <c r="F56" s="2">
+        <v>1</v>
+      </c>
+      <c r="G56" s="1">
+        <v>9</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="I56" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="J56" s="1">
+        <v>4</v>
+      </c>
+      <c r="K56" t="s">
+        <v>59</v>
+      </c>
+      <c r="L56" s="5">
         <f t="shared" si="15"/>
-        <v>10507</v>
-      </c>
-      <c r="B56" s="1">
-        <v>5</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="D56" s="1">
-        <v>2</v>
-      </c>
-      <c r="E56" s="2">
-        <v>47044</v>
-      </c>
-      <c r="F56" s="2">
-        <v>0</v>
-      </c>
-      <c r="G56" s="1">
-        <v>7</v>
-      </c>
-      <c r="I56" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="J56" s="1">
-        <v>4</v>
-      </c>
-      <c r="K56" t="s">
-        <v>39</v>
-      </c>
-      <c r="L56" s="5">
-        <f t="shared" si="13"/>
-        <v>10508</v>
+        <v>10310</v>
       </c>
       <c r="M56" s="1">
-        <v>2100</v>
-      </c>
-      <c r="O56" s="1">
-        <v>22007</v>
+        <f t="shared" si="18"/>
+        <v>5400</v>
+      </c>
+      <c r="N56" s="1">
+        <v>7920</v>
       </c>
       <c r="P56" s="2">
-        <f t="shared" si="14"/>
-        <v>410507</v>
+        <f t="shared" si="17"/>
+        <v>410309</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="1:16">
       <c r="A57" s="1">
+        <f t="shared" si="16"/>
+        <v>10310</v>
+      </c>
+      <c r="B57" s="1">
+        <v>3</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D57" s="1">
+        <v>4</v>
+      </c>
+      <c r="E57" s="2">
+        <v>47029</v>
+      </c>
+      <c r="F57" s="2">
+        <v>1</v>
+      </c>
+      <c r="G57" s="1">
+        <v>10</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="J57" s="1">
+        <v>4</v>
+      </c>
+      <c r="K57" t="s">
+        <v>62</v>
+      </c>
+      <c r="L57" s="5">
         <f t="shared" si="15"/>
-        <v>10508</v>
-      </c>
-      <c r="B57" s="1">
-        <v>5</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="D57" s="1">
-        <v>2</v>
-      </c>
-      <c r="E57" s="2">
-        <v>47044</v>
-      </c>
-      <c r="F57" s="2">
-        <v>0</v>
-      </c>
-      <c r="G57" s="1">
-        <v>8</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="J57" s="1">
-        <v>4</v>
-      </c>
-      <c r="K57" t="s">
-        <v>39</v>
-      </c>
-      <c r="L57" s="5">
-        <f t="shared" si="13"/>
-        <v>10509</v>
+        <v>10311</v>
       </c>
       <c r="M57" s="1">
-        <v>2400</v>
-      </c>
-      <c r="O57" s="1">
-        <v>22008</v>
+        <f t="shared" ref="M57:M60" si="19">G57*1200</f>
+        <v>12000</v>
+      </c>
+      <c r="N57" s="1">
+        <v>9360</v>
       </c>
       <c r="P57" s="2">
-        <f t="shared" si="14"/>
-        <v>410508</v>
+        <f t="shared" si="17"/>
+        <v>410310</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="1:16">
       <c r="A58" s="1">
+        <f t="shared" ref="A58:A67" si="20">10000+G58+B58*100</f>
+        <v>10311</v>
+      </c>
+      <c r="B58" s="1">
+        <v>3</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D58" s="1">
+        <v>4</v>
+      </c>
+      <c r="E58" s="2">
+        <v>47029</v>
+      </c>
+      <c r="F58" s="2">
+        <v>1</v>
+      </c>
+      <c r="G58" s="1">
+        <v>11</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="J58" s="1">
+        <v>4</v>
+      </c>
+      <c r="K58" t="s">
+        <v>65</v>
+      </c>
+      <c r="L58" s="5">
         <f t="shared" si="15"/>
-        <v>10509</v>
-      </c>
-      <c r="B58" s="1">
-        <v>5</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="D58" s="1">
-        <v>2</v>
-      </c>
-      <c r="E58" s="2">
-        <v>47044</v>
-      </c>
-      <c r="F58" s="2">
-        <v>0</v>
-      </c>
-      <c r="G58" s="1">
-        <v>9</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="J58" s="1">
-        <v>4</v>
-      </c>
-      <c r="K58" t="s">
-        <v>39</v>
-      </c>
-      <c r="L58" s="5">
-        <f t="shared" si="13"/>
-        <v>10510</v>
+        <v>10312</v>
       </c>
       <c r="M58" s="1">
-        <v>2700</v>
-      </c>
-      <c r="O58" s="1">
-        <v>22009</v>
+        <f t="shared" si="19"/>
+        <v>13200</v>
+      </c>
+      <c r="N58" s="1">
+        <v>10800</v>
       </c>
       <c r="P58" s="2">
-        <f t="shared" si="14"/>
-        <v>410509</v>
+        <f t="shared" ref="P58:P67" si="21">400000+A58</f>
+        <v>410311</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="1:16">
       <c r="A59" s="1">
+        <f t="shared" si="20"/>
+        <v>10312</v>
+      </c>
+      <c r="B59" s="1">
+        <v>3</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D59" s="1">
+        <v>4</v>
+      </c>
+      <c r="E59" s="2">
+        <v>47029</v>
+      </c>
+      <c r="F59" s="2">
+        <v>1</v>
+      </c>
+      <c r="G59" s="1">
+        <v>12</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="J59" s="1">
+        <v>4</v>
+      </c>
+      <c r="K59" t="s">
+        <v>68</v>
+      </c>
+      <c r="L59" s="5">
         <f t="shared" si="15"/>
-        <v>10510</v>
-      </c>
-      <c r="B59" s="1">
-        <v>5</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="D59" s="1">
-        <v>2</v>
-      </c>
-      <c r="E59" s="2">
-        <v>47044</v>
-      </c>
-      <c r="F59" s="2">
-        <v>0</v>
-      </c>
-      <c r="G59" s="1">
-        <v>10</v>
-      </c>
-      <c r="J59" s="1">
-        <v>4</v>
-      </c>
-      <c r="K59"/>
-      <c r="O59" s="1">
-        <v>22010</v>
+        <v>10313</v>
+      </c>
+      <c r="M59" s="1">
+        <f t="shared" si="19"/>
+        <v>14400</v>
+      </c>
+      <c r="N59" s="1">
+        <v>18240</v>
       </c>
       <c r="P59" s="2">
-        <f t="shared" si="14"/>
-        <v>410510</v>
+        <f t="shared" si="21"/>
+        <v>410312</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="1:16">
       <c r="A60" s="1">
+        <f t="shared" si="20"/>
+        <v>10313</v>
+      </c>
+      <c r="B60" s="1">
+        <v>3</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D60" s="1">
+        <v>4</v>
+      </c>
+      <c r="E60" s="2">
+        <v>47029</v>
+      </c>
+      <c r="F60" s="2">
+        <v>1</v>
+      </c>
+      <c r="G60" s="1">
+        <v>13</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="J60" s="1">
+        <v>4</v>
+      </c>
+      <c r="K60" t="s">
+        <v>71</v>
+      </c>
+      <c r="L60" s="5">
         <f t="shared" si="15"/>
-        <v>10600</v>
-      </c>
-      <c r="B60" s="1">
-        <v>6</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="D60" s="1">
-        <v>4</v>
-      </c>
-      <c r="E60" s="2">
-        <v>47045</v>
-      </c>
-      <c r="F60" s="2">
-        <v>0</v>
-      </c>
-      <c r="G60" s="1">
-        <v>0</v>
-      </c>
-      <c r="I60" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="J60" s="1">
-        <v>4</v>
-      </c>
-      <c r="K60" t="s">
-        <v>36</v>
-      </c>
-      <c r="L60" s="5">
-        <f t="shared" ref="L60:L69" si="16">A61</f>
-        <v>10601</v>
+        <v>10314</v>
       </c>
       <c r="M60" s="1">
-        <v>100</v>
+        <f t="shared" si="19"/>
+        <v>15600</v>
       </c>
       <c r="N60" s="1">
-        <v>0</v>
+        <v>22080</v>
       </c>
       <c r="P60" s="2">
-        <v>0</v>
+        <f t="shared" si="21"/>
+        <v>410313</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="1:16">
       <c r="A61" s="1">
-        <f t="shared" ref="A61:A72" si="17">10000+G61+B61*100</f>
-        <v>10601</v>
+        <f t="shared" si="20"/>
+        <v>10314</v>
       </c>
       <c r="B61" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="D61" s="1">
         <v>4</v>
       </c>
       <c r="E61" s="2">
-        <v>47045</v>
+        <v>47029</v>
       </c>
       <c r="F61" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G61" s="1">
-        <v>1</v>
+        <v>14</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>135</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>92</v>
+        <v>136</v>
       </c>
       <c r="J61" s="1">
         <v>4</v>
       </c>
       <c r="K61" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="L61" s="5">
-        <f t="shared" si="16"/>
-        <v>10602</v>
+        <f t="shared" si="15"/>
+        <v>10315</v>
       </c>
       <c r="M61" s="1">
-        <v>300</v>
-      </c>
-      <c r="O61" s="1">
-        <v>11001</v>
+        <f t="shared" ref="M61:M63" si="22">G61*2400</f>
+        <v>33600</v>
+      </c>
+      <c r="N61" s="1">
+        <v>25920</v>
       </c>
       <c r="P61" s="2">
-        <f t="shared" ref="P61:P71" si="18">400000+A61</f>
-        <v>410601</v>
+        <f t="shared" si="21"/>
+        <v>410314</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="1:16">
       <c r="A62" s="1">
-        <f t="shared" si="17"/>
-        <v>10602</v>
+        <f t="shared" si="20"/>
+        <v>10315</v>
       </c>
       <c r="B62" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="D62" s="1">
         <v>4</v>
       </c>
       <c r="E62" s="2">
-        <v>47045</v>
+        <v>47029</v>
       </c>
       <c r="F62" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G62" s="1">
-        <v>2</v>
+        <v>15</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>137</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="J62" s="1">
         <v>4</v>
       </c>
       <c r="K62" t="s">
-        <v>39</v>
+        <v>77</v>
       </c>
       <c r="L62" s="5">
-        <f t="shared" si="16"/>
-        <v>10603</v>
+        <f t="shared" si="15"/>
+        <v>10316</v>
       </c>
       <c r="M62" s="1">
-        <v>600</v>
-      </c>
-      <c r="O62" s="1">
-        <v>11002</v>
+        <f t="shared" si="22"/>
+        <v>36000</v>
+      </c>
+      <c r="N62" s="1">
+        <v>39600</v>
       </c>
       <c r="P62" s="2">
-        <f t="shared" si="18"/>
-        <v>410602</v>
+        <f t="shared" si="21"/>
+        <v>410315</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="1:16">
       <c r="A63" s="1">
-        <f t="shared" si="17"/>
-        <v>10603</v>
+        <f t="shared" si="20"/>
+        <v>10316</v>
       </c>
       <c r="B63" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="D63" s="1">
         <v>4</v>
       </c>
       <c r="E63" s="2">
-        <v>47045</v>
+        <v>47029</v>
       </c>
       <c r="F63" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G63" s="1">
-        <v>3</v>
+        <v>16</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>138</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>94</v>
+        <v>139</v>
       </c>
       <c r="J63" s="1">
         <v>4</v>
       </c>
       <c r="K63" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="L63" s="5">
-        <f t="shared" si="16"/>
-        <v>10604</v>
+        <f t="shared" si="15"/>
+        <v>10317</v>
       </c>
       <c r="M63" s="1">
-        <v>900</v>
-      </c>
-      <c r="O63" s="1">
-        <v>11003</v>
+        <f t="shared" si="22"/>
+        <v>38400</v>
+      </c>
+      <c r="N63" s="1">
+        <v>46800</v>
       </c>
       <c r="P63" s="2">
-        <f t="shared" si="18"/>
-        <v>410603</v>
+        <f t="shared" si="21"/>
+        <v>410316</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="1:16">
       <c r="A64" s="1">
-        <f t="shared" si="17"/>
-        <v>10604</v>
+        <f t="shared" si="20"/>
+        <v>10317</v>
       </c>
       <c r="B64" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="D64" s="1">
         <v>4</v>
       </c>
       <c r="E64" s="2">
-        <v>47045</v>
+        <v>47029</v>
       </c>
       <c r="F64" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G64" s="1">
-        <v>4</v>
+        <v>17</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>140</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>95</v>
+        <v>136</v>
       </c>
       <c r="J64" s="1">
         <v>4</v>
       </c>
       <c r="K64" t="s">
-        <v>39</v>
+        <v>83</v>
       </c>
       <c r="L64" s="5">
-        <f t="shared" si="16"/>
-        <v>10605</v>
+        <f t="shared" si="15"/>
+        <v>10318</v>
       </c>
       <c r="M64" s="1">
-        <v>1200</v>
-      </c>
-      <c r="O64" s="1">
-        <v>11004</v>
+        <f t="shared" ref="M64:M66" si="23">G64*4800</f>
+        <v>81600</v>
+      </c>
+      <c r="N64" s="1">
+        <v>54000</v>
       </c>
       <c r="P64" s="2">
-        <f t="shared" si="18"/>
-        <v>410604</v>
+        <f t="shared" si="21"/>
+        <v>410317</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="1:16">
       <c r="A65" s="1">
-        <f t="shared" si="17"/>
-        <v>10605</v>
+        <f t="shared" si="20"/>
+        <v>10318</v>
       </c>
       <c r="B65" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="D65" s="1">
         <v>4</v>
       </c>
       <c r="E65" s="2">
-        <v>47045</v>
+        <v>47029</v>
       </c>
       <c r="F65" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G65" s="1">
-        <v>5</v>
+        <v>18</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>141</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="J65" s="1">
         <v>4</v>
       </c>
       <c r="K65" t="s">
-        <v>39</v>
+        <v>86</v>
       </c>
       <c r="L65" s="5">
-        <f t="shared" si="16"/>
-        <v>10606</v>
+        <f t="shared" si="15"/>
+        <v>10319</v>
       </c>
       <c r="M65" s="1">
-        <v>1500</v>
-      </c>
-      <c r="O65" s="1">
-        <v>11005</v>
+        <f t="shared" si="23"/>
+        <v>86400</v>
+      </c>
+      <c r="N65" s="1">
+        <v>76320</v>
       </c>
       <c r="P65" s="2">
-        <f t="shared" si="18"/>
-        <v>410605</v>
+        <f t="shared" si="21"/>
+        <v>410318</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="1:16">
       <c r="A66" s="1">
-        <f t="shared" si="17"/>
-        <v>10606</v>
+        <f t="shared" si="20"/>
+        <v>10319</v>
       </c>
       <c r="B66" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="D66" s="1">
         <v>4</v>
       </c>
       <c r="E66" s="2">
-        <v>47045</v>
+        <v>47029</v>
       </c>
       <c r="F66" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G66" s="1">
-        <v>6</v>
+        <v>19</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>142</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="J66" s="1">
         <v>4</v>
       </c>
       <c r="K66" t="s">
-        <v>39</v>
+        <v>89</v>
       </c>
       <c r="L66" s="5">
-        <f t="shared" si="16"/>
-        <v>10607</v>
+        <f t="shared" si="15"/>
+        <v>10320</v>
       </c>
       <c r="M66" s="1">
-        <v>1800</v>
-      </c>
-      <c r="O66" s="1">
-        <v>11006</v>
+        <f t="shared" si="23"/>
+        <v>91200</v>
+      </c>
+      <c r="N66" s="1">
+        <v>87840</v>
       </c>
       <c r="P66" s="2">
-        <f t="shared" si="18"/>
-        <v>410606</v>
+        <f t="shared" si="21"/>
+        <v>410319</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="1:16">
       <c r="A67" s="1">
-        <f t="shared" si="17"/>
-        <v>10607</v>
+        <f t="shared" si="20"/>
+        <v>10320</v>
       </c>
       <c r="B67" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="D67" s="1">
         <v>4</v>
       </c>
       <c r="E67" s="2">
-        <v>47045</v>
+        <v>47029</v>
       </c>
       <c r="F67" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G67" s="1">
-        <v>7</v>
-      </c>
-      <c r="I67" s="3" t="s">
-        <v>98</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="I67" s="3"/>
       <c r="J67" s="1">
         <v>4</v>
       </c>
-      <c r="K67" t="s">
-        <v>39</v>
-      </c>
-      <c r="L67" s="5">
-        <f t="shared" si="16"/>
-        <v>10608</v>
-      </c>
-      <c r="M67" s="1">
-        <v>2100</v>
-      </c>
-      <c r="O67" s="1">
-        <v>11007</v>
+      <c r="K67"/>
+      <c r="N67" s="1">
+        <v>99360</v>
       </c>
       <c r="P67" s="2">
-        <f t="shared" si="18"/>
-        <v>410607</v>
+        <f t="shared" si="21"/>
+        <v>410320</v>
       </c>
     </row>
     <row r="68" customHeight="1" spans="1:16">
       <c r="A68" s="1">
-        <f t="shared" si="17"/>
-        <v>10608</v>
+        <f>10000+G68+B68*100</f>
+        <v>10400</v>
       </c>
       <c r="B68" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>90</v>
+        <v>144</v>
       </c>
       <c r="D68" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E68" s="2">
-        <v>47045</v>
+        <v>47043</v>
       </c>
       <c r="F68" s="2">
         <v>0</v>
       </c>
       <c r="G68" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="J68" s="1">
-        <v>4</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="J68" s="1"/>
       <c r="K68" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="L68" s="5">
-        <f t="shared" si="16"/>
-        <v>10609</v>
+        <f t="shared" ref="L68:L87" si="24">A69</f>
+        <v>10401</v>
       </c>
       <c r="M68" s="1">
-        <v>2400</v>
-      </c>
-      <c r="O68" s="1">
-        <v>11008</v>
+        <v>100</v>
+      </c>
+      <c r="N68" s="1">
+        <v>0</v>
       </c>
       <c r="P68" s="2">
-        <f t="shared" si="18"/>
-        <v>410608</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69" customHeight="1" spans="1:16">
       <c r="A69" s="1">
-        <f t="shared" si="17"/>
-        <v>10609</v>
+        <f>10000+G69+B69*100</f>
+        <v>10401</v>
       </c>
       <c r="B69" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>90</v>
+        <v>144</v>
       </c>
       <c r="D69" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E69" s="2">
-        <v>47045</v>
+        <v>47043</v>
       </c>
       <c r="F69" s="2">
         <v>0</v>
       </c>
       <c r="G69" s="1">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="J69" s="1">
-        <v>4</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="J69" s="1"/>
       <c r="K69" t="s">
         <v>39</v>
       </c>
       <c r="L69" s="5">
-        <f t="shared" si="16"/>
-        <v>10610</v>
+        <f t="shared" si="24"/>
+        <v>10402</v>
       </c>
       <c r="M69" s="1">
-        <v>2700</v>
-      </c>
-      <c r="O69" s="1">
-        <v>11009</v>
+        <v>300</v>
       </c>
       <c r="P69" s="2">
-        <f t="shared" si="18"/>
-        <v>410609</v>
+        <f t="shared" ref="P69:P78" si="25">400000+A69</f>
+        <v>410401</v>
       </c>
     </row>
     <row r="70" customHeight="1" spans="1:16">
       <c r="A70" s="1">
-        <f t="shared" si="17"/>
-        <v>10610</v>
+        <f>10000+G70+B70*100</f>
+        <v>10402</v>
       </c>
       <c r="B70" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>90</v>
+        <v>144</v>
       </c>
       <c r="D70" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E70" s="2">
-        <v>47045</v>
+        <v>47043</v>
       </c>
       <c r="F70" s="2">
         <v>0</v>
       </c>
       <c r="G70" s="1">
-        <v>10</v>
-      </c>
-      <c r="J70" s="1">
-        <v>4</v>
-      </c>
-      <c r="K70"/>
-      <c r="O70" s="1">
-        <v>11010</v>
+        <v>2</v>
+      </c>
+      <c r="I70" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="J70" s="1"/>
+      <c r="K70" t="s">
+        <v>39</v>
+      </c>
+      <c r="L70" s="5">
+        <f t="shared" si="24"/>
+        <v>10403</v>
+      </c>
+      <c r="M70" s="1">
+        <v>600</v>
       </c>
       <c r="P70" s="2">
-        <f t="shared" si="18"/>
-        <v>410610</v>
+        <f t="shared" si="25"/>
+        <v>410402</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="1:16">
       <c r="A71" s="1">
-        <f t="shared" si="17"/>
-        <v>10700</v>
+        <f>10000+G71+B71*100</f>
+        <v>10403</v>
       </c>
       <c r="B71" s="1">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>101</v>
+        <v>144</v>
       </c>
       <c r="D71" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E71" s="2">
-        <f>300000+A71</f>
-        <v>310700</v>
+        <v>47043</v>
       </c>
       <c r="F71" s="2">
         <v>0</v>
       </c>
       <c r="G71" s="1">
-        <v>0</v>
-      </c>
-      <c r="J71" s="1">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="I71" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="J71" s="1"/>
+      <c r="K71" t="s">
+        <v>39</v>
       </c>
       <c r="L71" s="5">
-        <f>A72</f>
-        <v>10701</v>
+        <f t="shared" si="24"/>
+        <v>10404</v>
       </c>
       <c r="M71" s="1">
-        <v>100</v>
-      </c>
-      <c r="N71" s="1">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="P71" s="2">
-        <v>0</v>
+        <f t="shared" si="25"/>
+        <v>410403</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="1:16">
       <c r="A72" s="1">
-        <f t="shared" si="17"/>
+        <f>10000+G72+B72*100</f>
+        <v>10404</v>
+      </c>
+      <c r="B72" s="1">
+        <v>4</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D72" s="1">
+        <v>2</v>
+      </c>
+      <c r="E72" s="2">
+        <v>47043</v>
+      </c>
+      <c r="F72" s="2">
+        <v>0</v>
+      </c>
+      <c r="G72" s="1">
+        <v>4</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="J72" s="1"/>
+      <c r="K72" t="s">
+        <v>46</v>
+      </c>
+      <c r="L72" s="5">
+        <f t="shared" si="24"/>
+        <v>10405</v>
+      </c>
+      <c r="M72" s="1">
+        <v>1200</v>
+      </c>
+      <c r="P72" s="2">
+        <f t="shared" si="25"/>
+        <v>410404</v>
+      </c>
+    </row>
+    <row r="73" customHeight="1" spans="1:16">
+      <c r="A73" s="1">
+        <f>10000+G73+B73*100</f>
+        <v>10405</v>
+      </c>
+      <c r="B73" s="1">
+        <v>4</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D73" s="1">
+        <v>2</v>
+      </c>
+      <c r="E73" s="2">
+        <v>47043</v>
+      </c>
+      <c r="F73" s="2">
+        <v>0</v>
+      </c>
+      <c r="G73" s="1">
+        <v>5</v>
+      </c>
+      <c r="I73" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="J73" s="1"/>
+      <c r="K73" t="s">
+        <v>46</v>
+      </c>
+      <c r="L73" s="5">
+        <f t="shared" si="24"/>
+        <v>10406</v>
+      </c>
+      <c r="M73" s="1">
+        <v>1500</v>
+      </c>
+      <c r="P73" s="2">
+        <f t="shared" si="25"/>
+        <v>410405</v>
+      </c>
+    </row>
+    <row r="74" customHeight="1" spans="1:16">
+      <c r="A74" s="1">
+        <f>10000+G74+B74*100</f>
+        <v>10406</v>
+      </c>
+      <c r="B74" s="1">
+        <v>4</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D74" s="1">
+        <v>2</v>
+      </c>
+      <c r="E74" s="2">
+        <v>47043</v>
+      </c>
+      <c r="F74" s="2">
+        <v>0</v>
+      </c>
+      <c r="G74" s="1">
+        <v>6</v>
+      </c>
+      <c r="I74" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="J74" s="1"/>
+      <c r="K74" t="s">
+        <v>51</v>
+      </c>
+      <c r="L74" s="5">
+        <f t="shared" si="24"/>
+        <v>10407</v>
+      </c>
+      <c r="M74" s="1">
+        <f t="shared" ref="M74:M77" si="26">G74*600</f>
+        <v>3600</v>
+      </c>
+      <c r="P74" s="2">
+        <f t="shared" si="25"/>
+        <v>410406</v>
+      </c>
+    </row>
+    <row r="75" customHeight="1" spans="1:16">
+      <c r="A75" s="1">
+        <f>10000+G75+B75*100</f>
+        <v>10407</v>
+      </c>
+      <c r="B75" s="1">
+        <v>4</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D75" s="1">
+        <v>2</v>
+      </c>
+      <c r="E75" s="2">
+        <v>47043</v>
+      </c>
+      <c r="F75" s="2">
+        <v>0</v>
+      </c>
+      <c r="G75" s="1">
+        <v>7</v>
+      </c>
+      <c r="I75" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="J75" s="1"/>
+      <c r="K75" t="s">
+        <v>51</v>
+      </c>
+      <c r="L75" s="5">
+        <f t="shared" si="24"/>
+        <v>10408</v>
+      </c>
+      <c r="M75" s="1">
+        <f t="shared" si="26"/>
+        <v>4200</v>
+      </c>
+      <c r="P75" s="2">
+        <f t="shared" si="25"/>
+        <v>410407</v>
+      </c>
+    </row>
+    <row r="76" customHeight="1" spans="1:16">
+      <c r="A76" s="1">
+        <f>10000+G76+B76*100</f>
+        <v>10408</v>
+      </c>
+      <c r="B76" s="1">
+        <v>4</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D76" s="1">
+        <v>2</v>
+      </c>
+      <c r="E76" s="2">
+        <v>47043</v>
+      </c>
+      <c r="F76" s="2">
+        <v>0</v>
+      </c>
+      <c r="G76" s="1">
+        <v>8</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="J76" s="1"/>
+      <c r="K76" t="s">
+        <v>56</v>
+      </c>
+      <c r="L76" s="5">
+        <f t="shared" si="24"/>
+        <v>10409</v>
+      </c>
+      <c r="M76" s="1">
+        <f t="shared" si="26"/>
+        <v>4800</v>
+      </c>
+      <c r="P76" s="2">
+        <f t="shared" si="25"/>
+        <v>410408</v>
+      </c>
+    </row>
+    <row r="77" customHeight="1" spans="1:16">
+      <c r="A77" s="1">
+        <f>10000+G77+B77*100</f>
+        <v>10409</v>
+      </c>
+      <c r="B77" s="1">
+        <v>4</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D77" s="1">
+        <v>2</v>
+      </c>
+      <c r="E77" s="2">
+        <v>47043</v>
+      </c>
+      <c r="F77" s="2">
+        <v>0</v>
+      </c>
+      <c r="G77" s="1">
+        <v>9</v>
+      </c>
+      <c r="I77" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="J77" s="1"/>
+      <c r="K77" t="s">
+        <v>59</v>
+      </c>
+      <c r="L77" s="5">
+        <f t="shared" si="24"/>
+        <v>10410</v>
+      </c>
+      <c r="M77" s="1">
+        <f t="shared" si="26"/>
+        <v>5400</v>
+      </c>
+      <c r="P77" s="2">
+        <f t="shared" si="25"/>
+        <v>410409</v>
+      </c>
+    </row>
+    <row r="78" customHeight="1" spans="1:16">
+      <c r="A78" s="1">
+        <f>10000+G78+B78*100</f>
+        <v>10410</v>
+      </c>
+      <c r="B78" s="1">
+        <v>4</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D78" s="1">
+        <v>2</v>
+      </c>
+      <c r="E78" s="2">
+        <v>47043</v>
+      </c>
+      <c r="F78" s="2">
+        <v>0</v>
+      </c>
+      <c r="G78" s="1">
+        <v>10</v>
+      </c>
+      <c r="I78" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="J78" s="1"/>
+      <c r="K78" t="s">
+        <v>62</v>
+      </c>
+      <c r="L78" s="5">
+        <f t="shared" si="24"/>
+        <v>10411</v>
+      </c>
+      <c r="M78" s="1">
+        <f t="shared" ref="M78:M81" si="27">G78*1200</f>
+        <v>12000</v>
+      </c>
+      <c r="P78" s="2">
+        <f t="shared" si="25"/>
+        <v>410410</v>
+      </c>
+    </row>
+    <row r="79" customHeight="1" spans="1:16">
+      <c r="A79" s="1">
+        <f t="shared" ref="A79:A88" si="28">10000+G79+B79*100</f>
+        <v>10411</v>
+      </c>
+      <c r="B79" s="1">
+        <v>4</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D79" s="1">
+        <v>2</v>
+      </c>
+      <c r="E79" s="2">
+        <v>47043</v>
+      </c>
+      <c r="F79" s="2">
+        <v>0</v>
+      </c>
+      <c r="G79" s="1">
+        <v>11</v>
+      </c>
+      <c r="I79" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="J79" s="1"/>
+      <c r="K79" t="s">
+        <v>65</v>
+      </c>
+      <c r="L79" s="5">
+        <f t="shared" si="24"/>
+        <v>10412</v>
+      </c>
+      <c r="M79" s="1">
+        <f t="shared" si="27"/>
+        <v>13200</v>
+      </c>
+      <c r="P79" s="2">
+        <f t="shared" ref="P79:P88" si="29">400000+A79</f>
+        <v>410411</v>
+      </c>
+    </row>
+    <row r="80" customHeight="1" spans="1:16">
+      <c r="A80" s="1">
+        <f t="shared" si="28"/>
+        <v>10412</v>
+      </c>
+      <c r="B80" s="1">
+        <v>4</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D80" s="1">
+        <v>2</v>
+      </c>
+      <c r="E80" s="2">
+        <v>47043</v>
+      </c>
+      <c r="F80" s="2">
+        <v>0</v>
+      </c>
+      <c r="G80" s="1">
+        <v>12</v>
+      </c>
+      <c r="I80" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="J80" s="1"/>
+      <c r="K80" t="s">
+        <v>68</v>
+      </c>
+      <c r="L80" s="5">
+        <f t="shared" si="24"/>
+        <v>10413</v>
+      </c>
+      <c r="M80" s="1">
+        <f t="shared" si="27"/>
+        <v>14400</v>
+      </c>
+      <c r="P80" s="2">
+        <f t="shared" si="29"/>
+        <v>410412</v>
+      </c>
+    </row>
+    <row r="81" customHeight="1" spans="1:16">
+      <c r="A81" s="1">
+        <f t="shared" si="28"/>
+        <v>10413</v>
+      </c>
+      <c r="B81" s="1">
+        <v>4</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D81" s="1">
+        <v>2</v>
+      </c>
+      <c r="E81" s="2">
+        <v>47043</v>
+      </c>
+      <c r="F81" s="2">
+        <v>0</v>
+      </c>
+      <c r="G81" s="1">
+        <v>13</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="J81" s="1"/>
+      <c r="K81" t="s">
+        <v>71</v>
+      </c>
+      <c r="L81" s="5">
+        <f t="shared" si="24"/>
+        <v>10414</v>
+      </c>
+      <c r="M81" s="1">
+        <f t="shared" si="27"/>
+        <v>15600</v>
+      </c>
+      <c r="P81" s="2">
+        <f t="shared" si="29"/>
+        <v>410413</v>
+      </c>
+    </row>
+    <row r="82" customHeight="1" spans="1:16">
+      <c r="A82" s="1">
+        <f t="shared" si="28"/>
+        <v>10414</v>
+      </c>
+      <c r="B82" s="1">
+        <v>4</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D82" s="1">
+        <v>2</v>
+      </c>
+      <c r="E82" s="2">
+        <v>47043</v>
+      </c>
+      <c r="F82" s="2">
+        <v>0</v>
+      </c>
+      <c r="G82" s="1">
+        <v>14</v>
+      </c>
+      <c r="I82" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="J82" s="1"/>
+      <c r="K82" t="s">
+        <v>74</v>
+      </c>
+      <c r="L82" s="5">
+        <f t="shared" si="24"/>
+        <v>10415</v>
+      </c>
+      <c r="M82" s="1">
+        <f t="shared" ref="M82:M84" si="30">G82*2400</f>
+        <v>33600</v>
+      </c>
+      <c r="P82" s="2">
+        <f t="shared" si="29"/>
+        <v>410414</v>
+      </c>
+    </row>
+    <row r="83" customHeight="1" spans="1:16">
+      <c r="A83" s="1">
+        <f t="shared" si="28"/>
+        <v>10415</v>
+      </c>
+      <c r="B83" s="1">
+        <v>4</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D83" s="1">
+        <v>2</v>
+      </c>
+      <c r="E83" s="2">
+        <v>47043</v>
+      </c>
+      <c r="F83" s="2">
+        <v>0</v>
+      </c>
+      <c r="G83" s="1">
+        <v>15</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="J83" s="1"/>
+      <c r="K83" t="s">
+        <v>77</v>
+      </c>
+      <c r="L83" s="5">
+        <f t="shared" si="24"/>
+        <v>10416</v>
+      </c>
+      <c r="M83" s="1">
+        <f t="shared" si="30"/>
+        <v>36000</v>
+      </c>
+      <c r="P83" s="2">
+        <f t="shared" si="29"/>
+        <v>410415</v>
+      </c>
+    </row>
+    <row r="84" customHeight="1" spans="1:16">
+      <c r="A84" s="1">
+        <f t="shared" si="28"/>
+        <v>10416</v>
+      </c>
+      <c r="B84" s="1">
+        <v>4</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D84" s="1">
+        <v>2</v>
+      </c>
+      <c r="E84" s="2">
+        <v>47043</v>
+      </c>
+      <c r="F84" s="2">
+        <v>0</v>
+      </c>
+      <c r="G84" s="1">
+        <v>16</v>
+      </c>
+      <c r="I84" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="J84" s="1"/>
+      <c r="K84" t="s">
+        <v>80</v>
+      </c>
+      <c r="L84" s="5">
+        <f t="shared" si="24"/>
+        <v>10417</v>
+      </c>
+      <c r="M84" s="1">
+        <f t="shared" si="30"/>
+        <v>38400</v>
+      </c>
+      <c r="P84" s="2">
+        <f t="shared" si="29"/>
+        <v>410416</v>
+      </c>
+    </row>
+    <row r="85" customHeight="1" spans="1:16">
+      <c r="A85" s="1">
+        <f t="shared" si="28"/>
+        <v>10417</v>
+      </c>
+      <c r="B85" s="1">
+        <v>4</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D85" s="1">
+        <v>2</v>
+      </c>
+      <c r="E85" s="2">
+        <v>47043</v>
+      </c>
+      <c r="F85" s="2">
+        <v>0</v>
+      </c>
+      <c r="G85" s="1">
+        <v>17</v>
+      </c>
+      <c r="I85" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="J85" s="1"/>
+      <c r="K85" t="s">
+        <v>83</v>
+      </c>
+      <c r="L85" s="5">
+        <f t="shared" si="24"/>
+        <v>10418</v>
+      </c>
+      <c r="M85" s="1">
+        <f t="shared" ref="M85:M87" si="31">G85*4800</f>
+        <v>81600</v>
+      </c>
+      <c r="P85" s="2">
+        <f t="shared" si="29"/>
+        <v>410417</v>
+      </c>
+    </row>
+    <row r="86" customHeight="1" spans="1:16">
+      <c r="A86" s="1">
+        <f t="shared" si="28"/>
+        <v>10418</v>
+      </c>
+      <c r="B86" s="1">
+        <v>4</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D86" s="1">
+        <v>2</v>
+      </c>
+      <c r="E86" s="2">
+        <v>47043</v>
+      </c>
+      <c r="F86" s="2">
+        <v>0</v>
+      </c>
+      <c r="G86" s="1">
+        <v>18</v>
+      </c>
+      <c r="I86" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="J86" s="1"/>
+      <c r="K86" t="s">
+        <v>86</v>
+      </c>
+      <c r="L86" s="5">
+        <f t="shared" si="24"/>
+        <v>10419</v>
+      </c>
+      <c r="M86" s="1">
+        <f t="shared" si="31"/>
+        <v>86400</v>
+      </c>
+      <c r="P86" s="2">
+        <f t="shared" si="29"/>
+        <v>410418</v>
+      </c>
+    </row>
+    <row r="87" customHeight="1" spans="1:16">
+      <c r="A87" s="1">
+        <f t="shared" si="28"/>
+        <v>10419</v>
+      </c>
+      <c r="B87" s="1">
+        <v>4</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D87" s="1">
+        <v>2</v>
+      </c>
+      <c r="E87" s="2">
+        <v>47043</v>
+      </c>
+      <c r="F87" s="2">
+        <v>0</v>
+      </c>
+      <c r="G87" s="1">
+        <v>19</v>
+      </c>
+      <c r="I87" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="J87" s="1"/>
+      <c r="K87" t="s">
+        <v>89</v>
+      </c>
+      <c r="L87" s="5">
+        <f t="shared" si="24"/>
+        <v>10420</v>
+      </c>
+      <c r="M87" s="1">
+        <f t="shared" si="31"/>
+        <v>91200</v>
+      </c>
+      <c r="P87" s="2">
+        <f t="shared" si="29"/>
+        <v>410419</v>
+      </c>
+    </row>
+    <row r="88" customHeight="1" spans="1:16">
+      <c r="A88" s="1">
+        <f t="shared" si="28"/>
+        <v>10420</v>
+      </c>
+      <c r="B88" s="1">
+        <v>4</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D88" s="1">
+        <v>2</v>
+      </c>
+      <c r="E88" s="2">
+        <v>47043</v>
+      </c>
+      <c r="F88" s="2">
+        <v>0</v>
+      </c>
+      <c r="G88" s="1">
+        <v>20</v>
+      </c>
+      <c r="J88" s="1"/>
+      <c r="K88"/>
+      <c r="P88" s="2">
+        <f t="shared" si="29"/>
+        <v>410420</v>
+      </c>
+    </row>
+    <row r="89" customHeight="1" spans="1:16">
+      <c r="A89" s="1">
+        <f t="shared" ref="A89:A94" si="32">10000+G89+B89*100</f>
+        <v>10500</v>
+      </c>
+      <c r="B89" s="1">
+        <v>5</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D89" s="1">
+        <v>2</v>
+      </c>
+      <c r="E89" s="2">
+        <v>47044</v>
+      </c>
+      <c r="F89" s="2">
+        <v>0</v>
+      </c>
+      <c r="G89" s="1">
+        <v>0</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="J89" s="1">
+        <v>4</v>
+      </c>
+      <c r="K89" t="s">
+        <v>36</v>
+      </c>
+      <c r="L89" s="5">
+        <f t="shared" ref="L89:L108" si="33">A90</f>
+        <v>10501</v>
+      </c>
+      <c r="M89" s="1">
+        <v>100</v>
+      </c>
+      <c r="N89" s="1">
+        <v>0</v>
+      </c>
+      <c r="P89" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" customHeight="1" spans="1:16">
+      <c r="A90" s="1">
+        <f t="shared" si="32"/>
+        <v>10501</v>
+      </c>
+      <c r="B90" s="1">
+        <v>5</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D90" s="1">
+        <v>2</v>
+      </c>
+      <c r="E90" s="2">
+        <v>47044</v>
+      </c>
+      <c r="F90" s="2">
+        <v>0</v>
+      </c>
+      <c r="G90" s="1">
+        <v>1</v>
+      </c>
+      <c r="I90" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="J90" s="1">
+        <v>4</v>
+      </c>
+      <c r="K90" t="s">
+        <v>39</v>
+      </c>
+      <c r="L90" s="5">
+        <f t="shared" si="33"/>
+        <v>10502</v>
+      </c>
+      <c r="M90" s="1">
+        <v>300</v>
+      </c>
+      <c r="O90" s="1">
+        <v>22001</v>
+      </c>
+      <c r="P90" s="2">
+        <f t="shared" ref="P90:P99" si="34">400000+A90</f>
+        <v>410501</v>
+      </c>
+    </row>
+    <row r="91" customHeight="1" spans="1:16">
+      <c r="A91" s="1">
+        <f t="shared" si="32"/>
+        <v>10502</v>
+      </c>
+      <c r="B91" s="1">
+        <v>5</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D91" s="1">
+        <v>2</v>
+      </c>
+      <c r="E91" s="2">
+        <v>47044</v>
+      </c>
+      <c r="F91" s="2">
+        <v>0</v>
+      </c>
+      <c r="G91" s="1">
+        <v>2</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="J91" s="1">
+        <v>4</v>
+      </c>
+      <c r="K91" t="s">
+        <v>39</v>
+      </c>
+      <c r="L91" s="5">
+        <f t="shared" si="33"/>
+        <v>10503</v>
+      </c>
+      <c r="M91" s="1">
+        <v>600</v>
+      </c>
+      <c r="O91" s="1">
+        <v>22002</v>
+      </c>
+      <c r="P91" s="2">
+        <f t="shared" si="34"/>
+        <v>410502</v>
+      </c>
+    </row>
+    <row r="92" customHeight="1" spans="1:16">
+      <c r="A92" s="1">
+        <f t="shared" si="32"/>
+        <v>10503</v>
+      </c>
+      <c r="B92" s="1">
+        <v>5</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D92" s="1">
+        <v>2</v>
+      </c>
+      <c r="E92" s="2">
+        <v>47044</v>
+      </c>
+      <c r="F92" s="2">
+        <v>0</v>
+      </c>
+      <c r="G92" s="1">
+        <v>3</v>
+      </c>
+      <c r="I92" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="J92" s="1">
+        <v>4</v>
+      </c>
+      <c r="K92" t="s">
+        <v>39</v>
+      </c>
+      <c r="L92" s="5">
+        <f t="shared" si="33"/>
+        <v>10504</v>
+      </c>
+      <c r="M92" s="1">
+        <v>900</v>
+      </c>
+      <c r="O92" s="1">
+        <v>22003</v>
+      </c>
+      <c r="P92" s="2">
+        <f t="shared" si="34"/>
+        <v>410503</v>
+      </c>
+    </row>
+    <row r="93" customHeight="1" spans="1:16">
+      <c r="A93" s="1">
+        <f t="shared" si="32"/>
+        <v>10504</v>
+      </c>
+      <c r="B93" s="1">
+        <v>5</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D93" s="1">
+        <v>2</v>
+      </c>
+      <c r="E93" s="2">
+        <v>47044</v>
+      </c>
+      <c r="F93" s="2">
+        <v>0</v>
+      </c>
+      <c r="G93" s="1">
+        <v>4</v>
+      </c>
+      <c r="I93" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="J93" s="1">
+        <v>4</v>
+      </c>
+      <c r="K93" t="s">
+        <v>46</v>
+      </c>
+      <c r="L93" s="5">
+        <f t="shared" si="33"/>
+        <v>10505</v>
+      </c>
+      <c r="M93" s="1">
+        <v>1200</v>
+      </c>
+      <c r="O93" s="1">
+        <v>22004</v>
+      </c>
+      <c r="P93" s="2">
+        <f t="shared" si="34"/>
+        <v>410504</v>
+      </c>
+    </row>
+    <row r="94" customHeight="1" spans="1:16">
+      <c r="A94" s="1">
+        <f t="shared" si="32"/>
+        <v>10505</v>
+      </c>
+      <c r="B94" s="1">
+        <v>5</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D94" s="1">
+        <v>2</v>
+      </c>
+      <c r="E94" s="2">
+        <v>47044</v>
+      </c>
+      <c r="F94" s="2">
+        <v>0</v>
+      </c>
+      <c r="G94" s="1">
+        <v>5</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="J94" s="1">
+        <v>4</v>
+      </c>
+      <c r="K94" t="s">
+        <v>46</v>
+      </c>
+      <c r="L94" s="5">
+        <f t="shared" si="33"/>
+        <v>10506</v>
+      </c>
+      <c r="M94" s="1">
+        <v>1500</v>
+      </c>
+      <c r="O94" s="1">
+        <v>22005</v>
+      </c>
+      <c r="P94" s="2">
+        <f t="shared" si="34"/>
+        <v>410505</v>
+      </c>
+    </row>
+    <row r="95" customHeight="1" spans="1:16">
+      <c r="A95" s="1">
+        <f>10000+G95+B95*100</f>
+        <v>10506</v>
+      </c>
+      <c r="B95" s="1">
+        <v>5</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D95" s="1">
+        <v>2</v>
+      </c>
+      <c r="E95" s="2">
+        <v>47044</v>
+      </c>
+      <c r="F95" s="2">
+        <v>0</v>
+      </c>
+      <c r="G95" s="1">
+        <v>6</v>
+      </c>
+      <c r="I95" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="J95" s="1">
+        <v>4</v>
+      </c>
+      <c r="K95" t="s">
+        <v>51</v>
+      </c>
+      <c r="L95" s="5">
+        <f t="shared" si="33"/>
+        <v>10507</v>
+      </c>
+      <c r="M95" s="1">
+        <f t="shared" ref="M95:M98" si="35">G95*600</f>
+        <v>3600</v>
+      </c>
+      <c r="O95" s="1">
+        <v>22006</v>
+      </c>
+      <c r="P95" s="2">
+        <f t="shared" si="34"/>
+        <v>410506</v>
+      </c>
+    </row>
+    <row r="96" customHeight="1" spans="1:16">
+      <c r="A96" s="1">
+        <f>10000+G96+B96*100</f>
+        <v>10507</v>
+      </c>
+      <c r="B96" s="1">
+        <v>5</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D96" s="1">
+        <v>2</v>
+      </c>
+      <c r="E96" s="2">
+        <v>47044</v>
+      </c>
+      <c r="F96" s="2">
+        <v>0</v>
+      </c>
+      <c r="G96" s="1">
+        <v>7</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="J96" s="1">
+        <v>4</v>
+      </c>
+      <c r="K96" t="s">
+        <v>51</v>
+      </c>
+      <c r="L96" s="5">
+        <f t="shared" si="33"/>
+        <v>10508</v>
+      </c>
+      <c r="M96" s="1">
+        <f t="shared" si="35"/>
+        <v>4200</v>
+      </c>
+      <c r="O96" s="1">
+        <v>22007</v>
+      </c>
+      <c r="P96" s="2">
+        <f t="shared" si="34"/>
+        <v>410507</v>
+      </c>
+    </row>
+    <row r="97" customHeight="1" spans="1:16">
+      <c r="A97" s="1">
+        <f>10000+G97+B97*100</f>
+        <v>10508</v>
+      </c>
+      <c r="B97" s="1">
+        <v>5</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D97" s="1">
+        <v>2</v>
+      </c>
+      <c r="E97" s="2">
+        <v>47044</v>
+      </c>
+      <c r="F97" s="2">
+        <v>0</v>
+      </c>
+      <c r="G97" s="1">
+        <v>8</v>
+      </c>
+      <c r="I97" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="J97" s="1">
+        <v>4</v>
+      </c>
+      <c r="K97" t="s">
+        <v>56</v>
+      </c>
+      <c r="L97" s="5">
+        <f t="shared" si="33"/>
+        <v>10509</v>
+      </c>
+      <c r="M97" s="1">
+        <f t="shared" si="35"/>
+        <v>4800</v>
+      </c>
+      <c r="O97" s="1">
+        <v>22008</v>
+      </c>
+      <c r="P97" s="2">
+        <f t="shared" si="34"/>
+        <v>410508</v>
+      </c>
+    </row>
+    <row r="98" customHeight="1" spans="1:16">
+      <c r="A98" s="1">
+        <f>10000+G98+B98*100</f>
+        <v>10509</v>
+      </c>
+      <c r="B98" s="1">
+        <v>5</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D98" s="1">
+        <v>2</v>
+      </c>
+      <c r="E98" s="2">
+        <v>47044</v>
+      </c>
+      <c r="F98" s="2">
+        <v>0</v>
+      </c>
+      <c r="G98" s="1">
+        <v>9</v>
+      </c>
+      <c r="I98" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="J98" s="1">
+        <v>4</v>
+      </c>
+      <c r="K98" t="s">
+        <v>59</v>
+      </c>
+      <c r="L98" s="5">
+        <f t="shared" si="33"/>
+        <v>10510</v>
+      </c>
+      <c r="M98" s="1">
+        <f t="shared" si="35"/>
+        <v>5400</v>
+      </c>
+      <c r="O98" s="1">
+        <v>22009</v>
+      </c>
+      <c r="P98" s="2">
+        <f t="shared" si="34"/>
+        <v>410509</v>
+      </c>
+    </row>
+    <row r="99" customHeight="1" spans="1:16">
+      <c r="A99" s="1">
+        <f>10000+G99+B99*100</f>
+        <v>10510</v>
+      </c>
+      <c r="B99" s="1">
+        <v>5</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D99" s="1">
+        <v>2</v>
+      </c>
+      <c r="E99" s="2">
+        <v>47044</v>
+      </c>
+      <c r="F99" s="2">
+        <v>0</v>
+      </c>
+      <c r="G99" s="1">
+        <v>10</v>
+      </c>
+      <c r="I99" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="J99" s="1">
+        <v>4</v>
+      </c>
+      <c r="K99" t="s">
+        <v>62</v>
+      </c>
+      <c r="L99" s="5">
+        <f t="shared" si="33"/>
+        <v>10511</v>
+      </c>
+      <c r="M99" s="1">
+        <f t="shared" ref="M99:M102" si="36">G99*1200</f>
+        <v>12000</v>
+      </c>
+      <c r="O99" s="1">
+        <v>22010</v>
+      </c>
+      <c r="P99" s="2">
+        <f t="shared" si="34"/>
+        <v>410510</v>
+      </c>
+    </row>
+    <row r="100" customHeight="1" spans="1:16">
+      <c r="A100" s="1">
+        <f t="shared" ref="A100:A109" si="37">10000+G100+B100*100</f>
+        <v>10511</v>
+      </c>
+      <c r="B100" s="1">
+        <v>5</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D100" s="1">
+        <v>2</v>
+      </c>
+      <c r="E100" s="2">
+        <v>47044</v>
+      </c>
+      <c r="F100" s="2">
+        <v>0</v>
+      </c>
+      <c r="G100" s="1">
+        <v>11</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="J100" s="1">
+        <v>4</v>
+      </c>
+      <c r="K100" t="s">
+        <v>65</v>
+      </c>
+      <c r="L100" s="5">
+        <f t="shared" si="33"/>
+        <v>10512</v>
+      </c>
+      <c r="M100" s="1">
+        <f t="shared" si="36"/>
+        <v>13200</v>
+      </c>
+      <c r="O100" s="1">
+        <v>22011</v>
+      </c>
+      <c r="P100" s="2">
+        <f t="shared" ref="P100:P109" si="38">400000+A100</f>
+        <v>410511</v>
+      </c>
+    </row>
+    <row r="101" customHeight="1" spans="1:16">
+      <c r="A101" s="1">
+        <f t="shared" si="37"/>
+        <v>10512</v>
+      </c>
+      <c r="B101" s="1">
+        <v>5</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D101" s="1">
+        <v>2</v>
+      </c>
+      <c r="E101" s="2">
+        <v>47044</v>
+      </c>
+      <c r="F101" s="2">
+        <v>0</v>
+      </c>
+      <c r="G101" s="1">
+        <v>12</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="J101" s="1">
+        <v>4</v>
+      </c>
+      <c r="K101" t="s">
+        <v>68</v>
+      </c>
+      <c r="L101" s="5">
+        <f t="shared" si="33"/>
+        <v>10513</v>
+      </c>
+      <c r="M101" s="1">
+        <f t="shared" si="36"/>
+        <v>14400</v>
+      </c>
+      <c r="O101" s="1">
+        <v>22012</v>
+      </c>
+      <c r="P101" s="2">
+        <f t="shared" si="38"/>
+        <v>410512</v>
+      </c>
+    </row>
+    <row r="102" customHeight="1" spans="1:16">
+      <c r="A102" s="1">
+        <f t="shared" si="37"/>
+        <v>10513</v>
+      </c>
+      <c r="B102" s="1">
+        <v>5</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D102" s="1">
+        <v>2</v>
+      </c>
+      <c r="E102" s="2">
+        <v>47044</v>
+      </c>
+      <c r="F102" s="2">
+        <v>0</v>
+      </c>
+      <c r="G102" s="1">
+        <v>13</v>
+      </c>
+      <c r="I102" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="J102" s="1">
+        <v>4</v>
+      </c>
+      <c r="K102" t="s">
+        <v>71</v>
+      </c>
+      <c r="L102" s="5">
+        <f t="shared" si="33"/>
+        <v>10514</v>
+      </c>
+      <c r="M102" s="1">
+        <f t="shared" si="36"/>
+        <v>15600</v>
+      </c>
+      <c r="O102" s="1">
+        <v>22013</v>
+      </c>
+      <c r="P102" s="2">
+        <f t="shared" si="38"/>
+        <v>410513</v>
+      </c>
+    </row>
+    <row r="103" customHeight="1" spans="1:16">
+      <c r="A103" s="1">
+        <f t="shared" si="37"/>
+        <v>10514</v>
+      </c>
+      <c r="B103" s="1">
+        <v>5</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D103" s="1">
+        <v>2</v>
+      </c>
+      <c r="E103" s="2">
+        <v>47044</v>
+      </c>
+      <c r="F103" s="2">
+        <v>0</v>
+      </c>
+      <c r="G103" s="1">
+        <v>14</v>
+      </c>
+      <c r="I103" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="J103" s="1">
+        <v>4</v>
+      </c>
+      <c r="K103" t="s">
+        <v>74</v>
+      </c>
+      <c r="L103" s="5">
+        <f t="shared" si="33"/>
+        <v>10515</v>
+      </c>
+      <c r="M103" s="1">
+        <f t="shared" ref="M103:M105" si="39">G103*2400</f>
+        <v>33600</v>
+      </c>
+      <c r="O103" s="1">
+        <v>22014</v>
+      </c>
+      <c r="P103" s="2">
+        <f t="shared" si="38"/>
+        <v>410514</v>
+      </c>
+    </row>
+    <row r="104" customHeight="1" spans="1:16">
+      <c r="A104" s="1">
+        <f t="shared" si="37"/>
+        <v>10515</v>
+      </c>
+      <c r="B104" s="1">
+        <v>5</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D104" s="1">
+        <v>2</v>
+      </c>
+      <c r="E104" s="2">
+        <v>47044</v>
+      </c>
+      <c r="F104" s="2">
+        <v>0</v>
+      </c>
+      <c r="G104" s="1">
+        <v>15</v>
+      </c>
+      <c r="I104" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="J104" s="1">
+        <v>4</v>
+      </c>
+      <c r="K104" t="s">
+        <v>77</v>
+      </c>
+      <c r="L104" s="5">
+        <f t="shared" si="33"/>
+        <v>10516</v>
+      </c>
+      <c r="M104" s="1">
+        <f t="shared" si="39"/>
+        <v>36000</v>
+      </c>
+      <c r="O104" s="1">
+        <v>22015</v>
+      </c>
+      <c r="P104" s="2">
+        <f t="shared" si="38"/>
+        <v>410515</v>
+      </c>
+    </row>
+    <row r="105" customHeight="1" spans="1:16">
+      <c r="A105" s="1">
+        <f t="shared" si="37"/>
+        <v>10516</v>
+      </c>
+      <c r="B105" s="1">
+        <v>5</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D105" s="1">
+        <v>2</v>
+      </c>
+      <c r="E105" s="2">
+        <v>47044</v>
+      </c>
+      <c r="F105" s="2">
+        <v>0</v>
+      </c>
+      <c r="G105" s="1">
+        <v>16</v>
+      </c>
+      <c r="I105" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="J105" s="1">
+        <v>4</v>
+      </c>
+      <c r="K105" t="s">
+        <v>80</v>
+      </c>
+      <c r="L105" s="5">
+        <f t="shared" si="33"/>
+        <v>10517</v>
+      </c>
+      <c r="M105" s="1">
+        <f t="shared" si="39"/>
+        <v>38400</v>
+      </c>
+      <c r="O105" s="1">
+        <v>22016</v>
+      </c>
+      <c r="P105" s="2">
+        <f t="shared" si="38"/>
+        <v>410516</v>
+      </c>
+    </row>
+    <row r="106" customHeight="1" spans="1:16">
+      <c r="A106" s="1">
+        <f t="shared" si="37"/>
+        <v>10517</v>
+      </c>
+      <c r="B106" s="1">
+        <v>5</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D106" s="1">
+        <v>2</v>
+      </c>
+      <c r="E106" s="2">
+        <v>47044</v>
+      </c>
+      <c r="F106" s="2">
+        <v>0</v>
+      </c>
+      <c r="G106" s="1">
+        <v>17</v>
+      </c>
+      <c r="I106" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="J106" s="1">
+        <v>4</v>
+      </c>
+      <c r="K106" t="s">
+        <v>83</v>
+      </c>
+      <c r="L106" s="5">
+        <f t="shared" si="33"/>
+        <v>10518</v>
+      </c>
+      <c r="M106" s="1">
+        <f t="shared" ref="M106:M108" si="40">G106*4800</f>
+        <v>81600</v>
+      </c>
+      <c r="O106" s="1">
+        <v>22017</v>
+      </c>
+      <c r="P106" s="2">
+        <f t="shared" si="38"/>
+        <v>410517</v>
+      </c>
+    </row>
+    <row r="107" customHeight="1" spans="1:16">
+      <c r="A107" s="1">
+        <f t="shared" si="37"/>
+        <v>10518</v>
+      </c>
+      <c r="B107" s="1">
+        <v>5</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D107" s="1">
+        <v>2</v>
+      </c>
+      <c r="E107" s="2">
+        <v>47044</v>
+      </c>
+      <c r="F107" s="2">
+        <v>0</v>
+      </c>
+      <c r="G107" s="1">
+        <v>18</v>
+      </c>
+      <c r="I107" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="J107" s="1">
+        <v>4</v>
+      </c>
+      <c r="K107" t="s">
+        <v>86</v>
+      </c>
+      <c r="L107" s="5">
+        <f t="shared" si="33"/>
+        <v>10519</v>
+      </c>
+      <c r="M107" s="1">
+        <f t="shared" si="40"/>
+        <v>86400</v>
+      </c>
+      <c r="O107" s="1">
+        <v>22018</v>
+      </c>
+      <c r="P107" s="2">
+        <f t="shared" si="38"/>
+        <v>410518</v>
+      </c>
+    </row>
+    <row r="108" customHeight="1" spans="1:16">
+      <c r="A108" s="1">
+        <f t="shared" si="37"/>
+        <v>10519</v>
+      </c>
+      <c r="B108" s="1">
+        <v>5</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D108" s="1">
+        <v>2</v>
+      </c>
+      <c r="E108" s="2">
+        <v>47044</v>
+      </c>
+      <c r="F108" s="2">
+        <v>0</v>
+      </c>
+      <c r="G108" s="1">
+        <v>19</v>
+      </c>
+      <c r="I108" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="J108" s="1">
+        <v>4</v>
+      </c>
+      <c r="K108" t="s">
+        <v>89</v>
+      </c>
+      <c r="L108" s="5">
+        <f t="shared" si="33"/>
+        <v>10520</v>
+      </c>
+      <c r="M108" s="1">
+        <f t="shared" si="40"/>
+        <v>91200</v>
+      </c>
+      <c r="O108" s="1">
+        <v>22019</v>
+      </c>
+      <c r="P108" s="2">
+        <f t="shared" si="38"/>
+        <v>410519</v>
+      </c>
+    </row>
+    <row r="109" customHeight="1" spans="1:16">
+      <c r="A109" s="1">
+        <f t="shared" si="37"/>
+        <v>10520</v>
+      </c>
+      <c r="B109" s="1">
+        <v>5</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D109" s="1">
+        <v>2</v>
+      </c>
+      <c r="E109" s="2">
+        <v>47044</v>
+      </c>
+      <c r="F109" s="2">
+        <v>0</v>
+      </c>
+      <c r="G109" s="1">
+        <v>20</v>
+      </c>
+      <c r="J109" s="1">
+        <v>4</v>
+      </c>
+      <c r="K109"/>
+      <c r="O109" s="1">
+        <v>22020</v>
+      </c>
+      <c r="P109" s="2">
+        <f t="shared" si="38"/>
+        <v>410520</v>
+      </c>
+    </row>
+    <row r="110" customHeight="1" spans="1:16">
+      <c r="A110" s="1">
+        <f>10000+G110+B110*100</f>
+        <v>10600</v>
+      </c>
+      <c r="B110" s="1">
+        <v>6</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="D110" s="1">
+        <v>4</v>
+      </c>
+      <c r="E110" s="2">
+        <v>47045</v>
+      </c>
+      <c r="F110" s="2">
+        <v>0</v>
+      </c>
+      <c r="G110" s="1">
+        <v>0</v>
+      </c>
+      <c r="I110" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="J110" s="1">
+        <v>4</v>
+      </c>
+      <c r="K110" t="s">
+        <v>36</v>
+      </c>
+      <c r="L110" s="5">
+        <f t="shared" ref="L110:L129" si="41">A111</f>
+        <v>10601</v>
+      </c>
+      <c r="M110" s="1">
+        <v>100</v>
+      </c>
+      <c r="N110" s="1">
+        <v>0</v>
+      </c>
+      <c r="P110" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" customHeight="1" spans="1:16">
+      <c r="A111" s="1">
+        <f t="shared" ref="A111:A122" si="42">10000+G111+B111*100</f>
+        <v>10601</v>
+      </c>
+      <c r="B111" s="1">
+        <v>6</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="D111" s="1">
+        <v>4</v>
+      </c>
+      <c r="E111" s="2">
+        <v>47045</v>
+      </c>
+      <c r="F111" s="2">
+        <v>0</v>
+      </c>
+      <c r="G111" s="1">
+        <v>1</v>
+      </c>
+      <c r="I111" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="J111" s="1">
+        <v>4</v>
+      </c>
+      <c r="K111" t="s">
+        <v>39</v>
+      </c>
+      <c r="L111" s="5">
+        <f t="shared" si="41"/>
+        <v>10602</v>
+      </c>
+      <c r="M111" s="1">
+        <v>300</v>
+      </c>
+      <c r="O111" s="1">
+        <v>11001</v>
+      </c>
+      <c r="P111" s="2">
+        <f t="shared" ref="P111:P121" si="43">400000+A111</f>
+        <v>410601</v>
+      </c>
+    </row>
+    <row r="112" customHeight="1" spans="1:16">
+      <c r="A112" s="1">
+        <f t="shared" si="42"/>
+        <v>10602</v>
+      </c>
+      <c r="B112" s="1">
+        <v>6</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="D112" s="1">
+        <v>4</v>
+      </c>
+      <c r="E112" s="2">
+        <v>47045</v>
+      </c>
+      <c r="F112" s="2">
+        <v>0</v>
+      </c>
+      <c r="G112" s="1">
+        <v>2</v>
+      </c>
+      <c r="I112" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="J112" s="1">
+        <v>4</v>
+      </c>
+      <c r="K112" t="s">
+        <v>39</v>
+      </c>
+      <c r="L112" s="5">
+        <f t="shared" si="41"/>
+        <v>10603</v>
+      </c>
+      <c r="M112" s="1">
+        <v>600</v>
+      </c>
+      <c r="O112" s="1">
+        <v>11002</v>
+      </c>
+      <c r="P112" s="2">
+        <f t="shared" si="43"/>
+        <v>410602</v>
+      </c>
+    </row>
+    <row r="113" customHeight="1" spans="1:16">
+      <c r="A113" s="1">
+        <f t="shared" si="42"/>
+        <v>10603</v>
+      </c>
+      <c r="B113" s="1">
+        <v>6</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="D113" s="1">
+        <v>4</v>
+      </c>
+      <c r="E113" s="2">
+        <v>47045</v>
+      </c>
+      <c r="F113" s="2">
+        <v>0</v>
+      </c>
+      <c r="G113" s="1">
+        <v>3</v>
+      </c>
+      <c r="I113" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="J113" s="1">
+        <v>4</v>
+      </c>
+      <c r="K113" t="s">
+        <v>39</v>
+      </c>
+      <c r="L113" s="5">
+        <f t="shared" si="41"/>
+        <v>10604</v>
+      </c>
+      <c r="M113" s="1">
+        <v>900</v>
+      </c>
+      <c r="O113" s="1">
+        <v>11003</v>
+      </c>
+      <c r="P113" s="2">
+        <f t="shared" si="43"/>
+        <v>410603</v>
+      </c>
+    </row>
+    <row r="114" customHeight="1" spans="1:16">
+      <c r="A114" s="1">
+        <f t="shared" si="42"/>
+        <v>10604</v>
+      </c>
+      <c r="B114" s="1">
+        <v>6</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="D114" s="1">
+        <v>4</v>
+      </c>
+      <c r="E114" s="2">
+        <v>47045</v>
+      </c>
+      <c r="F114" s="2">
+        <v>0</v>
+      </c>
+      <c r="G114" s="1">
+        <v>4</v>
+      </c>
+      <c r="I114" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="J114" s="1">
+        <v>4</v>
+      </c>
+      <c r="K114" t="s">
+        <v>46</v>
+      </c>
+      <c r="L114" s="5">
+        <f t="shared" si="41"/>
+        <v>10605</v>
+      </c>
+      <c r="M114" s="1">
+        <v>1200</v>
+      </c>
+      <c r="O114" s="1">
+        <v>11004</v>
+      </c>
+      <c r="P114" s="2">
+        <f t="shared" si="43"/>
+        <v>410604</v>
+      </c>
+    </row>
+    <row r="115" customHeight="1" spans="1:16">
+      <c r="A115" s="1">
+        <f t="shared" si="42"/>
+        <v>10605</v>
+      </c>
+      <c r="B115" s="1">
+        <v>6</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="D115" s="1">
+        <v>4</v>
+      </c>
+      <c r="E115" s="2">
+        <v>47045</v>
+      </c>
+      <c r="F115" s="2">
+        <v>0</v>
+      </c>
+      <c r="G115" s="1">
+        <v>5</v>
+      </c>
+      <c r="I115" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="J115" s="1">
+        <v>4</v>
+      </c>
+      <c r="K115" t="s">
+        <v>46</v>
+      </c>
+      <c r="L115" s="5">
+        <f t="shared" si="41"/>
+        <v>10606</v>
+      </c>
+      <c r="M115" s="1">
+        <v>1500</v>
+      </c>
+      <c r="O115" s="1">
+        <v>11005</v>
+      </c>
+      <c r="P115" s="2">
+        <f t="shared" si="43"/>
+        <v>410605</v>
+      </c>
+    </row>
+    <row r="116" customHeight="1" spans="1:16">
+      <c r="A116" s="1">
+        <f t="shared" si="42"/>
+        <v>10606</v>
+      </c>
+      <c r="B116" s="1">
+        <v>6</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="D116" s="1">
+        <v>4</v>
+      </c>
+      <c r="E116" s="2">
+        <v>47045</v>
+      </c>
+      <c r="F116" s="2">
+        <v>0</v>
+      </c>
+      <c r="G116" s="1">
+        <v>6</v>
+      </c>
+      <c r="I116" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="J116" s="1">
+        <v>4</v>
+      </c>
+      <c r="K116" t="s">
+        <v>51</v>
+      </c>
+      <c r="L116" s="5">
+        <f t="shared" si="41"/>
+        <v>10607</v>
+      </c>
+      <c r="M116" s="1">
+        <f t="shared" ref="M116:M119" si="44">G116*600</f>
+        <v>3600</v>
+      </c>
+      <c r="O116" s="1">
+        <v>11006</v>
+      </c>
+      <c r="P116" s="2">
+        <f t="shared" si="43"/>
+        <v>410606</v>
+      </c>
+    </row>
+    <row r="117" customHeight="1" spans="1:16">
+      <c r="A117" s="1">
+        <f t="shared" si="42"/>
+        <v>10607</v>
+      </c>
+      <c r="B117" s="1">
+        <v>6</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="D117" s="1">
+        <v>4</v>
+      </c>
+      <c r="E117" s="2">
+        <v>47045</v>
+      </c>
+      <c r="F117" s="2">
+        <v>0</v>
+      </c>
+      <c r="G117" s="1">
+        <v>7</v>
+      </c>
+      <c r="I117" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="J117" s="1">
+        <v>4</v>
+      </c>
+      <c r="K117" t="s">
+        <v>51</v>
+      </c>
+      <c r="L117" s="5">
+        <f t="shared" si="41"/>
+        <v>10608</v>
+      </c>
+      <c r="M117" s="1">
+        <f t="shared" si="44"/>
+        <v>4200</v>
+      </c>
+      <c r="O117" s="1">
+        <v>11007</v>
+      </c>
+      <c r="P117" s="2">
+        <f t="shared" si="43"/>
+        <v>410607</v>
+      </c>
+    </row>
+    <row r="118" customHeight="1" spans="1:16">
+      <c r="A118" s="1">
+        <f t="shared" si="42"/>
+        <v>10608</v>
+      </c>
+      <c r="B118" s="1">
+        <v>6</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="D118" s="1">
+        <v>4</v>
+      </c>
+      <c r="E118" s="2">
+        <v>47045</v>
+      </c>
+      <c r="F118" s="2">
+        <v>0</v>
+      </c>
+      <c r="G118" s="1">
+        <v>8</v>
+      </c>
+      <c r="I118" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="J118" s="1">
+        <v>4</v>
+      </c>
+      <c r="K118" t="s">
+        <v>56</v>
+      </c>
+      <c r="L118" s="5">
+        <f t="shared" si="41"/>
+        <v>10609</v>
+      </c>
+      <c r="M118" s="1">
+        <f t="shared" si="44"/>
+        <v>4800</v>
+      </c>
+      <c r="O118" s="1">
+        <v>11008</v>
+      </c>
+      <c r="P118" s="2">
+        <f t="shared" si="43"/>
+        <v>410608</v>
+      </c>
+    </row>
+    <row r="119" customHeight="1" spans="1:16">
+      <c r="A119" s="1">
+        <f t="shared" si="42"/>
+        <v>10609</v>
+      </c>
+      <c r="B119" s="1">
+        <v>6</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="D119" s="1">
+        <v>4</v>
+      </c>
+      <c r="E119" s="2">
+        <v>47045</v>
+      </c>
+      <c r="F119" s="2">
+        <v>0</v>
+      </c>
+      <c r="G119" s="1">
+        <v>9</v>
+      </c>
+      <c r="I119" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="J119" s="1">
+        <v>4</v>
+      </c>
+      <c r="K119" t="s">
+        <v>59</v>
+      </c>
+      <c r="L119" s="5">
+        <f t="shared" si="41"/>
+        <v>10610</v>
+      </c>
+      <c r="M119" s="1">
+        <f t="shared" si="44"/>
+        <v>5400</v>
+      </c>
+      <c r="O119" s="1">
+        <v>11009</v>
+      </c>
+      <c r="P119" s="2">
+        <f t="shared" si="43"/>
+        <v>410609</v>
+      </c>
+    </row>
+    <row r="120" customHeight="1" spans="1:16">
+      <c r="A120" s="1">
+        <f t="shared" si="42"/>
+        <v>10610</v>
+      </c>
+      <c r="B120" s="1">
+        <v>6</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="D120" s="1">
+        <v>4</v>
+      </c>
+      <c r="E120" s="2">
+        <v>47045</v>
+      </c>
+      <c r="F120" s="2">
+        <v>0</v>
+      </c>
+      <c r="G120" s="1">
+        <v>10</v>
+      </c>
+      <c r="I120" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="J120" s="1">
+        <v>4</v>
+      </c>
+      <c r="K120" t="s">
+        <v>62</v>
+      </c>
+      <c r="L120" s="5">
+        <f t="shared" si="41"/>
+        <v>10611</v>
+      </c>
+      <c r="M120" s="1">
+        <f t="shared" ref="M120:M123" si="45">G120*1200</f>
+        <v>12000</v>
+      </c>
+      <c r="O120" s="1">
+        <v>11010</v>
+      </c>
+      <c r="P120" s="2">
+        <f t="shared" si="43"/>
+        <v>410610</v>
+      </c>
+    </row>
+    <row r="121" customHeight="1" spans="1:16">
+      <c r="A121" s="1">
+        <f t="shared" ref="A121:A130" si="46">10000+G121+B121*100</f>
+        <v>10611</v>
+      </c>
+      <c r="B121" s="1">
+        <v>6</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="D121" s="1">
+        <v>4</v>
+      </c>
+      <c r="E121" s="2">
+        <v>47045</v>
+      </c>
+      <c r="F121" s="2">
+        <v>0</v>
+      </c>
+      <c r="G121" s="1">
+        <v>11</v>
+      </c>
+      <c r="I121" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="J121" s="1">
+        <v>4</v>
+      </c>
+      <c r="K121" t="s">
+        <v>65</v>
+      </c>
+      <c r="L121" s="5">
+        <f t="shared" si="41"/>
+        <v>10612</v>
+      </c>
+      <c r="M121" s="1">
+        <f t="shared" si="45"/>
+        <v>13200</v>
+      </c>
+      <c r="O121" s="1">
+        <v>11011</v>
+      </c>
+      <c r="P121" s="2">
+        <f t="shared" ref="P121:P130" si="47">400000+A121</f>
+        <v>410611</v>
+      </c>
+    </row>
+    <row r="122" customHeight="1" spans="1:16">
+      <c r="A122" s="1">
+        <f t="shared" si="46"/>
+        <v>10612</v>
+      </c>
+      <c r="B122" s="1">
+        <v>6</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="D122" s="1">
+        <v>4</v>
+      </c>
+      <c r="E122" s="2">
+        <v>47045</v>
+      </c>
+      <c r="F122" s="2">
+        <v>0</v>
+      </c>
+      <c r="G122" s="1">
+        <v>12</v>
+      </c>
+      <c r="I122" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="J122" s="1">
+        <v>4</v>
+      </c>
+      <c r="K122" t="s">
+        <v>68</v>
+      </c>
+      <c r="L122" s="5">
+        <f t="shared" si="41"/>
+        <v>10613</v>
+      </c>
+      <c r="M122" s="1">
+        <f t="shared" si="45"/>
+        <v>14400</v>
+      </c>
+      <c r="O122" s="1">
+        <v>11012</v>
+      </c>
+      <c r="P122" s="2">
+        <f t="shared" si="47"/>
+        <v>410612</v>
+      </c>
+    </row>
+    <row r="123" customHeight="1" spans="1:16">
+      <c r="A123" s="1">
+        <f t="shared" si="46"/>
+        <v>10613</v>
+      </c>
+      <c r="B123" s="1">
+        <v>6</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="D123" s="1">
+        <v>4</v>
+      </c>
+      <c r="E123" s="2">
+        <v>47045</v>
+      </c>
+      <c r="F123" s="2">
+        <v>0</v>
+      </c>
+      <c r="G123" s="1">
+        <v>13</v>
+      </c>
+      <c r="I123" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="J123" s="1">
+        <v>4</v>
+      </c>
+      <c r="K123" t="s">
+        <v>71</v>
+      </c>
+      <c r="L123" s="5">
+        <f t="shared" si="41"/>
+        <v>10614</v>
+      </c>
+      <c r="M123" s="1">
+        <f t="shared" si="45"/>
+        <v>15600</v>
+      </c>
+      <c r="O123" s="1">
+        <v>11013</v>
+      </c>
+      <c r="P123" s="2">
+        <f t="shared" si="47"/>
+        <v>410613</v>
+      </c>
+    </row>
+    <row r="124" customHeight="1" spans="1:16">
+      <c r="A124" s="1">
+        <f t="shared" si="46"/>
+        <v>10614</v>
+      </c>
+      <c r="B124" s="1">
+        <v>6</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="D124" s="1">
+        <v>4</v>
+      </c>
+      <c r="E124" s="2">
+        <v>47045</v>
+      </c>
+      <c r="F124" s="2">
+        <v>0</v>
+      </c>
+      <c r="G124" s="1">
+        <v>14</v>
+      </c>
+      <c r="I124" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="J124" s="1">
+        <v>4</v>
+      </c>
+      <c r="K124" t="s">
+        <v>74</v>
+      </c>
+      <c r="L124" s="5">
+        <f t="shared" si="41"/>
+        <v>10615</v>
+      </c>
+      <c r="M124" s="1">
+        <f t="shared" ref="M124:M126" si="48">G124*2400</f>
+        <v>33600</v>
+      </c>
+      <c r="O124" s="1">
+        <v>11014</v>
+      </c>
+      <c r="P124" s="2">
+        <f t="shared" si="47"/>
+        <v>410614</v>
+      </c>
+    </row>
+    <row r="125" customHeight="1" spans="1:16">
+      <c r="A125" s="1">
+        <f t="shared" si="46"/>
+        <v>10615</v>
+      </c>
+      <c r="B125" s="1">
+        <v>6</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="D125" s="1">
+        <v>4</v>
+      </c>
+      <c r="E125" s="2">
+        <v>47045</v>
+      </c>
+      <c r="F125" s="2">
+        <v>0</v>
+      </c>
+      <c r="G125" s="1">
+        <v>15</v>
+      </c>
+      <c r="I125" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="J125" s="1">
+        <v>4</v>
+      </c>
+      <c r="K125" t="s">
+        <v>77</v>
+      </c>
+      <c r="L125" s="5">
+        <f t="shared" si="41"/>
+        <v>10616</v>
+      </c>
+      <c r="M125" s="1">
+        <f t="shared" si="48"/>
+        <v>36000</v>
+      </c>
+      <c r="O125" s="1">
+        <v>11015</v>
+      </c>
+      <c r="P125" s="2">
+        <f t="shared" si="47"/>
+        <v>410615</v>
+      </c>
+    </row>
+    <row r="126" customHeight="1" spans="1:16">
+      <c r="A126" s="1">
+        <f t="shared" si="46"/>
+        <v>10616</v>
+      </c>
+      <c r="B126" s="1">
+        <v>6</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="D126" s="1">
+        <v>4</v>
+      </c>
+      <c r="E126" s="2">
+        <v>47045</v>
+      </c>
+      <c r="F126" s="2">
+        <v>0</v>
+      </c>
+      <c r="G126" s="1">
+        <v>16</v>
+      </c>
+      <c r="I126" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="J126" s="1">
+        <v>4</v>
+      </c>
+      <c r="K126" t="s">
+        <v>80</v>
+      </c>
+      <c r="L126" s="5">
+        <f t="shared" si="41"/>
+        <v>10617</v>
+      </c>
+      <c r="M126" s="1">
+        <f t="shared" si="48"/>
+        <v>38400</v>
+      </c>
+      <c r="O126" s="1">
+        <v>11016</v>
+      </c>
+      <c r="P126" s="2">
+        <f t="shared" si="47"/>
+        <v>410616</v>
+      </c>
+    </row>
+    <row r="127" customHeight="1" spans="1:16">
+      <c r="A127" s="1">
+        <f t="shared" si="46"/>
+        <v>10617</v>
+      </c>
+      <c r="B127" s="1">
+        <v>6</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="D127" s="1">
+        <v>4</v>
+      </c>
+      <c r="E127" s="2">
+        <v>47045</v>
+      </c>
+      <c r="F127" s="2">
+        <v>0</v>
+      </c>
+      <c r="G127" s="1">
+        <v>17</v>
+      </c>
+      <c r="I127" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="J127" s="1">
+        <v>4</v>
+      </c>
+      <c r="K127" t="s">
+        <v>83</v>
+      </c>
+      <c r="L127" s="5">
+        <f t="shared" si="41"/>
+        <v>10618</v>
+      </c>
+      <c r="M127" s="1">
+        <f t="shared" ref="M127:M129" si="49">G127*4800</f>
+        <v>81600</v>
+      </c>
+      <c r="O127" s="1">
+        <v>11017</v>
+      </c>
+      <c r="P127" s="2">
+        <f t="shared" si="47"/>
+        <v>410617</v>
+      </c>
+    </row>
+    <row r="128" customHeight="1" spans="1:16">
+      <c r="A128" s="1">
+        <f t="shared" si="46"/>
+        <v>10618</v>
+      </c>
+      <c r="B128" s="1">
+        <v>6</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="D128" s="1">
+        <v>4</v>
+      </c>
+      <c r="E128" s="2">
+        <v>47045</v>
+      </c>
+      <c r="F128" s="2">
+        <v>0</v>
+      </c>
+      <c r="G128" s="1">
+        <v>18</v>
+      </c>
+      <c r="I128" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="J128" s="1">
+        <v>4</v>
+      </c>
+      <c r="K128" t="s">
+        <v>86</v>
+      </c>
+      <c r="L128" s="5">
+        <f t="shared" si="41"/>
+        <v>10619</v>
+      </c>
+      <c r="M128" s="1">
+        <f t="shared" si="49"/>
+        <v>86400</v>
+      </c>
+      <c r="O128" s="1">
+        <v>11018</v>
+      </c>
+      <c r="P128" s="2">
+        <f t="shared" si="47"/>
+        <v>410618</v>
+      </c>
+    </row>
+    <row r="129" customHeight="1" spans="1:16">
+      <c r="A129" s="1">
+        <f t="shared" si="46"/>
+        <v>10619</v>
+      </c>
+      <c r="B129" s="1">
+        <v>6</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="D129" s="1">
+        <v>4</v>
+      </c>
+      <c r="E129" s="2">
+        <v>47045</v>
+      </c>
+      <c r="F129" s="2">
+        <v>0</v>
+      </c>
+      <c r="G129" s="1">
+        <v>19</v>
+      </c>
+      <c r="I129" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="J129" s="1">
+        <v>4</v>
+      </c>
+      <c r="K129" t="s">
+        <v>89</v>
+      </c>
+      <c r="L129" s="5">
+        <f t="shared" si="41"/>
+        <v>10620</v>
+      </c>
+      <c r="M129" s="1">
+        <f t="shared" si="49"/>
+        <v>91200</v>
+      </c>
+      <c r="O129" s="1">
+        <v>11019</v>
+      </c>
+      <c r="P129" s="2">
+        <f t="shared" si="47"/>
+        <v>410619</v>
+      </c>
+    </row>
+    <row r="130" customHeight="1" spans="1:16">
+      <c r="A130" s="1">
+        <f t="shared" si="46"/>
+        <v>10620</v>
+      </c>
+      <c r="B130" s="1">
+        <v>6</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="D130" s="1">
+        <v>4</v>
+      </c>
+      <c r="E130" s="2">
+        <v>47045</v>
+      </c>
+      <c r="F130" s="2">
+        <v>0</v>
+      </c>
+      <c r="G130" s="1">
+        <v>20</v>
+      </c>
+      <c r="J130" s="1">
+        <v>4</v>
+      </c>
+      <c r="K130"/>
+      <c r="O130" s="1">
+        <v>11020</v>
+      </c>
+      <c r="P130" s="2">
+        <f t="shared" si="47"/>
+        <v>410620</v>
+      </c>
+    </row>
+    <row r="131" customHeight="1" spans="1:16">
+      <c r="A131" s="1">
+        <f>10000+G131+B131*100</f>
+        <v>10700</v>
+      </c>
+      <c r="B131" s="1">
+        <v>7</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="D131" s="1">
+        <v>4</v>
+      </c>
+      <c r="E131" s="2">
+        <f>300000+A131</f>
+        <v>310700</v>
+      </c>
+      <c r="F131" s="2">
+        <v>0</v>
+      </c>
+      <c r="G131" s="1">
+        <v>0</v>
+      </c>
+      <c r="J131" s="1">
+        <v>4</v>
+      </c>
+      <c r="L131" s="5">
+        <f>A132</f>
         <v>10701</v>
       </c>
-      <c r="B72" s="1">
+      <c r="M131" s="1">
+        <v>100</v>
+      </c>
+      <c r="N131" s="1">
+        <v>0</v>
+      </c>
+      <c r="P131" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" customHeight="1" spans="1:16">
+      <c r="A132" s="1">
+        <f>10000+G132+B132*100</f>
+        <v>10701</v>
+      </c>
+      <c r="B132" s="1">
         <v>7</v>
       </c>
-      <c r="C72" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="D72" s="1">
-        <v>4</v>
-      </c>
-      <c r="E72" s="2">
-        <f>300000+A72</f>
+      <c r="C132" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="D132" s="1">
+        <v>4</v>
+      </c>
+      <c r="E132" s="2">
+        <f>300000+A132</f>
         <v>310701</v>
       </c>
-      <c r="F72" s="2">
-        <v>0</v>
-      </c>
-      <c r="G72" s="1">
-        <v>1</v>
-      </c>
-      <c r="J72" s="1">
-        <v>4</v>
-      </c>
-      <c r="M72" s="1">
-        <v>0</v>
-      </c>
-      <c r="P72" s="2">
-        <f>400000+A72</f>
+      <c r="F132" s="2">
+        <v>0</v>
+      </c>
+      <c r="G132" s="1">
+        <v>1</v>
+      </c>
+      <c r="J132" s="1">
+        <v>4</v>
+      </c>
+      <c r="M132" s="1">
+        <v>0</v>
+      </c>
+      <c r="P132" s="2">
+        <f>400000+A132</f>
         <v>410701</v>
       </c>
     </row>

--- a/hall/resources/sample/BuildingFunction.xlsx
+++ b/hall/resources/sample/BuildingFunction.xlsx
@@ -131,7 +131,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="221">
   <si>
     <t>id</t>
   </si>
@@ -238,7 +238,7 @@
     <t>slot机台</t>
   </si>
   <si>
-    <t>1023001_2</t>
+    <t>1023001_4</t>
   </si>
   <si>
     <t>1_1</t>
@@ -247,7 +247,7 @@
     <t>5_1990000_20</t>
   </si>
   <si>
-    <t>1023001_4</t>
+    <t>1023001_8</t>
   </si>
   <si>
     <t>1_10</t>
@@ -256,19 +256,19 @@
     <t>5_1990000_30</t>
   </si>
   <si>
-    <t>1023001_8</t>
+    <t>1023001_16</t>
   </si>
   <si>
     <t>5_1990000_40</t>
   </si>
   <si>
-    <t>1023001_12</t>
+    <t>1023001_24</t>
   </si>
   <si>
     <t>5_1990000_50</t>
   </si>
   <si>
-    <t>1023001_16</t>
+    <t>1023001_32</t>
   </si>
   <si>
     <t>1_20</t>
@@ -277,13 +277,13 @@
     <t>5_1990000_60</t>
   </si>
   <si>
-    <t>1023001_20;1980000_10</t>
+    <t>1023001_40;1980000_10</t>
   </si>
   <si>
     <t>5_1990000_70</t>
   </si>
   <si>
-    <t>1023002_4</t>
+    <t>1023002_8</t>
   </si>
   <si>
     <t>1_30</t>
@@ -292,13 +292,13 @@
     <t>5_1990000_80</t>
   </si>
   <si>
-    <t>1023002_8</t>
+    <t>1023002_16</t>
   </si>
   <si>
     <t>5_1990000_90</t>
   </si>
   <si>
-    <t>1023002_16</t>
+    <t>1023002_32</t>
   </si>
   <si>
     <t>1_40</t>
@@ -307,7 +307,7 @@
     <t>5_1990000_110</t>
   </si>
   <si>
-    <t>1023002_24;1980000_100</t>
+    <t>1023002_48;1980000_100</t>
   </si>
   <si>
     <t>1_50</t>
@@ -316,7 +316,7 @@
     <t>5_1990000_130</t>
   </si>
   <si>
-    <t>1023003_4</t>
+    <t>1023003_8</t>
   </si>
   <si>
     <t>1_60</t>
@@ -325,7 +325,7 @@
     <t>5_1990000_150</t>
   </si>
   <si>
-    <t>1023003_8</t>
+    <t>1023003_16</t>
   </si>
   <si>
     <t>1_70</t>
@@ -334,7 +334,7 @@
     <t>5_1990000_190</t>
   </si>
   <si>
-    <t>1023003_16</t>
+    <t>1023003_32</t>
   </si>
   <si>
     <t>1_80</t>
@@ -343,7 +343,7 @@
     <t>5_1990000_230</t>
   </si>
   <si>
-    <t>1023003_24;1980000_300</t>
+    <t>1023003_48;1980000_300</t>
   </si>
   <si>
     <t>1_90</t>
@@ -352,7 +352,7 @@
     <t>5_1990000_270</t>
   </si>
   <si>
-    <t>1023004_6</t>
+    <t>1023004_12</t>
   </si>
   <si>
     <t>1_100</t>
@@ -361,7 +361,7 @@
     <t>5_1990000_330</t>
   </si>
   <si>
-    <t>1023004_12</t>
+    <t>1023004_24</t>
   </si>
   <si>
     <t>1_110</t>
@@ -370,7 +370,7 @@
     <t>5_1990000_390</t>
   </si>
   <si>
-    <t>1023004_24;1980000_600</t>
+    <t>1023004_48;1980000_600</t>
   </si>
   <si>
     <t>1_120</t>
@@ -379,7 +379,7 @@
     <t>5_1990000_450</t>
   </si>
   <si>
-    <t>1023005_6</t>
+    <t>1023005_12</t>
   </si>
   <si>
     <t>1_130</t>
@@ -388,7 +388,7 @@
     <t>5_1990000_530</t>
   </si>
   <si>
-    <t>1023005_12</t>
+    <t>1023005_24</t>
   </si>
   <si>
     <t>1_140</t>
@@ -397,7 +397,7 @@
     <t>5_1990000_610</t>
   </si>
   <si>
-    <t>1023005_24</t>
+    <t>1023005_48</t>
   </si>
   <si>
     <t>1_150</t>
@@ -436,69 +436,99 @@
     <t>5_1990000_140</t>
   </si>
   <si>
+    <t>1023102_4</t>
+  </si>
+  <si>
     <t>5_1990000_160</t>
   </si>
   <si>
+    <t>1023102_8</t>
+  </si>
+  <si>
     <t>5_1990000_180</t>
   </si>
   <si>
+    <t>1023102_16</t>
+  </si>
+  <si>
     <t>5_1990000_220</t>
   </si>
   <si>
-    <t>1023101_24;1980000_100</t>
+    <t>1023102_24;1980000_100</t>
   </si>
   <si>
     <t>5_1990000_260</t>
   </si>
   <si>
+    <t>1023103_4</t>
+  </si>
+  <si>
     <t>5_1990000_300</t>
   </si>
   <si>
+    <t>1023103_8</t>
+  </si>
+  <si>
     <t>5_1990000_380</t>
   </si>
   <si>
+    <t>1023103_16</t>
+  </si>
+  <si>
     <t>5_1990000_460</t>
   </si>
   <si>
-    <t>1023101_24;1980000_300</t>
+    <t>1023103_24;1980000_300</t>
   </si>
   <si>
     <t>5_1990000_540</t>
   </si>
   <si>
+    <t>1023104_6</t>
+  </si>
+  <si>
+    <t>5_1990000_660</t>
+  </si>
+  <si>
+    <t>1023104_12</t>
+  </si>
+  <si>
+    <t>5_1990000_780</t>
+  </si>
+  <si>
+    <t>1023104_24;1980000_600</t>
+  </si>
+  <si>
+    <t>5_1990000_900</t>
+  </si>
+  <si>
+    <t>1023105_6</t>
+  </si>
+  <si>
+    <t>5_1990000_1060</t>
+  </si>
+  <si>
+    <t>1023105_12</t>
+  </si>
+  <si>
+    <t>5_1990000_1220</t>
+  </si>
+  <si>
+    <t>1023105_24</t>
+  </si>
+  <si>
+    <t>5_1990000_1380</t>
+  </si>
+  <si>
+    <t>幸运转盘</t>
+  </si>
+  <si>
+    <t>1023101_1</t>
+  </si>
+  <si>
     <t>1023101_6</t>
   </si>
   <si>
-    <t>5_1990000_660</t>
-  </si>
-  <si>
-    <t>5_1990000_780</t>
-  </si>
-  <si>
-    <t>1023101_24;1980000_600</t>
-  </si>
-  <si>
-    <t>5_1990000_900</t>
-  </si>
-  <si>
-    <t>5_1990000_1060</t>
-  </si>
-  <si>
-    <t>5_1990000_1220</t>
-  </si>
-  <si>
-    <t>1023101_24</t>
-  </si>
-  <si>
-    <t>5_1990000_1380</t>
-  </si>
-  <si>
-    <t>幸运转盘</t>
-  </si>
-  <si>
-    <t>1023101_1</t>
-  </si>
-  <si>
     <t>5_1990000_200</t>
   </si>
   <si>
@@ -511,6 +541,9 @@
     <t>5_1990000_280</t>
   </si>
   <si>
+    <t>1023102_2</t>
+  </si>
+  <si>
     <t>5_1990000_320</t>
   </si>
   <si>
@@ -520,12 +553,15 @@
     <t>5_1990000_440</t>
   </si>
   <si>
-    <t>1023101_12;1980000_100</t>
+    <t>1023102_12;1980000_100</t>
   </si>
   <si>
     <t>5_1990000_520</t>
   </si>
   <si>
+    <t>1023103_2</t>
+  </si>
+  <si>
     <t>5_1990000_600</t>
   </si>
   <si>
@@ -535,13 +571,13 @@
     <t>5_1990000_920</t>
   </si>
   <si>
-    <t>1023101_12;1980000_300</t>
+    <t>1023103_12;1980000_300</t>
   </si>
   <si>
     <t>5_1990000_1080</t>
   </si>
   <si>
-    <t>1023101_3</t>
+    <t>1023104_3</t>
   </si>
   <si>
     <t>5_1990000_1320</t>
@@ -550,12 +586,15 @@
     <t>5_1990000_1560</t>
   </si>
   <si>
-    <t>1023101_12;1980000_600</t>
+    <t>1023104_12;1980000_600</t>
   </si>
   <si>
     <t>5_1990000_1800</t>
   </si>
   <si>
+    <t>1023105_3</t>
+  </si>
+  <si>
     <t>5_1990000_2120</t>
   </si>
   <si>
@@ -568,190 +607,190 @@
     <t>吧台区</t>
   </si>
   <si>
-    <t>1023401_1</t>
-  </si>
-  <si>
-    <t>1023401_2</t>
-  </si>
-  <si>
     <t>1023401_4</t>
   </si>
   <si>
-    <t>1023401_6</t>
-  </si>
-  <si>
     <t>1023401_8</t>
   </si>
   <si>
-    <t>1023401_10;1980000_10</t>
-  </si>
-  <si>
-    <t>1023402_2</t>
-  </si>
-  <si>
-    <t>1023402_4</t>
+    <t>1023401_16</t>
+  </si>
+  <si>
+    <t>1023401_24</t>
+  </si>
+  <si>
+    <t>1023401_32</t>
+  </si>
+  <si>
+    <t>1023401_40;1980000_10</t>
   </si>
   <si>
     <t>1023402_8</t>
   </si>
   <si>
-    <t>1023402_12;1980000_100</t>
-  </si>
-  <si>
-    <t>1023403_2</t>
-  </si>
-  <si>
-    <t>1023403_4</t>
+    <t>1023402_16</t>
+  </si>
+  <si>
+    <t>1023402_32</t>
+  </si>
+  <si>
+    <t>1023402_48;1980000_100</t>
   </si>
   <si>
     <t>1023403_8</t>
   </si>
   <si>
-    <t>1023403_12;1980000_300</t>
-  </si>
-  <si>
-    <t>1023404_3</t>
-  </si>
-  <si>
-    <t>1023404_6</t>
-  </si>
-  <si>
-    <t>1023404_12;1980000_600</t>
-  </si>
-  <si>
-    <t>1023405_3</t>
-  </si>
-  <si>
-    <t>1023405_6</t>
+    <t>1023403_16</t>
+  </si>
+  <si>
+    <t>1023403_32</t>
+  </si>
+  <si>
+    <t>1023403_48;1980000_300</t>
+  </si>
+  <si>
+    <t>1023404_12</t>
+  </si>
+  <si>
+    <t>1023404_24</t>
+  </si>
+  <si>
+    <t>1023404_48;1980000_600</t>
   </si>
   <si>
     <t>1023405_12</t>
   </si>
   <si>
+    <t>1023405_24</t>
+  </si>
+  <si>
+    <t>1023405_48</t>
+  </si>
+  <si>
     <t>休息区</t>
   </si>
   <si>
-    <t>1023301_1</t>
-  </si>
-  <si>
-    <t>1023301_2</t>
-  </si>
-  <si>
-    <t>1023301_4</t>
-  </si>
-  <si>
-    <t>1023301_6</t>
-  </si>
-  <si>
     <t>1023301_8</t>
   </si>
   <si>
-    <t>1023301_10;1980000_10</t>
-  </si>
-  <si>
-    <t>1023302_2</t>
-  </si>
-  <si>
-    <t>1023302_4</t>
-  </si>
-  <si>
-    <t>1023302_8</t>
-  </si>
-  <si>
-    <t>1023302_12;1980000_100</t>
-  </si>
-  <si>
-    <t>1023303_2</t>
-  </si>
-  <si>
-    <t>1023303_4</t>
-  </si>
-  <si>
-    <t>1023303_8</t>
-  </si>
-  <si>
-    <t>1023303_12;1980000_300</t>
-  </si>
-  <si>
-    <t>1023304_3</t>
-  </si>
-  <si>
-    <t>1023304_6</t>
-  </si>
-  <si>
-    <t>1023304_12;1980000_600</t>
-  </si>
-  <si>
-    <t>1023305_3</t>
-  </si>
-  <si>
-    <t>1023305_6</t>
-  </si>
-  <si>
-    <t>1023305_12</t>
+    <t>1023301_16</t>
+  </si>
+  <si>
+    <t>1023301_32</t>
+  </si>
+  <si>
+    <t>1023301_48</t>
+  </si>
+  <si>
+    <t>1023301_64</t>
+  </si>
+  <si>
+    <t>1023301_80;1980000_10</t>
+  </si>
+  <si>
+    <t>1023302_16</t>
+  </si>
+  <si>
+    <t>1023302_32</t>
+  </si>
+  <si>
+    <t>1023302_64</t>
+  </si>
+  <si>
+    <t>1023302_96;1980000_100</t>
+  </si>
+  <si>
+    <t>1023303_16</t>
+  </si>
+  <si>
+    <t>1023303_32</t>
+  </si>
+  <si>
+    <t>1023303_64</t>
+  </si>
+  <si>
+    <t>1023303_96;1980000_300</t>
+  </si>
+  <si>
+    <t>1023304_24</t>
+  </si>
+  <si>
+    <t>1023304_48</t>
+  </si>
+  <si>
+    <t>1023304_96;1980000_600</t>
+  </si>
+  <si>
+    <t>1023305_24</t>
+  </si>
+  <si>
+    <t>1023305_48</t>
+  </si>
+  <si>
+    <t>1023305_96</t>
   </si>
   <si>
     <t>提款机</t>
   </si>
   <si>
-    <t>1023201_1</t>
-  </si>
-  <si>
-    <t>1023201_2</t>
-  </si>
-  <si>
-    <t>1023201_4</t>
-  </si>
-  <si>
     <t>1023201_6</t>
   </si>
   <si>
-    <t>1023201_8</t>
-  </si>
-  <si>
-    <t>1023201_10;1980000_10</t>
-  </si>
-  <si>
-    <t>1023202_2</t>
-  </si>
-  <si>
-    <t>1023202_4</t>
-  </si>
-  <si>
-    <t>1023202_8</t>
-  </si>
-  <si>
-    <t>1023202_12;1980000_100</t>
-  </si>
-  <si>
-    <t>1023203_2</t>
-  </si>
-  <si>
-    <t>1023203_4</t>
-  </si>
-  <si>
-    <t>1023203_8</t>
-  </si>
-  <si>
-    <t>1023203_12;1980000_300</t>
-  </si>
-  <si>
-    <t>1023204_3</t>
-  </si>
-  <si>
-    <t>1023204_6</t>
-  </si>
-  <si>
-    <t>1023204_12;1980000_600</t>
-  </si>
-  <si>
-    <t>1023205_3</t>
-  </si>
-  <si>
-    <t>1023205_6</t>
-  </si>
-  <si>
-    <t>1023205_12</t>
+    <t>1023201_12</t>
+  </si>
+  <si>
+    <t>1023201_24</t>
+  </si>
+  <si>
+    <t>1023201_36</t>
+  </si>
+  <si>
+    <t>1023201_48</t>
+  </si>
+  <si>
+    <t>1023201_60;1980000_10</t>
+  </si>
+  <si>
+    <t>1023202_12</t>
+  </si>
+  <si>
+    <t>1023202_24</t>
+  </si>
+  <si>
+    <t>1023202_48</t>
+  </si>
+  <si>
+    <t>1023202_72;1980000_100</t>
+  </si>
+  <si>
+    <t>1023203_12</t>
+  </si>
+  <si>
+    <t>1023203_24</t>
+  </si>
+  <si>
+    <t>1023203_48</t>
+  </si>
+  <si>
+    <t>1023203_72;1980000_300</t>
+  </si>
+  <si>
+    <t>1023204_18</t>
+  </si>
+  <si>
+    <t>1023204_36</t>
+  </si>
+  <si>
+    <t>1023204_72;1980000_600</t>
+  </si>
+  <si>
+    <t>1023205_18</t>
+  </si>
+  <si>
+    <t>1023205_36</t>
+  </si>
+  <si>
+    <t>1023205_72</t>
   </si>
   <si>
     <t>停机坪</t>
@@ -926,12 +965,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1914,7 +1953,7 @@
     </row>
     <row r="5" customHeight="1" spans="1:16">
       <c r="A5" s="1">
-        <f t="shared" ref="A5:A10" si="0">10000+G5+B5*100</f>
+        <f t="shared" ref="A5:A15" si="0">10000+G5+B5*100</f>
         <v>10100</v>
       </c>
       <c r="B5" s="1">
@@ -2211,7 +2250,7 @@
     </row>
     <row r="11" customHeight="1" spans="1:16">
       <c r="A11" s="1">
-        <f>10000+G11+B11*100</f>
+        <f t="shared" si="0"/>
         <v>10106</v>
       </c>
       <c r="B11" s="1">
@@ -2262,7 +2301,7 @@
     </row>
     <row r="12" customHeight="1" spans="1:16">
       <c r="A12" s="1">
-        <f>10000+G12+B12*100</f>
+        <f t="shared" si="0"/>
         <v>10107</v>
       </c>
       <c r="B12" s="1">
@@ -2313,7 +2352,7 @@
     </row>
     <row r="13" customHeight="1" spans="1:16">
       <c r="A13" s="1">
-        <f>10000+G13+B13*100</f>
+        <f t="shared" si="0"/>
         <v>10108</v>
       </c>
       <c r="B13" s="1">
@@ -2364,7 +2403,7 @@
     </row>
     <row r="14" customHeight="1" spans="1:16">
       <c r="A14" s="1">
-        <f>10000+G14+B14*100</f>
+        <f t="shared" si="0"/>
         <v>10109</v>
       </c>
       <c r="B14" s="1">
@@ -2415,7 +2454,7 @@
     </row>
     <row r="15" customHeight="1" spans="1:16">
       <c r="A15" s="1">
-        <f>10000+G15+B15*100</f>
+        <f t="shared" si="0"/>
         <v>10110</v>
       </c>
       <c r="B15" s="1">
@@ -2949,7 +2988,6 @@
       <c r="H25" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="I25" s="3"/>
       <c r="J25" s="1">
         <v>4</v>
       </c>
@@ -2964,7 +3002,7 @@
     </row>
     <row r="26" customHeight="1" spans="1:16">
       <c r="A26" s="1">
-        <f t="shared" ref="A26:A31" si="6">10000+G26+B26*100</f>
+        <f t="shared" ref="A26:A36" si="6">10000+G26+B26*100</f>
         <v>10200</v>
       </c>
       <c r="B26" s="1">
@@ -3261,7 +3299,7 @@
     </row>
     <row r="32" customHeight="1" spans="1:16">
       <c r="A32" s="1">
-        <f>10000+G32+B32*100</f>
+        <f t="shared" si="6"/>
         <v>10206</v>
       </c>
       <c r="B32" s="1">
@@ -3286,7 +3324,7 @@
         <v>100</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="J32" s="1">
         <v>4</v>
@@ -3312,7 +3350,7 @@
     </row>
     <row r="33" customHeight="1" spans="1:16">
       <c r="A33" s="1">
-        <f>10000+G33+B33*100</f>
+        <f t="shared" si="6"/>
         <v>10207</v>
       </c>
       <c r="B33" s="1">
@@ -3334,10 +3372,10 @@
         <v>7</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="J33" s="1">
         <v>4</v>
@@ -3363,7 +3401,7 @@
     </row>
     <row r="34" customHeight="1" spans="1:16">
       <c r="A34" s="1">
-        <f>10000+G34+B34*100</f>
+        <f t="shared" si="6"/>
         <v>10208</v>
       </c>
       <c r="B34" s="1">
@@ -3385,10 +3423,10 @@
         <v>8</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="J34" s="1">
         <v>4</v>
@@ -3414,7 +3452,7 @@
     </row>
     <row r="35" customHeight="1" spans="1:16">
       <c r="A35" s="1">
-        <f>10000+G35+B35*100</f>
+        <f t="shared" si="6"/>
         <v>10209</v>
       </c>
       <c r="B35" s="1">
@@ -3436,10 +3474,10 @@
         <v>9</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="J35" s="1">
         <v>4</v>
@@ -3465,7 +3503,7 @@
     </row>
     <row r="36" customHeight="1" spans="1:16">
       <c r="A36" s="1">
-        <f>10000+G36+B36*100</f>
+        <f t="shared" si="6"/>
         <v>10210</v>
       </c>
       <c r="B36" s="1">
@@ -3487,10 +3525,10 @@
         <v>10</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="J36" s="1">
         <v>4</v>
@@ -3516,7 +3554,7 @@
     </row>
     <row r="37" customHeight="1" spans="1:16">
       <c r="A37" s="1">
-        <f t="shared" ref="A37:A46" si="11">10000+G37+B37*100</f>
+        <f t="shared" ref="A37:A47" si="11">10000+G37+B37*100</f>
         <v>10211</v>
       </c>
       <c r="B37" s="1">
@@ -3538,10 +3576,10 @@
         <v>11</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="J37" s="1">
         <v>4</v>
@@ -3589,10 +3627,10 @@
         <v>12</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="J38" s="1">
         <v>4</v>
@@ -3640,10 +3678,10 @@
         <v>13</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="J39" s="1">
         <v>4</v>
@@ -3691,10 +3729,10 @@
         <v>14</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="J40" s="1">
         <v>4</v>
@@ -3742,10 +3780,10 @@
         <v>15</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>95</v>
+        <v>119</v>
       </c>
       <c r="J41" s="1">
         <v>4</v>
@@ -3793,10 +3831,10 @@
         <v>16</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="J42" s="1">
         <v>4</v>
@@ -3844,10 +3882,10 @@
         <v>17</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="J43" s="1">
         <v>4</v>
@@ -3895,10 +3933,10 @@
         <v>18</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>95</v>
+        <v>125</v>
       </c>
       <c r="J44" s="1">
         <v>4</v>
@@ -3946,10 +3984,10 @@
         <v>19</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="J45" s="1">
         <v>4</v>
@@ -3997,9 +4035,8 @@
         <v>20</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="I46" s="3"/>
+        <v>128</v>
+      </c>
       <c r="J46" s="1">
         <v>4</v>
       </c>
@@ -4014,14 +4051,14 @@
     </row>
     <row r="47" customHeight="1" spans="1:16">
       <c r="A47" s="1">
-        <f>10000+G47+B47*100</f>
+        <f t="shared" si="11"/>
         <v>10300</v>
       </c>
       <c r="B47" s="1">
         <v>3</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="D47" s="1">
         <v>4</v>
@@ -4037,7 +4074,7 @@
       </c>
       <c r="H47" s="2"/>
       <c r="I47" s="3" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="J47" s="1">
         <v>4</v>
@@ -4068,7 +4105,7 @@
         <v>3</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="D48" s="1">
         <v>4</v>
@@ -4118,7 +4155,7 @@
         <v>3</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="D49" s="1">
         <v>4</v>
@@ -4168,7 +4205,7 @@
         <v>3</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="D50" s="1">
         <v>4</v>
@@ -4183,10 +4220,10 @@
         <v>3</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="J50" s="1">
         <v>4</v>
@@ -4218,7 +4255,7 @@
         <v>3</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="D51" s="1">
         <v>4</v>
@@ -4233,7 +4270,7 @@
         <v>4</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="I51" s="3" t="s">
         <v>94</v>
@@ -4268,7 +4305,7 @@
         <v>3</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="D52" s="1">
         <v>4</v>
@@ -4283,10 +4320,10 @@
         <v>5</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="J52" s="1">
         <v>4</v>
@@ -4318,7 +4355,7 @@
         <v>3</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="D53" s="1">
         <v>4</v>
@@ -4333,10 +4370,10 @@
         <v>6</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>92</v>
+        <v>136</v>
       </c>
       <c r="J53" s="1">
         <v>4</v>
@@ -4369,7 +4406,7 @@
         <v>3</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="D54" s="1">
         <v>4</v>
@@ -4384,10 +4421,10 @@
         <v>7</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="J54" s="1">
         <v>4</v>
@@ -4420,7 +4457,7 @@
         <v>3</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="D55" s="1">
         <v>4</v>
@@ -4435,10 +4472,10 @@
         <v>8</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="J55" s="1">
         <v>4</v>
@@ -4471,7 +4508,7 @@
         <v>3</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="D56" s="1">
         <v>4</v>
@@ -4486,10 +4523,10 @@
         <v>9</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="J56" s="1">
         <v>4</v>
@@ -4522,7 +4559,7 @@
         <v>3</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="D57" s="1">
         <v>4</v>
@@ -4537,10 +4574,10 @@
         <v>10</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>92</v>
+        <v>142</v>
       </c>
       <c r="J57" s="1">
         <v>4</v>
@@ -4566,14 +4603,14 @@
     </row>
     <row r="58" customHeight="1" spans="1:16">
       <c r="A58" s="1">
-        <f t="shared" ref="A58:A67" si="20">10000+G58+B58*100</f>
+        <f t="shared" ref="A58:A78" si="20">10000+G58+B58*100</f>
         <v>10311</v>
       </c>
       <c r="B58" s="1">
         <v>3</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="D58" s="1">
         <v>4</v>
@@ -4588,10 +4625,10 @@
         <v>11</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="J58" s="1">
         <v>4</v>
@@ -4624,7 +4661,7 @@
         <v>3</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="D59" s="1">
         <v>4</v>
@@ -4639,10 +4676,10 @@
         <v>12</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="J59" s="1">
         <v>4</v>
@@ -4675,7 +4712,7 @@
         <v>3</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="D60" s="1">
         <v>4</v>
@@ -4690,10 +4727,10 @@
         <v>13</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="J60" s="1">
         <v>4</v>
@@ -4726,7 +4763,7 @@
         <v>3</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="D61" s="1">
         <v>4</v>
@@ -4741,10 +4778,10 @@
         <v>14</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="J61" s="1">
         <v>4</v>
@@ -4777,7 +4814,7 @@
         <v>3</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="D62" s="1">
         <v>4</v>
@@ -4792,10 +4829,10 @@
         <v>15</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="J62" s="1">
         <v>4</v>
@@ -4828,7 +4865,7 @@
         <v>3</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="D63" s="1">
         <v>4</v>
@@ -4843,10 +4880,10 @@
         <v>16</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="J63" s="1">
         <v>4</v>
@@ -4879,7 +4916,7 @@
         <v>3</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="D64" s="1">
         <v>4</v>
@@ -4894,10 +4931,10 @@
         <v>17</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>136</v>
+        <v>153</v>
       </c>
       <c r="J64" s="1">
         <v>4</v>
@@ -4930,7 +4967,7 @@
         <v>3</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="D65" s="1">
         <v>4</v>
@@ -4945,10 +4982,10 @@
         <v>18</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="J65" s="1">
         <v>4</v>
@@ -4981,7 +5018,7 @@
         <v>3</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="D66" s="1">
         <v>4</v>
@@ -4996,10 +5033,10 @@
         <v>19</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>95</v>
+        <v>125</v>
       </c>
       <c r="J66" s="1">
         <v>4</v>
@@ -5032,7 +5069,7 @@
         <v>3</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="D67" s="1">
         <v>4</v>
@@ -5047,9 +5084,8 @@
         <v>20</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="I67" s="3"/>
+        <v>156</v>
+      </c>
       <c r="J67" s="1">
         <v>4</v>
       </c>
@@ -5064,14 +5100,14 @@
     </row>
     <row r="68" customHeight="1" spans="1:16">
       <c r="A68" s="1">
-        <f>10000+G68+B68*100</f>
+        <f t="shared" si="20"/>
         <v>10400</v>
       </c>
       <c r="B68" s="1">
         <v>4</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="D68" s="1">
         <v>2</v>
@@ -5086,7 +5122,7 @@
         <v>0</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
       <c r="J68" s="1"/>
       <c r="K68" t="s">
@@ -5108,14 +5144,14 @@
     </row>
     <row r="69" customHeight="1" spans="1:16">
       <c r="A69" s="1">
-        <f>10000+G69+B69*100</f>
+        <f t="shared" si="20"/>
         <v>10401</v>
       </c>
       <c r="B69" s="1">
         <v>4</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="D69" s="1">
         <v>2</v>
@@ -5130,7 +5166,7 @@
         <v>1</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>146</v>
+        <v>159</v>
       </c>
       <c r="J69" s="1"/>
       <c r="K69" t="s">
@@ -5150,14 +5186,14 @@
     </row>
     <row r="70" customHeight="1" spans="1:16">
       <c r="A70" s="1">
-        <f>10000+G70+B70*100</f>
+        <f t="shared" si="20"/>
         <v>10402</v>
       </c>
       <c r="B70" s="1">
         <v>4</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="D70" s="1">
         <v>2</v>
@@ -5172,7 +5208,7 @@
         <v>2</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="J70" s="1"/>
       <c r="K70" t="s">
@@ -5192,14 +5228,14 @@
     </row>
     <row r="71" customHeight="1" spans="1:16">
       <c r="A71" s="1">
-        <f>10000+G71+B71*100</f>
+        <f t="shared" si="20"/>
         <v>10403</v>
       </c>
       <c r="B71" s="1">
         <v>4</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="D71" s="1">
         <v>2</v>
@@ -5214,7 +5250,7 @@
         <v>3</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="J71" s="1"/>
       <c r="K71" t="s">
@@ -5234,14 +5270,14 @@
     </row>
     <row r="72" customHeight="1" spans="1:16">
       <c r="A72" s="1">
-        <f>10000+G72+B72*100</f>
+        <f t="shared" si="20"/>
         <v>10404</v>
       </c>
       <c r="B72" s="1">
         <v>4</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="D72" s="1">
         <v>2</v>
@@ -5256,7 +5292,7 @@
         <v>4</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="J72" s="1"/>
       <c r="K72" t="s">
@@ -5276,14 +5312,14 @@
     </row>
     <row r="73" customHeight="1" spans="1:16">
       <c r="A73" s="1">
-        <f>10000+G73+B73*100</f>
+        <f t="shared" si="20"/>
         <v>10405</v>
       </c>
       <c r="B73" s="1">
         <v>4</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="D73" s="1">
         <v>2</v>
@@ -5298,7 +5334,7 @@
         <v>5</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="J73" s="1"/>
       <c r="K73" t="s">
@@ -5318,14 +5354,14 @@
     </row>
     <row r="74" customHeight="1" spans="1:16">
       <c r="A74" s="1">
-        <f>10000+G74+B74*100</f>
+        <f t="shared" si="20"/>
         <v>10406</v>
       </c>
       <c r="B74" s="1">
         <v>4</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="D74" s="1">
         <v>2</v>
@@ -5340,7 +5376,7 @@
         <v>6</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="J74" s="1"/>
       <c r="K74" t="s">
@@ -5361,14 +5397,14 @@
     </row>
     <row r="75" customHeight="1" spans="1:16">
       <c r="A75" s="1">
-        <f>10000+G75+B75*100</f>
+        <f t="shared" si="20"/>
         <v>10407</v>
       </c>
       <c r="B75" s="1">
         <v>4</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="D75" s="1">
         <v>2</v>
@@ -5383,7 +5419,7 @@
         <v>7</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="J75" s="1"/>
       <c r="K75" t="s">
@@ -5404,14 +5440,14 @@
     </row>
     <row r="76" customHeight="1" spans="1:16">
       <c r="A76" s="1">
-        <f>10000+G76+B76*100</f>
+        <f t="shared" si="20"/>
         <v>10408</v>
       </c>
       <c r="B76" s="1">
         <v>4</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="D76" s="1">
         <v>2</v>
@@ -5426,7 +5462,7 @@
         <v>8</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="J76" s="1"/>
       <c r="K76" t="s">
@@ -5447,14 +5483,14 @@
     </row>
     <row r="77" customHeight="1" spans="1:16">
       <c r="A77" s="1">
-        <f>10000+G77+B77*100</f>
+        <f t="shared" si="20"/>
         <v>10409</v>
       </c>
       <c r="B77" s="1">
         <v>4</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="D77" s="1">
         <v>2</v>
@@ -5469,7 +5505,7 @@
         <v>9</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="J77" s="1"/>
       <c r="K77" t="s">
@@ -5490,14 +5526,14 @@
     </row>
     <row r="78" customHeight="1" spans="1:16">
       <c r="A78" s="1">
-        <f>10000+G78+B78*100</f>
+        <f t="shared" si="20"/>
         <v>10410</v>
       </c>
       <c r="B78" s="1">
         <v>4</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="D78" s="1">
         <v>2</v>
@@ -5512,7 +5548,7 @@
         <v>10</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="J78" s="1"/>
       <c r="K78" t="s">
@@ -5540,7 +5576,7 @@
         <v>4</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="D79" s="1">
         <v>2</v>
@@ -5555,7 +5591,7 @@
         <v>11</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="J79" s="1"/>
       <c r="K79" t="s">
@@ -5583,7 +5619,7 @@
         <v>4</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="D80" s="1">
         <v>2</v>
@@ -5598,7 +5634,7 @@
         <v>12</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="J80" s="1"/>
       <c r="K80" t="s">
@@ -5626,7 +5662,7 @@
         <v>4</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="D81" s="1">
         <v>2</v>
@@ -5641,7 +5677,7 @@
         <v>13</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="J81" s="1"/>
       <c r="K81" t="s">
@@ -5669,7 +5705,7 @@
         <v>4</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="D82" s="1">
         <v>2</v>
@@ -5684,7 +5720,7 @@
         <v>14</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="J82" s="1"/>
       <c r="K82" t="s">
@@ -5712,7 +5748,7 @@
         <v>4</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="D83" s="1">
         <v>2</v>
@@ -5727,7 +5763,7 @@
         <v>15</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="J83" s="1"/>
       <c r="K83" t="s">
@@ -5755,7 +5791,7 @@
         <v>4</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="D84" s="1">
         <v>2</v>
@@ -5770,7 +5806,7 @@
         <v>16</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="J84" s="1"/>
       <c r="K84" t="s">
@@ -5798,7 +5834,7 @@
         <v>4</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="D85" s="1">
         <v>2</v>
@@ -5813,7 +5849,7 @@
         <v>17</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="J85" s="1"/>
       <c r="K85" t="s">
@@ -5841,7 +5877,7 @@
         <v>4</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="D86" s="1">
         <v>2</v>
@@ -5856,7 +5892,7 @@
         <v>18</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="J86" s="1"/>
       <c r="K86" t="s">
@@ -5884,7 +5920,7 @@
         <v>4</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="D87" s="1">
         <v>2</v>
@@ -5899,7 +5935,7 @@
         <v>19</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="J87" s="1"/>
       <c r="K87" t="s">
@@ -5927,7 +5963,7 @@
         <v>4</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="D88" s="1">
         <v>2</v>
@@ -5950,14 +5986,14 @@
     </row>
     <row r="89" customHeight="1" spans="1:16">
       <c r="A89" s="1">
-        <f t="shared" ref="A89:A94" si="32">10000+G89+B89*100</f>
+        <f t="shared" ref="A89:A99" si="32">10000+G89+B89*100</f>
         <v>10500</v>
       </c>
       <c r="B89" s="1">
         <v>5</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="D89" s="1">
         <v>2</v>
@@ -5972,7 +6008,7 @@
         <v>0</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="J89" s="1">
         <v>4</v>
@@ -6003,7 +6039,7 @@
         <v>5</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="D90" s="1">
         <v>2</v>
@@ -6018,7 +6054,7 @@
         <v>1</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="J90" s="1">
         <v>4</v>
@@ -6050,7 +6086,7 @@
         <v>5</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="D91" s="1">
         <v>2</v>
@@ -6065,7 +6101,7 @@
         <v>2</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="J91" s="1">
         <v>4</v>
@@ -6097,7 +6133,7 @@
         <v>5</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="D92" s="1">
         <v>2</v>
@@ -6112,7 +6148,7 @@
         <v>3</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="J92" s="1">
         <v>4</v>
@@ -6144,7 +6180,7 @@
         <v>5</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="D93" s="1">
         <v>2</v>
@@ -6159,7 +6195,7 @@
         <v>4</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="J93" s="1">
         <v>4</v>
@@ -6191,7 +6227,7 @@
         <v>5</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="D94" s="1">
         <v>2</v>
@@ -6206,7 +6242,7 @@
         <v>5</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="J94" s="1">
         <v>4</v>
@@ -6231,14 +6267,14 @@
     </row>
     <row r="95" customHeight="1" spans="1:16">
       <c r="A95" s="1">
-        <f>10000+G95+B95*100</f>
+        <f t="shared" si="32"/>
         <v>10506</v>
       </c>
       <c r="B95" s="1">
         <v>5</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="D95" s="1">
         <v>2</v>
@@ -6253,7 +6289,7 @@
         <v>6</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="J95" s="1">
         <v>4</v>
@@ -6279,14 +6315,14 @@
     </row>
     <row r="96" customHeight="1" spans="1:16">
       <c r="A96" s="1">
-        <f>10000+G96+B96*100</f>
+        <f t="shared" si="32"/>
         <v>10507</v>
       </c>
       <c r="B96" s="1">
         <v>5</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="D96" s="1">
         <v>2</v>
@@ -6301,7 +6337,7 @@
         <v>7</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="J96" s="1">
         <v>4</v>
@@ -6327,14 +6363,14 @@
     </row>
     <row r="97" customHeight="1" spans="1:16">
       <c r="A97" s="1">
-        <f>10000+G97+B97*100</f>
+        <f t="shared" si="32"/>
         <v>10508</v>
       </c>
       <c r="B97" s="1">
         <v>5</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="D97" s="1">
         <v>2</v>
@@ -6349,7 +6385,7 @@
         <v>8</v>
       </c>
       <c r="I97" s="3" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="J97" s="1">
         <v>4</v>
@@ -6375,14 +6411,14 @@
     </row>
     <row r="98" customHeight="1" spans="1:16">
       <c r="A98" s="1">
-        <f>10000+G98+B98*100</f>
+        <f t="shared" si="32"/>
         <v>10509</v>
       </c>
       <c r="B98" s="1">
         <v>5</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="D98" s="1">
         <v>2</v>
@@ -6397,7 +6433,7 @@
         <v>9</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="J98" s="1">
         <v>4</v>
@@ -6423,14 +6459,14 @@
     </row>
     <row r="99" customHeight="1" spans="1:16">
       <c r="A99" s="1">
-        <f>10000+G99+B99*100</f>
+        <f t="shared" si="32"/>
         <v>10510</v>
       </c>
       <c r="B99" s="1">
         <v>5</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="D99" s="1">
         <v>2</v>
@@ -6445,7 +6481,7 @@
         <v>10</v>
       </c>
       <c r="I99" s="3" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="J99" s="1">
         <v>4</v>
@@ -6471,14 +6507,14 @@
     </row>
     <row r="100" customHeight="1" spans="1:16">
       <c r="A100" s="1">
-        <f t="shared" ref="A100:A109" si="37">10000+G100+B100*100</f>
+        <f t="shared" ref="A100:A110" si="37">10000+G100+B100*100</f>
         <v>10511</v>
       </c>
       <c r="B100" s="1">
         <v>5</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="D100" s="1">
         <v>2</v>
@@ -6493,7 +6529,7 @@
         <v>11</v>
       </c>
       <c r="I100" s="3" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="J100" s="1">
         <v>4</v>
@@ -6526,7 +6562,7 @@
         <v>5</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="D101" s="1">
         <v>2</v>
@@ -6541,7 +6577,7 @@
         <v>12</v>
       </c>
       <c r="I101" s="3" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="J101" s="1">
         <v>4</v>
@@ -6574,7 +6610,7 @@
         <v>5</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="D102" s="1">
         <v>2</v>
@@ -6589,7 +6625,7 @@
         <v>13</v>
       </c>
       <c r="I102" s="3" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="J102" s="1">
         <v>4</v>
@@ -6622,7 +6658,7 @@
         <v>5</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="D103" s="1">
         <v>2</v>
@@ -6637,7 +6673,7 @@
         <v>14</v>
       </c>
       <c r="I103" s="3" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="J103" s="1">
         <v>4</v>
@@ -6670,7 +6706,7 @@
         <v>5</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="D104" s="1">
         <v>2</v>
@@ -6685,7 +6721,7 @@
         <v>15</v>
       </c>
       <c r="I104" s="3" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="J104" s="1">
         <v>4</v>
@@ -6718,7 +6754,7 @@
         <v>5</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="D105" s="1">
         <v>2</v>
@@ -6733,7 +6769,7 @@
         <v>16</v>
       </c>
       <c r="I105" s="3" t="s">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="J105" s="1">
         <v>4</v>
@@ -6766,7 +6802,7 @@
         <v>5</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="D106" s="1">
         <v>2</v>
@@ -6781,7 +6817,7 @@
         <v>17</v>
       </c>
       <c r="I106" s="3" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="J106" s="1">
         <v>4</v>
@@ -6814,7 +6850,7 @@
         <v>5</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="D107" s="1">
         <v>2</v>
@@ -6829,7 +6865,7 @@
         <v>18</v>
       </c>
       <c r="I107" s="3" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="J107" s="1">
         <v>4</v>
@@ -6862,7 +6898,7 @@
         <v>5</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="D108" s="1">
         <v>2</v>
@@ -6877,7 +6913,7 @@
         <v>19</v>
       </c>
       <c r="I108" s="3" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="J108" s="1">
         <v>4</v>
@@ -6910,7 +6946,7 @@
         <v>5</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="D109" s="1">
         <v>2</v>
@@ -6938,14 +6974,14 @@
     </row>
     <row r="110" customHeight="1" spans="1:16">
       <c r="A110" s="1">
-        <f>10000+G110+B110*100</f>
+        <f t="shared" si="37"/>
         <v>10600</v>
       </c>
       <c r="B110" s="1">
         <v>6</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="D110" s="1">
         <v>4</v>
@@ -6960,7 +6996,7 @@
         <v>0</v>
       </c>
       <c r="I110" s="3" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="J110" s="1">
         <v>4</v>
@@ -6991,7 +7027,7 @@
         <v>6</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="D111" s="1">
         <v>4</v>
@@ -7006,7 +7042,7 @@
         <v>1</v>
       </c>
       <c r="I111" s="3" t="s">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="J111" s="1">
         <v>4</v>
@@ -7038,7 +7074,7 @@
         <v>6</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="D112" s="1">
         <v>4</v>
@@ -7053,7 +7089,7 @@
         <v>2</v>
       </c>
       <c r="I112" s="3" t="s">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="J112" s="1">
         <v>4</v>
@@ -7085,7 +7121,7 @@
         <v>6</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="D113" s="1">
         <v>4</v>
@@ -7100,7 +7136,7 @@
         <v>3</v>
       </c>
       <c r="I113" s="3" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="J113" s="1">
         <v>4</v>
@@ -7132,7 +7168,7 @@
         <v>6</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="D114" s="1">
         <v>4</v>
@@ -7147,7 +7183,7 @@
         <v>4</v>
       </c>
       <c r="I114" s="3" t="s">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="J114" s="1">
         <v>4</v>
@@ -7179,7 +7215,7 @@
         <v>6</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="D115" s="1">
         <v>4</v>
@@ -7194,7 +7230,7 @@
         <v>5</v>
       </c>
       <c r="I115" s="3" t="s">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="J115" s="1">
         <v>4</v>
@@ -7226,7 +7262,7 @@
         <v>6</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="D116" s="1">
         <v>4</v>
@@ -7241,7 +7277,7 @@
         <v>6</v>
       </c>
       <c r="I116" s="3" t="s">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="J116" s="1">
         <v>4</v>
@@ -7274,7 +7310,7 @@
         <v>6</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="D117" s="1">
         <v>4</v>
@@ -7289,7 +7325,7 @@
         <v>7</v>
       </c>
       <c r="I117" s="3" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="J117" s="1">
         <v>4</v>
@@ -7322,7 +7358,7 @@
         <v>6</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="D118" s="1">
         <v>4</v>
@@ -7337,7 +7373,7 @@
         <v>8</v>
       </c>
       <c r="I118" s="3" t="s">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="J118" s="1">
         <v>4</v>
@@ -7370,7 +7406,7 @@
         <v>6</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="D119" s="1">
         <v>4</v>
@@ -7385,7 +7421,7 @@
         <v>9</v>
       </c>
       <c r="I119" s="3" t="s">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="J119" s="1">
         <v>4</v>
@@ -7418,7 +7454,7 @@
         <v>6</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="D120" s="1">
         <v>4</v>
@@ -7433,7 +7469,7 @@
         <v>10</v>
       </c>
       <c r="I120" s="3" t="s">
-        <v>197</v>
+        <v>210</v>
       </c>
       <c r="J120" s="1">
         <v>4</v>
@@ -7459,14 +7495,14 @@
     </row>
     <row r="121" customHeight="1" spans="1:16">
       <c r="A121" s="1">
-        <f t="shared" ref="A121:A130" si="46">10000+G121+B121*100</f>
+        <f t="shared" ref="A121:A132" si="46">10000+G121+B121*100</f>
         <v>10611</v>
       </c>
       <c r="B121" s="1">
         <v>6</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="D121" s="1">
         <v>4</v>
@@ -7481,7 +7517,7 @@
         <v>11</v>
       </c>
       <c r="I121" s="3" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="J121" s="1">
         <v>4</v>
@@ -7514,7 +7550,7 @@
         <v>6</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="D122" s="1">
         <v>4</v>
@@ -7529,7 +7565,7 @@
         <v>12</v>
       </c>
       <c r="I122" s="3" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="J122" s="1">
         <v>4</v>
@@ -7562,7 +7598,7 @@
         <v>6</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="D123" s="1">
         <v>4</v>
@@ -7577,7 +7613,7 @@
         <v>13</v>
       </c>
       <c r="I123" s="3" t="s">
-        <v>200</v>
+        <v>213</v>
       </c>
       <c r="J123" s="1">
         <v>4</v>
@@ -7610,7 +7646,7 @@
         <v>6</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="D124" s="1">
         <v>4</v>
@@ -7625,7 +7661,7 @@
         <v>14</v>
       </c>
       <c r="I124" s="3" t="s">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="J124" s="1">
         <v>4</v>
@@ -7658,7 +7694,7 @@
         <v>6</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="D125" s="1">
         <v>4</v>
@@ -7673,7 +7709,7 @@
         <v>15</v>
       </c>
       <c r="I125" s="3" t="s">
-        <v>202</v>
+        <v>215</v>
       </c>
       <c r="J125" s="1">
         <v>4</v>
@@ -7706,7 +7742,7 @@
         <v>6</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="D126" s="1">
         <v>4</v>
@@ -7721,7 +7757,7 @@
         <v>16</v>
       </c>
       <c r="I126" s="3" t="s">
-        <v>203</v>
+        <v>216</v>
       </c>
       <c r="J126" s="1">
         <v>4</v>
@@ -7754,7 +7790,7 @@
         <v>6</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="D127" s="1">
         <v>4</v>
@@ -7769,7 +7805,7 @@
         <v>17</v>
       </c>
       <c r="I127" s="3" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="J127" s="1">
         <v>4</v>
@@ -7802,7 +7838,7 @@
         <v>6</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="D128" s="1">
         <v>4</v>
@@ -7817,7 +7853,7 @@
         <v>18</v>
       </c>
       <c r="I128" s="3" t="s">
-        <v>205</v>
+        <v>218</v>
       </c>
       <c r="J128" s="1">
         <v>4</v>
@@ -7850,7 +7886,7 @@
         <v>6</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="D129" s="1">
         <v>4</v>
@@ -7865,7 +7901,7 @@
         <v>19</v>
       </c>
       <c r="I129" s="3" t="s">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="J129" s="1">
         <v>4</v>
@@ -7898,7 +7934,7 @@
         <v>6</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="D130" s="1">
         <v>4</v>
@@ -7926,14 +7962,14 @@
     </row>
     <row r="131" customHeight="1" spans="1:16">
       <c r="A131" s="1">
-        <f>10000+G131+B131*100</f>
+        <f t="shared" si="46"/>
         <v>10700</v>
       </c>
       <c r="B131" s="1">
         <v>7</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>207</v>
+        <v>220</v>
       </c>
       <c r="D131" s="1">
         <v>4</v>
@@ -7967,14 +8003,14 @@
     </row>
     <row r="132" customHeight="1" spans="1:16">
       <c r="A132" s="1">
-        <f>10000+G132+B132*100</f>
+        <f t="shared" si="46"/>
         <v>10701</v>
       </c>
       <c r="B132" s="1">
         <v>7</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>207</v>
+        <v>220</v>
       </c>
       <c r="D132" s="1">
         <v>4</v>

--- a/hall/resources/sample/BuildingFunction.xlsx
+++ b/hall/resources/sample/BuildingFunction.xlsx
@@ -154,7 +154,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="597" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="597" uniqueCount="306">
   <si>
     <t>id</t>
   </si>
@@ -267,7 +267,7 @@
     <t>1_1</t>
   </si>
   <si>
-    <t>5_1990000_20</t>
+    <t>5_1990000_60</t>
   </si>
   <si>
     <t>1023001_8</t>
@@ -276,19 +276,19 @@
     <t>1_10</t>
   </si>
   <si>
-    <t>5_1990000_30</t>
+    <t>5_1990000_140</t>
   </si>
   <si>
     <t>1023001_16</t>
   </si>
   <si>
-    <t>5_1990000_40</t>
+    <t>5_1990000_220</t>
   </si>
   <si>
     <t>1023001_24</t>
   </si>
   <si>
-    <t>5_1990000_50</t>
+    <t>5_1990000_310</t>
   </si>
   <si>
     <t>1023001_32</t>
@@ -297,124 +297,136 @@
     <t>1_20</t>
   </si>
   <si>
-    <t>5_1990000_60</t>
+    <t>5_1990000_390</t>
+  </si>
+  <si>
+    <t>1023001_40</t>
+  </si>
+  <si>
+    <t>5_1990000_510</t>
+  </si>
+  <si>
+    <t>1023001_10</t>
+  </si>
+  <si>
+    <t>1_30</t>
+  </si>
+  <si>
+    <t>5_1990000_630</t>
+  </si>
+  <si>
+    <t>1023001_20</t>
+  </si>
+  <si>
+    <t>5_1990000_740</t>
   </si>
   <si>
     <t>1023001_40|1980000_10</t>
   </si>
   <si>
-    <t>5_1990000_70</t>
-  </si>
-  <si>
-    <t>1023001_12</t>
-  </si>
-  <si>
-    <t>1_30</t>
-  </si>
-  <si>
-    <t>5_1990000_80</t>
-  </si>
-  <si>
-    <t>5_1990000_90</t>
+    <t>1_40</t>
+  </si>
+  <si>
+    <t>5_1990000_910</t>
+  </si>
+  <si>
+    <t>1023001_58</t>
+  </si>
+  <si>
+    <t>1_50</t>
+  </si>
+  <si>
+    <t>5_1990000_1070</t>
+  </si>
+  <si>
+    <t>1023001_14</t>
+  </si>
+  <si>
+    <t>1_60</t>
+  </si>
+  <si>
+    <t>5_1990000_1240</t>
+  </si>
+  <si>
+    <t>1023001_26|1980000_10</t>
+  </si>
+  <si>
+    <t>1_70</t>
+  </si>
+  <si>
+    <t>5_1990000_1470</t>
+  </si>
+  <si>
+    <t>1023001_52</t>
+  </si>
+  <si>
+    <t>1_80</t>
+  </si>
+  <si>
+    <t>5_1990000_1700</t>
+  </si>
+  <si>
+    <t>1023001_78</t>
+  </si>
+  <si>
+    <t>1_90</t>
+  </si>
+  <si>
+    <t>5_1990000_1930</t>
+  </si>
+  <si>
+    <t>1023001_24|1980000_30</t>
+  </si>
+  <si>
+    <t>1_100</t>
+  </si>
+  <si>
+    <t>5_1990000_2250</t>
   </si>
   <si>
     <t>1023001_48</t>
   </si>
   <si>
-    <t>1_40</t>
-  </si>
-  <si>
-    <t>5_1990000_110</t>
-  </si>
-  <si>
-    <t>1023001_72|1980000_100</t>
-  </si>
-  <si>
-    <t>1_50</t>
-  </si>
-  <si>
-    <t>5_1990000_130</t>
-  </si>
-  <si>
-    <t>1_60</t>
-  </si>
-  <si>
-    <t>5_1990000_150</t>
-  </si>
-  <si>
-    <t>1_70</t>
-  </si>
-  <si>
-    <t>5_1990000_190</t>
-  </si>
-  <si>
-    <t>1023001_64</t>
-  </si>
-  <si>
-    <t>1_80</t>
-  </si>
-  <si>
-    <t>5_1990000_230</t>
-  </si>
-  <si>
-    <t>1023001_96|1980000_300</t>
-  </si>
-  <si>
-    <t>1_90</t>
-  </si>
-  <si>
-    <t>5_1990000_270</t>
-  </si>
-  <si>
-    <t>1023001_36</t>
-  </si>
-  <si>
-    <t>1_100</t>
-  </si>
-  <si>
-    <t>5_1990000_330</t>
+    <t>1_110</t>
+  </si>
+  <si>
+    <t>5_1990000_2570</t>
+  </si>
+  <si>
+    <t>1023001_96</t>
+  </si>
+  <si>
+    <t>1_120</t>
+  </si>
+  <si>
+    <t>5_1990000_2900</t>
+  </si>
+  <si>
+    <t>1023001_36|1980000_70</t>
+  </si>
+  <si>
+    <t>1_130</t>
+  </si>
+  <si>
+    <t>5_1990000_3350</t>
   </si>
   <si>
     <t>1023001_72</t>
   </si>
   <si>
-    <t>1_110</t>
-  </si>
-  <si>
-    <t>5_1990000_390</t>
-  </si>
-  <si>
-    <t>1023001_144|1980000_600</t>
-  </si>
-  <si>
-    <t>1_120</t>
-  </si>
-  <si>
-    <t>5_1990000_450</t>
-  </si>
-  <si>
-    <t>1_130</t>
-  </si>
-  <si>
-    <t>5_1990000_530</t>
-  </si>
-  <si>
-    <t>1023001_144</t>
-  </si>
-  <si>
     <t>1_140</t>
   </si>
   <si>
-    <t>5_1990000_610</t>
-  </si>
-  <si>
-    <t>1023001_288</t>
+    <t>5_1990000_3800</t>
+  </si>
+  <si>
+    <t>1023001_142</t>
   </si>
   <si>
     <t>1_150</t>
   </si>
   <si>
-    <t>5_1990000_690</t>
+    <t>5_1990000_4250</t>
   </si>
   <si>
     <t>扑克牌桌</t>
@@ -423,424 +435,484 @@
     <t>1023101_2</t>
   </si>
   <si>
+    <t>5_1990000_120</t>
+  </si>
+  <si>
     <t>1023101_4</t>
   </si>
   <si>
+    <t>5_1990000_280</t>
+  </si>
+  <si>
     <t>1023101_8</t>
   </si>
   <si>
+    <t>5_1990000_440</t>
+  </si>
+  <si>
     <t>1023101_12</t>
   </si>
   <si>
-    <t>5_1990000_100</t>
+    <t>5_1990000_620</t>
   </si>
   <si>
     <t>1023101_16</t>
   </si>
   <si>
-    <t>5_1990000_120</t>
+    <t>5_1990000_780</t>
+  </si>
+  <si>
+    <t>1023101_20</t>
+  </si>
+  <si>
+    <t>5_1990000_1020</t>
+  </si>
+  <si>
+    <t>1023101_6</t>
+  </si>
+  <si>
+    <t>5_1990000_1260</t>
+  </si>
+  <si>
+    <t>1023101_10</t>
+  </si>
+  <si>
+    <t>5_1990000_1480</t>
   </si>
   <si>
     <t>1023101_20|1980000_10</t>
   </si>
   <si>
-    <t>5_1990000_140</t>
-  </si>
-  <si>
-    <t>1023101_6</t>
-  </si>
-  <si>
-    <t>5_1990000_160</t>
-  </si>
-  <si>
-    <t>5_1990000_180</t>
+    <t>5_1990000_1820</t>
+  </si>
+  <si>
+    <t>1023101_30</t>
+  </si>
+  <si>
+    <t>5_1990000_2140</t>
+  </si>
+  <si>
+    <t>5_1990000_2480</t>
+  </si>
+  <si>
+    <t>1023101_14|1980000_20</t>
+  </si>
+  <si>
+    <t>5_1990000_2940</t>
+  </si>
+  <si>
+    <t>1023101_26</t>
+  </si>
+  <si>
+    <t>5_1990000_3400</t>
+  </si>
+  <si>
+    <t>1023101_40</t>
+  </si>
+  <si>
+    <t>5_1990000_3860</t>
+  </si>
+  <si>
+    <t>1023101_12|1980000_60</t>
+  </si>
+  <si>
+    <t>5_1990000_4500</t>
   </si>
   <si>
     <t>1023101_24</t>
   </si>
   <si>
-    <t>5_1990000_220</t>
-  </si>
-  <si>
-    <t>1023101_36|1980000_100</t>
-  </si>
-  <si>
-    <t>5_1990000_260</t>
-  </si>
-  <si>
-    <t>5_1990000_300</t>
-  </si>
-  <si>
-    <t>5_1990000_380</t>
-  </si>
-  <si>
-    <t>1023101_32</t>
-  </si>
-  <si>
-    <t>5_1990000_460</t>
-  </si>
-  <si>
-    <t>1023101_48|1980000_300</t>
-  </si>
-  <si>
-    <t>5_1990000_540</t>
+    <t>5_1990000_5140</t>
+  </si>
+  <si>
+    <t>1023101_48</t>
+  </si>
+  <si>
+    <t>5_1990000_5800</t>
+  </si>
+  <si>
+    <t>1023101_18|1980000_140</t>
+  </si>
+  <si>
+    <t>5_1990000_6700</t>
+  </si>
+  <si>
+    <t>1023101_36</t>
+  </si>
+  <si>
+    <t>5_1990000_7600</t>
+  </si>
+  <si>
+    <t>1023101_72</t>
+  </si>
+  <si>
+    <t>5_1990000_8500</t>
+  </si>
+  <si>
+    <t>幸运转盘</t>
+  </si>
+  <si>
+    <t>5_1990000_240</t>
+  </si>
+  <si>
+    <t>5_1990000_560</t>
+  </si>
+  <si>
+    <t>5_1990000_880</t>
+  </si>
+  <si>
+    <t>5_1990000_1560</t>
+  </si>
+  <si>
+    <t>5_1990000_2040</t>
+  </si>
+  <si>
+    <t>5_1990000_2520</t>
+  </si>
+  <si>
+    <t>5_1990000_2960</t>
+  </si>
+  <si>
+    <t>1023101_10|1980000_10</t>
+  </si>
+  <si>
+    <t>5_1990000_3640</t>
+  </si>
+  <si>
+    <t>5_1990000_4280</t>
+  </si>
+  <si>
+    <t>5_1990000_4960</t>
+  </si>
+  <si>
+    <t>1023101_8|1980000_30</t>
+  </si>
+  <si>
+    <t>5_1990000_5880</t>
+  </si>
+  <si>
+    <t>1023101_14</t>
+  </si>
+  <si>
+    <t>5_1990000_6800</t>
+  </si>
+  <si>
+    <t>5_1990000_7720</t>
+  </si>
+  <si>
+    <t>1023101_6|1980000_120</t>
+  </si>
+  <si>
+    <t>5_1990000_9000</t>
+  </si>
+  <si>
+    <t>5_1990000_10280</t>
+  </si>
+  <si>
+    <t>5_1990000_11600</t>
+  </si>
+  <si>
+    <t>1023101_10|1980000_280</t>
+  </si>
+  <si>
+    <t>5_1990000_13400</t>
   </si>
   <si>
     <t>1023101_18</t>
   </si>
   <si>
-    <t>5_1990000_660</t>
-  </si>
-  <si>
-    <t>1023101_36</t>
-  </si>
-  <si>
-    <t>5_1990000_780</t>
-  </si>
-  <si>
-    <t>1023101_72|1980000_600</t>
-  </si>
-  <si>
-    <t>5_1990000_900</t>
-  </si>
-  <si>
-    <t>5_1990000_1060</t>
-  </si>
-  <si>
-    <t>1023101_72</t>
-  </si>
-  <si>
-    <t>5_1990000_1220</t>
-  </si>
-  <si>
-    <t>1023101_144</t>
-  </si>
-  <si>
-    <t>5_1990000_1380</t>
-  </si>
-  <si>
-    <t>幸运转盘</t>
+    <t>5_1990000_15200</t>
+  </si>
+  <si>
+    <t>5_1990000_17000</t>
+  </si>
+  <si>
+    <t>吧台区</t>
+  </si>
+  <si>
+    <t>1023401_4</t>
+  </si>
+  <si>
+    <t>1023401_8</t>
+  </si>
+  <si>
+    <t>1023401_16</t>
+  </si>
+  <si>
+    <t>1023401_24</t>
+  </si>
+  <si>
+    <t>1023401_32</t>
+  </si>
+  <si>
+    <t>1023401_40</t>
+  </si>
+  <si>
+    <t>1023401_10</t>
+  </si>
+  <si>
+    <t>1023401_20</t>
+  </si>
+  <si>
+    <t>1023401_40|1980000_10</t>
+  </si>
+  <si>
+    <t>1023401_58</t>
+  </si>
+  <si>
+    <t>1023401_14</t>
+  </si>
+  <si>
+    <t>1023401_26|1980000_170</t>
+  </si>
+  <si>
+    <t>1023401_52</t>
+  </si>
+  <si>
+    <t>1023401_78</t>
+  </si>
+  <si>
+    <t>1023401_24|1980000_690</t>
+  </si>
+  <si>
+    <t>1023401_48</t>
+  </si>
+  <si>
+    <t>1023401_96</t>
+  </si>
+  <si>
+    <t>1023401_36|1980000_1680</t>
+  </si>
+  <si>
+    <t>1023401_72</t>
+  </si>
+  <si>
+    <t>1023401_142</t>
+  </si>
+  <si>
+    <t>休息区</t>
+  </si>
+  <si>
+    <t>1023301_8</t>
+  </si>
+  <si>
+    <t>1023301_16</t>
+  </si>
+  <si>
+    <t>1023301_32</t>
+  </si>
+  <si>
+    <t>1023301_48</t>
+  </si>
+  <si>
+    <t>1023301_64</t>
+  </si>
+  <si>
+    <t>1023301_80</t>
+  </si>
+  <si>
+    <t>1023301_20</t>
+  </si>
+  <si>
+    <t>1023301_40</t>
+  </si>
+  <si>
+    <t>1023301_78|1980000_10</t>
+  </si>
+  <si>
+    <t>1023301_116</t>
+  </si>
+  <si>
+    <t>1023301_26</t>
+  </si>
+  <si>
+    <t>1023301_52|1980000_170</t>
+  </si>
+  <si>
+    <t>1023301_102</t>
+  </si>
+  <si>
+    <t>1023301_154</t>
+  </si>
+  <si>
+    <t>1023301_48|1980000_690</t>
+  </si>
+  <si>
+    <t>1023301_96</t>
+  </si>
+  <si>
+    <t>1023301_190</t>
+  </si>
+  <si>
+    <t>1023301_72|1980000_1680</t>
+  </si>
+  <si>
+    <t>1023301_142</t>
+  </si>
+  <si>
+    <t>1023301_284</t>
+  </si>
+  <si>
+    <t>提款机</t>
+  </si>
+  <si>
+    <t>1023201_6</t>
+  </si>
+  <si>
+    <t>1023201_12</t>
+  </si>
+  <si>
+    <t>1023201_24</t>
+  </si>
+  <si>
+    <t>1023201_36</t>
+  </si>
+  <si>
+    <t>1023201_48</t>
+  </si>
+  <si>
+    <t>1023201_60</t>
+  </si>
+  <si>
+    <t>1023201_16</t>
+  </si>
+  <si>
+    <t>1023201_30</t>
+  </si>
+  <si>
+    <t>1023201_58|1980000_10</t>
+  </si>
+  <si>
+    <t>1023201_86</t>
+  </si>
+  <si>
+    <t>1023201_20</t>
+  </si>
+  <si>
+    <t>1023201_40|1980000_90</t>
+  </si>
+  <si>
+    <t>1023201_78</t>
+  </si>
+  <si>
+    <t>1023201_116</t>
+  </si>
+  <si>
+    <t>1023201_36|1980000_350</t>
+  </si>
+  <si>
+    <t>1023201_72</t>
+  </si>
+  <si>
+    <t>1023201_142</t>
+  </si>
+  <si>
+    <t>1023201_54|1980000_840</t>
+  </si>
+  <si>
+    <t>1023201_108</t>
+  </si>
+  <si>
+    <t>1023201_214</t>
+  </si>
+  <si>
+    <t>停机坪</t>
+  </si>
+  <si>
+    <t>map&lt;int{_}long&gt;{;}</t>
+  </si>
+  <si>
+    <t>1023001_40;1980000_10</t>
+  </si>
+  <si>
+    <t>1023002_8</t>
+  </si>
+  <si>
+    <t>1023002_16</t>
+  </si>
+  <si>
+    <t>1023002_32</t>
+  </si>
+  <si>
+    <t>1023002_48;1980000_100</t>
+  </si>
+  <si>
+    <t>1023003_8</t>
+  </si>
+  <si>
+    <t>1023003_16</t>
+  </si>
+  <si>
+    <t>1023003_32</t>
+  </si>
+  <si>
+    <t>1023003_48;1980000_300</t>
+  </si>
+  <si>
+    <t>1023004_12</t>
+  </si>
+  <si>
+    <t>1023004_24</t>
+  </si>
+  <si>
+    <t>1023004_48;1980000_600</t>
+  </si>
+  <si>
+    <t>1023005_12</t>
+  </si>
+  <si>
+    <t>1023005_24</t>
+  </si>
+  <si>
+    <t>1023005_48</t>
+  </si>
+  <si>
+    <t>1023101_20;1980000_10</t>
+  </si>
+  <si>
+    <t>1023102_4</t>
+  </si>
+  <si>
+    <t>1023102_8</t>
+  </si>
+  <si>
+    <t>1023102_16</t>
+  </si>
+  <si>
+    <t>1023102_24;1980000_100</t>
+  </si>
+  <si>
+    <t>1023103_4</t>
+  </si>
+  <si>
+    <t>1023103_8</t>
+  </si>
+  <si>
+    <t>1023103_16</t>
+  </si>
+  <si>
+    <t>1023103_24;1980000_300</t>
+  </si>
+  <si>
+    <t>1023104_6</t>
+  </si>
+  <si>
+    <t>1023104_12</t>
+  </si>
+  <si>
+    <t>1023104_24;1980000_600</t>
+  </si>
+  <si>
+    <t>1023105_6</t>
+  </si>
+  <si>
+    <t>1023105_12</t>
+  </si>
+  <si>
+    <t>1023105_24</t>
   </si>
   <si>
     <t>1023101_1</t>
-  </si>
-  <si>
-    <t>5_1990000_200</t>
-  </si>
-  <si>
-    <t>5_1990000_240</t>
-  </si>
-  <si>
-    <t>1023101_10|1980000_10</t>
-  </si>
-  <si>
-    <t>5_1990000_280</t>
-  </si>
-  <si>
-    <t>1023101_3</t>
-  </si>
-  <si>
-    <t>5_1990000_320</t>
-  </si>
-  <si>
-    <t>5_1990000_360</t>
-  </si>
-  <si>
-    <t>5_1990000_440</t>
-  </si>
-  <si>
-    <t>1023101_18|1980000_100</t>
-  </si>
-  <si>
-    <t>5_1990000_520</t>
-  </si>
-  <si>
-    <t>5_1990000_600</t>
-  </si>
-  <si>
-    <t>5_1990000_760</t>
-  </si>
-  <si>
-    <t>5_1990000_920</t>
-  </si>
-  <si>
-    <t>1023101_24|1980000_300</t>
-  </si>
-  <si>
-    <t>5_1990000_1080</t>
-  </si>
-  <si>
-    <t>1023101_9</t>
-  </si>
-  <si>
-    <t>5_1990000_1320</t>
-  </si>
-  <si>
-    <t>5_1990000_1560</t>
-  </si>
-  <si>
-    <t>1023101_36|1980000_600</t>
-  </si>
-  <si>
-    <t>5_1990000_1800</t>
-  </si>
-  <si>
-    <t>5_1990000_2120</t>
-  </si>
-  <si>
-    <t>5_1990000_2440</t>
-  </si>
-  <si>
-    <t>5_1990000_2760</t>
-  </si>
-  <si>
-    <t>吧台区</t>
-  </si>
-  <si>
-    <t>1023401_4</t>
-  </si>
-  <si>
-    <t>1023401_8</t>
-  </si>
-  <si>
-    <t>1023401_16</t>
-  </si>
-  <si>
-    <t>1023401_24</t>
-  </si>
-  <si>
-    <t>1023401_32</t>
-  </si>
-  <si>
-    <t>1023401_40|1980000_10</t>
-  </si>
-  <si>
-    <t>1023401_12</t>
-  </si>
-  <si>
-    <t>1023401_48</t>
-  </si>
-  <si>
-    <t>1023401_72|1980000_100</t>
-  </si>
-  <si>
-    <t>1023401_64</t>
-  </si>
-  <si>
-    <t>1023401_96|1980000_300</t>
-  </si>
-  <si>
-    <t>1023401_36</t>
-  </si>
-  <si>
-    <t>1023401_72</t>
-  </si>
-  <si>
-    <t>1023401_144|1980000_600</t>
-  </si>
-  <si>
-    <t>1023401_144</t>
-  </si>
-  <si>
-    <t>1023401_288</t>
-  </si>
-  <si>
-    <t>休息区</t>
-  </si>
-  <si>
-    <t>1023301_8</t>
-  </si>
-  <si>
-    <t>1023301_16</t>
-  </si>
-  <si>
-    <t>1023301_32</t>
-  </si>
-  <si>
-    <t>1023301_48</t>
-  </si>
-  <si>
-    <t>1023301_64</t>
-  </si>
-  <si>
-    <t>1023301_80|1980000_10</t>
-  </si>
-  <si>
-    <t>1023301_24</t>
-  </si>
-  <si>
-    <t>1023301_96</t>
-  </si>
-  <si>
-    <t>1023301_144|1980000_100</t>
-  </si>
-  <si>
-    <t>1023301_128</t>
-  </si>
-  <si>
-    <t>1023301_192|1980000_300</t>
-  </si>
-  <si>
-    <t>1023301_72</t>
-  </si>
-  <si>
-    <t>1023301_144</t>
-  </si>
-  <si>
-    <t>1023301_288|1980000_600</t>
-  </si>
-  <si>
-    <t>1023301_288</t>
-  </si>
-  <si>
-    <t>1023301_576</t>
-  </si>
-  <si>
-    <t>提款机</t>
-  </si>
-  <si>
-    <t>1023201_6</t>
-  </si>
-  <si>
-    <t>1023201_12</t>
-  </si>
-  <si>
-    <t>1023201_24</t>
-  </si>
-  <si>
-    <t>1023201_36</t>
-  </si>
-  <si>
-    <t>1023201_48</t>
-  </si>
-  <si>
-    <t>1023201_60|1980000_10</t>
-  </si>
-  <si>
-    <t>1023201_18</t>
-  </si>
-  <si>
-    <t>1023201_72</t>
-  </si>
-  <si>
-    <t>1023201_108|1980000_100</t>
-  </si>
-  <si>
-    <t>1023201_96</t>
-  </si>
-  <si>
-    <t>1023201_144|1980000_300</t>
-  </si>
-  <si>
-    <t>1023201_54</t>
-  </si>
-  <si>
-    <t>1023201_108</t>
-  </si>
-  <si>
-    <t>1023201_216|1980000_600</t>
-  </si>
-  <si>
-    <t>1023201_216</t>
-  </si>
-  <si>
-    <t>1023201_432</t>
-  </si>
-  <si>
-    <t>停机坪</t>
-  </si>
-  <si>
-    <t>map&lt;int{_}long&gt;{;}</t>
-  </si>
-  <si>
-    <t>1023001_40;1980000_10</t>
-  </si>
-  <si>
-    <t>1023002_8</t>
-  </si>
-  <si>
-    <t>1023002_16</t>
-  </si>
-  <si>
-    <t>1023002_32</t>
-  </si>
-  <si>
-    <t>1023002_48;1980000_100</t>
-  </si>
-  <si>
-    <t>1023003_8</t>
-  </si>
-  <si>
-    <t>1023003_16</t>
-  </si>
-  <si>
-    <t>1023003_32</t>
-  </si>
-  <si>
-    <t>1023003_48;1980000_300</t>
-  </si>
-  <si>
-    <t>1023004_12</t>
-  </si>
-  <si>
-    <t>1023004_24</t>
-  </si>
-  <si>
-    <t>1023004_48;1980000_600</t>
-  </si>
-  <si>
-    <t>1023005_12</t>
-  </si>
-  <si>
-    <t>1023005_24</t>
-  </si>
-  <si>
-    <t>1023005_48</t>
-  </si>
-  <si>
-    <t>1023101_20;1980000_10</t>
-  </si>
-  <si>
-    <t>1023102_4</t>
-  </si>
-  <si>
-    <t>1023102_8</t>
-  </si>
-  <si>
-    <t>1023102_16</t>
-  </si>
-  <si>
-    <t>1023102_24;1980000_100</t>
-  </si>
-  <si>
-    <t>1023103_4</t>
-  </si>
-  <si>
-    <t>1023103_8</t>
-  </si>
-  <si>
-    <t>1023103_16</t>
-  </si>
-  <si>
-    <t>1023103_24;1980000_300</t>
-  </si>
-  <si>
-    <t>1023104_6</t>
-  </si>
-  <si>
-    <t>1023104_12</t>
-  </si>
-  <si>
-    <t>1023104_24;1980000_600</t>
-  </si>
-  <si>
-    <t>1023105_6</t>
-  </si>
-  <si>
-    <t>1023105_12</t>
-  </si>
-  <si>
-    <t>1023105_24</t>
   </si>
   <si>
     <t>1023101_10;1980000_10</t>
@@ -2247,7 +2319,7 @@
         <v>300</v>
       </c>
       <c r="N6" s="3">
-        <v>240</v>
+        <v>2880</v>
       </c>
       <c r="P6" s="2">
         <f t="shared" ref="P6:P15" si="2">400000+A6</f>
@@ -2297,7 +2369,7 @@
         <v>600</v>
       </c>
       <c r="N7" s="3">
-        <v>360</v>
+        <v>6720</v>
       </c>
       <c r="P7" s="2">
         <f t="shared" si="2"/>
@@ -2347,7 +2419,7 @@
         <v>900</v>
       </c>
       <c r="N8" s="3">
-        <v>480</v>
+        <v>10560</v>
       </c>
       <c r="P8" s="2">
         <f t="shared" si="2"/>
@@ -2397,7 +2469,7 @@
         <v>1200</v>
       </c>
       <c r="N9" s="3">
-        <v>600</v>
+        <v>14880</v>
       </c>
       <c r="P9" s="2">
         <f t="shared" si="2"/>
@@ -2447,7 +2519,7 @@
         <v>1500</v>
       </c>
       <c r="N10" s="3">
-        <v>720</v>
+        <v>18720</v>
       </c>
       <c r="P10" s="2">
         <f t="shared" si="2"/>
@@ -2498,7 +2570,7 @@
         <v>3600</v>
       </c>
       <c r="N11" s="3">
-        <v>1260</v>
+        <v>24480</v>
       </c>
       <c r="P11" s="2">
         <f t="shared" si="2"/>
@@ -2532,7 +2604,7 @@
         <v>52</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="J12" s="3">
         <v>4</v>
@@ -2549,7 +2621,7 @@
         <v>4200</v>
       </c>
       <c r="N12" s="3">
-        <v>1440</v>
+        <v>30240</v>
       </c>
       <c r="P12" s="2">
         <f t="shared" si="2"/>
@@ -2580,16 +2652,16 @@
         <v>8</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J13" s="3">
         <v>4</v>
       </c>
       <c r="K13" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L13" s="5">
         <f t="shared" si="3"/>
@@ -2600,7 +2672,7 @@
         <v>4800</v>
       </c>
       <c r="N13" s="3">
-        <v>1620</v>
+        <v>35520</v>
       </c>
       <c r="P13" s="2">
         <f t="shared" si="2"/>
@@ -2631,16 +2703,16 @@
         <v>9</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J14" s="3">
         <v>4</v>
       </c>
       <c r="K14" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L14" s="5">
         <f t="shared" si="3"/>
@@ -2651,7 +2723,7 @@
         <v>5400</v>
       </c>
       <c r="N14" s="3">
-        <v>1980</v>
+        <v>43680</v>
       </c>
       <c r="P14" s="2">
         <f t="shared" si="2"/>
@@ -2682,16 +2754,16 @@
         <v>10</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="J15" s="3">
         <v>4</v>
       </c>
       <c r="K15" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="L15" s="5">
         <f t="shared" si="3"/>
@@ -2702,7 +2774,7 @@
         <v>12000</v>
       </c>
       <c r="N15" s="3">
-        <v>2340</v>
+        <v>51360</v>
       </c>
       <c r="P15" s="2">
         <f t="shared" si="2"/>
@@ -2733,16 +2805,16 @@
         <v>11</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="J16" s="3">
         <v>4</v>
       </c>
       <c r="K16" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="L16" s="5">
         <f t="shared" si="3"/>
@@ -2753,7 +2825,7 @@
         <v>13200</v>
       </c>
       <c r="N16" s="3">
-        <v>2700</v>
+        <v>59520</v>
       </c>
       <c r="P16" s="2">
         <f t="shared" ref="P16:P25" si="5">400000+A16</f>
@@ -2784,16 +2856,16 @@
         <v>12</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="J17" s="3">
         <v>4</v>
       </c>
       <c r="K17" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="L17" s="5">
         <f t="shared" si="3"/>
@@ -2804,7 +2876,7 @@
         <v>14400</v>
       </c>
       <c r="N17" s="3">
-        <v>4560</v>
+        <v>70560</v>
       </c>
       <c r="P17" s="2">
         <f t="shared" si="5"/>
@@ -2835,16 +2907,16 @@
         <v>13</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="J18" s="3">
         <v>4</v>
       </c>
       <c r="K18" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="L18" s="5">
         <f t="shared" si="3"/>
@@ -2855,7 +2927,7 @@
         <v>15600</v>
       </c>
       <c r="N18" s="3">
-        <v>5520</v>
+        <v>81600</v>
       </c>
       <c r="P18" s="2">
         <f t="shared" si="5"/>
@@ -2886,16 +2958,16 @@
         <v>14</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="J19" s="3">
         <v>4</v>
       </c>
       <c r="K19" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="L19" s="5">
         <f t="shared" si="3"/>
@@ -2906,7 +2978,7 @@
         <v>33600</v>
       </c>
       <c r="N19" s="3">
-        <v>6480</v>
+        <v>92640</v>
       </c>
       <c r="P19" s="2">
         <f t="shared" si="5"/>
@@ -2937,16 +3009,16 @@
         <v>15</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="J20" s="3">
         <v>4</v>
       </c>
       <c r="K20" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="L20" s="5">
         <f t="shared" si="3"/>
@@ -2957,7 +3029,7 @@
         <v>36000</v>
       </c>
       <c r="N20" s="3">
-        <v>9900</v>
+        <v>108000</v>
       </c>
       <c r="P20" s="2">
         <f t="shared" si="5"/>
@@ -2988,16 +3060,16 @@
         <v>16</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="J21" s="3">
         <v>4</v>
       </c>
       <c r="K21" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="L21" s="5">
         <f t="shared" si="3"/>
@@ -3008,7 +3080,7 @@
         <v>38400</v>
       </c>
       <c r="N21" s="3">
-        <v>11700</v>
+        <v>123360</v>
       </c>
       <c r="P21" s="2">
         <f t="shared" si="5"/>
@@ -3039,16 +3111,16 @@
         <v>17</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="J22" s="3">
         <v>4</v>
       </c>
       <c r="K22" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="L22" s="5">
         <f t="shared" si="3"/>
@@ -3059,7 +3131,7 @@
         <v>81600</v>
       </c>
       <c r="N22" s="3">
-        <v>13500</v>
+        <v>139200</v>
       </c>
       <c r="P22" s="2">
         <f t="shared" si="5"/>
@@ -3090,16 +3162,16 @@
         <v>18</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="J23" s="3">
         <v>4</v>
       </c>
       <c r="K23" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="L23" s="5">
         <f t="shared" si="3"/>
@@ -3110,7 +3182,7 @@
         <v>86400</v>
       </c>
       <c r="N23" s="3">
-        <v>19080</v>
+        <v>160800</v>
       </c>
       <c r="P23" s="2">
         <f t="shared" si="5"/>
@@ -3141,16 +3213,16 @@
         <v>19</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="J24" s="3">
         <v>4</v>
       </c>
       <c r="K24" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="L24" s="5">
         <f t="shared" si="3"/>
@@ -3161,7 +3233,7 @@
         <v>91200</v>
       </c>
       <c r="N24" s="3">
-        <v>21960</v>
+        <v>182400</v>
       </c>
       <c r="P24" s="2">
         <f t="shared" si="5"/>
@@ -3192,14 +3264,14 @@
         <v>20</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="J25" s="3">
         <v>4</v>
       </c>
       <c r="K25"/>
       <c r="N25" s="3">
-        <v>24840</v>
+        <v>204000</v>
       </c>
       <c r="P25" s="2">
         <f t="shared" si="5"/>
@@ -3215,7 +3287,7 @@
         <v>2</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D26" s="3">
         <v>2</v>
@@ -3231,7 +3303,7 @@
       </c>
       <c r="H26" s="2"/>
       <c r="I26" s="1" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="J26" s="3">
         <v>4</v>
@@ -3262,7 +3334,7 @@
         <v>2</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D27" s="3">
         <v>2</v>
@@ -3277,10 +3349,10 @@
         <v>1</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>42</v>
+        <v>93</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="J27" s="3">
         <v>4</v>
@@ -3296,7 +3368,7 @@
         <v>300</v>
       </c>
       <c r="N27" s="3">
-        <v>480</v>
+        <v>5760</v>
       </c>
       <c r="P27" s="2">
         <f t="shared" ref="P27:P36" si="8">400000+A27</f>
@@ -3312,7 +3384,7 @@
         <v>2</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D28" s="3">
         <v>2</v>
@@ -3327,10 +3399,10 @@
         <v>2</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>47</v>
+        <v>95</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="J28" s="3">
         <v>4</v>
@@ -3346,7 +3418,7 @@
         <v>600</v>
       </c>
       <c r="N28" s="3">
-        <v>720</v>
+        <v>13440</v>
       </c>
       <c r="P28" s="2">
         <f t="shared" si="8"/>
@@ -3362,7 +3434,7 @@
         <v>2</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D29" s="3">
         <v>2</v>
@@ -3377,10 +3449,10 @@
         <v>3</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>52</v>
+        <v>97</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="J29" s="3">
         <v>4</v>
@@ -3396,7 +3468,7 @@
         <v>900</v>
       </c>
       <c r="N29" s="3">
-        <v>960</v>
+        <v>21120</v>
       </c>
       <c r="P29" s="2">
         <f t="shared" si="8"/>
@@ -3412,7 +3484,7 @@
         <v>2</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D30" s="3">
         <v>2</v>
@@ -3427,10 +3499,10 @@
         <v>4</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="J30" s="3">
         <v>4</v>
@@ -3446,7 +3518,7 @@
         <v>1200</v>
       </c>
       <c r="N30" s="3">
-        <v>1200</v>
+        <v>29760</v>
       </c>
       <c r="P30" s="2">
         <f t="shared" si="8"/>
@@ -3462,7 +3534,7 @@
         <v>2</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D31" s="3">
         <v>2</v>
@@ -3477,10 +3549,10 @@
         <v>5</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="J31" s="3">
         <v>4</v>
@@ -3496,7 +3568,7 @@
         <v>1500</v>
       </c>
       <c r="N31" s="3">
-        <v>1440</v>
+        <v>37440</v>
       </c>
       <c r="P31" s="2">
         <f t="shared" si="8"/>
@@ -3512,7 +3584,7 @@
         <v>2</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D32" s="3">
         <v>2</v>
@@ -3527,10 +3599,10 @@
         <v>6</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="J32" s="3">
         <v>4</v>
@@ -3547,7 +3619,7 @@
         <v>3600</v>
       </c>
       <c r="N32" s="3">
-        <v>2520</v>
+        <v>48960</v>
       </c>
       <c r="P32" s="2">
         <f t="shared" si="8"/>
@@ -3563,7 +3635,7 @@
         <v>2</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D33" s="3">
         <v>2</v>
@@ -3578,10 +3650,10 @@
         <v>7</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="J33" s="3">
         <v>4</v>
@@ -3598,7 +3670,7 @@
         <v>4200</v>
       </c>
       <c r="N33" s="3">
-        <v>2880</v>
+        <v>60480</v>
       </c>
       <c r="P33" s="2">
         <f t="shared" si="8"/>
@@ -3614,7 +3686,7 @@
         <v>2</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D34" s="3">
         <v>2</v>
@@ -3629,16 +3701,16 @@
         <v>8</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="J34" s="3">
         <v>4</v>
       </c>
       <c r="K34" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L34" s="5">
         <f t="shared" si="7"/>
@@ -3649,7 +3721,7 @@
         <v>4800</v>
       </c>
       <c r="N34" s="3">
-        <v>3240</v>
+        <v>71040</v>
       </c>
       <c r="P34" s="2">
         <f t="shared" si="8"/>
@@ -3665,7 +3737,7 @@
         <v>2</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D35" s="3">
         <v>2</v>
@@ -3680,16 +3752,16 @@
         <v>9</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="J35" s="3">
         <v>4</v>
       </c>
       <c r="K35" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L35" s="5">
         <f t="shared" si="7"/>
@@ -3700,7 +3772,7 @@
         <v>5400</v>
       </c>
       <c r="N35" s="3">
-        <v>3960</v>
+        <v>87360</v>
       </c>
       <c r="P35" s="2">
         <f t="shared" si="8"/>
@@ -3716,7 +3788,7 @@
         <v>2</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D36" s="3">
         <v>2</v>
@@ -3731,16 +3803,16 @@
         <v>10</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="J36" s="3">
         <v>4</v>
       </c>
       <c r="K36" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="L36" s="5">
         <f t="shared" si="7"/>
@@ -3751,7 +3823,7 @@
         <v>12000</v>
       </c>
       <c r="N36" s="3">
-        <v>4680</v>
+        <v>102720</v>
       </c>
       <c r="P36" s="2">
         <f t="shared" si="8"/>
@@ -3767,7 +3839,7 @@
         <v>2</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D37" s="3">
         <v>2</v>
@@ -3782,16 +3854,16 @@
         <v>11</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>93</v>
+        <v>113</v>
       </c>
       <c r="J37" s="3">
         <v>4</v>
       </c>
       <c r="K37" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="L37" s="5">
         <f t="shared" si="7"/>
@@ -3802,7 +3874,7 @@
         <v>13200</v>
       </c>
       <c r="N37" s="3">
-        <v>5400</v>
+        <v>119040</v>
       </c>
       <c r="P37" s="2">
         <f t="shared" ref="P37:P46" si="12">400000+A37</f>
@@ -3818,7 +3890,7 @@
         <v>2</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D38" s="3">
         <v>2</v>
@@ -3833,16 +3905,16 @@
         <v>12</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="J38" s="3">
         <v>4</v>
       </c>
       <c r="K38" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="L38" s="5">
         <f t="shared" si="7"/>
@@ -3853,7 +3925,7 @@
         <v>14400</v>
       </c>
       <c r="N38" s="3">
-        <v>9120</v>
+        <v>141120</v>
       </c>
       <c r="P38" s="2">
         <f t="shared" si="12"/>
@@ -3869,7 +3941,7 @@
         <v>2</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D39" s="3">
         <v>2</v>
@@ -3884,16 +3956,16 @@
         <v>13</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="J39" s="3">
         <v>4</v>
       </c>
       <c r="K39" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="L39" s="5">
         <f t="shared" si="7"/>
@@ -3904,7 +3976,7 @@
         <v>15600</v>
       </c>
       <c r="N39" s="3">
-        <v>11040</v>
+        <v>163200</v>
       </c>
       <c r="P39" s="2">
         <f t="shared" si="12"/>
@@ -3920,7 +3992,7 @@
         <v>2</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D40" s="3">
         <v>2</v>
@@ -3935,16 +4007,16 @@
         <v>14</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="J40" s="3">
         <v>4</v>
       </c>
       <c r="K40" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="L40" s="5">
         <f t="shared" si="7"/>
@@ -3955,7 +4027,7 @@
         <v>33600</v>
       </c>
       <c r="N40" s="3">
-        <v>12960</v>
+        <v>185280</v>
       </c>
       <c r="P40" s="2">
         <f t="shared" si="12"/>
@@ -3971,7 +4043,7 @@
         <v>2</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D41" s="3">
         <v>2</v>
@@ -3986,16 +4058,16 @@
         <v>15</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="J41" s="3">
         <v>4</v>
       </c>
       <c r="K41" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="L41" s="5">
         <f t="shared" si="7"/>
@@ -4006,7 +4078,7 @@
         <v>36000</v>
       </c>
       <c r="N41" s="3">
-        <v>19800</v>
+        <v>216000</v>
       </c>
       <c r="P41" s="2">
         <f t="shared" si="12"/>
@@ -4022,7 +4094,7 @@
         <v>2</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D42" s="3">
         <v>2</v>
@@ -4037,16 +4109,16 @@
         <v>16</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="J42" s="3">
         <v>4</v>
       </c>
       <c r="K42" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="L42" s="5">
         <f t="shared" si="7"/>
@@ -4057,7 +4129,7 @@
         <v>38400</v>
       </c>
       <c r="N42" s="3">
-        <v>23400</v>
+        <v>246720</v>
       </c>
       <c r="P42" s="2">
         <f t="shared" si="12"/>
@@ -4073,7 +4145,7 @@
         <v>2</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D43" s="3">
         <v>2</v>
@@ -4088,16 +4160,16 @@
         <v>17</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="J43" s="3">
         <v>4</v>
       </c>
       <c r="K43" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="L43" s="5">
         <f t="shared" si="7"/>
@@ -4108,7 +4180,7 @@
         <v>81600</v>
       </c>
       <c r="N43" s="3">
-        <v>27000</v>
+        <v>278400</v>
       </c>
       <c r="P43" s="2">
         <f t="shared" si="12"/>
@@ -4124,7 +4196,7 @@
         <v>2</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D44" s="3">
         <v>2</v>
@@ -4139,16 +4211,16 @@
         <v>18</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="J44" s="3">
         <v>4</v>
       </c>
       <c r="K44" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="L44" s="5">
         <f t="shared" si="7"/>
@@ -4159,7 +4231,7 @@
         <v>86400</v>
       </c>
       <c r="N44" s="3">
-        <v>38160</v>
+        <v>321600</v>
       </c>
       <c r="P44" s="2">
         <f t="shared" si="12"/>
@@ -4175,7 +4247,7 @@
         <v>2</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D45" s="3">
         <v>2</v>
@@ -4190,16 +4262,16 @@
         <v>19</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="J45" s="3">
         <v>4</v>
       </c>
       <c r="K45" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="L45" s="5">
         <f t="shared" si="7"/>
@@ -4210,7 +4282,7 @@
         <v>91200</v>
       </c>
       <c r="N45" s="3">
-        <v>43920</v>
+        <v>364800</v>
       </c>
       <c r="P45" s="2">
         <f t="shared" si="12"/>
@@ -4226,7 +4298,7 @@
         <v>2</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D46" s="3">
         <v>2</v>
@@ -4241,14 +4313,14 @@
         <v>20</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="J46" s="3">
         <v>4</v>
       </c>
       <c r="K46"/>
       <c r="N46" s="3">
-        <v>49680</v>
+        <v>408000</v>
       </c>
       <c r="P46" s="2">
         <f t="shared" si="12"/>
@@ -4264,7 +4336,7 @@
         <v>3</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="D47" s="3">
         <v>4</v>
@@ -4280,7 +4352,7 @@
       </c>
       <c r="H47" s="2"/>
       <c r="I47" s="1" t="s">
-        <v>122</v>
+        <v>92</v>
       </c>
       <c r="J47" s="3">
         <v>4</v>
@@ -4311,7 +4383,7 @@
         <v>3</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="D48" s="3">
         <v>4</v>
@@ -4326,10 +4398,10 @@
         <v>1</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>52</v>
+        <v>132</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="J48" s="3">
         <v>4</v>
@@ -4345,7 +4417,7 @@
         <v>300</v>
       </c>
       <c r="N48" s="3">
-        <v>960</v>
+        <v>11520</v>
       </c>
       <c r="P48" s="2">
         <f t="shared" ref="P48:P67" si="17">400000+A48</f>
@@ -4361,7 +4433,7 @@
         <v>3</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="D49" s="3">
         <v>4</v>
@@ -4376,10 +4448,10 @@
         <v>2</v>
       </c>
       <c r="H49" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="I49" s="1" t="s">
         <v>94</v>
-      </c>
-      <c r="I49" s="1" t="s">
-        <v>89</v>
       </c>
       <c r="J49" s="3">
         <v>4</v>
@@ -4395,7 +4467,7 @@
         <v>600</v>
       </c>
       <c r="N49" s="3">
-        <v>1440</v>
+        <v>26880</v>
       </c>
       <c r="P49" s="2">
         <f t="shared" si="17"/>
@@ -4411,7 +4483,7 @@
         <v>3</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="D50" s="3">
         <v>4</v>
@@ -4426,10 +4498,10 @@
         <v>3</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>98</v>
+        <v>134</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="J50" s="3">
         <v>4</v>
@@ -4445,7 +4517,7 @@
         <v>900</v>
       </c>
       <c r="N50" s="3">
-        <v>1920</v>
+        <v>42240</v>
       </c>
       <c r="P50" s="2">
         <f t="shared" si="17"/>
@@ -4461,7 +4533,7 @@
         <v>3</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="D51" s="3">
         <v>4</v>
@@ -4476,10 +4548,10 @@
         <v>4</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>123</v>
+        <v>63</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="J51" s="3">
         <v>4</v>
@@ -4495,7 +4567,7 @@
         <v>1200</v>
       </c>
       <c r="N51" s="3">
-        <v>2400</v>
+        <v>59520</v>
       </c>
       <c r="P51" s="2">
         <f t="shared" si="17"/>
@@ -4511,7 +4583,7 @@
         <v>3</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="D52" s="3">
         <v>4</v>
@@ -4526,10 +4598,10 @@
         <v>5</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="J52" s="3">
         <v>4</v>
@@ -4545,7 +4617,7 @@
         <v>1500</v>
       </c>
       <c r="N52" s="3">
-        <v>2880</v>
+        <v>74880</v>
       </c>
       <c r="P52" s="2">
         <f t="shared" si="17"/>
@@ -4561,7 +4633,7 @@
         <v>3</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="D53" s="3">
         <v>4</v>
@@ -4576,10 +4648,10 @@
         <v>6</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>127</v>
+        <v>94</v>
       </c>
       <c r="J53" s="3">
         <v>4</v>
@@ -4596,7 +4668,7 @@
         <v>3600</v>
       </c>
       <c r="N53" s="3">
-        <v>5040</v>
+        <v>97920</v>
       </c>
       <c r="P53" s="2">
         <f t="shared" si="17"/>
@@ -4612,7 +4684,7 @@
         <v>3</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="D54" s="3">
         <v>4</v>
@@ -4627,10 +4699,10 @@
         <v>7</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="J54" s="3">
         <v>4</v>
@@ -4647,7 +4719,7 @@
         <v>4200</v>
       </c>
       <c r="N54" s="3">
-        <v>5760</v>
+        <v>120960</v>
       </c>
       <c r="P54" s="2">
         <f t="shared" si="17"/>
@@ -4663,7 +4735,7 @@
         <v>3</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="D55" s="3">
         <v>4</v>
@@ -4678,16 +4750,16 @@
         <v>8</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>91</v>
+        <v>139</v>
       </c>
       <c r="J55" s="3">
         <v>4</v>
       </c>
       <c r="K55" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L55" s="5">
         <f t="shared" si="15"/>
@@ -4698,7 +4770,7 @@
         <v>4800</v>
       </c>
       <c r="N55" s="3">
-        <v>6480</v>
+        <v>142080</v>
       </c>
       <c r="P55" s="2">
         <f t="shared" si="17"/>
@@ -4714,7 +4786,7 @@
         <v>3</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="D56" s="3">
         <v>4</v>
@@ -4729,16 +4801,16 @@
         <v>9</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>131</v>
+        <v>100</v>
       </c>
       <c r="J56" s="3">
         <v>4</v>
       </c>
       <c r="K56" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L56" s="5">
         <f t="shared" si="15"/>
@@ -4749,7 +4821,7 @@
         <v>5400</v>
       </c>
       <c r="N56" s="3">
-        <v>7920</v>
+        <v>174720</v>
       </c>
       <c r="P56" s="2">
         <f t="shared" si="17"/>
@@ -4765,7 +4837,7 @@
         <v>3</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="D57" s="3">
         <v>4</v>
@@ -4780,16 +4852,16 @@
         <v>10</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="J57" s="3">
         <v>4</v>
       </c>
       <c r="K57" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="L57" s="5">
         <f t="shared" si="15"/>
@@ -4800,7 +4872,7 @@
         <v>12000</v>
       </c>
       <c r="N57" s="3">
-        <v>9360</v>
+        <v>205440</v>
       </c>
       <c r="P57" s="2">
         <f t="shared" si="17"/>
@@ -4816,7 +4888,7 @@
         <v>3</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="D58" s="3">
         <v>4</v>
@@ -4831,16 +4903,16 @@
         <v>11</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>90</v>
+        <v>143</v>
       </c>
       <c r="J58" s="3">
         <v>4</v>
       </c>
       <c r="K58" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="L58" s="5">
         <f t="shared" si="15"/>
@@ -4851,7 +4923,7 @@
         <v>13200</v>
       </c>
       <c r="N58" s="3">
-        <v>10800</v>
+        <v>238080</v>
       </c>
       <c r="P58" s="2">
         <f t="shared" ref="P58:P67" si="21">400000+A58</f>
@@ -4867,7 +4939,7 @@
         <v>3</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="D59" s="3">
         <v>4</v>
@@ -4882,16 +4954,16 @@
         <v>12</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>93</v>
+        <v>145</v>
       </c>
       <c r="J59" s="3">
         <v>4</v>
       </c>
       <c r="K59" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="L59" s="5">
         <f t="shared" si="15"/>
@@ -4902,7 +4974,7 @@
         <v>14400</v>
       </c>
       <c r="N59" s="3">
-        <v>18240</v>
+        <v>282240</v>
       </c>
       <c r="P59" s="2">
         <f t="shared" si="21"/>
@@ -4918,7 +4990,7 @@
         <v>3</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="D60" s="3">
         <v>4</v>
@@ -4933,16 +5005,16 @@
         <v>13</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="I60" s="1" t="s">
-        <v>136</v>
+        <v>102</v>
       </c>
       <c r="J60" s="3">
         <v>4</v>
       </c>
       <c r="K60" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="L60" s="5">
         <f t="shared" si="15"/>
@@ -4953,7 +5025,7 @@
         <v>15600</v>
       </c>
       <c r="N60" s="3">
-        <v>22080</v>
+        <v>326400</v>
       </c>
       <c r="P60" s="2">
         <f t="shared" si="21"/>
@@ -4969,7 +5041,7 @@
         <v>3</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="D61" s="3">
         <v>4</v>
@@ -4984,16 +5056,16 @@
         <v>14</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="J61" s="3">
         <v>4</v>
       </c>
       <c r="K61" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="L61" s="5">
         <f t="shared" si="15"/>
@@ -5004,7 +5076,7 @@
         <v>33600</v>
       </c>
       <c r="N61" s="3">
-        <v>25920</v>
+        <v>370560</v>
       </c>
       <c r="P61" s="2">
         <f t="shared" si="21"/>
@@ -5020,7 +5092,7 @@
         <v>3</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="D62" s="3">
         <v>4</v>
@@ -5035,16 +5107,16 @@
         <v>15</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="J62" s="3">
         <v>4</v>
       </c>
       <c r="K62" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="L62" s="5">
         <f t="shared" si="15"/>
@@ -5055,7 +5127,7 @@
         <v>36000</v>
       </c>
       <c r="N62" s="3">
-        <v>39600</v>
+        <v>432000</v>
       </c>
       <c r="P62" s="2">
         <f t="shared" si="21"/>
@@ -5071,7 +5143,7 @@
         <v>3</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="D63" s="3">
         <v>4</v>
@@ -5086,16 +5158,16 @@
         <v>16</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="J63" s="3">
         <v>4</v>
       </c>
       <c r="K63" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="L63" s="5">
         <f t="shared" si="15"/>
@@ -5106,7 +5178,7 @@
         <v>38400</v>
       </c>
       <c r="N63" s="3">
-        <v>46800</v>
+        <v>493440</v>
       </c>
       <c r="P63" s="2">
         <f t="shared" si="21"/>
@@ -5122,7 +5194,7 @@
         <v>3</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="D64" s="3">
         <v>4</v>
@@ -5137,16 +5209,16 @@
         <v>17</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>110</v>
+        <v>152</v>
       </c>
       <c r="J64" s="3">
         <v>4</v>
       </c>
       <c r="K64" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="L64" s="5">
         <f t="shared" si="15"/>
@@ -5157,7 +5229,7 @@
         <v>81600</v>
       </c>
       <c r="N64" s="3">
-        <v>54000</v>
+        <v>556800</v>
       </c>
       <c r="P64" s="2">
         <f t="shared" si="21"/>
@@ -5173,7 +5245,7 @@
         <v>3</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="D65" s="3">
         <v>4</v>
@@ -5188,16 +5260,16 @@
         <v>18</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="I65" s="1" t="s">
-        <v>112</v>
+        <v>154</v>
       </c>
       <c r="J65" s="3">
         <v>4</v>
       </c>
       <c r="K65" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="L65" s="5">
         <f t="shared" si="15"/>
@@ -5208,7 +5280,7 @@
         <v>86400</v>
       </c>
       <c r="N65" s="3">
-        <v>76320</v>
+        <v>643200</v>
       </c>
       <c r="P65" s="2">
         <f t="shared" si="21"/>
@@ -5224,7 +5296,7 @@
         <v>3</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="D66" s="3">
         <v>4</v>
@@ -5239,16 +5311,16 @@
         <v>19</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="J66" s="3">
         <v>4</v>
       </c>
       <c r="K66" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="L66" s="5">
         <f t="shared" si="15"/>
@@ -5259,7 +5331,7 @@
         <v>91200</v>
       </c>
       <c r="N66" s="3">
-        <v>87840</v>
+        <v>729600</v>
       </c>
       <c r="P66" s="2">
         <f t="shared" si="21"/>
@@ -5275,7 +5347,7 @@
         <v>3</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="D67" s="3">
         <v>4</v>
@@ -5290,14 +5362,14 @@
         <v>20</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="J67" s="3">
         <v>4</v>
       </c>
       <c r="K67"/>
       <c r="N67" s="3">
-        <v>99360</v>
+        <v>816000</v>
       </c>
       <c r="P67" s="2">
         <f t="shared" si="21"/>
@@ -5313,7 +5385,7 @@
         <v>4</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="D68" s="3">
         <v>2</v>
@@ -5328,7 +5400,7 @@
         <v>0</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="J68" s="3"/>
       <c r="K68" t="s">
@@ -5357,7 +5429,7 @@
         <v>4</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="D69" s="3">
         <v>2</v>
@@ -5372,7 +5444,7 @@
         <v>1</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="J69" s="3"/>
       <c r="K69" t="s">
@@ -5399,7 +5471,7 @@
         <v>4</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="D70" s="3">
         <v>2</v>
@@ -5414,7 +5486,7 @@
         <v>2</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="J70" s="3"/>
       <c r="K70" t="s">
@@ -5441,7 +5513,7 @@
         <v>4</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="D71" s="3">
         <v>2</v>
@@ -5456,7 +5528,7 @@
         <v>3</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="J71" s="3"/>
       <c r="K71" t="s">
@@ -5483,7 +5555,7 @@
         <v>4</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="D72" s="3">
         <v>2</v>
@@ -5498,7 +5570,7 @@
         <v>4</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="J72" s="3"/>
       <c r="K72" t="s">
@@ -5525,7 +5597,7 @@
         <v>4</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="D73" s="3">
         <v>2</v>
@@ -5540,7 +5612,7 @@
         <v>5</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="J73" s="3"/>
       <c r="K73" t="s">
@@ -5567,7 +5639,7 @@
         <v>4</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="D74" s="3">
         <v>2</v>
@@ -5582,7 +5654,7 @@
         <v>6</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="J74" s="3"/>
       <c r="K74" t="s">
@@ -5610,7 +5682,7 @@
         <v>4</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="D75" s="3">
         <v>2</v>
@@ -5625,7 +5697,7 @@
         <v>7</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="J75" s="3"/>
       <c r="K75" t="s">
@@ -5653,7 +5725,7 @@
         <v>4</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="D76" s="3">
         <v>2</v>
@@ -5668,11 +5740,11 @@
         <v>8</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="J76" s="3"/>
       <c r="K76" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L76" s="5">
         <f t="shared" si="24"/>
@@ -5696,7 +5768,7 @@
         <v>4</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="D77" s="3">
         <v>2</v>
@@ -5711,11 +5783,11 @@
         <v>9</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="J77" s="3"/>
       <c r="K77" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L77" s="5">
         <f t="shared" si="24"/>
@@ -5739,7 +5811,7 @@
         <v>4</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="D78" s="3">
         <v>2</v>
@@ -5754,11 +5826,11 @@
         <v>10</v>
       </c>
       <c r="I78" s="1" t="s">
-        <v>149</v>
+        <v>168</v>
       </c>
       <c r="J78" s="3"/>
       <c r="K78" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="L78" s="5">
         <f t="shared" si="24"/>
@@ -5782,7 +5854,7 @@
         <v>4</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="D79" s="3">
         <v>2</v>
@@ -5797,11 +5869,11 @@
         <v>11</v>
       </c>
       <c r="I79" s="1" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="J79" s="3"/>
       <c r="K79" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="L79" s="5">
         <f t="shared" si="24"/>
@@ -5825,7 +5897,7 @@
         <v>4</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="D80" s="3">
         <v>2</v>
@@ -5840,11 +5912,11 @@
         <v>12</v>
       </c>
       <c r="I80" s="1" t="s">
-        <v>156</v>
+        <v>170</v>
       </c>
       <c r="J80" s="3"/>
       <c r="K80" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="L80" s="5">
         <f t="shared" si="24"/>
@@ -5868,7 +5940,7 @@
         <v>4</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="D81" s="3">
         <v>2</v>
@@ -5883,11 +5955,11 @@
         <v>13</v>
       </c>
       <c r="I81" s="1" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
       <c r="J81" s="3"/>
       <c r="K81" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="L81" s="5">
         <f t="shared" si="24"/>
@@ -5911,7 +5983,7 @@
         <v>4</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="D82" s="3">
         <v>2</v>
@@ -5926,11 +5998,11 @@
         <v>14</v>
       </c>
       <c r="I82" s="1" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="J82" s="3"/>
       <c r="K82" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="L82" s="5">
         <f t="shared" si="24"/>
@@ -5954,7 +6026,7 @@
         <v>4</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="D83" s="3">
         <v>2</v>
@@ -5969,11 +6041,11 @@
         <v>15</v>
       </c>
       <c r="I83" s="1" t="s">
-        <v>159</v>
+        <v>173</v>
       </c>
       <c r="J83" s="3"/>
       <c r="K83" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="L83" s="5">
         <f t="shared" si="24"/>
@@ -5997,7 +6069,7 @@
         <v>4</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="D84" s="3">
         <v>2</v>
@@ -6012,11 +6084,11 @@
         <v>16</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="J84" s="3"/>
       <c r="K84" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="L84" s="5">
         <f t="shared" si="24"/>
@@ -6040,7 +6112,7 @@
         <v>4</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="D85" s="3">
         <v>2</v>
@@ -6055,11 +6127,11 @@
         <v>17</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>159</v>
+        <v>175</v>
       </c>
       <c r="J85" s="3"/>
       <c r="K85" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="L85" s="5">
         <f t="shared" si="24"/>
@@ -6083,7 +6155,7 @@
         <v>4</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="D86" s="3">
         <v>2</v>
@@ -6098,11 +6170,11 @@
         <v>18</v>
       </c>
       <c r="I86" s="1" t="s">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="J86" s="3"/>
       <c r="K86" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="L86" s="5">
         <f t="shared" si="24"/>
@@ -6126,7 +6198,7 @@
         <v>4</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="D87" s="3">
         <v>2</v>
@@ -6141,11 +6213,11 @@
         <v>19</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="J87" s="3"/>
       <c r="K87" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="L87" s="5">
         <f t="shared" si="24"/>
@@ -6169,7 +6241,7 @@
         <v>4</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="D88" s="3">
         <v>2</v>
@@ -6199,7 +6271,7 @@
         <v>5</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="D89" s="3">
         <v>2</v>
@@ -6214,7 +6286,7 @@
         <v>0</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="J89" s="3">
         <v>4</v>
@@ -6245,7 +6317,7 @@
         <v>5</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="D90" s="3">
         <v>2</v>
@@ -6260,7 +6332,7 @@
         <v>1</v>
       </c>
       <c r="I90" s="1" t="s">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="J90" s="3">
         <v>4</v>
@@ -6292,7 +6364,7 @@
         <v>5</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="D91" s="3">
         <v>2</v>
@@ -6307,7 +6379,7 @@
         <v>2</v>
       </c>
       <c r="I91" s="1" t="s">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="J91" s="3">
         <v>4</v>
@@ -6339,7 +6411,7 @@
         <v>5</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="D92" s="3">
         <v>2</v>
@@ -6354,7 +6426,7 @@
         <v>3</v>
       </c>
       <c r="I92" s="1" t="s">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="J92" s="3">
         <v>4</v>
@@ -6386,7 +6458,7 @@
         <v>5</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="D93" s="3">
         <v>2</v>
@@ -6401,7 +6473,7 @@
         <v>4</v>
       </c>
       <c r="I93" s="1" t="s">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="J93" s="3">
         <v>4</v>
@@ -6433,7 +6505,7 @@
         <v>5</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="D94" s="3">
         <v>2</v>
@@ -6448,7 +6520,7 @@
         <v>5</v>
       </c>
       <c r="I94" s="1" t="s">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="J94" s="3">
         <v>4</v>
@@ -6480,7 +6552,7 @@
         <v>5</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="D95" s="3">
         <v>2</v>
@@ -6495,7 +6567,7 @@
         <v>6</v>
       </c>
       <c r="I95" s="1" t="s">
-        <v>170</v>
+        <v>185</v>
       </c>
       <c r="J95" s="3">
         <v>4</v>
@@ -6528,7 +6600,7 @@
         <v>5</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="D96" s="3">
         <v>2</v>
@@ -6543,7 +6615,7 @@
         <v>7</v>
       </c>
       <c r="I96" s="1" t="s">
-        <v>167</v>
+        <v>186</v>
       </c>
       <c r="J96" s="3">
         <v>4</v>
@@ -6576,7 +6648,7 @@
         <v>5</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="D97" s="3">
         <v>2</v>
@@ -6591,13 +6663,13 @@
         <v>8</v>
       </c>
       <c r="I97" s="1" t="s">
-        <v>171</v>
+        <v>187</v>
       </c>
       <c r="J97" s="3">
         <v>4</v>
       </c>
       <c r="K97" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L97" s="5">
         <f t="shared" si="33"/>
@@ -6624,7 +6696,7 @@
         <v>5</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="D98" s="3">
         <v>2</v>
@@ -6639,13 +6711,13 @@
         <v>9</v>
       </c>
       <c r="I98" s="1" t="s">
-        <v>172</v>
+        <v>188</v>
       </c>
       <c r="J98" s="3">
         <v>4</v>
       </c>
       <c r="K98" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L98" s="5">
         <f t="shared" si="33"/>
@@ -6672,7 +6744,7 @@
         <v>5</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="D99" s="3">
         <v>2</v>
@@ -6687,13 +6759,13 @@
         <v>10</v>
       </c>
       <c r="I99" s="1" t="s">
-        <v>166</v>
+        <v>189</v>
       </c>
       <c r="J99" s="3">
         <v>4</v>
       </c>
       <c r="K99" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="L99" s="5">
         <f t="shared" si="33"/>
@@ -6720,7 +6792,7 @@
         <v>5</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="D100" s="3">
         <v>2</v>
@@ -6735,13 +6807,13 @@
         <v>11</v>
       </c>
       <c r="I100" s="1" t="s">
-        <v>168</v>
+        <v>190</v>
       </c>
       <c r="J100" s="3">
         <v>4</v>
       </c>
       <c r="K100" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="L100" s="5">
         <f t="shared" si="33"/>
@@ -6768,7 +6840,7 @@
         <v>5</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="D101" s="3">
         <v>2</v>
@@ -6783,13 +6855,13 @@
         <v>12</v>
       </c>
       <c r="I101" s="1" t="s">
-        <v>173</v>
+        <v>191</v>
       </c>
       <c r="J101" s="3">
         <v>4</v>
       </c>
       <c r="K101" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="L101" s="5">
         <f t="shared" si="33"/>
@@ -6816,7 +6888,7 @@
         <v>5</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="D102" s="3">
         <v>2</v>
@@ -6831,13 +6903,13 @@
         <v>13</v>
       </c>
       <c r="I102" s="1" t="s">
-        <v>174</v>
+        <v>192</v>
       </c>
       <c r="J102" s="3">
         <v>4</v>
       </c>
       <c r="K102" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="L102" s="5">
         <f t="shared" si="33"/>
@@ -6864,7 +6936,7 @@
         <v>5</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="D103" s="3">
         <v>2</v>
@@ -6879,13 +6951,13 @@
         <v>14</v>
       </c>
       <c r="I103" s="1" t="s">
-        <v>175</v>
+        <v>193</v>
       </c>
       <c r="J103" s="3">
         <v>4</v>
       </c>
       <c r="K103" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="L103" s="5">
         <f t="shared" si="33"/>
@@ -6912,7 +6984,7 @@
         <v>5</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="D104" s="3">
         <v>2</v>
@@ -6927,13 +6999,13 @@
         <v>15</v>
       </c>
       <c r="I104" s="1" t="s">
-        <v>176</v>
+        <v>194</v>
       </c>
       <c r="J104" s="3">
         <v>4</v>
       </c>
       <c r="K104" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="L104" s="5">
         <f t="shared" si="33"/>
@@ -6960,7 +7032,7 @@
         <v>5</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="D105" s="3">
         <v>2</v>
@@ -6975,13 +7047,13 @@
         <v>16</v>
       </c>
       <c r="I105" s="1" t="s">
-        <v>177</v>
+        <v>195</v>
       </c>
       <c r="J105" s="3">
         <v>4</v>
       </c>
       <c r="K105" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="L105" s="5">
         <f t="shared" si="33"/>
@@ -7008,7 +7080,7 @@
         <v>5</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="D106" s="3">
         <v>2</v>
@@ -7023,13 +7095,13 @@
         <v>17</v>
       </c>
       <c r="I106" s="1" t="s">
-        <v>176</v>
+        <v>196</v>
       </c>
       <c r="J106" s="3">
         <v>4</v>
       </c>
       <c r="K106" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="L106" s="5">
         <f t="shared" si="33"/>
@@ -7056,7 +7128,7 @@
         <v>5</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="D107" s="3">
         <v>2</v>
@@ -7071,13 +7143,13 @@
         <v>18</v>
       </c>
       <c r="I107" s="1" t="s">
-        <v>178</v>
+        <v>197</v>
       </c>
       <c r="J107" s="3">
         <v>4</v>
       </c>
       <c r="K107" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="L107" s="5">
         <f t="shared" si="33"/>
@@ -7104,7 +7176,7 @@
         <v>5</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="D108" s="3">
         <v>2</v>
@@ -7119,13 +7191,13 @@
         <v>19</v>
       </c>
       <c r="I108" s="1" t="s">
-        <v>179</v>
+        <v>198</v>
       </c>
       <c r="J108" s="3">
         <v>4</v>
       </c>
       <c r="K108" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="L108" s="5">
         <f t="shared" si="33"/>
@@ -7152,7 +7224,7 @@
         <v>5</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="D109" s="3">
         <v>2</v>
@@ -7187,7 +7259,7 @@
         <v>6</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="D110" s="3">
         <v>4</v>
@@ -7202,7 +7274,7 @@
         <v>0</v>
       </c>
       <c r="I110" s="1" t="s">
-        <v>181</v>
+        <v>200</v>
       </c>
       <c r="J110" s="3">
         <v>4</v>
@@ -7233,7 +7305,7 @@
         <v>6</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="D111" s="3">
         <v>4</v>
@@ -7248,7 +7320,7 @@
         <v>1</v>
       </c>
       <c r="I111" s="1" t="s">
-        <v>182</v>
+        <v>201</v>
       </c>
       <c r="J111" s="3">
         <v>4</v>
@@ -7280,7 +7352,7 @@
         <v>6</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="D112" s="3">
         <v>4</v>
@@ -7295,7 +7367,7 @@
         <v>2</v>
       </c>
       <c r="I112" s="1" t="s">
-        <v>183</v>
+        <v>202</v>
       </c>
       <c r="J112" s="3">
         <v>4</v>
@@ -7327,7 +7399,7 @@
         <v>6</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="D113" s="3">
         <v>4</v>
@@ -7342,7 +7414,7 @@
         <v>3</v>
       </c>
       <c r="I113" s="1" t="s">
-        <v>184</v>
+        <v>203</v>
       </c>
       <c r="J113" s="3">
         <v>4</v>
@@ -7374,7 +7446,7 @@
         <v>6</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="D114" s="3">
         <v>4</v>
@@ -7389,7 +7461,7 @@
         <v>4</v>
       </c>
       <c r="I114" s="1" t="s">
-        <v>185</v>
+        <v>204</v>
       </c>
       <c r="J114" s="3">
         <v>4</v>
@@ -7421,7 +7493,7 @@
         <v>6</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="D115" s="3">
         <v>4</v>
@@ -7436,7 +7508,7 @@
         <v>5</v>
       </c>
       <c r="I115" s="1" t="s">
-        <v>186</v>
+        <v>205</v>
       </c>
       <c r="J115" s="3">
         <v>4</v>
@@ -7468,7 +7540,7 @@
         <v>6</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="D116" s="3">
         <v>4</v>
@@ -7483,7 +7555,7 @@
         <v>6</v>
       </c>
       <c r="I116" s="1" t="s">
-        <v>187</v>
+        <v>206</v>
       </c>
       <c r="J116" s="3">
         <v>4</v>
@@ -7516,7 +7588,7 @@
         <v>6</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="D117" s="3">
         <v>4</v>
@@ -7531,7 +7603,7 @@
         <v>7</v>
       </c>
       <c r="I117" s="1" t="s">
-        <v>184</v>
+        <v>207</v>
       </c>
       <c r="J117" s="3">
         <v>4</v>
@@ -7564,7 +7636,7 @@
         <v>6</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="D118" s="3">
         <v>4</v>
@@ -7579,13 +7651,13 @@
         <v>8</v>
       </c>
       <c r="I118" s="1" t="s">
-        <v>188</v>
+        <v>208</v>
       </c>
       <c r="J118" s="3">
         <v>4</v>
       </c>
       <c r="K118" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L118" s="5">
         <f t="shared" si="41"/>
@@ -7612,7 +7684,7 @@
         <v>6</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="D119" s="3">
         <v>4</v>
@@ -7627,13 +7699,13 @@
         <v>9</v>
       </c>
       <c r="I119" s="1" t="s">
-        <v>189</v>
+        <v>209</v>
       </c>
       <c r="J119" s="3">
         <v>4</v>
       </c>
       <c r="K119" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L119" s="5">
         <f t="shared" si="41"/>
@@ -7660,7 +7732,7 @@
         <v>6</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="D120" s="3">
         <v>4</v>
@@ -7675,13 +7747,13 @@
         <v>10</v>
       </c>
       <c r="I120" s="1" t="s">
-        <v>183</v>
+        <v>210</v>
       </c>
       <c r="J120" s="3">
         <v>4</v>
       </c>
       <c r="K120" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="L120" s="5">
         <f t="shared" si="41"/>
@@ -7708,7 +7780,7 @@
         <v>6</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="D121" s="3">
         <v>4</v>
@@ -7723,13 +7795,13 @@
         <v>11</v>
       </c>
       <c r="I121" s="1" t="s">
-        <v>185</v>
+        <v>211</v>
       </c>
       <c r="J121" s="3">
         <v>4</v>
       </c>
       <c r="K121" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="L121" s="5">
         <f t="shared" si="41"/>
@@ -7756,7 +7828,7 @@
         <v>6</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="D122" s="3">
         <v>4</v>
@@ -7771,13 +7843,13 @@
         <v>12</v>
       </c>
       <c r="I122" s="1" t="s">
-        <v>190</v>
+        <v>212</v>
       </c>
       <c r="J122" s="3">
         <v>4</v>
       </c>
       <c r="K122" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="L122" s="5">
         <f t="shared" si="41"/>
@@ -7804,7 +7876,7 @@
         <v>6</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="D123" s="3">
         <v>4</v>
@@ -7819,13 +7891,13 @@
         <v>13</v>
       </c>
       <c r="I123" s="1" t="s">
-        <v>191</v>
+        <v>213</v>
       </c>
       <c r="J123" s="3">
         <v>4</v>
       </c>
       <c r="K123" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="L123" s="5">
         <f t="shared" si="41"/>
@@ -7852,7 +7924,7 @@
         <v>6</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="D124" s="3">
         <v>4</v>
@@ -7867,13 +7939,13 @@
         <v>14</v>
       </c>
       <c r="I124" s="1" t="s">
-        <v>192</v>
+        <v>214</v>
       </c>
       <c r="J124" s="3">
         <v>4</v>
       </c>
       <c r="K124" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="L124" s="5">
         <f t="shared" si="41"/>
@@ -7900,7 +7972,7 @@
         <v>6</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="D125" s="3">
         <v>4</v>
@@ -7915,13 +7987,13 @@
         <v>15</v>
       </c>
       <c r="I125" s="1" t="s">
-        <v>193</v>
+        <v>215</v>
       </c>
       <c r="J125" s="3">
         <v>4</v>
       </c>
       <c r="K125" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="L125" s="5">
         <f t="shared" si="41"/>
@@ -7948,7 +8020,7 @@
         <v>6</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="D126" s="3">
         <v>4</v>
@@ -7963,13 +8035,13 @@
         <v>16</v>
       </c>
       <c r="I126" s="1" t="s">
-        <v>194</v>
+        <v>216</v>
       </c>
       <c r="J126" s="3">
         <v>4</v>
       </c>
       <c r="K126" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="L126" s="5">
         <f t="shared" si="41"/>
@@ -7996,7 +8068,7 @@
         <v>6</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="D127" s="3">
         <v>4</v>
@@ -8011,13 +8083,13 @@
         <v>17</v>
       </c>
       <c r="I127" s="1" t="s">
-        <v>193</v>
+        <v>217</v>
       </c>
       <c r="J127" s="3">
         <v>4</v>
       </c>
       <c r="K127" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="L127" s="5">
         <f t="shared" si="41"/>
@@ -8044,7 +8116,7 @@
         <v>6</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="D128" s="3">
         <v>4</v>
@@ -8059,13 +8131,13 @@
         <v>18</v>
       </c>
       <c r="I128" s="1" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="J128" s="3">
         <v>4</v>
       </c>
       <c r="K128" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="L128" s="5">
         <f t="shared" si="41"/>
@@ -8092,7 +8164,7 @@
         <v>6</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="D129" s="3">
         <v>4</v>
@@ -8107,13 +8179,13 @@
         <v>19</v>
       </c>
       <c r="I129" s="1" t="s">
-        <v>196</v>
+        <v>219</v>
       </c>
       <c r="J129" s="3">
         <v>4</v>
       </c>
       <c r="K129" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="L129" s="5">
         <f t="shared" si="41"/>
@@ -8140,7 +8212,7 @@
         <v>6</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="D130" s="3">
         <v>4</v>
@@ -8175,7 +8247,7 @@
         <v>7</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="D131" s="3">
         <v>4</v>
@@ -8216,7 +8288,7 @@
         <v>7</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="D132" s="3">
         <v>4</v>
@@ -8269,7 +8341,7 @@
     </row>
     <row r="2" ht="14.25" spans="1:16">
       <c r="A2" s="2" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -8513,7 +8585,7 @@
     </row>
     <row r="10" spans="1:16">
       <c r="A10" s="1" t="s">
-        <v>199</v>
+        <v>222</v>
       </c>
       <c r="B10" t="str" cm="1">
         <f t="array" ref="B10:C10">_xlfn.TEXTSPLIT(A10,";")</f>
@@ -8565,7 +8637,7 @@
     </row>
     <row r="11" spans="1:16">
       <c r="A11" s="1" t="s">
-        <v>200</v>
+        <v>223</v>
       </c>
       <c r="B11" t="str" cm="1">
         <f t="array" ref="B11">_xlfn.TEXTSPLIT(A11,";")</f>
@@ -8611,7 +8683,7 @@
     </row>
     <row r="12" spans="1:16">
       <c r="A12" s="1" t="s">
-        <v>201</v>
+        <v>224</v>
       </c>
       <c r="B12" t="str" cm="1">
         <f t="array" ref="B12">_xlfn.TEXTSPLIT(A12,";")</f>
@@ -8657,7 +8729,7 @@
     </row>
     <row r="13" spans="1:16">
       <c r="A13" s="1" t="s">
-        <v>202</v>
+        <v>225</v>
       </c>
       <c r="B13" t="str" cm="1">
         <f t="array" ref="B13">_xlfn.TEXTSPLIT(A13,";")</f>
@@ -8703,7 +8775,7 @@
     </row>
     <row r="14" spans="1:16">
       <c r="A14" s="1" t="s">
-        <v>203</v>
+        <v>226</v>
       </c>
       <c r="B14" t="str" cm="1">
         <f t="array" ref="B14:C14">_xlfn.TEXTSPLIT(A14,";")</f>
@@ -8755,7 +8827,7 @@
     </row>
     <row r="15" spans="1:16">
       <c r="A15" s="1" t="s">
-        <v>204</v>
+        <v>227</v>
       </c>
       <c r="B15" t="str" cm="1">
         <f t="array" ref="B15">_xlfn.TEXTSPLIT(A15,";")</f>
@@ -8801,7 +8873,7 @@
     </row>
     <row r="16" spans="1:16">
       <c r="A16" s="1" t="s">
-        <v>205</v>
+        <v>228</v>
       </c>
       <c r="B16" t="str" cm="1">
         <f t="array" ref="B16">_xlfn.TEXTSPLIT(A16,";")</f>
@@ -8847,7 +8919,7 @@
     </row>
     <row r="17" spans="1:16">
       <c r="A17" s="1" t="s">
-        <v>206</v>
+        <v>229</v>
       </c>
       <c r="B17" t="str" cm="1">
         <f t="array" ref="B17">_xlfn.TEXTSPLIT(A17,";")</f>
@@ -8893,7 +8965,7 @@
     </row>
     <row r="18" spans="1:16">
       <c r="A18" s="1" t="s">
-        <v>207</v>
+        <v>230</v>
       </c>
       <c r="B18" t="str" cm="1">
         <f t="array" ref="B18:C18">_xlfn.TEXTSPLIT(A18,";")</f>
@@ -8945,7 +9017,7 @@
     </row>
     <row r="19" spans="1:16">
       <c r="A19" s="1" t="s">
-        <v>208</v>
+        <v>231</v>
       </c>
       <c r="B19" t="str" cm="1">
         <f t="array" ref="B19">_xlfn.TEXTSPLIT(A19,";")</f>
@@ -8991,7 +9063,7 @@
     </row>
     <row r="20" spans="1:16">
       <c r="A20" s="1" t="s">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="B20" t="str" cm="1">
         <f t="array" ref="B20">_xlfn.TEXTSPLIT(A20,";")</f>
@@ -9037,7 +9109,7 @@
     </row>
     <row r="21" spans="1:16">
       <c r="A21" s="1" t="s">
-        <v>210</v>
+        <v>233</v>
       </c>
       <c r="B21" t="str" cm="1">
         <f t="array" ref="B21:C21">_xlfn.TEXTSPLIT(A21,";")</f>
@@ -9089,7 +9161,7 @@
     </row>
     <row r="22" spans="1:16">
       <c r="A22" s="1" t="s">
-        <v>211</v>
+        <v>234</v>
       </c>
       <c r="B22" t="str" cm="1">
         <f t="array" ref="B22">_xlfn.TEXTSPLIT(A22,";")</f>
@@ -9135,7 +9207,7 @@
     </row>
     <row r="23" spans="1:16">
       <c r="A23" s="1" t="s">
-        <v>212</v>
+        <v>235</v>
       </c>
       <c r="B23" t="str" cm="1">
         <f t="array" ref="B23">_xlfn.TEXTSPLIT(A23,";")</f>
@@ -9181,7 +9253,7 @@
     </row>
     <row r="24" spans="1:16">
       <c r="A24" s="1" t="s">
-        <v>213</v>
+        <v>236</v>
       </c>
       <c r="B24" t="str" cm="1">
         <f t="array" ref="B24">_xlfn.TEXTSPLIT(A24,";")</f>
@@ -9235,7 +9307,7 @@
     </row>
     <row r="26" spans="1:16">
       <c r="A26" s="1" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B26" t="str" cm="1">
         <f t="array" ref="B26">_xlfn.TEXTSPLIT(A26,";")</f>
@@ -9285,7 +9357,7 @@
     </row>
     <row r="27" spans="1:16">
       <c r="A27" s="1" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="B27" t="str" cm="1">
         <f t="array" ref="B27">_xlfn.TEXTSPLIT(A27,";")</f>
@@ -9331,7 +9403,7 @@
     </row>
     <row r="28" spans="1:16">
       <c r="A28" s="1" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B28" t="str" cm="1">
         <f t="array" ref="B28">_xlfn.TEXTSPLIT(A28,";")</f>
@@ -9377,7 +9449,7 @@
     </row>
     <row r="29" spans="1:16">
       <c r="A29" s="1" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="B29" t="str" cm="1">
         <f t="array" ref="B29">_xlfn.TEXTSPLIT(A29,";")</f>
@@ -9423,7 +9495,7 @@
     </row>
     <row r="30" spans="1:16">
       <c r="A30" s="1" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="B30" t="str" cm="1">
         <f t="array" ref="B30">_xlfn.TEXTSPLIT(A30,";")</f>
@@ -9463,7 +9535,7 @@
     </row>
     <row r="31" spans="1:16">
       <c r="A31" s="1" t="s">
-        <v>214</v>
+        <v>237</v>
       </c>
       <c r="B31" t="str" cm="1">
         <f t="array" ref="B31:C31">_xlfn.TEXTSPLIT(A31,";")</f>
@@ -9509,7 +9581,7 @@
     </row>
     <row r="32" spans="1:16">
       <c r="A32" s="1" t="s">
-        <v>215</v>
+        <v>238</v>
       </c>
       <c r="B32" t="str" cm="1">
         <f t="array" ref="B32">_xlfn.TEXTSPLIT(A32,";")</f>
@@ -9549,7 +9621,7 @@
     </row>
     <row r="33" spans="1:13">
       <c r="A33" s="1" t="s">
-        <v>216</v>
+        <v>239</v>
       </c>
       <c r="B33" t="str" cm="1">
         <f t="array" ref="B33">_xlfn.TEXTSPLIT(A33,";")</f>
@@ -9589,7 +9661,7 @@
     </row>
     <row r="34" spans="1:13">
       <c r="A34" s="1" t="s">
-        <v>217</v>
+        <v>240</v>
       </c>
       <c r="B34" t="str" cm="1">
         <f t="array" ref="B34">_xlfn.TEXTSPLIT(A34,";")</f>
@@ -9629,7 +9701,7 @@
     </row>
     <row r="35" spans="1:13">
       <c r="A35" s="1" t="s">
-        <v>218</v>
+        <v>241</v>
       </c>
       <c r="B35" t="str" cm="1">
         <f t="array" ref="B35:C35">_xlfn.TEXTSPLIT(A35,";")</f>
@@ -9675,7 +9747,7 @@
     </row>
     <row r="36" spans="1:13">
       <c r="A36" s="1" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="B36" t="str" cm="1">
         <f t="array" ref="B36">_xlfn.TEXTSPLIT(A36,";")</f>
@@ -9715,7 +9787,7 @@
     </row>
     <row r="37" spans="1:13">
       <c r="A37" s="1" t="s">
-        <v>220</v>
+        <v>243</v>
       </c>
       <c r="B37" t="str" cm="1">
         <f t="array" ref="B37">_xlfn.TEXTSPLIT(A37,";")</f>
@@ -9755,7 +9827,7 @@
     </row>
     <row r="38" spans="1:13">
       <c r="A38" s="1" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="B38" t="str" cm="1">
         <f t="array" ref="B38">_xlfn.TEXTSPLIT(A38,";")</f>
@@ -9795,7 +9867,7 @@
     </row>
     <row r="39" spans="1:13">
       <c r="A39" s="1" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="B39" t="str" cm="1">
         <f t="array" ref="B39:C39">_xlfn.TEXTSPLIT(A39,";")</f>
@@ -9841,7 +9913,7 @@
     </row>
     <row r="40" spans="1:13">
       <c r="A40" s="1" t="s">
-        <v>223</v>
+        <v>246</v>
       </c>
       <c r="B40" t="str" cm="1">
         <f t="array" ref="B40">_xlfn.TEXTSPLIT(A40,";")</f>
@@ -9881,7 +9953,7 @@
     </row>
     <row r="41" spans="1:13">
       <c r="A41" s="1" t="s">
-        <v>224</v>
+        <v>247</v>
       </c>
       <c r="B41" t="str" cm="1">
         <f t="array" ref="B41">_xlfn.TEXTSPLIT(A41,";")</f>
@@ -9921,7 +9993,7 @@
     </row>
     <row r="42" spans="1:13">
       <c r="A42" s="1" t="s">
-        <v>225</v>
+        <v>248</v>
       </c>
       <c r="B42" t="str" cm="1">
         <f t="array" ref="B42:C42">_xlfn.TEXTSPLIT(A42,";")</f>
@@ -9967,7 +10039,7 @@
     </row>
     <row r="43" spans="1:13">
       <c r="A43" s="1" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="B43" t="str" cm="1">
         <f t="array" ref="B43">_xlfn.TEXTSPLIT(A43,";")</f>
@@ -10007,7 +10079,7 @@
     </row>
     <row r="44" spans="1:13">
       <c r="A44" s="1" t="s">
-        <v>227</v>
+        <v>250</v>
       </c>
       <c r="B44" t="str" cm="1">
         <f t="array" ref="B44">_xlfn.TEXTSPLIT(A44,";")</f>
@@ -10047,7 +10119,7 @@
     </row>
     <row r="45" spans="1:13">
       <c r="A45" s="1" t="s">
-        <v>228</v>
+        <v>251</v>
       </c>
       <c r="B45" t="str" cm="1">
         <f t="array" ref="B45">_xlfn.TEXTSPLIT(A45,";")</f>
@@ -10087,7 +10159,7 @@
     </row>
     <row r="47" spans="1:13">
       <c r="A47" s="1" t="s">
-        <v>122</v>
+        <v>252</v>
       </c>
       <c r="B47" t="str" cm="1">
         <f t="array" ref="B47">_xlfn.TEXTSPLIT(A47,";")</f>
@@ -10131,7 +10203,7 @@
     </row>
     <row r="48" spans="1:13">
       <c r="A48" s="1" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B48" t="str" cm="1">
         <f t="array" ref="B48">_xlfn.TEXTSPLIT(A48,";")</f>
@@ -10171,7 +10243,7 @@
     </row>
     <row r="49" spans="1:13">
       <c r="A49" s="1" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="B49" t="str" cm="1">
         <f t="array" ref="B49">_xlfn.TEXTSPLIT(A49,";")</f>
@@ -10211,7 +10283,7 @@
     </row>
     <row r="50" spans="1:13">
       <c r="A50" s="1" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="B50" t="str" cm="1">
         <f t="array" ref="B50">_xlfn.TEXTSPLIT(A50,";")</f>
@@ -10251,7 +10323,7 @@
     </row>
     <row r="51" spans="1:13">
       <c r="A51" s="1" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B51" t="str" cm="1">
         <f t="array" ref="B51">_xlfn.TEXTSPLIT(A51,";")</f>
@@ -10291,7 +10363,7 @@
     </row>
     <row r="52" spans="1:13">
       <c r="A52" s="1" t="s">
-        <v>229</v>
+        <v>253</v>
       </c>
       <c r="B52" t="str" cm="1">
         <f t="array" ref="B52:C52">_xlfn.TEXTSPLIT(A52,";")</f>
@@ -10337,7 +10409,7 @@
     </row>
     <row r="53" spans="1:13">
       <c r="A53" s="1" t="s">
-        <v>230</v>
+        <v>254</v>
       </c>
       <c r="B53" t="str" cm="1">
         <f t="array" ref="B53">_xlfn.TEXTSPLIT(A53,";")</f>
@@ -10377,7 +10449,7 @@
     </row>
     <row r="54" spans="1:13">
       <c r="A54" s="1" t="s">
-        <v>215</v>
+        <v>238</v>
       </c>
       <c r="B54" t="str" cm="1">
         <f t="array" ref="B54">_xlfn.TEXTSPLIT(A54,";")</f>
@@ -10417,7 +10489,7 @@
     </row>
     <row r="55" spans="1:13">
       <c r="A55" s="1" t="s">
-        <v>216</v>
+        <v>239</v>
       </c>
       <c r="B55" t="str" cm="1">
         <f t="array" ref="B55">_xlfn.TEXTSPLIT(A55,";")</f>
@@ -10457,7 +10529,7 @@
     </row>
     <row r="56" spans="1:13">
       <c r="A56" s="1" t="s">
-        <v>231</v>
+        <v>255</v>
       </c>
       <c r="B56" t="str" cm="1">
         <f t="array" ref="B56:C56">_xlfn.TEXTSPLIT(A56,";")</f>
@@ -10503,7 +10575,7 @@
     </row>
     <row r="57" spans="1:13">
       <c r="A57" s="1" t="s">
-        <v>232</v>
+        <v>256</v>
       </c>
       <c r="B57" t="str" cm="1">
         <f t="array" ref="B57">_xlfn.TEXTSPLIT(A57,";")</f>
@@ -10543,7 +10615,7 @@
     </row>
     <row r="58" spans="1:13">
       <c r="A58" s="1" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="B58" t="str" cm="1">
         <f t="array" ref="B58">_xlfn.TEXTSPLIT(A58,";")</f>
@@ -10583,7 +10655,7 @@
     </row>
     <row r="59" spans="1:13">
       <c r="A59" s="1" t="s">
-        <v>220</v>
+        <v>243</v>
       </c>
       <c r="B59" t="str" cm="1">
         <f t="array" ref="B59">_xlfn.TEXTSPLIT(A59,";")</f>
@@ -10623,7 +10695,7 @@
     </row>
     <row r="60" spans="1:13">
       <c r="A60" s="1" t="s">
-        <v>233</v>
+        <v>257</v>
       </c>
       <c r="B60" t="str" cm="1">
         <f t="array" ref="B60:C60">_xlfn.TEXTSPLIT(A60,";")</f>
@@ -10669,7 +10741,7 @@
     </row>
     <row r="61" spans="1:13">
       <c r="A61" s="1" t="s">
-        <v>234</v>
+        <v>258</v>
       </c>
       <c r="B61" t="str" cm="1">
         <f t="array" ref="B61">_xlfn.TEXTSPLIT(A61,";")</f>
@@ -10709,7 +10781,7 @@
     </row>
     <row r="62" spans="1:13">
       <c r="A62" s="1" t="s">
-        <v>223</v>
+        <v>246</v>
       </c>
       <c r="B62" t="str" cm="1">
         <f t="array" ref="B62">_xlfn.TEXTSPLIT(A62,";")</f>
@@ -10749,7 +10821,7 @@
     </row>
     <row r="63" spans="1:13">
       <c r="A63" s="1" t="s">
-        <v>235</v>
+        <v>259</v>
       </c>
       <c r="B63" t="str" cm="1">
         <f t="array" ref="B63:C63">_xlfn.TEXTSPLIT(A63,";")</f>
@@ -10795,7 +10867,7 @@
     </row>
     <row r="64" spans="1:13">
       <c r="A64" s="1" t="s">
-        <v>236</v>
+        <v>260</v>
       </c>
       <c r="B64" t="str" cm="1">
         <f t="array" ref="B64">_xlfn.TEXTSPLIT(A64,";")</f>
@@ -10835,7 +10907,7 @@
     </row>
     <row r="65" spans="1:13">
       <c r="A65" s="1" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="B65" t="str" cm="1">
         <f t="array" ref="B65">_xlfn.TEXTSPLIT(A65,";")</f>
@@ -10875,7 +10947,7 @@
     </row>
     <row r="66" spans="1:13">
       <c r="A66" s="1" t="s">
-        <v>227</v>
+        <v>250</v>
       </c>
       <c r="B66" t="str" cm="1">
         <f t="array" ref="B66">_xlfn.TEXTSPLIT(A66,";")</f>
@@ -10915,7 +10987,7 @@
     </row>
     <row r="68" spans="1:13">
       <c r="A68" s="1" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="B68" t="str" cm="1">
         <f t="array" ref="B68">_xlfn.TEXTSPLIT(A68,";")</f>
@@ -10959,7 +11031,7 @@
     </row>
     <row r="69" spans="1:13">
       <c r="A69" s="1" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="B69" t="str" cm="1">
         <f t="array" ref="B69">_xlfn.TEXTSPLIT(A69,";")</f>
@@ -10999,7 +11071,7 @@
     </row>
     <row r="70" spans="1:13">
       <c r="A70" s="1" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="B70" t="str" cm="1">
         <f t="array" ref="B70">_xlfn.TEXTSPLIT(A70,";")</f>
@@ -11039,7 +11111,7 @@
     </row>
     <row r="71" spans="1:13">
       <c r="A71" s="1" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="B71" t="str" cm="1">
         <f t="array" ref="B71">_xlfn.TEXTSPLIT(A71,";")</f>
@@ -11079,7 +11151,7 @@
     </row>
     <row r="72" spans="1:13">
       <c r="A72" s="1" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="B72" t="str" cm="1">
         <f t="array" ref="B72">_xlfn.TEXTSPLIT(A72,";")</f>
@@ -11119,7 +11191,7 @@
     </row>
     <row r="73" spans="1:13">
       <c r="A73" s="1" t="s">
-        <v>237</v>
+        <v>261</v>
       </c>
       <c r="B73" t="str" cm="1">
         <f t="array" ref="B73:C73">_xlfn.TEXTSPLIT(A73,";")</f>
@@ -11165,7 +11237,7 @@
     </row>
     <row r="74" spans="1:13">
       <c r="A74" s="1" t="s">
-        <v>238</v>
+        <v>262</v>
       </c>
       <c r="B74" t="str" cm="1">
         <f t="array" ref="B74">_xlfn.TEXTSPLIT(A74,";")</f>
@@ -11205,7 +11277,7 @@
     </row>
     <row r="75" spans="1:13">
       <c r="A75" s="1" t="s">
-        <v>239</v>
+        <v>263</v>
       </c>
       <c r="B75" t="str" cm="1">
         <f t="array" ref="B75">_xlfn.TEXTSPLIT(A75,";")</f>
@@ -11245,7 +11317,7 @@
     </row>
     <row r="76" spans="1:13">
       <c r="A76" s="1" t="s">
-        <v>240</v>
+        <v>264</v>
       </c>
       <c r="B76" t="str" cm="1">
         <f t="array" ref="B76">_xlfn.TEXTSPLIT(A76,";")</f>
@@ -11285,7 +11357,7 @@
     </row>
     <row r="77" spans="1:13">
       <c r="A77" s="1" t="s">
-        <v>241</v>
+        <v>265</v>
       </c>
       <c r="B77" t="str" cm="1">
         <f t="array" ref="B77:C77">_xlfn.TEXTSPLIT(A77,";")</f>
@@ -11331,7 +11403,7 @@
     </row>
     <row r="78" spans="1:13">
       <c r="A78" s="1" t="s">
-        <v>242</v>
+        <v>266</v>
       </c>
       <c r="B78" t="str" cm="1">
         <f t="array" ref="B78">_xlfn.TEXTSPLIT(A78,";")</f>
@@ -11371,7 +11443,7 @@
     </row>
     <row r="79" spans="1:13">
       <c r="A79" s="1" t="s">
-        <v>243</v>
+        <v>267</v>
       </c>
       <c r="B79" t="str" cm="1">
         <f t="array" ref="B79">_xlfn.TEXTSPLIT(A79,";")</f>
@@ -11411,7 +11483,7 @@
     </row>
     <row r="80" spans="1:13">
       <c r="A80" s="1" t="s">
-        <v>244</v>
+        <v>268</v>
       </c>
       <c r="B80" t="str" cm="1">
         <f t="array" ref="B80">_xlfn.TEXTSPLIT(A80,";")</f>
@@ -11451,7 +11523,7 @@
     </row>
     <row r="81" spans="1:13">
       <c r="A81" s="1" t="s">
-        <v>245</v>
+        <v>269</v>
       </c>
       <c r="B81" t="str" cm="1">
         <f t="array" ref="B81:C81">_xlfn.TEXTSPLIT(A81,";")</f>
@@ -11497,7 +11569,7 @@
     </row>
     <row r="82" spans="1:13">
       <c r="A82" s="1" t="s">
-        <v>246</v>
+        <v>270</v>
       </c>
       <c r="B82" t="str" cm="1">
         <f t="array" ref="B82">_xlfn.TEXTSPLIT(A82,";")</f>
@@ -11537,7 +11609,7 @@
     </row>
     <row r="83" spans="1:13">
       <c r="A83" s="1" t="s">
-        <v>247</v>
+        <v>271</v>
       </c>
       <c r="B83" t="str" cm="1">
         <f t="array" ref="B83">_xlfn.TEXTSPLIT(A83,";")</f>
@@ -11577,7 +11649,7 @@
     </row>
     <row r="84" spans="1:13">
       <c r="A84" s="1" t="s">
-        <v>248</v>
+        <v>272</v>
       </c>
       <c r="B84" t="str" cm="1">
         <f t="array" ref="B84:C84">_xlfn.TEXTSPLIT(A84,";")</f>
@@ -11623,7 +11695,7 @@
     </row>
     <row r="85" spans="1:13">
       <c r="A85" s="1" t="s">
-        <v>249</v>
+        <v>273</v>
       </c>
       <c r="B85" t="str" cm="1">
         <f t="array" ref="B85">_xlfn.TEXTSPLIT(A85,";")</f>
@@ -11663,7 +11735,7 @@
     </row>
     <row r="86" spans="1:13">
       <c r="A86" s="1" t="s">
-        <v>250</v>
+        <v>274</v>
       </c>
       <c r="B86" t="str" cm="1">
         <f t="array" ref="B86">_xlfn.TEXTSPLIT(A86,";")</f>
@@ -11703,7 +11775,7 @@
     </row>
     <row r="87" spans="1:13">
       <c r="A87" s="1" t="s">
-        <v>251</v>
+        <v>275</v>
       </c>
       <c r="B87" t="str" cm="1">
         <f t="array" ref="B87">_xlfn.TEXTSPLIT(A87,";")</f>
@@ -11743,7 +11815,7 @@
     </row>
     <row r="89" spans="1:13">
       <c r="A89" s="1" t="s">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="B89" t="str" cm="1">
         <f t="array" ref="B89">_xlfn.TEXTSPLIT(A89,";")</f>
@@ -11787,7 +11859,7 @@
     </row>
     <row r="90" spans="1:13">
       <c r="A90" s="1" t="s">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="B90" t="str" cm="1">
         <f t="array" ref="B90">_xlfn.TEXTSPLIT(A90,";")</f>
@@ -11827,7 +11899,7 @@
     </row>
     <row r="91" spans="1:13">
       <c r="A91" s="1" t="s">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="B91" t="str" cm="1">
         <f t="array" ref="B91">_xlfn.TEXTSPLIT(A91,";")</f>
@@ -11867,7 +11939,7 @@
     </row>
     <row r="92" spans="1:13">
       <c r="A92" s="1" t="s">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="B92" t="str" cm="1">
         <f t="array" ref="B92">_xlfn.TEXTSPLIT(A92,";")</f>
@@ -11907,7 +11979,7 @@
     </row>
     <row r="93" spans="1:13">
       <c r="A93" s="1" t="s">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="B93" t="str" cm="1">
         <f t="array" ref="B93">_xlfn.TEXTSPLIT(A93,";")</f>
@@ -11947,7 +12019,7 @@
     </row>
     <row r="94" spans="1:13">
       <c r="A94" s="1" t="s">
-        <v>252</v>
+        <v>276</v>
       </c>
       <c r="B94" t="str" cm="1">
         <f t="array" ref="B94:C94">_xlfn.TEXTSPLIT(A94,";")</f>
@@ -11993,7 +12065,7 @@
     </row>
     <row r="95" spans="1:13">
       <c r="A95" s="1" t="s">
-        <v>253</v>
+        <v>277</v>
       </c>
       <c r="B95" t="str" cm="1">
         <f t="array" ref="B95">_xlfn.TEXTSPLIT(A95,";")</f>
@@ -12033,7 +12105,7 @@
     </row>
     <row r="96" spans="1:13">
       <c r="A96" s="1" t="s">
-        <v>254</v>
+        <v>278</v>
       </c>
       <c r="B96" t="str" cm="1">
         <f t="array" ref="B96">_xlfn.TEXTSPLIT(A96,";")</f>
@@ -12073,7 +12145,7 @@
     </row>
     <row r="97" spans="1:13">
       <c r="A97" s="1" t="s">
-        <v>255</v>
+        <v>279</v>
       </c>
       <c r="B97" t="str" cm="1">
         <f t="array" ref="B97">_xlfn.TEXTSPLIT(A97,";")</f>
@@ -12113,7 +12185,7 @@
     </row>
     <row r="98" spans="1:13">
       <c r="A98" s="1" t="s">
-        <v>256</v>
+        <v>280</v>
       </c>
       <c r="B98" t="str" cm="1">
         <f t="array" ref="B98:C98">_xlfn.TEXTSPLIT(A98,";")</f>
@@ -12159,7 +12231,7 @@
     </row>
     <row r="99" spans="1:13">
       <c r="A99" s="1" t="s">
-        <v>257</v>
+        <v>281</v>
       </c>
       <c r="B99" t="str" cm="1">
         <f t="array" ref="B99">_xlfn.TEXTSPLIT(A99,";")</f>
@@ -12199,7 +12271,7 @@
     </row>
     <row r="100" spans="1:13">
       <c r="A100" s="1" t="s">
-        <v>258</v>
+        <v>282</v>
       </c>
       <c r="B100" t="str" cm="1">
         <f t="array" ref="B100">_xlfn.TEXTSPLIT(A100,";")</f>
@@ -12239,7 +12311,7 @@
     </row>
     <row r="101" spans="1:13">
       <c r="A101" s="1" t="s">
-        <v>259</v>
+        <v>283</v>
       </c>
       <c r="B101" t="str" cm="1">
         <f t="array" ref="B101">_xlfn.TEXTSPLIT(A101,";")</f>
@@ -12279,7 +12351,7 @@
     </row>
     <row r="102" spans="1:13">
       <c r="A102" s="1" t="s">
-        <v>260</v>
+        <v>284</v>
       </c>
       <c r="B102" t="str" cm="1">
         <f t="array" ref="B102:C102">_xlfn.TEXTSPLIT(A102,";")</f>
@@ -12325,7 +12397,7 @@
     </row>
     <row r="103" spans="1:13">
       <c r="A103" s="1" t="s">
-        <v>261</v>
+        <v>285</v>
       </c>
       <c r="B103" t="str" cm="1">
         <f t="array" ref="B103">_xlfn.TEXTSPLIT(A103,";")</f>
@@ -12365,7 +12437,7 @@
     </row>
     <row r="104" spans="1:13">
       <c r="A104" s="1" t="s">
-        <v>262</v>
+        <v>286</v>
       </c>
       <c r="B104" t="str" cm="1">
         <f t="array" ref="B104">_xlfn.TEXTSPLIT(A104,";")</f>
@@ -12405,7 +12477,7 @@
     </row>
     <row r="105" spans="1:13">
       <c r="A105" s="1" t="s">
-        <v>263</v>
+        <v>287</v>
       </c>
       <c r="B105" t="str" cm="1">
         <f t="array" ref="B105:C105">_xlfn.TEXTSPLIT(A105,";")</f>
@@ -12451,7 +12523,7 @@
     </row>
     <row r="106" spans="1:13">
       <c r="A106" s="1" t="s">
-        <v>264</v>
+        <v>288</v>
       </c>
       <c r="B106" t="str" cm="1">
         <f t="array" ref="B106">_xlfn.TEXTSPLIT(A106,";")</f>
@@ -12491,7 +12563,7 @@
     </row>
     <row r="107" spans="1:13">
       <c r="A107" s="1" t="s">
-        <v>265</v>
+        <v>289</v>
       </c>
       <c r="B107" t="str" cm="1">
         <f t="array" ref="B107">_xlfn.TEXTSPLIT(A107,";")</f>
@@ -12531,7 +12603,7 @@
     </row>
     <row r="108" spans="1:13">
       <c r="A108" s="1" t="s">
-        <v>266</v>
+        <v>290</v>
       </c>
       <c r="B108" t="str" cm="1">
         <f t="array" ref="B108">_xlfn.TEXTSPLIT(A108,";")</f>
@@ -12571,7 +12643,7 @@
     </row>
     <row r="110" spans="1:13">
       <c r="A110" s="1" t="s">
-        <v>181</v>
+        <v>200</v>
       </c>
       <c r="B110" t="str" cm="1">
         <f t="array" ref="B110">_xlfn.TEXTSPLIT(A110,";")</f>
@@ -12615,7 +12687,7 @@
     </row>
     <row r="111" spans="1:13">
       <c r="A111" s="1" t="s">
-        <v>182</v>
+        <v>201</v>
       </c>
       <c r="B111" t="str" cm="1">
         <f t="array" ref="B111">_xlfn.TEXTSPLIT(A111,";")</f>
@@ -12655,7 +12727,7 @@
     </row>
     <row r="112" spans="1:13">
       <c r="A112" s="1" t="s">
-        <v>183</v>
+        <v>202</v>
       </c>
       <c r="B112" t="str" cm="1">
         <f t="array" ref="B112">_xlfn.TEXTSPLIT(A112,";")</f>
@@ -12695,7 +12767,7 @@
     </row>
     <row r="113" spans="1:13">
       <c r="A113" s="1" t="s">
-        <v>184</v>
+        <v>203</v>
       </c>
       <c r="B113" t="str" cm="1">
         <f t="array" ref="B113">_xlfn.TEXTSPLIT(A113,";")</f>
@@ -12735,7 +12807,7 @@
     </row>
     <row r="114" spans="1:13">
       <c r="A114" s="1" t="s">
-        <v>185</v>
+        <v>204</v>
       </c>
       <c r="B114" t="str" cm="1">
         <f t="array" ref="B114">_xlfn.TEXTSPLIT(A114,";")</f>
@@ -12775,7 +12847,7 @@
     </row>
     <row r="115" spans="1:13">
       <c r="A115" s="1" t="s">
-        <v>267</v>
+        <v>291</v>
       </c>
       <c r="B115" t="str" cm="1">
         <f t="array" ref="B115:C115">_xlfn.TEXTSPLIT(A115,";")</f>
@@ -12821,7 +12893,7 @@
     </row>
     <row r="116" spans="1:13">
       <c r="A116" s="1" t="s">
-        <v>268</v>
+        <v>292</v>
       </c>
       <c r="B116" t="str" cm="1">
         <f t="array" ref="B116">_xlfn.TEXTSPLIT(A116,";")</f>
@@ -12861,7 +12933,7 @@
     </row>
     <row r="117" spans="1:13">
       <c r="A117" s="1" t="s">
-        <v>269</v>
+        <v>293</v>
       </c>
       <c r="B117" t="str" cm="1">
         <f t="array" ref="B117">_xlfn.TEXTSPLIT(A117,";")</f>
@@ -12901,7 +12973,7 @@
     </row>
     <row r="118" spans="1:13">
       <c r="A118" s="1" t="s">
-        <v>270</v>
+        <v>294</v>
       </c>
       <c r="B118" t="str" cm="1">
         <f t="array" ref="B118">_xlfn.TEXTSPLIT(A118,";")</f>
@@ -12941,7 +13013,7 @@
     </row>
     <row r="119" spans="1:13">
       <c r="A119" s="1" t="s">
-        <v>271</v>
+        <v>295</v>
       </c>
       <c r="B119" t="str" cm="1">
         <f t="array" ref="B119:C119">_xlfn.TEXTSPLIT(A119,";")</f>
@@ -12987,7 +13059,7 @@
     </row>
     <row r="120" spans="1:13">
       <c r="A120" s="1" t="s">
-        <v>272</v>
+        <v>296</v>
       </c>
       <c r="B120" t="str" cm="1">
         <f t="array" ref="B120">_xlfn.TEXTSPLIT(A120,";")</f>
@@ -13027,7 +13099,7 @@
     </row>
     <row r="121" spans="1:13">
       <c r="A121" s="1" t="s">
-        <v>273</v>
+        <v>297</v>
       </c>
       <c r="B121" t="str" cm="1">
         <f t="array" ref="B121">_xlfn.TEXTSPLIT(A121,";")</f>
@@ -13067,7 +13139,7 @@
     </row>
     <row r="122" spans="1:13">
       <c r="A122" s="1" t="s">
-        <v>274</v>
+        <v>298</v>
       </c>
       <c r="B122" t="str" cm="1">
         <f t="array" ref="B122">_xlfn.TEXTSPLIT(A122,";")</f>
@@ -13107,7 +13179,7 @@
     </row>
     <row r="123" spans="1:13">
       <c r="A123" s="1" t="s">
-        <v>275</v>
+        <v>299</v>
       </c>
       <c r="B123" t="str" cm="1">
         <f t="array" ref="B123:C123">_xlfn.TEXTSPLIT(A123,";")</f>
@@ -13153,7 +13225,7 @@
     </row>
     <row r="124" spans="1:13">
       <c r="A124" s="1" t="s">
-        <v>276</v>
+        <v>300</v>
       </c>
       <c r="B124" t="str" cm="1">
         <f t="array" ref="B124">_xlfn.TEXTSPLIT(A124,";")</f>
@@ -13193,7 +13265,7 @@
     </row>
     <row r="125" spans="1:13">
       <c r="A125" s="1" t="s">
-        <v>277</v>
+        <v>301</v>
       </c>
       <c r="B125" t="str" cm="1">
         <f t="array" ref="B125">_xlfn.TEXTSPLIT(A125,";")</f>
@@ -13233,7 +13305,7 @@
     </row>
     <row r="126" spans="1:13">
       <c r="A126" s="1" t="s">
-        <v>278</v>
+        <v>302</v>
       </c>
       <c r="B126" t="str" cm="1">
         <f t="array" ref="B126:C126">_xlfn.TEXTSPLIT(A126,";")</f>
@@ -13279,7 +13351,7 @@
     </row>
     <row r="127" spans="1:13">
       <c r="A127" s="1" t="s">
-        <v>279</v>
+        <v>303</v>
       </c>
       <c r="B127" t="str" cm="1">
         <f t="array" ref="B127">_xlfn.TEXTSPLIT(A127,";")</f>
@@ -13319,7 +13391,7 @@
     </row>
     <row r="128" spans="1:13">
       <c r="A128" s="1" t="s">
-        <v>280</v>
+        <v>304</v>
       </c>
       <c r="B128" t="str" cm="1">
         <f t="array" ref="B128">_xlfn.TEXTSPLIT(A128,";")</f>
@@ -13359,7 +13431,7 @@
     </row>
     <row r="129" spans="1:13">
       <c r="A129" s="1" t="s">
-        <v>281</v>
+        <v>305</v>
       </c>
       <c r="B129" t="str" cm="1">
         <f t="array" ref="B129">_xlfn.TEXTSPLIT(A129,";")</f>

--- a/hall/resources/sample/BuildingFunction.xlsx
+++ b/hall/resources/sample/BuildingFunction.xlsx
@@ -154,7 +154,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="597" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="597" uniqueCount="321">
   <si>
     <t>id</t>
   </si>
@@ -270,370 +270,691 @@
     <t>5_1990000_60</t>
   </si>
   <si>
+    <t>1023001_6</t>
+  </si>
+  <si>
+    <t>1_10</t>
+  </si>
+  <si>
+    <t>5_1990000_140</t>
+  </si>
+  <si>
     <t>1023001_8</t>
   </si>
   <si>
-    <t>1_10</t>
-  </si>
-  <si>
-    <t>5_1990000_140</t>
+    <t>5_1990000_220</t>
+  </si>
+  <si>
+    <t>1023001_10</t>
+  </si>
+  <si>
+    <t>5_1990000_310</t>
+  </si>
+  <si>
+    <t>1_20</t>
+  </si>
+  <si>
+    <t>5_1990000_390</t>
+  </si>
+  <si>
+    <t>1023001_20</t>
+  </si>
+  <si>
+    <t>5_1990000_510</t>
+  </si>
+  <si>
+    <t>1023001_34</t>
+  </si>
+  <si>
+    <t>1_30</t>
+  </si>
+  <si>
+    <t>5_1990000_630</t>
+  </si>
+  <si>
+    <t>1023001_50</t>
+  </si>
+  <si>
+    <t>5_1990000_740</t>
+  </si>
+  <si>
+    <t>1023001_68|1980000_10</t>
+  </si>
+  <si>
+    <t>1_40</t>
+  </si>
+  <si>
+    <t>5_1990000_910</t>
+  </si>
+  <si>
+    <t>1023001_84</t>
+  </si>
+  <si>
+    <t>1_50</t>
+  </si>
+  <si>
+    <t>5_1990000_1070</t>
+  </si>
+  <si>
+    <t>1023001_100</t>
+  </si>
+  <si>
+    <t>1_60</t>
+  </si>
+  <si>
+    <t>5_1990000_1240</t>
+  </si>
+  <si>
+    <t>1023001_150|1980000_10</t>
+  </si>
+  <si>
+    <t>1_70</t>
+  </si>
+  <si>
+    <t>5_1990000_1470</t>
+  </si>
+  <si>
+    <t>1023001_200</t>
+  </si>
+  <si>
+    <t>1_80</t>
+  </si>
+  <si>
+    <t>5_1990000_1700</t>
+  </si>
+  <si>
+    <t>1023001_250</t>
+  </si>
+  <si>
+    <t>1_90</t>
+  </si>
+  <si>
+    <t>5_1990000_1930</t>
+  </si>
+  <si>
+    <t>1023001_374|1980000_30</t>
+  </si>
+  <si>
+    <t>1_100</t>
+  </si>
+  <si>
+    <t>5_1990000_2250</t>
+  </si>
+  <si>
+    <t>1023001_468</t>
+  </si>
+  <si>
+    <t>1_110</t>
+  </si>
+  <si>
+    <t>5_1990000_2570</t>
+  </si>
+  <si>
+    <t>1023001_560</t>
+  </si>
+  <si>
+    <t>1_120</t>
+  </si>
+  <si>
+    <t>5_1990000_2900</t>
+  </si>
+  <si>
+    <t>1023001_720|1980000_70</t>
+  </si>
+  <si>
+    <t>1_130</t>
+  </si>
+  <si>
+    <t>5_1990000_3350</t>
+  </si>
+  <si>
+    <t>1023001_824</t>
+  </si>
+  <si>
+    <t>1_140</t>
+  </si>
+  <si>
+    <t>5_1990000_3800</t>
+  </si>
+  <si>
+    <t>1023001_926</t>
+  </si>
+  <si>
+    <t>1_150</t>
+  </si>
+  <si>
+    <t>5_1990000_4250</t>
+  </si>
+  <si>
+    <t>扑克牌桌</t>
+  </si>
+  <si>
+    <t>1023101_2</t>
+  </si>
+  <si>
+    <t>5_1990000_120</t>
+  </si>
+  <si>
+    <t>1023101_4</t>
+  </si>
+  <si>
+    <t>5_1990000_280</t>
+  </si>
+  <si>
+    <t>5_1990000_440</t>
+  </si>
+  <si>
+    <t>1023101_6</t>
+  </si>
+  <si>
+    <t>5_1990000_620</t>
+  </si>
+  <si>
+    <t>5_1990000_780</t>
+  </si>
+  <si>
+    <t>1023101_10</t>
+  </si>
+  <si>
+    <t>5_1990000_1020</t>
+  </si>
+  <si>
+    <t>1023101_18</t>
+  </si>
+  <si>
+    <t>5_1990000_1260</t>
+  </si>
+  <si>
+    <t>1023101_26</t>
+  </si>
+  <si>
+    <t>5_1990000_1480</t>
+  </si>
+  <si>
+    <t>1023101_34|1980000_10</t>
+  </si>
+  <si>
+    <t>5_1990000_1820</t>
+  </si>
+  <si>
+    <t>1023101_42</t>
+  </si>
+  <si>
+    <t>5_1990000_2140</t>
+  </si>
+  <si>
+    <t>1023101_50</t>
+  </si>
+  <si>
+    <t>5_1990000_2480</t>
+  </si>
+  <si>
+    <t>1023101_76|1980000_20</t>
+  </si>
+  <si>
+    <t>5_1990000_2940</t>
+  </si>
+  <si>
+    <t>1023101_100</t>
+  </si>
+  <si>
+    <t>5_1990000_3400</t>
+  </si>
+  <si>
+    <t>1023101_126</t>
+  </si>
+  <si>
+    <t>5_1990000_3860</t>
+  </si>
+  <si>
+    <t>1023101_188|1980000_60</t>
+  </si>
+  <si>
+    <t>5_1990000_4500</t>
+  </si>
+  <si>
+    <t>1023101_234</t>
+  </si>
+  <si>
+    <t>5_1990000_5140</t>
+  </si>
+  <si>
+    <t>1023101_280</t>
+  </si>
+  <si>
+    <t>5_1990000_5800</t>
+  </si>
+  <si>
+    <t>1023101_360|1980000_140</t>
+  </si>
+  <si>
+    <t>5_1990000_6700</t>
+  </si>
+  <si>
+    <t>1023101_412</t>
+  </si>
+  <si>
+    <t>5_1990000_7600</t>
+  </si>
+  <si>
+    <t>1023101_464</t>
+  </si>
+  <si>
+    <t>5_1990000_8500</t>
+  </si>
+  <si>
+    <t>幸运转盘</t>
+  </si>
+  <si>
+    <t>5_1990000_240</t>
+  </si>
+  <si>
+    <t>5_1990000_560</t>
+  </si>
+  <si>
+    <t>5_1990000_880</t>
+  </si>
+  <si>
+    <t>5_1990000_1560</t>
+  </si>
+  <si>
+    <t>5_1990000_2040</t>
+  </si>
+  <si>
+    <t>5_1990000_2520</t>
+  </si>
+  <si>
+    <t>1023101_14</t>
+  </si>
+  <si>
+    <t>5_1990000_2960</t>
+  </si>
+  <si>
+    <t>1023101_18|1980000_10</t>
+  </si>
+  <si>
+    <t>5_1990000_3640</t>
+  </si>
+  <si>
+    <t>1023101_22</t>
+  </si>
+  <si>
+    <t>5_1990000_4280</t>
+  </si>
+  <si>
+    <t>5_1990000_4960</t>
+  </si>
+  <si>
+    <t>1023101_38|1980000_30</t>
+  </si>
+  <si>
+    <t>5_1990000_5880</t>
+  </si>
+  <si>
+    <t>5_1990000_6800</t>
+  </si>
+  <si>
+    <t>1023101_64</t>
+  </si>
+  <si>
+    <t>5_1990000_7720</t>
+  </si>
+  <si>
+    <t>1023101_94|1980000_120</t>
+  </si>
+  <si>
+    <t>5_1990000_9000</t>
+  </si>
+  <si>
+    <t>1023101_118</t>
+  </si>
+  <si>
+    <t>5_1990000_10280</t>
+  </si>
+  <si>
+    <t>1023101_140</t>
+  </si>
+  <si>
+    <t>5_1990000_11600</t>
+  </si>
+  <si>
+    <t>1023101_180|1980000_280</t>
+  </si>
+  <si>
+    <t>5_1990000_13400</t>
+  </si>
+  <si>
+    <t>1023101_206</t>
+  </si>
+  <si>
+    <t>5_1990000_15200</t>
+  </si>
+  <si>
+    <t>1023101_232</t>
+  </si>
+  <si>
+    <t>5_1990000_17000</t>
+  </si>
+  <si>
+    <t>吧台区</t>
+  </si>
+  <si>
+    <t>1023401_4</t>
+  </si>
+  <si>
+    <t>1023401_6</t>
+  </si>
+  <si>
+    <t>1023401_8</t>
+  </si>
+  <si>
+    <t>1023401_10</t>
+  </si>
+  <si>
+    <t>1023401_20</t>
+  </si>
+  <si>
+    <t>1023401_34</t>
+  </si>
+  <si>
+    <t>1023401_50</t>
+  </si>
+  <si>
+    <t>1023401_68|1980000_10</t>
+  </si>
+  <si>
+    <t>1023401_84</t>
+  </si>
+  <si>
+    <t>1023401_100</t>
+  </si>
+  <si>
+    <t>1023401_150|1980000_170</t>
+  </si>
+  <si>
+    <t>1023401_200</t>
+  </si>
+  <si>
+    <t>1023401_250</t>
+  </si>
+  <si>
+    <t>1023401_374|1980000_690</t>
+  </si>
+  <si>
+    <t>1023401_468</t>
+  </si>
+  <si>
+    <t>1023401_560</t>
+  </si>
+  <si>
+    <t>1023401_720|1980000_1680</t>
+  </si>
+  <si>
+    <t>1023401_824</t>
+  </si>
+  <si>
+    <t>1023401_926</t>
+  </si>
+  <si>
+    <t>休息区</t>
+  </si>
+  <si>
+    <t>1023301_8</t>
+  </si>
+  <si>
+    <t>1023301_12</t>
+  </si>
+  <si>
+    <t>1023301_16</t>
+  </si>
+  <si>
+    <t>1023301_20</t>
+  </si>
+  <si>
+    <t>1023301_40</t>
+  </si>
+  <si>
+    <t>1023301_68</t>
+  </si>
+  <si>
+    <t>1023301_100</t>
+  </si>
+  <si>
+    <t>1023301_134|1980000_10</t>
+  </si>
+  <si>
+    <t>1023301_168</t>
+  </si>
+  <si>
+    <t>1023301_200</t>
+  </si>
+  <si>
+    <t>1023301_300|1980000_170</t>
+  </si>
+  <si>
+    <t>1023301_400</t>
+  </si>
+  <si>
+    <t>1023301_500</t>
+  </si>
+  <si>
+    <t>1023301_746|1980000_690</t>
+  </si>
+  <si>
+    <t>1023301_934</t>
+  </si>
+  <si>
+    <t>1023301_1120</t>
+  </si>
+  <si>
+    <t>1023301_1440|1980000_1680</t>
+  </si>
+  <si>
+    <t>1023301_1646</t>
+  </si>
+  <si>
+    <t>1023301_1850</t>
+  </si>
+  <si>
+    <t>提款机</t>
+  </si>
+  <si>
+    <t>1023201_6</t>
+  </si>
+  <si>
+    <t>1023201_10</t>
+  </si>
+  <si>
+    <t>1023201_12</t>
+  </si>
+  <si>
+    <t>1023201_16</t>
+  </si>
+  <si>
+    <t>1023201_30</t>
+  </si>
+  <si>
+    <t>1023201_50</t>
+  </si>
+  <si>
+    <t>1023201_76</t>
+  </si>
+  <si>
+    <t>1023201_100|1980000_10</t>
+  </si>
+  <si>
+    <t>1023201_126</t>
+  </si>
+  <si>
+    <t>1023201_150</t>
+  </si>
+  <si>
+    <t>1023201_226|1980000_90</t>
+  </si>
+  <si>
+    <t>1023201_300</t>
+  </si>
+  <si>
+    <t>1023201_376</t>
+  </si>
+  <si>
+    <t>1023201_560|1980000_350</t>
+  </si>
+  <si>
+    <t>1023201_700</t>
+  </si>
+  <si>
+    <t>1023201_840</t>
+  </si>
+  <si>
+    <t>1023201_1080|1980000_840</t>
+  </si>
+  <si>
+    <t>1023201_1234</t>
+  </si>
+  <si>
+    <t>1023201_1388</t>
+  </si>
+  <si>
+    <t>停机坪</t>
+  </si>
+  <si>
+    <t>map&lt;int{_}long&gt;{;}</t>
   </si>
   <si>
     <t>1023001_16</t>
   </si>
   <si>
-    <t>5_1990000_220</t>
-  </si>
-  <si>
     <t>1023001_24</t>
   </si>
   <si>
-    <t>5_1990000_310</t>
-  </si>
-  <si>
     <t>1023001_32</t>
   </si>
   <si>
-    <t>1_20</t>
-  </si>
-  <si>
-    <t>5_1990000_390</t>
-  </si>
-  <si>
-    <t>1023001_40</t>
-  </si>
-  <si>
-    <t>5_1990000_510</t>
-  </si>
-  <si>
-    <t>1023001_10</t>
-  </si>
-  <si>
-    <t>1_30</t>
-  </si>
-  <si>
-    <t>5_1990000_630</t>
-  </si>
-  <si>
-    <t>1023001_20</t>
-  </si>
-  <si>
-    <t>5_1990000_740</t>
-  </si>
-  <si>
-    <t>1023001_40|1980000_10</t>
-  </si>
-  <si>
-    <t>1_40</t>
-  </si>
-  <si>
-    <t>5_1990000_910</t>
-  </si>
-  <si>
-    <t>1023001_58</t>
-  </si>
-  <si>
-    <t>1_50</t>
-  </si>
-  <si>
-    <t>5_1990000_1070</t>
-  </si>
-  <si>
-    <t>1023001_14</t>
-  </si>
-  <si>
-    <t>1_60</t>
-  </si>
-  <si>
-    <t>5_1990000_1240</t>
-  </si>
-  <si>
-    <t>1023001_26|1980000_10</t>
-  </si>
-  <si>
-    <t>1_70</t>
-  </si>
-  <si>
-    <t>5_1990000_1470</t>
-  </si>
-  <si>
-    <t>1023001_52</t>
-  </si>
-  <si>
-    <t>1_80</t>
-  </si>
-  <si>
-    <t>5_1990000_1700</t>
-  </si>
-  <si>
-    <t>1023001_78</t>
-  </si>
-  <si>
-    <t>1_90</t>
-  </si>
-  <si>
-    <t>5_1990000_1930</t>
-  </si>
-  <si>
-    <t>1023001_24|1980000_30</t>
-  </si>
-  <si>
-    <t>1_100</t>
-  </si>
-  <si>
-    <t>5_1990000_2250</t>
-  </si>
-  <si>
-    <t>1023001_48</t>
-  </si>
-  <si>
-    <t>1_110</t>
-  </si>
-  <si>
-    <t>5_1990000_2570</t>
-  </si>
-  <si>
-    <t>1023001_96</t>
-  </si>
-  <si>
-    <t>1_120</t>
-  </si>
-  <si>
-    <t>5_1990000_2900</t>
-  </si>
-  <si>
-    <t>1023001_36|1980000_70</t>
-  </si>
-  <si>
-    <t>1_130</t>
-  </si>
-  <si>
-    <t>5_1990000_3350</t>
-  </si>
-  <si>
-    <t>1023001_72</t>
-  </si>
-  <si>
-    <t>1_140</t>
-  </si>
-  <si>
-    <t>5_1990000_3800</t>
-  </si>
-  <si>
-    <t>1023001_142</t>
-  </si>
-  <si>
-    <t>1_150</t>
-  </si>
-  <si>
-    <t>5_1990000_4250</t>
-  </si>
-  <si>
-    <t>扑克牌桌</t>
-  </si>
-  <si>
-    <t>1023101_2</t>
-  </si>
-  <si>
-    <t>5_1990000_120</t>
-  </si>
-  <si>
-    <t>1023101_4</t>
-  </si>
-  <si>
-    <t>5_1990000_280</t>
+    <t>1023001_40;1980000_10</t>
+  </si>
+  <si>
+    <t>1023002_8</t>
+  </si>
+  <si>
+    <t>1023002_16</t>
+  </si>
+  <si>
+    <t>1023002_32</t>
+  </si>
+  <si>
+    <t>1023002_48;1980000_100</t>
+  </si>
+  <si>
+    <t>1023003_8</t>
+  </si>
+  <si>
+    <t>1023003_16</t>
+  </si>
+  <si>
+    <t>1023003_32</t>
+  </si>
+  <si>
+    <t>1023003_48;1980000_300</t>
+  </si>
+  <si>
+    <t>1023004_12</t>
+  </si>
+  <si>
+    <t>1023004_24</t>
+  </si>
+  <si>
+    <t>1023004_48;1980000_600</t>
+  </si>
+  <si>
+    <t>1023005_12</t>
+  </si>
+  <si>
+    <t>1023005_24</t>
+  </si>
+  <si>
+    <t>1023005_48</t>
   </si>
   <si>
     <t>1023101_8</t>
   </si>
   <si>
-    <t>5_1990000_440</t>
-  </si>
-  <si>
     <t>1023101_12</t>
   </si>
   <si>
-    <t>5_1990000_620</t>
-  </si>
-  <si>
     <t>1023101_16</t>
   </si>
   <si>
-    <t>5_1990000_780</t>
-  </si>
-  <si>
-    <t>1023101_20</t>
-  </si>
-  <si>
-    <t>5_1990000_1020</t>
-  </si>
-  <si>
-    <t>1023101_6</t>
-  </si>
-  <si>
-    <t>5_1990000_1260</t>
-  </si>
-  <si>
-    <t>1023101_10</t>
-  </si>
-  <si>
-    <t>5_1990000_1480</t>
-  </si>
-  <si>
-    <t>1023101_20|1980000_10</t>
-  </si>
-  <si>
-    <t>5_1990000_1820</t>
-  </si>
-  <si>
-    <t>1023101_30</t>
-  </si>
-  <si>
-    <t>5_1990000_2140</t>
-  </si>
-  <si>
-    <t>5_1990000_2480</t>
-  </si>
-  <si>
-    <t>1023101_14|1980000_20</t>
-  </si>
-  <si>
-    <t>5_1990000_2940</t>
-  </si>
-  <si>
-    <t>1023101_26</t>
-  </si>
-  <si>
-    <t>5_1990000_3400</t>
-  </si>
-  <si>
-    <t>1023101_40</t>
-  </si>
-  <si>
-    <t>5_1990000_3860</t>
-  </si>
-  <si>
-    <t>1023101_12|1980000_60</t>
-  </si>
-  <si>
-    <t>5_1990000_4500</t>
-  </si>
-  <si>
-    <t>1023101_24</t>
-  </si>
-  <si>
-    <t>5_1990000_5140</t>
-  </si>
-  <si>
-    <t>1023101_48</t>
-  </si>
-  <si>
-    <t>5_1990000_5800</t>
-  </si>
-  <si>
-    <t>1023101_18|1980000_140</t>
-  </si>
-  <si>
-    <t>5_1990000_6700</t>
-  </si>
-  <si>
-    <t>1023101_36</t>
-  </si>
-  <si>
-    <t>5_1990000_7600</t>
-  </si>
-  <si>
-    <t>1023101_72</t>
-  </si>
-  <si>
-    <t>5_1990000_8500</t>
-  </si>
-  <si>
-    <t>幸运转盘</t>
-  </si>
-  <si>
-    <t>5_1990000_240</t>
-  </si>
-  <si>
-    <t>5_1990000_560</t>
-  </si>
-  <si>
-    <t>5_1990000_880</t>
-  </si>
-  <si>
-    <t>5_1990000_1560</t>
-  </si>
-  <si>
-    <t>5_1990000_2040</t>
-  </si>
-  <si>
-    <t>5_1990000_2520</t>
-  </si>
-  <si>
-    <t>5_1990000_2960</t>
-  </si>
-  <si>
-    <t>1023101_10|1980000_10</t>
-  </si>
-  <si>
-    <t>5_1990000_3640</t>
-  </si>
-  <si>
-    <t>5_1990000_4280</t>
-  </si>
-  <si>
-    <t>5_1990000_4960</t>
-  </si>
-  <si>
-    <t>1023101_8|1980000_30</t>
-  </si>
-  <si>
-    <t>5_1990000_5880</t>
-  </si>
-  <si>
-    <t>1023101_14</t>
-  </si>
-  <si>
-    <t>5_1990000_6800</t>
-  </si>
-  <si>
-    <t>5_1990000_7720</t>
-  </si>
-  <si>
-    <t>1023101_6|1980000_120</t>
-  </si>
-  <si>
-    <t>5_1990000_9000</t>
-  </si>
-  <si>
-    <t>5_1990000_10280</t>
-  </si>
-  <si>
-    <t>5_1990000_11600</t>
-  </si>
-  <si>
-    <t>1023101_10|1980000_280</t>
-  </si>
-  <si>
-    <t>5_1990000_13400</t>
-  </si>
-  <si>
-    <t>1023101_18</t>
-  </si>
-  <si>
-    <t>5_1990000_15200</t>
-  </si>
-  <si>
-    <t>5_1990000_17000</t>
-  </si>
-  <si>
-    <t>吧台区</t>
-  </si>
-  <si>
-    <t>1023401_4</t>
-  </si>
-  <si>
-    <t>1023401_8</t>
+    <t>1023101_20;1980000_10</t>
+  </si>
+  <si>
+    <t>1023102_4</t>
+  </si>
+  <si>
+    <t>1023102_8</t>
+  </si>
+  <si>
+    <t>1023102_16</t>
+  </si>
+  <si>
+    <t>1023102_24;1980000_100</t>
+  </si>
+  <si>
+    <t>1023103_4</t>
+  </si>
+  <si>
+    <t>1023103_8</t>
+  </si>
+  <si>
+    <t>1023103_16</t>
+  </si>
+  <si>
+    <t>1023103_24;1980000_300</t>
+  </si>
+  <si>
+    <t>1023104_6</t>
+  </si>
+  <si>
+    <t>1023104_12</t>
+  </si>
+  <si>
+    <t>1023104_24;1980000_600</t>
+  </si>
+  <si>
+    <t>1023105_6</t>
+  </si>
+  <si>
+    <t>1023105_12</t>
+  </si>
+  <si>
+    <t>1023105_24</t>
+  </si>
+  <si>
+    <t>1023101_1</t>
+  </si>
+  <si>
+    <t>1023101_10;1980000_10</t>
+  </si>
+  <si>
+    <t>1023102_2</t>
+  </si>
+  <si>
+    <t>1023102_12;1980000_100</t>
+  </si>
+  <si>
+    <t>1023103_2</t>
+  </si>
+  <si>
+    <t>1023103_12;1980000_300</t>
+  </si>
+  <si>
+    <t>1023104_3</t>
+  </si>
+  <si>
+    <t>1023104_12;1980000_600</t>
+  </si>
+  <si>
+    <t>1023105_3</t>
   </si>
   <si>
     <t>1023401_16</t>
@@ -645,58 +966,49 @@
     <t>1023401_32</t>
   </si>
   <si>
-    <t>1023401_40</t>
-  </si>
-  <si>
-    <t>1023401_10</t>
-  </si>
-  <si>
-    <t>1023401_20</t>
-  </si>
-  <si>
-    <t>1023401_40|1980000_10</t>
-  </si>
-  <si>
-    <t>1023401_58</t>
-  </si>
-  <si>
-    <t>1023401_14</t>
-  </si>
-  <si>
-    <t>1023401_26|1980000_170</t>
-  </si>
-  <si>
-    <t>1023401_52</t>
-  </si>
-  <si>
-    <t>1023401_78</t>
-  </si>
-  <si>
-    <t>1023401_24|1980000_690</t>
-  </si>
-  <si>
-    <t>1023401_48</t>
-  </si>
-  <si>
-    <t>1023401_96</t>
-  </si>
-  <si>
-    <t>1023401_36|1980000_1680</t>
-  </si>
-  <si>
-    <t>1023401_72</t>
-  </si>
-  <si>
-    <t>1023401_142</t>
-  </si>
-  <si>
-    <t>休息区</t>
-  </si>
-  <si>
-    <t>1023301_8</t>
-  </si>
-  <si>
-    <t>1023301_16</t>
+    <t>1023401_40;1980000_10</t>
+  </si>
+  <si>
+    <t>1023402_8</t>
+  </si>
+  <si>
+    <t>1023402_16</t>
+  </si>
+  <si>
+    <t>1023402_32</t>
+  </si>
+  <si>
+    <t>1023402_48;1980000_100</t>
+  </si>
+  <si>
+    <t>1023403_8</t>
+  </si>
+  <si>
+    <t>1023403_16</t>
+  </si>
+  <si>
+    <t>1023403_32</t>
+  </si>
+  <si>
+    <t>1023403_48;1980000_300</t>
+  </si>
+  <si>
+    <t>1023404_12</t>
+  </si>
+  <si>
+    <t>1023404_24</t>
+  </si>
+  <si>
+    <t>1023404_48;1980000_600</t>
+  </si>
+  <si>
+    <t>1023405_12</t>
+  </si>
+  <si>
+    <t>1023405_24</t>
+  </si>
+  <si>
+    <t>1023405_48</t>
   </si>
   <si>
     <t>1023301_32</t>
@@ -708,58 +1020,49 @@
     <t>1023301_64</t>
   </si>
   <si>
-    <t>1023301_80</t>
-  </si>
-  <si>
-    <t>1023301_20</t>
-  </si>
-  <si>
-    <t>1023301_40</t>
-  </si>
-  <si>
-    <t>1023301_78|1980000_10</t>
-  </si>
-  <si>
-    <t>1023301_116</t>
-  </si>
-  <si>
-    <t>1023301_26</t>
-  </si>
-  <si>
-    <t>1023301_52|1980000_170</t>
-  </si>
-  <si>
-    <t>1023301_102</t>
-  </si>
-  <si>
-    <t>1023301_154</t>
-  </si>
-  <si>
-    <t>1023301_48|1980000_690</t>
-  </si>
-  <si>
-    <t>1023301_96</t>
-  </si>
-  <si>
-    <t>1023301_190</t>
-  </si>
-  <si>
-    <t>1023301_72|1980000_1680</t>
-  </si>
-  <si>
-    <t>1023301_142</t>
-  </si>
-  <si>
-    <t>1023301_284</t>
-  </si>
-  <si>
-    <t>提款机</t>
-  </si>
-  <si>
-    <t>1023201_6</t>
-  </si>
-  <si>
-    <t>1023201_12</t>
+    <t>1023301_80;1980000_10</t>
+  </si>
+  <si>
+    <t>1023302_16</t>
+  </si>
+  <si>
+    <t>1023302_32</t>
+  </si>
+  <si>
+    <t>1023302_64</t>
+  </si>
+  <si>
+    <t>1023302_96;1980000_100</t>
+  </si>
+  <si>
+    <t>1023303_16</t>
+  </si>
+  <si>
+    <t>1023303_32</t>
+  </si>
+  <si>
+    <t>1023303_64</t>
+  </si>
+  <si>
+    <t>1023303_96;1980000_300</t>
+  </si>
+  <si>
+    <t>1023304_24</t>
+  </si>
+  <si>
+    <t>1023304_48</t>
+  </si>
+  <si>
+    <t>1023304_96;1980000_600</t>
+  </si>
+  <si>
+    <t>1023305_24</t>
+  </si>
+  <si>
+    <t>1023305_48</t>
+  </si>
+  <si>
+    <t>1023305_96</t>
   </si>
   <si>
     <t>1023201_24</t>
@@ -769,264 +1072,6 @@
   </si>
   <si>
     <t>1023201_48</t>
-  </si>
-  <si>
-    <t>1023201_60</t>
-  </si>
-  <si>
-    <t>1023201_16</t>
-  </si>
-  <si>
-    <t>1023201_30</t>
-  </si>
-  <si>
-    <t>1023201_58|1980000_10</t>
-  </si>
-  <si>
-    <t>1023201_86</t>
-  </si>
-  <si>
-    <t>1023201_20</t>
-  </si>
-  <si>
-    <t>1023201_40|1980000_90</t>
-  </si>
-  <si>
-    <t>1023201_78</t>
-  </si>
-  <si>
-    <t>1023201_116</t>
-  </si>
-  <si>
-    <t>1023201_36|1980000_350</t>
-  </si>
-  <si>
-    <t>1023201_72</t>
-  </si>
-  <si>
-    <t>1023201_142</t>
-  </si>
-  <si>
-    <t>1023201_54|1980000_840</t>
-  </si>
-  <si>
-    <t>1023201_108</t>
-  </si>
-  <si>
-    <t>1023201_214</t>
-  </si>
-  <si>
-    <t>停机坪</t>
-  </si>
-  <si>
-    <t>map&lt;int{_}long&gt;{;}</t>
-  </si>
-  <si>
-    <t>1023001_40;1980000_10</t>
-  </si>
-  <si>
-    <t>1023002_8</t>
-  </si>
-  <si>
-    <t>1023002_16</t>
-  </si>
-  <si>
-    <t>1023002_32</t>
-  </si>
-  <si>
-    <t>1023002_48;1980000_100</t>
-  </si>
-  <si>
-    <t>1023003_8</t>
-  </si>
-  <si>
-    <t>1023003_16</t>
-  </si>
-  <si>
-    <t>1023003_32</t>
-  </si>
-  <si>
-    <t>1023003_48;1980000_300</t>
-  </si>
-  <si>
-    <t>1023004_12</t>
-  </si>
-  <si>
-    <t>1023004_24</t>
-  </si>
-  <si>
-    <t>1023004_48;1980000_600</t>
-  </si>
-  <si>
-    <t>1023005_12</t>
-  </si>
-  <si>
-    <t>1023005_24</t>
-  </si>
-  <si>
-    <t>1023005_48</t>
-  </si>
-  <si>
-    <t>1023101_20;1980000_10</t>
-  </si>
-  <si>
-    <t>1023102_4</t>
-  </si>
-  <si>
-    <t>1023102_8</t>
-  </si>
-  <si>
-    <t>1023102_16</t>
-  </si>
-  <si>
-    <t>1023102_24;1980000_100</t>
-  </si>
-  <si>
-    <t>1023103_4</t>
-  </si>
-  <si>
-    <t>1023103_8</t>
-  </si>
-  <si>
-    <t>1023103_16</t>
-  </si>
-  <si>
-    <t>1023103_24;1980000_300</t>
-  </si>
-  <si>
-    <t>1023104_6</t>
-  </si>
-  <si>
-    <t>1023104_12</t>
-  </si>
-  <si>
-    <t>1023104_24;1980000_600</t>
-  </si>
-  <si>
-    <t>1023105_6</t>
-  </si>
-  <si>
-    <t>1023105_12</t>
-  </si>
-  <si>
-    <t>1023105_24</t>
-  </si>
-  <si>
-    <t>1023101_1</t>
-  </si>
-  <si>
-    <t>1023101_10;1980000_10</t>
-  </si>
-  <si>
-    <t>1023102_2</t>
-  </si>
-  <si>
-    <t>1023102_12;1980000_100</t>
-  </si>
-  <si>
-    <t>1023103_2</t>
-  </si>
-  <si>
-    <t>1023103_12;1980000_300</t>
-  </si>
-  <si>
-    <t>1023104_3</t>
-  </si>
-  <si>
-    <t>1023104_12;1980000_600</t>
-  </si>
-  <si>
-    <t>1023105_3</t>
-  </si>
-  <si>
-    <t>1023401_40;1980000_10</t>
-  </si>
-  <si>
-    <t>1023402_8</t>
-  </si>
-  <si>
-    <t>1023402_16</t>
-  </si>
-  <si>
-    <t>1023402_32</t>
-  </si>
-  <si>
-    <t>1023402_48;1980000_100</t>
-  </si>
-  <si>
-    <t>1023403_8</t>
-  </si>
-  <si>
-    <t>1023403_16</t>
-  </si>
-  <si>
-    <t>1023403_32</t>
-  </si>
-  <si>
-    <t>1023403_48;1980000_300</t>
-  </si>
-  <si>
-    <t>1023404_12</t>
-  </si>
-  <si>
-    <t>1023404_24</t>
-  </si>
-  <si>
-    <t>1023404_48;1980000_600</t>
-  </si>
-  <si>
-    <t>1023405_12</t>
-  </si>
-  <si>
-    <t>1023405_24</t>
-  </si>
-  <si>
-    <t>1023405_48</t>
-  </si>
-  <si>
-    <t>1023301_80;1980000_10</t>
-  </si>
-  <si>
-    <t>1023302_16</t>
-  </si>
-  <si>
-    <t>1023302_32</t>
-  </si>
-  <si>
-    <t>1023302_64</t>
-  </si>
-  <si>
-    <t>1023302_96;1980000_100</t>
-  </si>
-  <si>
-    <t>1023303_16</t>
-  </si>
-  <si>
-    <t>1023303_32</t>
-  </si>
-  <si>
-    <t>1023303_64</t>
-  </si>
-  <si>
-    <t>1023303_96;1980000_300</t>
-  </si>
-  <si>
-    <t>1023304_24</t>
-  </si>
-  <si>
-    <t>1023304_48</t>
-  </si>
-  <si>
-    <t>1023304_96;1980000_600</t>
-  </si>
-  <si>
-    <t>1023305_24</t>
-  </si>
-  <si>
-    <t>1023305_48</t>
-  </si>
-  <si>
-    <t>1023305_96</t>
   </si>
   <si>
     <t>1023201_60;1980000_10</t>
@@ -2453,13 +2498,13 @@
         <v>44</v>
       </c>
       <c r="I9" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J9" s="3">
+        <v>4</v>
+      </c>
+      <c r="K9" t="s">
         <v>45</v>
-      </c>
-      <c r="J9" s="3">
-        <v>4</v>
-      </c>
-      <c r="K9" t="s">
-        <v>46</v>
       </c>
       <c r="L9" s="5">
         <f t="shared" si="1"/>
@@ -2500,16 +2545,16 @@
         <v>5</v>
       </c>
       <c r="H10" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="I10" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I10" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="J10" s="3">
         <v>4</v>
       </c>
       <c r="K10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L10" s="5">
         <f t="shared" ref="L10:L24" si="3">A11</f>
@@ -2550,16 +2595,16 @@
         <v>6</v>
       </c>
       <c r="H11" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="I11" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="I11" s="1" t="s">
+      <c r="J11" s="3">
+        <v>4</v>
+      </c>
+      <c r="K11" t="s">
         <v>50</v>
-      </c>
-      <c r="J11" s="3">
-        <v>4</v>
-      </c>
-      <c r="K11" t="s">
-        <v>51</v>
       </c>
       <c r="L11" s="5">
         <f t="shared" si="3"/>
@@ -2601,16 +2646,16 @@
         <v>7</v>
       </c>
       <c r="H12" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="I12" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="I12" s="1" t="s">
-        <v>53</v>
-      </c>
       <c r="J12" s="3">
         <v>4</v>
       </c>
       <c r="K12" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L12" s="5">
         <f t="shared" si="3"/>
@@ -2652,16 +2697,16 @@
         <v>8</v>
       </c>
       <c r="H13" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="I13" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="I13" s="1" t="s">
+      <c r="J13" s="3">
+        <v>4</v>
+      </c>
+      <c r="K13" t="s">
         <v>55</v>
-      </c>
-      <c r="J13" s="3">
-        <v>4</v>
-      </c>
-      <c r="K13" t="s">
-        <v>56</v>
       </c>
       <c r="L13" s="5">
         <f t="shared" si="3"/>
@@ -2703,16 +2748,16 @@
         <v>9</v>
       </c>
       <c r="H14" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I14" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="I14" s="1" t="s">
+      <c r="J14" s="3">
+        <v>4</v>
+      </c>
+      <c r="K14" t="s">
         <v>58</v>
-      </c>
-      <c r="J14" s="3">
-        <v>4</v>
-      </c>
-      <c r="K14" t="s">
-        <v>59</v>
       </c>
       <c r="L14" s="5">
         <f t="shared" si="3"/>
@@ -2754,16 +2799,16 @@
         <v>10</v>
       </c>
       <c r="H15" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="I15" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="I15" s="1" t="s">
+      <c r="J15" s="3">
+        <v>4</v>
+      </c>
+      <c r="K15" t="s">
         <v>61</v>
-      </c>
-      <c r="J15" s="3">
-        <v>4</v>
-      </c>
-      <c r="K15" t="s">
-        <v>62</v>
       </c>
       <c r="L15" s="5">
         <f t="shared" si="3"/>
@@ -2805,16 +2850,16 @@
         <v>11</v>
       </c>
       <c r="H16" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="I16" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="I16" s="1" t="s">
+      <c r="J16" s="3">
+        <v>4</v>
+      </c>
+      <c r="K16" t="s">
         <v>64</v>
-      </c>
-      <c r="J16" s="3">
-        <v>4</v>
-      </c>
-      <c r="K16" t="s">
-        <v>65</v>
       </c>
       <c r="L16" s="5">
         <f t="shared" si="3"/>
@@ -2856,16 +2901,16 @@
         <v>12</v>
       </c>
       <c r="H17" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="I17" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="I17" s="1" t="s">
+      <c r="J17" s="3">
+        <v>4</v>
+      </c>
+      <c r="K17" t="s">
         <v>67</v>
-      </c>
-      <c r="J17" s="3">
-        <v>4</v>
-      </c>
-      <c r="K17" t="s">
-        <v>68</v>
       </c>
       <c r="L17" s="5">
         <f t="shared" si="3"/>
@@ -2907,16 +2952,16 @@
         <v>13</v>
       </c>
       <c r="H18" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="I18" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="I18" s="1" t="s">
+      <c r="J18" s="3">
+        <v>4</v>
+      </c>
+      <c r="K18" t="s">
         <v>70</v>
-      </c>
-      <c r="J18" s="3">
-        <v>4</v>
-      </c>
-      <c r="K18" t="s">
-        <v>71</v>
       </c>
       <c r="L18" s="5">
         <f t="shared" si="3"/>
@@ -2958,16 +3003,16 @@
         <v>14</v>
       </c>
       <c r="H19" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="I19" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="I19" s="1" t="s">
+      <c r="J19" s="3">
+        <v>4</v>
+      </c>
+      <c r="K19" t="s">
         <v>73</v>
-      </c>
-      <c r="J19" s="3">
-        <v>4</v>
-      </c>
-      <c r="K19" t="s">
-        <v>74</v>
       </c>
       <c r="L19" s="5">
         <f t="shared" si="3"/>
@@ -3009,16 +3054,16 @@
         <v>15</v>
       </c>
       <c r="H20" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="I20" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="I20" s="1" t="s">
+      <c r="J20" s="3">
+        <v>4</v>
+      </c>
+      <c r="K20" t="s">
         <v>76</v>
-      </c>
-      <c r="J20" s="3">
-        <v>4</v>
-      </c>
-      <c r="K20" t="s">
-        <v>77</v>
       </c>
       <c r="L20" s="5">
         <f t="shared" si="3"/>
@@ -3060,16 +3105,16 @@
         <v>16</v>
       </c>
       <c r="H21" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="I21" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="I21" s="1" t="s">
+      <c r="J21" s="3">
+        <v>4</v>
+      </c>
+      <c r="K21" t="s">
         <v>79</v>
-      </c>
-      <c r="J21" s="3">
-        <v>4</v>
-      </c>
-      <c r="K21" t="s">
-        <v>80</v>
       </c>
       <c r="L21" s="5">
         <f t="shared" si="3"/>
@@ -3111,16 +3156,16 @@
         <v>17</v>
       </c>
       <c r="H22" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="I22" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="I22" s="1" t="s">
+      <c r="J22" s="3">
+        <v>4</v>
+      </c>
+      <c r="K22" t="s">
         <v>82</v>
-      </c>
-      <c r="J22" s="3">
-        <v>4</v>
-      </c>
-      <c r="K22" t="s">
-        <v>83</v>
       </c>
       <c r="L22" s="5">
         <f t="shared" si="3"/>
@@ -3162,16 +3207,16 @@
         <v>18</v>
       </c>
       <c r="H23" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="I23" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="I23" s="1" t="s">
+      <c r="J23" s="3">
+        <v>4</v>
+      </c>
+      <c r="K23" t="s">
         <v>85</v>
-      </c>
-      <c r="J23" s="3">
-        <v>4</v>
-      </c>
-      <c r="K23" t="s">
-        <v>86</v>
       </c>
       <c r="L23" s="5">
         <f t="shared" si="3"/>
@@ -3213,16 +3258,16 @@
         <v>19</v>
       </c>
       <c r="H24" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="I24" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="I24" s="1" t="s">
+      <c r="J24" s="3">
+        <v>4</v>
+      </c>
+      <c r="K24" t="s">
         <v>88</v>
-      </c>
-      <c r="J24" s="3">
-        <v>4</v>
-      </c>
-      <c r="K24" t="s">
-        <v>89</v>
       </c>
       <c r="L24" s="5">
         <f t="shared" si="3"/>
@@ -3264,7 +3309,7 @@
         <v>20</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J25" s="3">
         <v>4</v>
@@ -3287,7 +3332,7 @@
         <v>2</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D26" s="3">
         <v>2</v>
@@ -3303,7 +3348,7 @@
       </c>
       <c r="H26" s="2"/>
       <c r="I26" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J26" s="3">
         <v>4</v>
@@ -3334,7 +3379,7 @@
         <v>2</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D27" s="3">
         <v>2</v>
@@ -3349,10 +3394,10 @@
         <v>1</v>
       </c>
       <c r="H27" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="I27" s="1" t="s">
         <v>93</v>
-      </c>
-      <c r="I27" s="1" t="s">
-        <v>94</v>
       </c>
       <c r="J27" s="3">
         <v>4</v>
@@ -3384,7 +3429,7 @@
         <v>2</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D28" s="3">
         <v>2</v>
@@ -3399,10 +3444,10 @@
         <v>2</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="J28" s="3">
         <v>4</v>
@@ -3434,7 +3479,7 @@
         <v>2</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D29" s="3">
         <v>2</v>
@@ -3449,10 +3494,10 @@
         <v>3</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="J29" s="3">
         <v>4</v>
@@ -3484,7 +3529,7 @@
         <v>2</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D30" s="3">
         <v>2</v>
@@ -3499,16 +3544,16 @@
         <v>4</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="J30" s="3">
         <v>4</v>
       </c>
       <c r="K30" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L30" s="5">
         <f t="shared" si="7"/>
@@ -3534,7 +3579,7 @@
         <v>2</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D31" s="3">
         <v>2</v>
@@ -3549,16 +3594,16 @@
         <v>5</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="J31" s="3">
         <v>4</v>
       </c>
       <c r="K31" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L31" s="5">
         <f t="shared" si="7"/>
@@ -3584,7 +3629,7 @@
         <v>2</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D32" s="3">
         <v>2</v>
@@ -3599,16 +3644,16 @@
         <v>6</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="J32" s="3">
         <v>4</v>
       </c>
       <c r="K32" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L32" s="5">
         <f t="shared" si="7"/>
@@ -3635,7 +3680,7 @@
         <v>2</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D33" s="3">
         <v>2</v>
@@ -3650,16 +3695,16 @@
         <v>7</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="J33" s="3">
         <v>4</v>
       </c>
       <c r="K33" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L33" s="5">
         <f t="shared" si="7"/>
@@ -3686,7 +3731,7 @@
         <v>2</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D34" s="3">
         <v>2</v>
@@ -3701,16 +3746,16 @@
         <v>8</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="J34" s="3">
         <v>4</v>
       </c>
       <c r="K34" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L34" s="5">
         <f t="shared" si="7"/>
@@ -3737,7 +3782,7 @@
         <v>2</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D35" s="3">
         <v>2</v>
@@ -3752,16 +3797,16 @@
         <v>9</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="J35" s="3">
         <v>4</v>
       </c>
       <c r="K35" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L35" s="5">
         <f t="shared" si="7"/>
@@ -3788,7 +3833,7 @@
         <v>2</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D36" s="3">
         <v>2</v>
@@ -3803,16 +3848,16 @@
         <v>10</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="J36" s="3">
         <v>4</v>
       </c>
       <c r="K36" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L36" s="5">
         <f t="shared" si="7"/>
@@ -3839,7 +3884,7 @@
         <v>2</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D37" s="3">
         <v>2</v>
@@ -3854,16 +3899,16 @@
         <v>11</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="J37" s="3">
         <v>4</v>
       </c>
       <c r="K37" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="L37" s="5">
         <f t="shared" si="7"/>
@@ -3890,7 +3935,7 @@
         <v>2</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D38" s="3">
         <v>2</v>
@@ -3905,16 +3950,16 @@
         <v>12</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="J38" s="3">
         <v>4</v>
       </c>
       <c r="K38" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L38" s="5">
         <f t="shared" si="7"/>
@@ -3941,7 +3986,7 @@
         <v>2</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D39" s="3">
         <v>2</v>
@@ -3956,16 +4001,16 @@
         <v>13</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="J39" s="3">
         <v>4</v>
       </c>
       <c r="K39" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L39" s="5">
         <f t="shared" si="7"/>
@@ -3992,7 +4037,7 @@
         <v>2</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D40" s="3">
         <v>2</v>
@@ -4007,16 +4052,16 @@
         <v>14</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="J40" s="3">
         <v>4</v>
       </c>
       <c r="K40" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="L40" s="5">
         <f t="shared" si="7"/>
@@ -4043,7 +4088,7 @@
         <v>2</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D41" s="3">
         <v>2</v>
@@ -4058,16 +4103,16 @@
         <v>15</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J41" s="3">
         <v>4</v>
       </c>
       <c r="K41" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L41" s="5">
         <f t="shared" si="7"/>
@@ -4094,7 +4139,7 @@
         <v>2</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D42" s="3">
         <v>2</v>
@@ -4109,16 +4154,16 @@
         <v>16</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="J42" s="3">
         <v>4</v>
       </c>
       <c r="K42" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L42" s="5">
         <f t="shared" si="7"/>
@@ -4145,7 +4190,7 @@
         <v>2</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D43" s="3">
         <v>2</v>
@@ -4160,16 +4205,16 @@
         <v>17</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="J43" s="3">
         <v>4</v>
       </c>
       <c r="K43" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="L43" s="5">
         <f t="shared" si="7"/>
@@ -4196,7 +4241,7 @@
         <v>2</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D44" s="3">
         <v>2</v>
@@ -4211,16 +4256,16 @@
         <v>18</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="J44" s="3">
         <v>4</v>
       </c>
       <c r="K44" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L44" s="5">
         <f t="shared" si="7"/>
@@ -4247,7 +4292,7 @@
         <v>2</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D45" s="3">
         <v>2</v>
@@ -4262,16 +4307,16 @@
         <v>19</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="J45" s="3">
         <v>4</v>
       </c>
       <c r="K45" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L45" s="5">
         <f t="shared" si="7"/>
@@ -4298,7 +4343,7 @@
         <v>2</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D46" s="3">
         <v>2</v>
@@ -4313,7 +4358,7 @@
         <v>20</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="J46" s="3">
         <v>4</v>
@@ -4336,7 +4381,7 @@
         <v>3</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D47" s="3">
         <v>4</v>
@@ -4352,7 +4397,7 @@
       </c>
       <c r="H47" s="2"/>
       <c r="I47" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J47" s="3">
         <v>4</v>
@@ -4383,7 +4428,7 @@
         <v>3</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D48" s="3">
         <v>4</v>
@@ -4398,10 +4443,10 @@
         <v>1</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J48" s="3">
         <v>4</v>
@@ -4433,7 +4478,7 @@
         <v>3</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D49" s="3">
         <v>4</v>
@@ -4448,10 +4493,10 @@
         <v>2</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="J49" s="3">
         <v>4</v>
@@ -4483,7 +4528,7 @@
         <v>3</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D50" s="3">
         <v>4</v>
@@ -4498,10 +4543,10 @@
         <v>3</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="J50" s="3">
         <v>4</v>
@@ -4533,7 +4578,7 @@
         <v>3</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D51" s="3">
         <v>4</v>
@@ -4548,16 +4593,16 @@
         <v>4</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="J51" s="3">
         <v>4</v>
       </c>
       <c r="K51" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L51" s="5">
         <f t="shared" si="15"/>
@@ -4583,7 +4628,7 @@
         <v>3</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D52" s="3">
         <v>4</v>
@@ -4598,16 +4643,16 @@
         <v>5</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="J52" s="3">
         <v>4</v>
       </c>
       <c r="K52" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L52" s="5">
         <f t="shared" si="15"/>
@@ -4633,7 +4678,7 @@
         <v>3</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D53" s="3">
         <v>4</v>
@@ -4648,16 +4693,16 @@
         <v>6</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="J53" s="3">
         <v>4</v>
       </c>
       <c r="K53" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L53" s="5">
         <f t="shared" si="15"/>
@@ -4684,7 +4729,7 @@
         <v>3</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D54" s="3">
         <v>4</v>
@@ -4699,16 +4744,16 @@
         <v>7</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="J54" s="3">
         <v>4</v>
       </c>
       <c r="K54" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L54" s="5">
         <f t="shared" si="15"/>
@@ -4735,7 +4780,7 @@
         <v>3</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D55" s="3">
         <v>4</v>
@@ -4750,16 +4795,16 @@
         <v>8</v>
       </c>
       <c r="H55" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="I55" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="I55" s="1" t="s">
-        <v>139</v>
-      </c>
       <c r="J55" s="3">
         <v>4</v>
       </c>
       <c r="K55" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L55" s="5">
         <f t="shared" si="15"/>
@@ -4786,7 +4831,7 @@
         <v>3</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D56" s="3">
         <v>4</v>
@@ -4801,16 +4846,16 @@
         <v>9</v>
       </c>
       <c r="H56" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="I56" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="I56" s="1" t="s">
-        <v>100</v>
-      </c>
       <c r="J56" s="3">
         <v>4</v>
       </c>
       <c r="K56" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L56" s="5">
         <f t="shared" si="15"/>
@@ -4837,7 +4882,7 @@
         <v>3</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D57" s="3">
         <v>4</v>
@@ -4855,13 +4900,13 @@
         <v>141</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="J57" s="3">
         <v>4</v>
       </c>
       <c r="K57" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L57" s="5">
         <f t="shared" si="15"/>
@@ -4888,7 +4933,7 @@
         <v>3</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D58" s="3">
         <v>4</v>
@@ -4912,7 +4957,7 @@
         <v>4</v>
       </c>
       <c r="K58" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="L58" s="5">
         <f t="shared" si="15"/>
@@ -4939,7 +4984,7 @@
         <v>3</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D59" s="3">
         <v>4</v>
@@ -4957,13 +5002,13 @@
         <v>144</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>145</v>
+        <v>109</v>
       </c>
       <c r="J59" s="3">
         <v>4</v>
       </c>
       <c r="K59" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L59" s="5">
         <f t="shared" si="15"/>
@@ -4990,7 +5035,7 @@
         <v>3</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D60" s="3">
         <v>4</v>
@@ -5005,16 +5050,16 @@
         <v>13</v>
       </c>
       <c r="H60" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="I60" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="I60" s="1" t="s">
-        <v>102</v>
-      </c>
       <c r="J60" s="3">
         <v>4</v>
       </c>
       <c r="K60" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L60" s="5">
         <f t="shared" si="15"/>
@@ -5041,7 +5086,7 @@
         <v>3</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D61" s="3">
         <v>4</v>
@@ -5065,7 +5110,7 @@
         <v>4</v>
       </c>
       <c r="K61" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="L61" s="5">
         <f t="shared" si="15"/>
@@ -5092,7 +5137,7 @@
         <v>3</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D62" s="3">
         <v>4</v>
@@ -5110,13 +5155,13 @@
         <v>149</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>98</v>
+        <v>150</v>
       </c>
       <c r="J62" s="3">
         <v>4</v>
       </c>
       <c r="K62" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L62" s="5">
         <f t="shared" si="15"/>
@@ -5143,7 +5188,7 @@
         <v>3</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D63" s="3">
         <v>4</v>
@@ -5158,16 +5203,16 @@
         <v>16</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>121</v>
+        <v>152</v>
       </c>
       <c r="J63" s="3">
         <v>4</v>
       </c>
       <c r="K63" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L63" s="5">
         <f t="shared" si="15"/>
@@ -5194,7 +5239,7 @@
         <v>3</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D64" s="3">
         <v>4</v>
@@ -5209,16 +5254,16 @@
         <v>17</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="J64" s="3">
         <v>4</v>
       </c>
       <c r="K64" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="L64" s="5">
         <f t="shared" si="15"/>
@@ -5245,7 +5290,7 @@
         <v>3</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D65" s="3">
         <v>4</v>
@@ -5260,16 +5305,16 @@
         <v>18</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I65" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="J65" s="3">
         <v>4</v>
       </c>
       <c r="K65" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L65" s="5">
         <f t="shared" si="15"/>
@@ -5296,7 +5341,7 @@
         <v>3</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D66" s="3">
         <v>4</v>
@@ -5311,16 +5356,16 @@
         <v>19</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>127</v>
+        <v>158</v>
       </c>
       <c r="J66" s="3">
         <v>4</v>
       </c>
       <c r="K66" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L66" s="5">
         <f t="shared" si="15"/>
@@ -5347,7 +5392,7 @@
         <v>3</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D67" s="3">
         <v>4</v>
@@ -5362,7 +5407,7 @@
         <v>20</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="J67" s="3">
         <v>4</v>
@@ -5385,7 +5430,7 @@
         <v>4</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D68" s="3">
         <v>2</v>
@@ -5400,7 +5445,7 @@
         <v>0</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="J68" s="3"/>
       <c r="K68" t="s">
@@ -5429,7 +5474,7 @@
         <v>4</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D69" s="3">
         <v>2</v>
@@ -5444,7 +5489,7 @@
         <v>1</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="J69" s="3"/>
       <c r="K69" t="s">
@@ -5471,7 +5516,7 @@
         <v>4</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D70" s="3">
         <v>2</v>
@@ -5486,7 +5531,7 @@
         <v>2</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="J70" s="3"/>
       <c r="K70" t="s">
@@ -5513,7 +5558,7 @@
         <v>4</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D71" s="3">
         <v>2</v>
@@ -5528,7 +5573,7 @@
         <v>3</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="J71" s="3"/>
       <c r="K71" t="s">
@@ -5555,7 +5600,7 @@
         <v>4</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D72" s="3">
         <v>2</v>
@@ -5570,11 +5615,11 @@
         <v>4</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="J72" s="3"/>
       <c r="K72" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L72" s="5">
         <f t="shared" si="24"/>
@@ -5597,7 +5642,7 @@
         <v>4</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D73" s="3">
         <v>2</v>
@@ -5612,11 +5657,11 @@
         <v>5</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="J73" s="3"/>
       <c r="K73" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L73" s="5">
         <f t="shared" si="24"/>
@@ -5639,7 +5684,7 @@
         <v>4</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D74" s="3">
         <v>2</v>
@@ -5654,11 +5699,11 @@
         <v>6</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="J74" s="3"/>
       <c r="K74" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L74" s="5">
         <f t="shared" si="24"/>
@@ -5682,7 +5727,7 @@
         <v>4</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D75" s="3">
         <v>2</v>
@@ -5697,11 +5742,11 @@
         <v>7</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="J75" s="3"/>
       <c r="K75" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L75" s="5">
         <f t="shared" si="24"/>
@@ -5725,7 +5770,7 @@
         <v>4</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D76" s="3">
         <v>2</v>
@@ -5740,11 +5785,11 @@
         <v>8</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="J76" s="3"/>
       <c r="K76" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L76" s="5">
         <f t="shared" si="24"/>
@@ -5768,7 +5813,7 @@
         <v>4</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D77" s="3">
         <v>2</v>
@@ -5783,11 +5828,11 @@
         <v>9</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="J77" s="3"/>
       <c r="K77" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L77" s="5">
         <f t="shared" si="24"/>
@@ -5811,7 +5856,7 @@
         <v>4</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D78" s="3">
         <v>2</v>
@@ -5826,11 +5871,11 @@
         <v>10</v>
       </c>
       <c r="I78" s="1" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="J78" s="3"/>
       <c r="K78" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L78" s="5">
         <f t="shared" si="24"/>
@@ -5854,7 +5899,7 @@
         <v>4</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D79" s="3">
         <v>2</v>
@@ -5869,11 +5914,11 @@
         <v>11</v>
       </c>
       <c r="I79" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="J79" s="3"/>
       <c r="K79" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="L79" s="5">
         <f t="shared" si="24"/>
@@ -5897,7 +5942,7 @@
         <v>4</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D80" s="3">
         <v>2</v>
@@ -5912,11 +5957,11 @@
         <v>12</v>
       </c>
       <c r="I80" s="1" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="J80" s="3"/>
       <c r="K80" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L80" s="5">
         <f t="shared" si="24"/>
@@ -5940,7 +5985,7 @@
         <v>4</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D81" s="3">
         <v>2</v>
@@ -5955,11 +6000,11 @@
         <v>13</v>
       </c>
       <c r="I81" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J81" s="3"/>
       <c r="K81" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L81" s="5">
         <f t="shared" si="24"/>
@@ -5983,7 +6028,7 @@
         <v>4</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D82" s="3">
         <v>2</v>
@@ -5998,11 +6043,11 @@
         <v>14</v>
       </c>
       <c r="I82" s="1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="J82" s="3"/>
       <c r="K82" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="L82" s="5">
         <f t="shared" si="24"/>
@@ -6026,7 +6071,7 @@
         <v>4</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D83" s="3">
         <v>2</v>
@@ -6041,11 +6086,11 @@
         <v>15</v>
       </c>
       <c r="I83" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="J83" s="3"/>
       <c r="K83" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L83" s="5">
         <f t="shared" si="24"/>
@@ -6069,7 +6114,7 @@
         <v>4</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D84" s="3">
         <v>2</v>
@@ -6084,11 +6129,11 @@
         <v>16</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="J84" s="3"/>
       <c r="K84" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L84" s="5">
         <f t="shared" si="24"/>
@@ -6112,7 +6157,7 @@
         <v>4</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D85" s="3">
         <v>2</v>
@@ -6127,11 +6172,11 @@
         <v>17</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="J85" s="3"/>
       <c r="K85" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="L85" s="5">
         <f t="shared" si="24"/>
@@ -6155,7 +6200,7 @@
         <v>4</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D86" s="3">
         <v>2</v>
@@ -6170,11 +6215,11 @@
         <v>18</v>
       </c>
       <c r="I86" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="J86" s="3"/>
       <c r="K86" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L86" s="5">
         <f t="shared" si="24"/>
@@ -6198,7 +6243,7 @@
         <v>4</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D87" s="3">
         <v>2</v>
@@ -6213,11 +6258,11 @@
         <v>19</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="J87" s="3"/>
       <c r="K87" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L87" s="5">
         <f t="shared" si="24"/>
@@ -6241,7 +6286,7 @@
         <v>4</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D88" s="3">
         <v>2</v>
@@ -6271,7 +6316,7 @@
         <v>5</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D89" s="3">
         <v>2</v>
@@ -6286,7 +6331,7 @@
         <v>0</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="J89" s="3">
         <v>4</v>
@@ -6317,7 +6362,7 @@
         <v>5</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D90" s="3">
         <v>2</v>
@@ -6332,7 +6377,7 @@
         <v>1</v>
       </c>
       <c r="I90" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="J90" s="3">
         <v>4</v>
@@ -6364,7 +6409,7 @@
         <v>5</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D91" s="3">
         <v>2</v>
@@ -6379,7 +6424,7 @@
         <v>2</v>
       </c>
       <c r="I91" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="J91" s="3">
         <v>4</v>
@@ -6411,7 +6456,7 @@
         <v>5</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D92" s="3">
         <v>2</v>
@@ -6426,7 +6471,7 @@
         <v>3</v>
       </c>
       <c r="I92" s="1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="J92" s="3">
         <v>4</v>
@@ -6458,7 +6503,7 @@
         <v>5</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D93" s="3">
         <v>2</v>
@@ -6473,13 +6518,13 @@
         <v>4</v>
       </c>
       <c r="I93" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J93" s="3">
         <v>4</v>
       </c>
       <c r="K93" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L93" s="5">
         <f t="shared" si="33"/>
@@ -6505,7 +6550,7 @@
         <v>5</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D94" s="3">
         <v>2</v>
@@ -6520,13 +6565,13 @@
         <v>5</v>
       </c>
       <c r="I94" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="J94" s="3">
         <v>4</v>
       </c>
       <c r="K94" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L94" s="5">
         <f t="shared" si="33"/>
@@ -6552,7 +6597,7 @@
         <v>5</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D95" s="3">
         <v>2</v>
@@ -6567,13 +6612,13 @@
         <v>6</v>
       </c>
       <c r="I95" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J95" s="3">
         <v>4</v>
       </c>
       <c r="K95" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L95" s="5">
         <f t="shared" si="33"/>
@@ -6600,7 +6645,7 @@
         <v>5</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D96" s="3">
         <v>2</v>
@@ -6615,13 +6660,13 @@
         <v>7</v>
       </c>
       <c r="I96" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="J96" s="3">
         <v>4</v>
       </c>
       <c r="K96" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L96" s="5">
         <f t="shared" si="33"/>
@@ -6648,7 +6693,7 @@
         <v>5</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D97" s="3">
         <v>2</v>
@@ -6663,13 +6708,13 @@
         <v>8</v>
       </c>
       <c r="I97" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="J97" s="3">
         <v>4</v>
       </c>
       <c r="K97" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L97" s="5">
         <f t="shared" si="33"/>
@@ -6696,7 +6741,7 @@
         <v>5</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D98" s="3">
         <v>2</v>
@@ -6711,13 +6756,13 @@
         <v>9</v>
       </c>
       <c r="I98" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="J98" s="3">
         <v>4</v>
       </c>
       <c r="K98" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L98" s="5">
         <f t="shared" si="33"/>
@@ -6744,7 +6789,7 @@
         <v>5</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D99" s="3">
         <v>2</v>
@@ -6759,13 +6804,13 @@
         <v>10</v>
       </c>
       <c r="I99" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="J99" s="3">
         <v>4</v>
       </c>
       <c r="K99" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L99" s="5">
         <f t="shared" si="33"/>
@@ -6792,7 +6837,7 @@
         <v>5</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D100" s="3">
         <v>2</v>
@@ -6807,13 +6852,13 @@
         <v>11</v>
       </c>
       <c r="I100" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="J100" s="3">
         <v>4</v>
       </c>
       <c r="K100" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="L100" s="5">
         <f t="shared" si="33"/>
@@ -6840,7 +6885,7 @@
         <v>5</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D101" s="3">
         <v>2</v>
@@ -6855,13 +6900,13 @@
         <v>12</v>
       </c>
       <c r="I101" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="J101" s="3">
         <v>4</v>
       </c>
       <c r="K101" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L101" s="5">
         <f t="shared" si="33"/>
@@ -6888,7 +6933,7 @@
         <v>5</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D102" s="3">
         <v>2</v>
@@ -6903,13 +6948,13 @@
         <v>13</v>
       </c>
       <c r="I102" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="J102" s="3">
         <v>4</v>
       </c>
       <c r="K102" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L102" s="5">
         <f t="shared" si="33"/>
@@ -6936,7 +6981,7 @@
         <v>5</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D103" s="3">
         <v>2</v>
@@ -6951,13 +6996,13 @@
         <v>14</v>
       </c>
       <c r="I103" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="J103" s="3">
         <v>4</v>
       </c>
       <c r="K103" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="L103" s="5">
         <f t="shared" si="33"/>
@@ -6984,7 +7029,7 @@
         <v>5</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D104" s="3">
         <v>2</v>
@@ -6999,13 +7044,13 @@
         <v>15</v>
       </c>
       <c r="I104" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J104" s="3">
         <v>4</v>
       </c>
       <c r="K104" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L104" s="5">
         <f t="shared" si="33"/>
@@ -7032,7 +7077,7 @@
         <v>5</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D105" s="3">
         <v>2</v>
@@ -7047,13 +7092,13 @@
         <v>16</v>
       </c>
       <c r="I105" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="J105" s="3">
         <v>4</v>
       </c>
       <c r="K105" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L105" s="5">
         <f t="shared" si="33"/>
@@ -7080,7 +7125,7 @@
         <v>5</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D106" s="3">
         <v>2</v>
@@ -7095,13 +7140,13 @@
         <v>17</v>
       </c>
       <c r="I106" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="J106" s="3">
         <v>4</v>
       </c>
       <c r="K106" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="L106" s="5">
         <f t="shared" si="33"/>
@@ -7128,7 +7173,7 @@
         <v>5</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D107" s="3">
         <v>2</v>
@@ -7143,13 +7188,13 @@
         <v>18</v>
       </c>
       <c r="I107" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="J107" s="3">
         <v>4</v>
       </c>
       <c r="K107" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L107" s="5">
         <f t="shared" si="33"/>
@@ -7176,7 +7221,7 @@
         <v>5</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D108" s="3">
         <v>2</v>
@@ -7191,13 +7236,13 @@
         <v>19</v>
       </c>
       <c r="I108" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="J108" s="3">
         <v>4</v>
       </c>
       <c r="K108" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L108" s="5">
         <f t="shared" si="33"/>
@@ -7224,7 +7269,7 @@
         <v>5</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D109" s="3">
         <v>2</v>
@@ -7259,7 +7304,7 @@
         <v>6</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D110" s="3">
         <v>4</v>
@@ -7274,7 +7319,7 @@
         <v>0</v>
       </c>
       <c r="I110" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="J110" s="3">
         <v>4</v>
@@ -7305,7 +7350,7 @@
         <v>6</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D111" s="3">
         <v>4</v>
@@ -7320,7 +7365,7 @@
         <v>1</v>
       </c>
       <c r="I111" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="J111" s="3">
         <v>4</v>
@@ -7352,7 +7397,7 @@
         <v>6</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D112" s="3">
         <v>4</v>
@@ -7367,7 +7412,7 @@
         <v>2</v>
       </c>
       <c r="I112" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="J112" s="3">
         <v>4</v>
@@ -7399,7 +7444,7 @@
         <v>6</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D113" s="3">
         <v>4</v>
@@ -7414,7 +7459,7 @@
         <v>3</v>
       </c>
       <c r="I113" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="J113" s="3">
         <v>4</v>
@@ -7446,7 +7491,7 @@
         <v>6</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D114" s="3">
         <v>4</v>
@@ -7467,7 +7512,7 @@
         <v>4</v>
       </c>
       <c r="K114" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L114" s="5">
         <f t="shared" si="41"/>
@@ -7493,7 +7538,7 @@
         <v>6</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D115" s="3">
         <v>4</v>
@@ -7514,7 +7559,7 @@
         <v>4</v>
       </c>
       <c r="K115" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L115" s="5">
         <f t="shared" si="41"/>
@@ -7540,7 +7585,7 @@
         <v>6</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D116" s="3">
         <v>4</v>
@@ -7561,7 +7606,7 @@
         <v>4</v>
       </c>
       <c r="K116" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L116" s="5">
         <f t="shared" si="41"/>
@@ -7588,7 +7633,7 @@
         <v>6</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D117" s="3">
         <v>4</v>
@@ -7609,7 +7654,7 @@
         <v>4</v>
       </c>
       <c r="K117" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L117" s="5">
         <f t="shared" si="41"/>
@@ -7636,7 +7681,7 @@
         <v>6</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D118" s="3">
         <v>4</v>
@@ -7657,7 +7702,7 @@
         <v>4</v>
       </c>
       <c r="K118" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L118" s="5">
         <f t="shared" si="41"/>
@@ -7684,7 +7729,7 @@
         <v>6</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D119" s="3">
         <v>4</v>
@@ -7705,7 +7750,7 @@
         <v>4</v>
       </c>
       <c r="K119" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L119" s="5">
         <f t="shared" si="41"/>
@@ -7732,7 +7777,7 @@
         <v>6</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D120" s="3">
         <v>4</v>
@@ -7753,7 +7798,7 @@
         <v>4</v>
       </c>
       <c r="K120" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L120" s="5">
         <f t="shared" si="41"/>
@@ -7780,7 +7825,7 @@
         <v>6</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D121" s="3">
         <v>4</v>
@@ -7801,7 +7846,7 @@
         <v>4</v>
       </c>
       <c r="K121" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="L121" s="5">
         <f t="shared" si="41"/>
@@ -7828,7 +7873,7 @@
         <v>6</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D122" s="3">
         <v>4</v>
@@ -7849,7 +7894,7 @@
         <v>4</v>
       </c>
       <c r="K122" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L122" s="5">
         <f t="shared" si="41"/>
@@ -7876,7 +7921,7 @@
         <v>6</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D123" s="3">
         <v>4</v>
@@ -7897,7 +7942,7 @@
         <v>4</v>
       </c>
       <c r="K123" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L123" s="5">
         <f t="shared" si="41"/>
@@ -7924,7 +7969,7 @@
         <v>6</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D124" s="3">
         <v>4</v>
@@ -7945,7 +7990,7 @@
         <v>4</v>
       </c>
       <c r="K124" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="L124" s="5">
         <f t="shared" si="41"/>
@@ -7972,7 +8017,7 @@
         <v>6</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D125" s="3">
         <v>4</v>
@@ -7993,7 +8038,7 @@
         <v>4</v>
       </c>
       <c r="K125" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L125" s="5">
         <f t="shared" si="41"/>
@@ -8020,7 +8065,7 @@
         <v>6</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D126" s="3">
         <v>4</v>
@@ -8041,7 +8086,7 @@
         <v>4</v>
       </c>
       <c r="K126" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L126" s="5">
         <f t="shared" si="41"/>
@@ -8068,7 +8113,7 @@
         <v>6</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D127" s="3">
         <v>4</v>
@@ -8089,7 +8134,7 @@
         <v>4</v>
       </c>
       <c r="K127" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="L127" s="5">
         <f t="shared" si="41"/>
@@ -8116,7 +8161,7 @@
         <v>6</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D128" s="3">
         <v>4</v>
@@ -8137,7 +8182,7 @@
         <v>4</v>
       </c>
       <c r="K128" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L128" s="5">
         <f t="shared" si="41"/>
@@ -8164,7 +8209,7 @@
         <v>6</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D129" s="3">
         <v>4</v>
@@ -8185,7 +8230,7 @@
         <v>4</v>
       </c>
       <c r="K129" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L129" s="5">
         <f t="shared" si="41"/>
@@ -8212,7 +8257,7 @@
         <v>6</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D130" s="3">
         <v>4</v>
@@ -8401,7 +8446,7 @@
     </row>
     <row r="6" spans="1:16">
       <c r="A6" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B6" t="str" cm="1">
         <f t="array" ref="B6">_xlfn.TEXTSPLIT(A6,";")</f>
@@ -8447,7 +8492,7 @@
     </row>
     <row r="7" spans="1:16">
       <c r="A7" s="1" t="s">
-        <v>41</v>
+        <v>222</v>
       </c>
       <c r="B7" t="str" cm="1">
         <f t="array" ref="B7">_xlfn.TEXTSPLIT(A7,";")</f>
@@ -8493,7 +8538,7 @@
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="1" t="s">
-        <v>43</v>
+        <v>223</v>
       </c>
       <c r="B8" t="str" cm="1">
         <f t="array" ref="B8">_xlfn.TEXTSPLIT(A8,";")</f>
@@ -8539,7 +8584,7 @@
     </row>
     <row r="9" spans="1:16">
       <c r="A9" s="1" t="s">
-        <v>45</v>
+        <v>224</v>
       </c>
       <c r="B9" t="str" cm="1">
         <f t="array" ref="B9">_xlfn.TEXTSPLIT(A9,";")</f>
@@ -8585,7 +8630,7 @@
     </row>
     <row r="10" spans="1:16">
       <c r="A10" s="1" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B10" t="str" cm="1">
         <f t="array" ref="B10:C10">_xlfn.TEXTSPLIT(A10,";")</f>
@@ -8637,7 +8682,7 @@
     </row>
     <row r="11" spans="1:16">
       <c r="A11" s="1" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B11" t="str" cm="1">
         <f t="array" ref="B11">_xlfn.TEXTSPLIT(A11,";")</f>
@@ -8683,7 +8728,7 @@
     </row>
     <row r="12" spans="1:16">
       <c r="A12" s="1" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="B12" t="str" cm="1">
         <f t="array" ref="B12">_xlfn.TEXTSPLIT(A12,";")</f>
@@ -8729,7 +8774,7 @@
     </row>
     <row r="13" spans="1:16">
       <c r="A13" s="1" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B13" t="str" cm="1">
         <f t="array" ref="B13">_xlfn.TEXTSPLIT(A13,";")</f>
@@ -8775,7 +8820,7 @@
     </row>
     <row r="14" spans="1:16">
       <c r="A14" s="1" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B14" t="str" cm="1">
         <f t="array" ref="B14:C14">_xlfn.TEXTSPLIT(A14,";")</f>
@@ -8827,7 +8872,7 @@
     </row>
     <row r="15" spans="1:16">
       <c r="A15" s="1" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B15" t="str" cm="1">
         <f t="array" ref="B15">_xlfn.TEXTSPLIT(A15,";")</f>
@@ -8873,7 +8918,7 @@
     </row>
     <row r="16" spans="1:16">
       <c r="A16" s="1" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B16" t="str" cm="1">
         <f t="array" ref="B16">_xlfn.TEXTSPLIT(A16,";")</f>
@@ -8919,7 +8964,7 @@
     </row>
     <row r="17" spans="1:16">
       <c r="A17" s="1" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B17" t="str" cm="1">
         <f t="array" ref="B17">_xlfn.TEXTSPLIT(A17,";")</f>
@@ -8965,7 +9010,7 @@
     </row>
     <row r="18" spans="1:16">
       <c r="A18" s="1" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B18" t="str" cm="1">
         <f t="array" ref="B18:C18">_xlfn.TEXTSPLIT(A18,";")</f>
@@ -9017,7 +9062,7 @@
     </row>
     <row r="19" spans="1:16">
       <c r="A19" s="1" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="B19" t="str" cm="1">
         <f t="array" ref="B19">_xlfn.TEXTSPLIT(A19,";")</f>
@@ -9063,7 +9108,7 @@
     </row>
     <row r="20" spans="1:16">
       <c r="A20" s="1" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B20" t="str" cm="1">
         <f t="array" ref="B20">_xlfn.TEXTSPLIT(A20,";")</f>
@@ -9109,7 +9154,7 @@
     </row>
     <row r="21" spans="1:16">
       <c r="A21" s="1" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B21" t="str" cm="1">
         <f t="array" ref="B21:C21">_xlfn.TEXTSPLIT(A21,";")</f>
@@ -9161,7 +9206,7 @@
     </row>
     <row r="22" spans="1:16">
       <c r="A22" s="1" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="B22" t="str" cm="1">
         <f t="array" ref="B22">_xlfn.TEXTSPLIT(A22,";")</f>
@@ -9207,7 +9252,7 @@
     </row>
     <row r="23" spans="1:16">
       <c r="A23" s="1" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="B23" t="str" cm="1">
         <f t="array" ref="B23">_xlfn.TEXTSPLIT(A23,";")</f>
@@ -9253,7 +9298,7 @@
     </row>
     <row r="24" spans="1:16">
       <c r="A24" s="1" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="B24" t="str" cm="1">
         <f t="array" ref="B24">_xlfn.TEXTSPLIT(A24,";")</f>
@@ -9307,7 +9352,7 @@
     </row>
     <row r="26" spans="1:16">
       <c r="A26" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B26" t="str" cm="1">
         <f t="array" ref="B26">_xlfn.TEXTSPLIT(A26,";")</f>
@@ -9357,7 +9402,7 @@
     </row>
     <row r="27" spans="1:16">
       <c r="A27" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B27" t="str" cm="1">
         <f t="array" ref="B27">_xlfn.TEXTSPLIT(A27,";")</f>
@@ -9403,7 +9448,7 @@
     </row>
     <row r="28" spans="1:16">
       <c r="A28" s="1" t="s">
-        <v>96</v>
+        <v>240</v>
       </c>
       <c r="B28" t="str" cm="1">
         <f t="array" ref="B28">_xlfn.TEXTSPLIT(A28,";")</f>
@@ -9449,7 +9494,7 @@
     </row>
     <row r="29" spans="1:16">
       <c r="A29" s="1" t="s">
-        <v>98</v>
+        <v>241</v>
       </c>
       <c r="B29" t="str" cm="1">
         <f t="array" ref="B29">_xlfn.TEXTSPLIT(A29,";")</f>
@@ -9495,7 +9540,7 @@
     </row>
     <row r="30" spans="1:16">
       <c r="A30" s="1" t="s">
-        <v>100</v>
+        <v>242</v>
       </c>
       <c r="B30" t="str" cm="1">
         <f t="array" ref="B30">_xlfn.TEXTSPLIT(A30,";")</f>
@@ -9535,7 +9580,7 @@
     </row>
     <row r="31" spans="1:16">
       <c r="A31" s="1" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="B31" t="str" cm="1">
         <f t="array" ref="B31:C31">_xlfn.TEXTSPLIT(A31,";")</f>
@@ -9581,7 +9626,7 @@
     </row>
     <row r="32" spans="1:16">
       <c r="A32" s="1" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="B32" t="str" cm="1">
         <f t="array" ref="B32">_xlfn.TEXTSPLIT(A32,";")</f>
@@ -9621,7 +9666,7 @@
     </row>
     <row r="33" spans="1:13">
       <c r="A33" s="1" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="B33" t="str" cm="1">
         <f t="array" ref="B33">_xlfn.TEXTSPLIT(A33,";")</f>
@@ -9661,7 +9706,7 @@
     </row>
     <row r="34" spans="1:13">
       <c r="A34" s="1" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="B34" t="str" cm="1">
         <f t="array" ref="B34">_xlfn.TEXTSPLIT(A34,";")</f>
@@ -9701,7 +9746,7 @@
     </row>
     <row r="35" spans="1:13">
       <c r="A35" s="1" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="B35" t="str" cm="1">
         <f t="array" ref="B35:C35">_xlfn.TEXTSPLIT(A35,";")</f>
@@ -9747,7 +9792,7 @@
     </row>
     <row r="36" spans="1:13">
       <c r="A36" s="1" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="B36" t="str" cm="1">
         <f t="array" ref="B36">_xlfn.TEXTSPLIT(A36,";")</f>
@@ -9787,7 +9832,7 @@
     </row>
     <row r="37" spans="1:13">
       <c r="A37" s="1" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="B37" t="str" cm="1">
         <f t="array" ref="B37">_xlfn.TEXTSPLIT(A37,";")</f>
@@ -9827,7 +9872,7 @@
     </row>
     <row r="38" spans="1:13">
       <c r="A38" s="1" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="B38" t="str" cm="1">
         <f t="array" ref="B38">_xlfn.TEXTSPLIT(A38,";")</f>
@@ -9867,7 +9912,7 @@
     </row>
     <row r="39" spans="1:13">
       <c r="A39" s="1" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="B39" t="str" cm="1">
         <f t="array" ref="B39:C39">_xlfn.TEXTSPLIT(A39,";")</f>
@@ -9913,7 +9958,7 @@
     </row>
     <row r="40" spans="1:13">
       <c r="A40" s="1" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="B40" t="str" cm="1">
         <f t="array" ref="B40">_xlfn.TEXTSPLIT(A40,";")</f>
@@ -9953,7 +9998,7 @@
     </row>
     <row r="41" spans="1:13">
       <c r="A41" s="1" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="B41" t="str" cm="1">
         <f t="array" ref="B41">_xlfn.TEXTSPLIT(A41,";")</f>
@@ -9993,7 +10038,7 @@
     </row>
     <row r="42" spans="1:13">
       <c r="A42" s="1" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="B42" t="str" cm="1">
         <f t="array" ref="B42:C42">_xlfn.TEXTSPLIT(A42,";")</f>
@@ -10039,7 +10084,7 @@
     </row>
     <row r="43" spans="1:13">
       <c r="A43" s="1" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="B43" t="str" cm="1">
         <f t="array" ref="B43">_xlfn.TEXTSPLIT(A43,";")</f>
@@ -10079,7 +10124,7 @@
     </row>
     <row r="44" spans="1:13">
       <c r="A44" s="1" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="B44" t="str" cm="1">
         <f t="array" ref="B44">_xlfn.TEXTSPLIT(A44,";")</f>
@@ -10119,7 +10164,7 @@
     </row>
     <row r="45" spans="1:13">
       <c r="A45" s="1" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="B45" t="str" cm="1">
         <f t="array" ref="B45">_xlfn.TEXTSPLIT(A45,";")</f>
@@ -10159,7 +10204,7 @@
     </row>
     <row r="47" spans="1:13">
       <c r="A47" s="1" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="B47" t="str" cm="1">
         <f t="array" ref="B47">_xlfn.TEXTSPLIT(A47,";")</f>
@@ -10203,7 +10248,7 @@
     </row>
     <row r="48" spans="1:13">
       <c r="A48" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B48" t="str" cm="1">
         <f t="array" ref="B48">_xlfn.TEXTSPLIT(A48,";")</f>
@@ -10243,7 +10288,7 @@
     </row>
     <row r="49" spans="1:13">
       <c r="A49" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B49" t="str" cm="1">
         <f t="array" ref="B49">_xlfn.TEXTSPLIT(A49,";")</f>
@@ -10283,7 +10328,7 @@
     </row>
     <row r="50" spans="1:13">
       <c r="A50" s="1" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="B50" t="str" cm="1">
         <f t="array" ref="B50">_xlfn.TEXTSPLIT(A50,";")</f>
@@ -10323,7 +10368,7 @@
     </row>
     <row r="51" spans="1:13">
       <c r="A51" s="1" t="s">
-        <v>96</v>
+        <v>240</v>
       </c>
       <c r="B51" t="str" cm="1">
         <f t="array" ref="B51">_xlfn.TEXTSPLIT(A51,";")</f>
@@ -10363,7 +10408,7 @@
     </row>
     <row r="52" spans="1:13">
       <c r="A52" s="1" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="B52" t="str" cm="1">
         <f t="array" ref="B52:C52">_xlfn.TEXTSPLIT(A52,";")</f>
@@ -10409,7 +10454,7 @@
     </row>
     <row r="53" spans="1:13">
       <c r="A53" s="1" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="B53" t="str" cm="1">
         <f t="array" ref="B53">_xlfn.TEXTSPLIT(A53,";")</f>
@@ -10449,7 +10494,7 @@
     </row>
     <row r="54" spans="1:13">
       <c r="A54" s="1" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="B54" t="str" cm="1">
         <f t="array" ref="B54">_xlfn.TEXTSPLIT(A54,";")</f>
@@ -10489,7 +10534,7 @@
     </row>
     <row r="55" spans="1:13">
       <c r="A55" s="1" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="B55" t="str" cm="1">
         <f t="array" ref="B55">_xlfn.TEXTSPLIT(A55,";")</f>
@@ -10529,7 +10574,7 @@
     </row>
     <row r="56" spans="1:13">
       <c r="A56" s="1" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="B56" t="str" cm="1">
         <f t="array" ref="B56:C56">_xlfn.TEXTSPLIT(A56,";")</f>
@@ -10575,7 +10620,7 @@
     </row>
     <row r="57" spans="1:13">
       <c r="A57" s="1" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="B57" t="str" cm="1">
         <f t="array" ref="B57">_xlfn.TEXTSPLIT(A57,";")</f>
@@ -10615,7 +10660,7 @@
     </row>
     <row r="58" spans="1:13">
       <c r="A58" s="1" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="B58" t="str" cm="1">
         <f t="array" ref="B58">_xlfn.TEXTSPLIT(A58,";")</f>
@@ -10655,7 +10700,7 @@
     </row>
     <row r="59" spans="1:13">
       <c r="A59" s="1" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="B59" t="str" cm="1">
         <f t="array" ref="B59">_xlfn.TEXTSPLIT(A59,";")</f>
@@ -10695,7 +10740,7 @@
     </row>
     <row r="60" spans="1:13">
       <c r="A60" s="1" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="B60" t="str" cm="1">
         <f t="array" ref="B60:C60">_xlfn.TEXTSPLIT(A60,";")</f>
@@ -10741,7 +10786,7 @@
     </row>
     <row r="61" spans="1:13">
       <c r="A61" s="1" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="B61" t="str" cm="1">
         <f t="array" ref="B61">_xlfn.TEXTSPLIT(A61,";")</f>
@@ -10781,7 +10826,7 @@
     </row>
     <row r="62" spans="1:13">
       <c r="A62" s="1" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="B62" t="str" cm="1">
         <f t="array" ref="B62">_xlfn.TEXTSPLIT(A62,";")</f>
@@ -10821,7 +10866,7 @@
     </row>
     <row r="63" spans="1:13">
       <c r="A63" s="1" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="B63" t="str" cm="1">
         <f t="array" ref="B63:C63">_xlfn.TEXTSPLIT(A63,";")</f>
@@ -10867,7 +10912,7 @@
     </row>
     <row r="64" spans="1:13">
       <c r="A64" s="1" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="B64" t="str" cm="1">
         <f t="array" ref="B64">_xlfn.TEXTSPLIT(A64,";")</f>
@@ -10907,7 +10952,7 @@
     </row>
     <row r="65" spans="1:13">
       <c r="A65" s="1" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="B65" t="str" cm="1">
         <f t="array" ref="B65">_xlfn.TEXTSPLIT(A65,";")</f>
@@ -10947,7 +10992,7 @@
     </row>
     <row r="66" spans="1:13">
       <c r="A66" s="1" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="B66" t="str" cm="1">
         <f t="array" ref="B66">_xlfn.TEXTSPLIT(A66,";")</f>
@@ -10987,7 +11032,7 @@
     </row>
     <row r="68" spans="1:13">
       <c r="A68" s="1" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B68" t="str" cm="1">
         <f t="array" ref="B68">_xlfn.TEXTSPLIT(A68,";")</f>
@@ -11031,7 +11076,7 @@
     </row>
     <row r="69" spans="1:13">
       <c r="A69" s="1" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B69" t="str" cm="1">
         <f t="array" ref="B69">_xlfn.TEXTSPLIT(A69,";")</f>
@@ -11071,7 +11116,7 @@
     </row>
     <row r="70" spans="1:13">
       <c r="A70" s="1" t="s">
-        <v>160</v>
+        <v>267</v>
       </c>
       <c r="B70" t="str" cm="1">
         <f t="array" ref="B70">_xlfn.TEXTSPLIT(A70,";")</f>
@@ -11111,7 +11156,7 @@
     </row>
     <row r="71" spans="1:13">
       <c r="A71" s="1" t="s">
-        <v>161</v>
+        <v>268</v>
       </c>
       <c r="B71" t="str" cm="1">
         <f t="array" ref="B71">_xlfn.TEXTSPLIT(A71,";")</f>
@@ -11151,7 +11196,7 @@
     </row>
     <row r="72" spans="1:13">
       <c r="A72" s="1" t="s">
-        <v>162</v>
+        <v>269</v>
       </c>
       <c r="B72" t="str" cm="1">
         <f t="array" ref="B72">_xlfn.TEXTSPLIT(A72,";")</f>
@@ -11191,7 +11236,7 @@
     </row>
     <row r="73" spans="1:13">
       <c r="A73" s="1" t="s">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="B73" t="str" cm="1">
         <f t="array" ref="B73:C73">_xlfn.TEXTSPLIT(A73,";")</f>
@@ -11237,7 +11282,7 @@
     </row>
     <row r="74" spans="1:13">
       <c r="A74" s="1" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="B74" t="str" cm="1">
         <f t="array" ref="B74">_xlfn.TEXTSPLIT(A74,";")</f>
@@ -11277,7 +11322,7 @@
     </row>
     <row r="75" spans="1:13">
       <c r="A75" s="1" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="B75" t="str" cm="1">
         <f t="array" ref="B75">_xlfn.TEXTSPLIT(A75,";")</f>
@@ -11317,7 +11362,7 @@
     </row>
     <row r="76" spans="1:13">
       <c r="A76" s="1" t="s">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="B76" t="str" cm="1">
         <f t="array" ref="B76">_xlfn.TEXTSPLIT(A76,";")</f>
@@ -11357,7 +11402,7 @@
     </row>
     <row r="77" spans="1:13">
       <c r="A77" s="1" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="B77" t="str" cm="1">
         <f t="array" ref="B77:C77">_xlfn.TEXTSPLIT(A77,";")</f>
@@ -11403,7 +11448,7 @@
     </row>
     <row r="78" spans="1:13">
       <c r="A78" s="1" t="s">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="B78" t="str" cm="1">
         <f t="array" ref="B78">_xlfn.TEXTSPLIT(A78,";")</f>
@@ -11443,7 +11488,7 @@
     </row>
     <row r="79" spans="1:13">
       <c r="A79" s="1" t="s">
-        <v>267</v>
+        <v>276</v>
       </c>
       <c r="B79" t="str" cm="1">
         <f t="array" ref="B79">_xlfn.TEXTSPLIT(A79,";")</f>
@@ -11483,7 +11528,7 @@
     </row>
     <row r="80" spans="1:13">
       <c r="A80" s="1" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="B80" t="str" cm="1">
         <f t="array" ref="B80">_xlfn.TEXTSPLIT(A80,";")</f>
@@ -11523,7 +11568,7 @@
     </row>
     <row r="81" spans="1:13">
       <c r="A81" s="1" t="s">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="B81" t="str" cm="1">
         <f t="array" ref="B81:C81">_xlfn.TEXTSPLIT(A81,";")</f>
@@ -11569,7 +11614,7 @@
     </row>
     <row r="82" spans="1:13">
       <c r="A82" s="1" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="B82" t="str" cm="1">
         <f t="array" ref="B82">_xlfn.TEXTSPLIT(A82,";")</f>
@@ -11609,7 +11654,7 @@
     </row>
     <row r="83" spans="1:13">
       <c r="A83" s="1" t="s">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="B83" t="str" cm="1">
         <f t="array" ref="B83">_xlfn.TEXTSPLIT(A83,";")</f>
@@ -11649,7 +11694,7 @@
     </row>
     <row r="84" spans="1:13">
       <c r="A84" s="1" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="B84" t="str" cm="1">
         <f t="array" ref="B84:C84">_xlfn.TEXTSPLIT(A84,";")</f>
@@ -11695,7 +11740,7 @@
     </row>
     <row r="85" spans="1:13">
       <c r="A85" s="1" t="s">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="B85" t="str" cm="1">
         <f t="array" ref="B85">_xlfn.TEXTSPLIT(A85,";")</f>
@@ -11735,7 +11780,7 @@
     </row>
     <row r="86" spans="1:13">
       <c r="A86" s="1" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="B86" t="str" cm="1">
         <f t="array" ref="B86">_xlfn.TEXTSPLIT(A86,";")</f>
@@ -11775,7 +11820,7 @@
     </row>
     <row r="87" spans="1:13">
       <c r="A87" s="1" t="s">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="B87" t="str" cm="1">
         <f t="array" ref="B87">_xlfn.TEXTSPLIT(A87,";")</f>
@@ -11815,7 +11860,7 @@
     </row>
     <row r="89" spans="1:13">
       <c r="A89" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B89" t="str" cm="1">
         <f t="array" ref="B89">_xlfn.TEXTSPLIT(A89,";")</f>
@@ -11859,7 +11904,7 @@
     </row>
     <row r="90" spans="1:13">
       <c r="A90" s="1" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B90" t="str" cm="1">
         <f t="array" ref="B90">_xlfn.TEXTSPLIT(A90,";")</f>
@@ -11899,7 +11944,7 @@
     </row>
     <row r="91" spans="1:13">
       <c r="A91" s="1" t="s">
-        <v>181</v>
+        <v>285</v>
       </c>
       <c r="B91" t="str" cm="1">
         <f t="array" ref="B91">_xlfn.TEXTSPLIT(A91,";")</f>
@@ -11939,7 +11984,7 @@
     </row>
     <row r="92" spans="1:13">
       <c r="A92" s="1" t="s">
-        <v>182</v>
+        <v>286</v>
       </c>
       <c r="B92" t="str" cm="1">
         <f t="array" ref="B92">_xlfn.TEXTSPLIT(A92,";")</f>
@@ -11979,7 +12024,7 @@
     </row>
     <row r="93" spans="1:13">
       <c r="A93" s="1" t="s">
-        <v>183</v>
+        <v>287</v>
       </c>
       <c r="B93" t="str" cm="1">
         <f t="array" ref="B93">_xlfn.TEXTSPLIT(A93,";")</f>
@@ -12019,7 +12064,7 @@
     </row>
     <row r="94" spans="1:13">
       <c r="A94" s="1" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="B94" t="str" cm="1">
         <f t="array" ref="B94:C94">_xlfn.TEXTSPLIT(A94,";")</f>
@@ -12065,7 +12110,7 @@
     </row>
     <row r="95" spans="1:13">
       <c r="A95" s="1" t="s">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="B95" t="str" cm="1">
         <f t="array" ref="B95">_xlfn.TEXTSPLIT(A95,";")</f>
@@ -12105,7 +12150,7 @@
     </row>
     <row r="96" spans="1:13">
       <c r="A96" s="1" t="s">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="B96" t="str" cm="1">
         <f t="array" ref="B96">_xlfn.TEXTSPLIT(A96,";")</f>
@@ -12145,7 +12190,7 @@
     </row>
     <row r="97" spans="1:13">
       <c r="A97" s="1" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="B97" t="str" cm="1">
         <f t="array" ref="B97">_xlfn.TEXTSPLIT(A97,";")</f>
@@ -12185,7 +12230,7 @@
     </row>
     <row r="98" spans="1:13">
       <c r="A98" s="1" t="s">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="B98" t="str" cm="1">
         <f t="array" ref="B98:C98">_xlfn.TEXTSPLIT(A98,";")</f>
@@ -12231,7 +12276,7 @@
     </row>
     <row r="99" spans="1:13">
       <c r="A99" s="1" t="s">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="B99" t="str" cm="1">
         <f t="array" ref="B99">_xlfn.TEXTSPLIT(A99,";")</f>
@@ -12271,7 +12316,7 @@
     </row>
     <row r="100" spans="1:13">
       <c r="A100" s="1" t="s">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="B100" t="str" cm="1">
         <f t="array" ref="B100">_xlfn.TEXTSPLIT(A100,";")</f>
@@ -12311,7 +12356,7 @@
     </row>
     <row r="101" spans="1:13">
       <c r="A101" s="1" t="s">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="B101" t="str" cm="1">
         <f t="array" ref="B101">_xlfn.TEXTSPLIT(A101,";")</f>
@@ -12351,7 +12396,7 @@
     </row>
     <row r="102" spans="1:13">
       <c r="A102" s="1" t="s">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="B102" t="str" cm="1">
         <f t="array" ref="B102:C102">_xlfn.TEXTSPLIT(A102,";")</f>
@@ -12397,7 +12442,7 @@
     </row>
     <row r="103" spans="1:13">
       <c r="A103" s="1" t="s">
-        <v>285</v>
+        <v>297</v>
       </c>
       <c r="B103" t="str" cm="1">
         <f t="array" ref="B103">_xlfn.TEXTSPLIT(A103,";")</f>
@@ -12437,7 +12482,7 @@
     </row>
     <row r="104" spans="1:13">
       <c r="A104" s="1" t="s">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="B104" t="str" cm="1">
         <f t="array" ref="B104">_xlfn.TEXTSPLIT(A104,";")</f>
@@ -12477,7 +12522,7 @@
     </row>
     <row r="105" spans="1:13">
       <c r="A105" s="1" t="s">
-        <v>287</v>
+        <v>299</v>
       </c>
       <c r="B105" t="str" cm="1">
         <f t="array" ref="B105:C105">_xlfn.TEXTSPLIT(A105,";")</f>
@@ -12523,7 +12568,7 @@
     </row>
     <row r="106" spans="1:13">
       <c r="A106" s="1" t="s">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="B106" t="str" cm="1">
         <f t="array" ref="B106">_xlfn.TEXTSPLIT(A106,";")</f>
@@ -12563,7 +12608,7 @@
     </row>
     <row r="107" spans="1:13">
       <c r="A107" s="1" t="s">
-        <v>289</v>
+        <v>301</v>
       </c>
       <c r="B107" t="str" cm="1">
         <f t="array" ref="B107">_xlfn.TEXTSPLIT(A107,";")</f>
@@ -12603,7 +12648,7 @@
     </row>
     <row r="108" spans="1:13">
       <c r="A108" s="1" t="s">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="B108" t="str" cm="1">
         <f t="array" ref="B108">_xlfn.TEXTSPLIT(A108,";")</f>
@@ -12643,7 +12688,7 @@
     </row>
     <row r="110" spans="1:13">
       <c r="A110" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B110" t="str" cm="1">
         <f t="array" ref="B110">_xlfn.TEXTSPLIT(A110,";")</f>
@@ -12687,7 +12732,7 @@
     </row>
     <row r="111" spans="1:13">
       <c r="A111" s="1" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B111" t="str" cm="1">
         <f t="array" ref="B111">_xlfn.TEXTSPLIT(A111,";")</f>
@@ -12727,7 +12772,7 @@
     </row>
     <row r="112" spans="1:13">
       <c r="A112" s="1" t="s">
-        <v>202</v>
+        <v>303</v>
       </c>
       <c r="B112" t="str" cm="1">
         <f t="array" ref="B112">_xlfn.TEXTSPLIT(A112,";")</f>
@@ -12767,7 +12812,7 @@
     </row>
     <row r="113" spans="1:13">
       <c r="A113" s="1" t="s">
-        <v>203</v>
+        <v>304</v>
       </c>
       <c r="B113" t="str" cm="1">
         <f t="array" ref="B113">_xlfn.TEXTSPLIT(A113,";")</f>
@@ -12807,7 +12852,7 @@
     </row>
     <row r="114" spans="1:13">
       <c r="A114" s="1" t="s">
-        <v>204</v>
+        <v>305</v>
       </c>
       <c r="B114" t="str" cm="1">
         <f t="array" ref="B114">_xlfn.TEXTSPLIT(A114,";")</f>
@@ -12847,7 +12892,7 @@
     </row>
     <row r="115" spans="1:13">
       <c r="A115" s="1" t="s">
-        <v>291</v>
+        <v>306</v>
       </c>
       <c r="B115" t="str" cm="1">
         <f t="array" ref="B115:C115">_xlfn.TEXTSPLIT(A115,";")</f>
@@ -12893,7 +12938,7 @@
     </row>
     <row r="116" spans="1:13">
       <c r="A116" s="1" t="s">
-        <v>292</v>
+        <v>307</v>
       </c>
       <c r="B116" t="str" cm="1">
         <f t="array" ref="B116">_xlfn.TEXTSPLIT(A116,";")</f>
@@ -12933,7 +12978,7 @@
     </row>
     <row r="117" spans="1:13">
       <c r="A117" s="1" t="s">
-        <v>293</v>
+        <v>308</v>
       </c>
       <c r="B117" t="str" cm="1">
         <f t="array" ref="B117">_xlfn.TEXTSPLIT(A117,";")</f>
@@ -12973,7 +13018,7 @@
     </row>
     <row r="118" spans="1:13">
       <c r="A118" s="1" t="s">
-        <v>294</v>
+        <v>309</v>
       </c>
       <c r="B118" t="str" cm="1">
         <f t="array" ref="B118">_xlfn.TEXTSPLIT(A118,";")</f>
@@ -13013,7 +13058,7 @@
     </row>
     <row r="119" spans="1:13">
       <c r="A119" s="1" t="s">
-        <v>295</v>
+        <v>310</v>
       </c>
       <c r="B119" t="str" cm="1">
         <f t="array" ref="B119:C119">_xlfn.TEXTSPLIT(A119,";")</f>
@@ -13059,7 +13104,7 @@
     </row>
     <row r="120" spans="1:13">
       <c r="A120" s="1" t="s">
-        <v>296</v>
+        <v>311</v>
       </c>
       <c r="B120" t="str" cm="1">
         <f t="array" ref="B120">_xlfn.TEXTSPLIT(A120,";")</f>
@@ -13099,7 +13144,7 @@
     </row>
     <row r="121" spans="1:13">
       <c r="A121" s="1" t="s">
-        <v>297</v>
+        <v>312</v>
       </c>
       <c r="B121" t="str" cm="1">
         <f t="array" ref="B121">_xlfn.TEXTSPLIT(A121,";")</f>
@@ -13139,7 +13184,7 @@
     </row>
     <row r="122" spans="1:13">
       <c r="A122" s="1" t="s">
-        <v>298</v>
+        <v>313</v>
       </c>
       <c r="B122" t="str" cm="1">
         <f t="array" ref="B122">_xlfn.TEXTSPLIT(A122,";")</f>
@@ -13179,7 +13224,7 @@
     </row>
     <row r="123" spans="1:13">
       <c r="A123" s="1" t="s">
-        <v>299</v>
+        <v>314</v>
       </c>
       <c r="B123" t="str" cm="1">
         <f t="array" ref="B123:C123">_xlfn.TEXTSPLIT(A123,";")</f>
@@ -13225,7 +13270,7 @@
     </row>
     <row r="124" spans="1:13">
       <c r="A124" s="1" t="s">
-        <v>300</v>
+        <v>315</v>
       </c>
       <c r="B124" t="str" cm="1">
         <f t="array" ref="B124">_xlfn.TEXTSPLIT(A124,";")</f>
@@ -13265,7 +13310,7 @@
     </row>
     <row r="125" spans="1:13">
       <c r="A125" s="1" t="s">
-        <v>301</v>
+        <v>316</v>
       </c>
       <c r="B125" t="str" cm="1">
         <f t="array" ref="B125">_xlfn.TEXTSPLIT(A125,";")</f>
@@ -13305,7 +13350,7 @@
     </row>
     <row r="126" spans="1:13">
       <c r="A126" s="1" t="s">
-        <v>302</v>
+        <v>317</v>
       </c>
       <c r="B126" t="str" cm="1">
         <f t="array" ref="B126:C126">_xlfn.TEXTSPLIT(A126,";")</f>
@@ -13351,7 +13396,7 @@
     </row>
     <row r="127" spans="1:13">
       <c r="A127" s="1" t="s">
-        <v>303</v>
+        <v>318</v>
       </c>
       <c r="B127" t="str" cm="1">
         <f t="array" ref="B127">_xlfn.TEXTSPLIT(A127,";")</f>
@@ -13391,7 +13436,7 @@
     </row>
     <row r="128" spans="1:13">
       <c r="A128" s="1" t="s">
-        <v>304</v>
+        <v>319</v>
       </c>
       <c r="B128" t="str" cm="1">
         <f t="array" ref="B128">_xlfn.TEXTSPLIT(A128,";")</f>
@@ -13431,7 +13476,7 @@
     </row>
     <row r="129" spans="1:13">
       <c r="A129" s="1" t="s">
-        <v>305</v>
+        <v>320</v>
       </c>
       <c r="B129" t="str" cm="1">
         <f t="array" ref="B129">_xlfn.TEXTSPLIT(A129,";")</f>
